--- a/4_pagos/efectivo/inputs/mesa_5.xlsx
+++ b/4_pagos/efectivo/inputs/mesa_5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wilde\PycharmProjects\jass_system\4_pagos\efectivo\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0F2D35C-648A-437D-B860-4D02B659BD88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8376533B-48C4-4A6E-ADC3-16F273FF2CC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26520" yWindow="720" windowWidth="14610" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="registro_1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="66">
   <si>
     <t>¿Quién cobró?</t>
   </si>
@@ -231,6 +231,9 @@
   </si>
   <si>
     <t>14B</t>
+  </si>
+  <si>
+    <t>Solicitud</t>
   </si>
 </sst>
 </file>
@@ -3781,7 +3784,7 @@
         <v>46178</v>
       </c>
       <c r="I117" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.35">

--- a/4_pagos/efectivo/inputs/mesa_5.xlsx
+++ b/4_pagos/efectivo/inputs/mesa_5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wilde\PycharmProjects\jass_system\4_pagos\efectivo\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8376533B-48C4-4A6E-ADC3-16F273FF2CC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80D16EB8-8593-4C30-AE86-795EC97F1E8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="67">
   <si>
     <t>¿Quién cobró?</t>
   </si>
@@ -152,9 +152,6 @@
     <t>2A</t>
   </si>
   <si>
-    <t>Pago fraccionado</t>
-  </si>
-  <si>
     <t>reclamo</t>
   </si>
   <si>
@@ -234,6 +231,12 @@
   </si>
   <si>
     <t>Solicitud</t>
+  </si>
+  <si>
+    <t>compromiso</t>
+  </si>
+  <si>
+    <t>8B</t>
   </si>
 </sst>
 </file>
@@ -1363,7 +1366,7 @@
         <v>46178</v>
       </c>
       <c r="I25" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
@@ -1447,7 +1450,7 @@
         <v>46178</v>
       </c>
       <c r="I28" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">
@@ -1510,7 +1513,7 @@
         <v>46181</v>
       </c>
       <c r="C31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D31" t="s">
         <v>33</v>
@@ -1536,7 +1539,7 @@
         <v>46181</v>
       </c>
       <c r="C32" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D32">
         <v>8</v>
@@ -1617,7 +1620,7 @@
         <v>46181</v>
       </c>
       <c r="C35" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D35">
         <v>18</v>
@@ -1698,7 +1701,7 @@
         <v>46181</v>
       </c>
       <c r="C38" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D38">
         <v>8</v>
@@ -1724,7 +1727,7 @@
         <v>46181</v>
       </c>
       <c r="C39" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D39">
         <v>12</v>
@@ -1750,7 +1753,7 @@
         <v>46181</v>
       </c>
       <c r="C40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D40">
         <v>4</v>
@@ -1794,7 +1797,7 @@
         <v>46178</v>
       </c>
       <c r="I41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.35">
@@ -1823,7 +1826,7 @@
         <v>46178</v>
       </c>
       <c r="I42" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.35">
@@ -1886,7 +1889,7 @@
         <v>46181</v>
       </c>
       <c r="C45" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D45">
         <v>11</v>
@@ -1912,7 +1915,7 @@
         <v>46181</v>
       </c>
       <c r="C46" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D46">
         <v>2</v>
@@ -1938,7 +1941,7 @@
         <v>46181</v>
       </c>
       <c r="C47" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D47">
         <v>17</v>
@@ -1964,7 +1967,7 @@
         <v>46181</v>
       </c>
       <c r="C48" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D48">
         <v>16</v>
@@ -1990,7 +1993,7 @@
         <v>46181</v>
       </c>
       <c r="C49" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D49">
         <v>18</v>
@@ -2042,7 +2045,7 @@
         <v>46181</v>
       </c>
       <c r="C51" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D51">
         <v>14</v>
@@ -2068,7 +2071,7 @@
         <v>46181</v>
       </c>
       <c r="C52" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D52">
         <v>12</v>
@@ -2176,7 +2179,7 @@
         <v>46181</v>
       </c>
       <c r="C56" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D56">
         <v>16</v>
@@ -2202,7 +2205,7 @@
         <v>46181</v>
       </c>
       <c r="C57" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D57">
         <v>1</v>
@@ -2280,7 +2283,7 @@
         <v>46181</v>
       </c>
       <c r="C60" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D60">
         <v>11</v>
@@ -2306,7 +2309,7 @@
         <v>46181</v>
       </c>
       <c r="C61" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D61">
         <v>3</v>
@@ -2332,7 +2335,7 @@
         <v>46181</v>
       </c>
       <c r="C62" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D62">
         <v>19</v>
@@ -2358,7 +2361,7 @@
         <v>46181</v>
       </c>
       <c r="C63" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D63">
         <v>13</v>
@@ -2436,7 +2439,7 @@
         <v>46181</v>
       </c>
       <c r="C66" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D66">
         <v>15</v>
@@ -2540,7 +2543,7 @@
         <v>46181</v>
       </c>
       <c r="C70" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D70">
         <v>1</v>
@@ -2722,7 +2725,7 @@
         <v>46181</v>
       </c>
       <c r="C77" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D77">
         <v>2</v>
@@ -2748,7 +2751,7 @@
         <v>46181</v>
       </c>
       <c r="C78" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D78">
         <v>2</v>
@@ -2774,7 +2777,7 @@
         <v>46181</v>
       </c>
       <c r="C79" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D79">
         <v>2</v>
@@ -2826,7 +2829,7 @@
         <v>46181</v>
       </c>
       <c r="C81" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D81">
         <v>8</v>
@@ -2852,7 +2855,7 @@
         <v>46181</v>
       </c>
       <c r="C82" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D82">
         <v>17</v>
@@ -2878,7 +2881,7 @@
         <v>46181</v>
       </c>
       <c r="C83" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D83">
         <v>12</v>
@@ -2904,7 +2907,7 @@
         <v>46181</v>
       </c>
       <c r="C84" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D84">
         <v>13</v>
@@ -2930,7 +2933,7 @@
         <v>46181</v>
       </c>
       <c r="C85" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D85">
         <v>6</v>
@@ -3034,7 +3037,7 @@
         <v>46181</v>
       </c>
       <c r="C89" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D89">
         <v>13</v>
@@ -3060,7 +3063,7 @@
         <v>46181</v>
       </c>
       <c r="C90" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D90">
         <v>7</v>
@@ -3086,7 +3089,7 @@
         <v>46181</v>
       </c>
       <c r="C91" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D91">
         <v>9</v>
@@ -3216,7 +3219,7 @@
         <v>46181</v>
       </c>
       <c r="C96" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D96">
         <v>10</v>
@@ -3242,7 +3245,7 @@
         <v>46181</v>
       </c>
       <c r="C97" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D97">
         <v>9</v>
@@ -3268,7 +3271,7 @@
         <v>46181</v>
       </c>
       <c r="C98" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D98">
         <v>20</v>
@@ -3294,7 +3297,7 @@
         <v>46181</v>
       </c>
       <c r="C99" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D99">
         <v>13</v>
@@ -3320,7 +3323,7 @@
         <v>46181</v>
       </c>
       <c r="C100" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D100">
         <v>4</v>
@@ -3346,7 +3349,7 @@
         <v>46181</v>
       </c>
       <c r="C101" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D101">
         <v>9</v>
@@ -3372,7 +3375,7 @@
         <v>46181</v>
       </c>
       <c r="C102" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D102">
         <v>3</v>
@@ -3398,7 +3401,7 @@
         <v>46181</v>
       </c>
       <c r="C103" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D103">
         <v>2</v>
@@ -3424,7 +3427,7 @@
         <v>46181</v>
       </c>
       <c r="C104" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D104">
         <v>16</v>
@@ -3506,7 +3509,7 @@
         <v>46181</v>
       </c>
       <c r="C107" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D107">
         <v>9</v>
@@ -3532,7 +3535,7 @@
         <v>46181</v>
       </c>
       <c r="C108" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D108">
         <v>13</v>
@@ -3558,7 +3561,7 @@
         <v>46181</v>
       </c>
       <c r="C109" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D109">
         <v>10</v>
@@ -3584,7 +3587,7 @@
         <v>46181</v>
       </c>
       <c r="C110" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D110">
         <v>9</v>
@@ -3610,7 +3613,7 @@
         <v>46181</v>
       </c>
       <c r="C111" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D111">
         <v>4</v>
@@ -3639,7 +3642,7 @@
         <v>15</v>
       </c>
       <c r="D112" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E112">
         <v>21</v>
@@ -3664,8 +3667,8 @@
       <c r="C113" t="s">
         <v>30</v>
       </c>
-      <c r="D113">
-        <v>88</v>
+      <c r="D113" t="s">
+        <v>66</v>
       </c>
       <c r="E113">
         <v>36</v>
@@ -3688,7 +3691,7 @@
         <v>46181</v>
       </c>
       <c r="C114" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D114">
         <v>3</v>
@@ -3714,7 +3717,7 @@
         <v>46181</v>
       </c>
       <c r="C115" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D115">
         <v>3</v>
@@ -3743,7 +3746,7 @@
         <v>22</v>
       </c>
       <c r="D116" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E116">
         <v>40</v>
@@ -3766,7 +3769,7 @@
         <v>46181</v>
       </c>
       <c r="C117" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D117">
         <v>4</v>
@@ -3784,7 +3787,7 @@
         <v>46178</v>
       </c>
       <c r="I117" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.35">
@@ -3795,7 +3798,7 @@
         <v>46181</v>
       </c>
       <c r="C118" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D118">
         <v>2</v>
@@ -3825,7 +3828,7 @@
         <v>46181</v>
       </c>
       <c r="C119" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D119">
         <v>7</v>
@@ -3851,7 +3854,7 @@
         <v>46181</v>
       </c>
       <c r="C120" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D120">
         <v>14</v>
@@ -3877,7 +3880,7 @@
         <v>46181</v>
       </c>
       <c r="C121" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D121">
         <v>5</v>
@@ -3903,7 +3906,7 @@
         <v>46181</v>
       </c>
       <c r="C122" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D122">
         <v>3</v>
@@ -3929,7 +3932,7 @@
         <v>46181</v>
       </c>
       <c r="C123" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D123">
         <v>3</v>
@@ -3955,7 +3958,7 @@
         <v>46181</v>
       </c>
       <c r="C124" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D124">
         <v>1</v>
@@ -4007,7 +4010,7 @@
         <v>46181</v>
       </c>
       <c r="C126" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D126">
         <v>8</v>
@@ -4085,7 +4088,7 @@
         <v>46181</v>
       </c>
       <c r="C129" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D129">
         <v>10</v>
@@ -4137,7 +4140,7 @@
         <v>46181</v>
       </c>
       <c r="C131" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D131">
         <v>17</v>
@@ -4189,7 +4192,7 @@
         <v>46181</v>
       </c>
       <c r="C133" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D133">
         <v>4</v>
@@ -4215,7 +4218,7 @@
         <v>46181</v>
       </c>
       <c r="C134" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D134">
         <v>8</v>
@@ -4241,7 +4244,7 @@
         <v>46181</v>
       </c>
       <c r="C135" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D135">
         <v>1</v>
@@ -4267,7 +4270,7 @@
         <v>46181</v>
       </c>
       <c r="C136" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D136">
         <v>8</v>
@@ -4293,7 +4296,7 @@
         <v>46181</v>
       </c>
       <c r="C137" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D137">
         <v>10</v>
@@ -4348,7 +4351,7 @@
         <v>30</v>
       </c>
       <c r="D139" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E139">
         <v>12</v>
@@ -4371,7 +4374,7 @@
         <v>46181</v>
       </c>
       <c r="C140" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D140">
         <v>3</v>
@@ -4423,7 +4426,7 @@
         <v>46181</v>
       </c>
       <c r="C142" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D142">
         <v>1</v>
@@ -4452,7 +4455,7 @@
         <v>35</v>
       </c>
       <c r="D143" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E143">
         <v>11</v>
@@ -4527,7 +4530,7 @@
         <v>46181</v>
       </c>
       <c r="C146" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D146">
         <v>18</v>
@@ -4553,7 +4556,7 @@
         <v>46181</v>
       </c>
       <c r="C147" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D147">
         <v>15</v>
@@ -4579,7 +4582,7 @@
         <v>46181</v>
       </c>
       <c r="C148" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D148">
         <v>6</v>
@@ -4605,7 +4608,7 @@
         <v>46181</v>
       </c>
       <c r="C149" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D149">
         <v>19</v>
@@ -4631,7 +4634,7 @@
         <v>46181</v>
       </c>
       <c r="C150" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D150">
         <v>11</v>
@@ -4657,7 +4660,7 @@
         <v>46181</v>
       </c>
       <c r="C151" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D151">
         <v>5</v>
@@ -4735,7 +4738,7 @@
         <v>46181</v>
       </c>
       <c r="C154" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D154">
         <v>7</v>

--- a/4_pagos/efectivo/inputs/mesa_5.xlsx
+++ b/4_pagos/efectivo/inputs/mesa_5.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -93,8 +93,20 @@
       <color rgb="009CA3AF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00880E4F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00880E4F"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -126,8 +138,13 @@
         <fgColor rgb="00FFF7ED"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4EC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -149,11 +166,55 @@
         <color rgb="00FFFFFF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00FFFFFF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00FFFFFF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00FFFFFF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00FFFFFF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00FFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00FFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -187,6 +248,14 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -553,7 +622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -566,6 +635,7 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="30" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -574,16 +644,21 @@
           <t>¿Quién cobró?</t>
         </is>
       </c>
+      <c r="B1" s="12" t="n"/>
       <c r="C1" s="2" t="inlineStr">
         <is>
           <t>¿Dónde vive?</t>
         </is>
       </c>
+      <c r="D1" s="12" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
           <t>¿Cuánto y cuándo?</t>
         </is>
       </c>
+      <c r="F1" s="13" t="n"/>
+      <c r="G1" s="13" t="n"/>
+      <c r="H1" s="12" t="n"/>
       <c r="I1" s="4" t="inlineStr">
         <is>
           <t>¿Alguna nota?</t>
@@ -592,6 +667,11 @@
       <c r="J1" s="5" t="inlineStr">
         <is>
           <t>¿Qué tipo?</t>
+        </is>
+      </c>
+      <c r="K1" s="14" t="inlineStr">
+        <is>
+          <t>¿Qué pasó?</t>
         </is>
       </c>
     </row>
@@ -644,6 +724,11 @@
       <c r="J2" s="10" t="inlineStr">
         <is>
           <t>CONCEPTO</t>
+        </is>
+      </c>
+      <c r="K2" s="15" t="inlineStr">
+        <is>
+          <t>CATEGORIA</t>
         </is>
       </c>
     </row>
@@ -697,6 +782,11 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="E1:H1"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="K4:K500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="CATEGORIA inválida" error="Valores: reclamo, compromiso, otros — o dejar vacío (pago normal)." type="list">
+      <formula1>"reclamo,compromiso,otros"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -707,7 +797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -720,6 +810,7 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="30" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -728,16 +819,21 @@
           <t>¿Quién cobró?</t>
         </is>
       </c>
+      <c r="B1" s="12" t="n"/>
       <c r="C1" s="2" t="inlineStr">
         <is>
           <t>¿Dónde vive?</t>
         </is>
       </c>
+      <c r="D1" s="12" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
           <t>¿Cuánto y cuándo?</t>
         </is>
       </c>
+      <c r="F1" s="13" t="n"/>
+      <c r="G1" s="13" t="n"/>
+      <c r="H1" s="12" t="n"/>
       <c r="I1" s="4" t="inlineStr">
         <is>
           <t>¿Alguna nota?</t>
@@ -746,6 +842,11 @@
       <c r="J1" s="5" t="inlineStr">
         <is>
           <t>¿Qué tipo?</t>
+        </is>
+      </c>
+      <c r="K1" s="14" t="inlineStr">
+        <is>
+          <t>¿Qué pasó?</t>
         </is>
       </c>
     </row>
@@ -798,6 +899,11 @@
       <c r="J2" s="10" t="inlineStr">
         <is>
           <t>CONCEPTO</t>
+        </is>
+      </c>
+      <c r="K2" s="15" t="inlineStr">
+        <is>
+          <t>CATEGORIA</t>
         </is>
       </c>
     </row>
@@ -851,6 +957,11 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="E1:H1"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="K4:K500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="CATEGORIA inválida" error="Valores: reclamo, compromiso, otros — o dejar vacío (pago normal)." type="list">
+      <formula1>"reclamo,compromiso,otros"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -861,7 +972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -874,6 +985,7 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="30" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -882,16 +994,21 @@
           <t>¿Quién cobró?</t>
         </is>
       </c>
+      <c r="B1" s="12" t="n"/>
       <c r="C1" s="2" t="inlineStr">
         <is>
           <t>¿Dónde vive?</t>
         </is>
       </c>
+      <c r="D1" s="12" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
           <t>¿Cuánto y cuándo?</t>
         </is>
       </c>
+      <c r="F1" s="13" t="n"/>
+      <c r="G1" s="13" t="n"/>
+      <c r="H1" s="12" t="n"/>
       <c r="I1" s="4" t="inlineStr">
         <is>
           <t>¿Alguna nota?</t>
@@ -900,6 +1017,11 @@
       <c r="J1" s="5" t="inlineStr">
         <is>
           <t>¿Qué tipo?</t>
+        </is>
+      </c>
+      <c r="K1" s="14" t="inlineStr">
+        <is>
+          <t>¿Qué pasó?</t>
         </is>
       </c>
     </row>
@@ -952,6 +1074,11 @@
       <c r="J2" s="10" t="inlineStr">
         <is>
           <t>CONCEPTO</t>
+        </is>
+      </c>
+      <c r="K2" s="15" t="inlineStr">
+        <is>
+          <t>CATEGORIA</t>
         </is>
       </c>
     </row>
@@ -1005,6 +1132,11 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="E1:H1"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="K4:K500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="CATEGORIA inválida" error="Valores: reclamo, compromiso, otros — o dejar vacío (pago normal)." type="list">
+      <formula1>"reclamo,compromiso,otros"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/4_pagos/efectivo/inputs/mesa_5.xlsx
+++ b/4_pagos/efectivo/inputs/mesa_5.xlsx
@@ -214,7 +214,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -256,6 +256,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -622,7 +625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -775,6 +778,1497 @@
       </c>
       <c r="I3" s="11" t="inlineStr"/>
       <c r="J3" s="11" t="inlineStr"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="I4" s="16" t="n"/>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="I5" s="16" t="n"/>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="I6" s="16" t="n"/>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="I7" s="16" t="n"/>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="I8" s="16" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="I9" s="16" t="n"/>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="I10" s="16" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="I11" s="16" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="I12" s="16" t="n"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="I13" s="16" t="n"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="I14" s="16" t="n"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="I15" s="16" t="n"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="I16" s="16" t="n"/>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="I17" s="16" t="n"/>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="I18" s="16" t="n"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="I19" s="16" t="n"/>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="I20" s="16" t="n"/>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="I21" s="16" t="n"/>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="I22" s="16" t="n"/>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="I23" s="16" t="n"/>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="I24" s="16" t="n"/>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="I25" s="16" t="n"/>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="I26" s="16" t="n"/>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="I27" s="16" t="n"/>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="I28" s="16" t="n"/>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="I29" s="16" t="n"/>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="I30" s="16" t="n"/>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="I31" s="16" t="n"/>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="I32" s="16" t="n"/>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="I33" s="16" t="n"/>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="I34" s="16" t="n"/>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="I35" s="16" t="n"/>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="I36" s="16" t="n"/>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="I37" s="16" t="n"/>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="I38" s="16" t="n"/>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="I39" s="16" t="n"/>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="I40" s="16" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="I41" s="16" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="I42" s="16" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="I43" s="16" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="I44" s="16" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="I45" s="16" t="n"/>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="I46" s="16" t="n"/>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="I47" s="16" t="n"/>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="I48" s="16" t="n"/>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="I49" s="16" t="n"/>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="I50" s="16" t="n"/>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="I51" s="16" t="n"/>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="I52" s="16" t="n"/>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="I53" s="16" t="n"/>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="I54" s="16" t="n"/>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="I55" s="16" t="n"/>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="I56" s="16" t="n"/>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="I57" s="16" t="n"/>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="I58" s="16" t="n"/>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="I59" s="16" t="n"/>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="I60" s="16" t="n"/>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="I61" s="16" t="n"/>
+    </row>
+    <row r="62" ht="18" customHeight="1">
+      <c r="I62" s="16" t="n"/>
+    </row>
+    <row r="63" ht="18" customHeight="1">
+      <c r="I63" s="16" t="n"/>
+    </row>
+    <row r="64" ht="18" customHeight="1">
+      <c r="I64" s="16" t="n"/>
+    </row>
+    <row r="65" ht="18" customHeight="1">
+      <c r="I65" s="16" t="n"/>
+    </row>
+    <row r="66" ht="18" customHeight="1">
+      <c r="I66" s="16" t="n"/>
+    </row>
+    <row r="67" ht="18" customHeight="1">
+      <c r="I67" s="16" t="n"/>
+    </row>
+    <row r="68" ht="18" customHeight="1">
+      <c r="I68" s="16" t="n"/>
+    </row>
+    <row r="69" ht="18" customHeight="1">
+      <c r="I69" s="16" t="n"/>
+    </row>
+    <row r="70" ht="18" customHeight="1">
+      <c r="I70" s="16" t="n"/>
+    </row>
+    <row r="71" ht="18" customHeight="1">
+      <c r="I71" s="16" t="n"/>
+    </row>
+    <row r="72" ht="18" customHeight="1">
+      <c r="I72" s="16" t="n"/>
+    </row>
+    <row r="73" ht="18" customHeight="1">
+      <c r="I73" s="16" t="n"/>
+    </row>
+    <row r="74" ht="18" customHeight="1">
+      <c r="I74" s="16" t="n"/>
+    </row>
+    <row r="75" ht="18" customHeight="1">
+      <c r="I75" s="16" t="n"/>
+    </row>
+    <row r="76" ht="18" customHeight="1">
+      <c r="I76" s="16" t="n"/>
+    </row>
+    <row r="77" ht="18" customHeight="1">
+      <c r="I77" s="16" t="n"/>
+    </row>
+    <row r="78" ht="18" customHeight="1">
+      <c r="I78" s="16" t="n"/>
+    </row>
+    <row r="79" ht="18" customHeight="1">
+      <c r="I79" s="16" t="n"/>
+    </row>
+    <row r="80" ht="18" customHeight="1">
+      <c r="I80" s="16" t="n"/>
+    </row>
+    <row r="81" ht="18" customHeight="1">
+      <c r="I81" s="16" t="n"/>
+    </row>
+    <row r="82" ht="18" customHeight="1">
+      <c r="I82" s="16" t="n"/>
+    </row>
+    <row r="83" ht="18" customHeight="1">
+      <c r="I83" s="16" t="n"/>
+    </row>
+    <row r="84" ht="18" customHeight="1">
+      <c r="I84" s="16" t="n"/>
+    </row>
+    <row r="85" ht="18" customHeight="1">
+      <c r="I85" s="16" t="n"/>
+    </row>
+    <row r="86" ht="18" customHeight="1">
+      <c r="I86" s="16" t="n"/>
+    </row>
+    <row r="87" ht="18" customHeight="1">
+      <c r="I87" s="16" t="n"/>
+    </row>
+    <row r="88" ht="18" customHeight="1">
+      <c r="I88" s="16" t="n"/>
+    </row>
+    <row r="89" ht="18" customHeight="1">
+      <c r="I89" s="16" t="n"/>
+    </row>
+    <row r="90" ht="18" customHeight="1">
+      <c r="I90" s="16" t="n"/>
+    </row>
+    <row r="91" ht="18" customHeight="1">
+      <c r="I91" s="16" t="n"/>
+    </row>
+    <row r="92" ht="18" customHeight="1">
+      <c r="I92" s="16" t="n"/>
+    </row>
+    <row r="93" ht="18" customHeight="1">
+      <c r="I93" s="16" t="n"/>
+    </row>
+    <row r="94" ht="18" customHeight="1">
+      <c r="I94" s="16" t="n"/>
+    </row>
+    <row r="95" ht="18" customHeight="1">
+      <c r="I95" s="16" t="n"/>
+    </row>
+    <row r="96" ht="18" customHeight="1">
+      <c r="I96" s="16" t="n"/>
+    </row>
+    <row r="97" ht="18" customHeight="1">
+      <c r="I97" s="16" t="n"/>
+    </row>
+    <row r="98" ht="18" customHeight="1">
+      <c r="I98" s="16" t="n"/>
+    </row>
+    <row r="99" ht="18" customHeight="1">
+      <c r="I99" s="16" t="n"/>
+    </row>
+    <row r="100" ht="18" customHeight="1">
+      <c r="I100" s="16" t="n"/>
+    </row>
+    <row r="101" ht="18" customHeight="1">
+      <c r="I101" s="16" t="n"/>
+    </row>
+    <row r="102" ht="18" customHeight="1">
+      <c r="I102" s="16" t="n"/>
+    </row>
+    <row r="103" ht="18" customHeight="1">
+      <c r="I103" s="16" t="n"/>
+    </row>
+    <row r="104" ht="18" customHeight="1">
+      <c r="I104" s="16" t="n"/>
+    </row>
+    <row r="105" ht="18" customHeight="1">
+      <c r="I105" s="16" t="n"/>
+    </row>
+    <row r="106" ht="18" customHeight="1">
+      <c r="I106" s="16" t="n"/>
+    </row>
+    <row r="107" ht="18" customHeight="1">
+      <c r="I107" s="16" t="n"/>
+    </row>
+    <row r="108" ht="18" customHeight="1">
+      <c r="I108" s="16" t="n"/>
+    </row>
+    <row r="109" ht="18" customHeight="1">
+      <c r="I109" s="16" t="n"/>
+    </row>
+    <row r="110" ht="18" customHeight="1">
+      <c r="I110" s="16" t="n"/>
+    </row>
+    <row r="111" ht="18" customHeight="1">
+      <c r="I111" s="16" t="n"/>
+    </row>
+    <row r="112" ht="18" customHeight="1">
+      <c r="I112" s="16" t="n"/>
+    </row>
+    <row r="113" ht="18" customHeight="1">
+      <c r="I113" s="16" t="n"/>
+    </row>
+    <row r="114" ht="18" customHeight="1">
+      <c r="I114" s="16" t="n"/>
+    </row>
+    <row r="115" ht="18" customHeight="1">
+      <c r="I115" s="16" t="n"/>
+    </row>
+    <row r="116" ht="18" customHeight="1">
+      <c r="I116" s="16" t="n"/>
+    </row>
+    <row r="117" ht="18" customHeight="1">
+      <c r="I117" s="16" t="n"/>
+    </row>
+    <row r="118" ht="18" customHeight="1">
+      <c r="I118" s="16" t="n"/>
+    </row>
+    <row r="119" ht="18" customHeight="1">
+      <c r="I119" s="16" t="n"/>
+    </row>
+    <row r="120" ht="18" customHeight="1">
+      <c r="I120" s="16" t="n"/>
+    </row>
+    <row r="121" ht="18" customHeight="1">
+      <c r="I121" s="16" t="n"/>
+    </row>
+    <row r="122" ht="18" customHeight="1">
+      <c r="I122" s="16" t="n"/>
+    </row>
+    <row r="123" ht="18" customHeight="1">
+      <c r="I123" s="16" t="n"/>
+    </row>
+    <row r="124" ht="18" customHeight="1">
+      <c r="I124" s="16" t="n"/>
+    </row>
+    <row r="125" ht="18" customHeight="1">
+      <c r="I125" s="16" t="n"/>
+    </row>
+    <row r="126" ht="18" customHeight="1">
+      <c r="I126" s="16" t="n"/>
+    </row>
+    <row r="127" ht="18" customHeight="1">
+      <c r="I127" s="16" t="n"/>
+    </row>
+    <row r="128" ht="18" customHeight="1">
+      <c r="I128" s="16" t="n"/>
+    </row>
+    <row r="129" ht="18" customHeight="1">
+      <c r="I129" s="16" t="n"/>
+    </row>
+    <row r="130" ht="18" customHeight="1">
+      <c r="I130" s="16" t="n"/>
+    </row>
+    <row r="131" ht="18" customHeight="1">
+      <c r="I131" s="16" t="n"/>
+    </row>
+    <row r="132" ht="18" customHeight="1">
+      <c r="I132" s="16" t="n"/>
+    </row>
+    <row r="133" ht="18" customHeight="1">
+      <c r="I133" s="16" t="n"/>
+    </row>
+    <row r="134" ht="18" customHeight="1">
+      <c r="I134" s="16" t="n"/>
+    </row>
+    <row r="135" ht="18" customHeight="1">
+      <c r="I135" s="16" t="n"/>
+    </row>
+    <row r="136" ht="18" customHeight="1">
+      <c r="I136" s="16" t="n"/>
+    </row>
+    <row r="137" ht="18" customHeight="1">
+      <c r="I137" s="16" t="n"/>
+    </row>
+    <row r="138" ht="18" customHeight="1">
+      <c r="I138" s="16" t="n"/>
+    </row>
+    <row r="139" ht="18" customHeight="1">
+      <c r="I139" s="16" t="n"/>
+    </row>
+    <row r="140" ht="18" customHeight="1">
+      <c r="I140" s="16" t="n"/>
+    </row>
+    <row r="141" ht="18" customHeight="1">
+      <c r="I141" s="16" t="n"/>
+    </row>
+    <row r="142" ht="18" customHeight="1">
+      <c r="I142" s="16" t="n"/>
+    </row>
+    <row r="143" ht="18" customHeight="1">
+      <c r="I143" s="16" t="n"/>
+    </row>
+    <row r="144" ht="18" customHeight="1">
+      <c r="I144" s="16" t="n"/>
+    </row>
+    <row r="145" ht="18" customHeight="1">
+      <c r="I145" s="16" t="n"/>
+    </row>
+    <row r="146" ht="18" customHeight="1">
+      <c r="I146" s="16" t="n"/>
+    </row>
+    <row r="147" ht="18" customHeight="1">
+      <c r="I147" s="16" t="n"/>
+    </row>
+    <row r="148" ht="18" customHeight="1">
+      <c r="I148" s="16" t="n"/>
+    </row>
+    <row r="149" ht="18" customHeight="1">
+      <c r="I149" s="16" t="n"/>
+    </row>
+    <row r="150" ht="18" customHeight="1">
+      <c r="I150" s="16" t="n"/>
+    </row>
+    <row r="151" ht="18" customHeight="1">
+      <c r="I151" s="16" t="n"/>
+    </row>
+    <row r="152" ht="18" customHeight="1">
+      <c r="I152" s="16" t="n"/>
+    </row>
+    <row r="153" ht="18" customHeight="1">
+      <c r="I153" s="16" t="n"/>
+    </row>
+    <row r="154" ht="18" customHeight="1">
+      <c r="I154" s="16" t="n"/>
+    </row>
+    <row r="155" ht="18" customHeight="1">
+      <c r="I155" s="16" t="n"/>
+    </row>
+    <row r="156" ht="18" customHeight="1">
+      <c r="I156" s="16" t="n"/>
+    </row>
+    <row r="157" ht="18" customHeight="1">
+      <c r="I157" s="16" t="n"/>
+    </row>
+    <row r="158" ht="18" customHeight="1">
+      <c r="I158" s="16" t="n"/>
+    </row>
+    <row r="159" ht="18" customHeight="1">
+      <c r="I159" s="16" t="n"/>
+    </row>
+    <row r="160" ht="18" customHeight="1">
+      <c r="I160" s="16" t="n"/>
+    </row>
+    <row r="161" ht="18" customHeight="1">
+      <c r="I161" s="16" t="n"/>
+    </row>
+    <row r="162" ht="18" customHeight="1">
+      <c r="I162" s="16" t="n"/>
+    </row>
+    <row r="163" ht="18" customHeight="1">
+      <c r="I163" s="16" t="n"/>
+    </row>
+    <row r="164" ht="18" customHeight="1">
+      <c r="I164" s="16" t="n"/>
+    </row>
+    <row r="165" ht="18" customHeight="1">
+      <c r="I165" s="16" t="n"/>
+    </row>
+    <row r="166" ht="18" customHeight="1">
+      <c r="I166" s="16" t="n"/>
+    </row>
+    <row r="167" ht="18" customHeight="1">
+      <c r="I167" s="16" t="n"/>
+    </row>
+    <row r="168" ht="18" customHeight="1">
+      <c r="I168" s="16" t="n"/>
+    </row>
+    <row r="169" ht="18" customHeight="1">
+      <c r="I169" s="16" t="n"/>
+    </row>
+    <row r="170" ht="18" customHeight="1">
+      <c r="I170" s="16" t="n"/>
+    </row>
+    <row r="171" ht="18" customHeight="1">
+      <c r="I171" s="16" t="n"/>
+    </row>
+    <row r="172" ht="18" customHeight="1">
+      <c r="I172" s="16" t="n"/>
+    </row>
+    <row r="173" ht="18" customHeight="1">
+      <c r="I173" s="16" t="n"/>
+    </row>
+    <row r="174" ht="18" customHeight="1">
+      <c r="I174" s="16" t="n"/>
+    </row>
+    <row r="175" ht="18" customHeight="1">
+      <c r="I175" s="16" t="n"/>
+    </row>
+    <row r="176" ht="18" customHeight="1">
+      <c r="I176" s="16" t="n"/>
+    </row>
+    <row r="177" ht="18" customHeight="1">
+      <c r="I177" s="16" t="n"/>
+    </row>
+    <row r="178" ht="18" customHeight="1">
+      <c r="I178" s="16" t="n"/>
+    </row>
+    <row r="179" ht="18" customHeight="1">
+      <c r="I179" s="16" t="n"/>
+    </row>
+    <row r="180" ht="18" customHeight="1">
+      <c r="I180" s="16" t="n"/>
+    </row>
+    <row r="181" ht="18" customHeight="1">
+      <c r="I181" s="16" t="n"/>
+    </row>
+    <row r="182" ht="18" customHeight="1">
+      <c r="I182" s="16" t="n"/>
+    </row>
+    <row r="183" ht="18" customHeight="1">
+      <c r="I183" s="16" t="n"/>
+    </row>
+    <row r="184" ht="18" customHeight="1">
+      <c r="I184" s="16" t="n"/>
+    </row>
+    <row r="185" ht="18" customHeight="1">
+      <c r="I185" s="16" t="n"/>
+    </row>
+    <row r="186" ht="18" customHeight="1">
+      <c r="I186" s="16" t="n"/>
+    </row>
+    <row r="187" ht="18" customHeight="1">
+      <c r="I187" s="16" t="n"/>
+    </row>
+    <row r="188" ht="18" customHeight="1">
+      <c r="I188" s="16" t="n"/>
+    </row>
+    <row r="189" ht="18" customHeight="1">
+      <c r="I189" s="16" t="n"/>
+    </row>
+    <row r="190" ht="18" customHeight="1">
+      <c r="I190" s="16" t="n"/>
+    </row>
+    <row r="191" ht="18" customHeight="1">
+      <c r="I191" s="16" t="n"/>
+    </row>
+    <row r="192" ht="18" customHeight="1">
+      <c r="I192" s="16" t="n"/>
+    </row>
+    <row r="193" ht="18" customHeight="1">
+      <c r="I193" s="16" t="n"/>
+    </row>
+    <row r="194" ht="18" customHeight="1">
+      <c r="I194" s="16" t="n"/>
+    </row>
+    <row r="195" ht="18" customHeight="1">
+      <c r="I195" s="16" t="n"/>
+    </row>
+    <row r="196" ht="18" customHeight="1">
+      <c r="I196" s="16" t="n"/>
+    </row>
+    <row r="197" ht="18" customHeight="1">
+      <c r="I197" s="16" t="n"/>
+    </row>
+    <row r="198" ht="18" customHeight="1">
+      <c r="I198" s="16" t="n"/>
+    </row>
+    <row r="199" ht="18" customHeight="1">
+      <c r="I199" s="16" t="n"/>
+    </row>
+    <row r="200" ht="18" customHeight="1">
+      <c r="I200" s="16" t="n"/>
+    </row>
+    <row r="201" ht="18" customHeight="1">
+      <c r="I201" s="16" t="n"/>
+    </row>
+    <row r="202" ht="18" customHeight="1">
+      <c r="I202" s="16" t="n"/>
+    </row>
+    <row r="203" ht="18" customHeight="1">
+      <c r="I203" s="16" t="n"/>
+    </row>
+    <row r="204" ht="18" customHeight="1">
+      <c r="I204" s="16" t="n"/>
+    </row>
+    <row r="205" ht="18" customHeight="1">
+      <c r="I205" s="16" t="n"/>
+    </row>
+    <row r="206" ht="18" customHeight="1">
+      <c r="I206" s="16" t="n"/>
+    </row>
+    <row r="207" ht="18" customHeight="1">
+      <c r="I207" s="16" t="n"/>
+    </row>
+    <row r="208" ht="18" customHeight="1">
+      <c r="I208" s="16" t="n"/>
+    </row>
+    <row r="209" ht="18" customHeight="1">
+      <c r="I209" s="16" t="n"/>
+    </row>
+    <row r="210" ht="18" customHeight="1">
+      <c r="I210" s="16" t="n"/>
+    </row>
+    <row r="211" ht="18" customHeight="1">
+      <c r="I211" s="16" t="n"/>
+    </row>
+    <row r="212" ht="18" customHeight="1">
+      <c r="I212" s="16" t="n"/>
+    </row>
+    <row r="213" ht="18" customHeight="1">
+      <c r="I213" s="16" t="n"/>
+    </row>
+    <row r="214" ht="18" customHeight="1">
+      <c r="I214" s="16" t="n"/>
+    </row>
+    <row r="215" ht="18" customHeight="1">
+      <c r="I215" s="16" t="n"/>
+    </row>
+    <row r="216" ht="18" customHeight="1">
+      <c r="I216" s="16" t="n"/>
+    </row>
+    <row r="217" ht="18" customHeight="1">
+      <c r="I217" s="16" t="n"/>
+    </row>
+    <row r="218" ht="18" customHeight="1">
+      <c r="I218" s="16" t="n"/>
+    </row>
+    <row r="219" ht="18" customHeight="1">
+      <c r="I219" s="16" t="n"/>
+    </row>
+    <row r="220" ht="18" customHeight="1">
+      <c r="I220" s="16" t="n"/>
+    </row>
+    <row r="221" ht="18" customHeight="1">
+      <c r="I221" s="16" t="n"/>
+    </row>
+    <row r="222" ht="18" customHeight="1">
+      <c r="I222" s="16" t="n"/>
+    </row>
+    <row r="223" ht="18" customHeight="1">
+      <c r="I223" s="16" t="n"/>
+    </row>
+    <row r="224" ht="18" customHeight="1">
+      <c r="I224" s="16" t="n"/>
+    </row>
+    <row r="225" ht="18" customHeight="1">
+      <c r="I225" s="16" t="n"/>
+    </row>
+    <row r="226" ht="18" customHeight="1">
+      <c r="I226" s="16" t="n"/>
+    </row>
+    <row r="227" ht="18" customHeight="1">
+      <c r="I227" s="16" t="n"/>
+    </row>
+    <row r="228" ht="18" customHeight="1">
+      <c r="I228" s="16" t="n"/>
+    </row>
+    <row r="229" ht="18" customHeight="1">
+      <c r="I229" s="16" t="n"/>
+    </row>
+    <row r="230" ht="18" customHeight="1">
+      <c r="I230" s="16" t="n"/>
+    </row>
+    <row r="231" ht="18" customHeight="1">
+      <c r="I231" s="16" t="n"/>
+    </row>
+    <row r="232" ht="18" customHeight="1">
+      <c r="I232" s="16" t="n"/>
+    </row>
+    <row r="233" ht="18" customHeight="1">
+      <c r="I233" s="16" t="n"/>
+    </row>
+    <row r="234" ht="18" customHeight="1">
+      <c r="I234" s="16" t="n"/>
+    </row>
+    <row r="235" ht="18" customHeight="1">
+      <c r="I235" s="16" t="n"/>
+    </row>
+    <row r="236" ht="18" customHeight="1">
+      <c r="I236" s="16" t="n"/>
+    </row>
+    <row r="237" ht="18" customHeight="1">
+      <c r="I237" s="16" t="n"/>
+    </row>
+    <row r="238" ht="18" customHeight="1">
+      <c r="I238" s="16" t="n"/>
+    </row>
+    <row r="239" ht="18" customHeight="1">
+      <c r="I239" s="16" t="n"/>
+    </row>
+    <row r="240" ht="18" customHeight="1">
+      <c r="I240" s="16" t="n"/>
+    </row>
+    <row r="241" ht="18" customHeight="1">
+      <c r="I241" s="16" t="n"/>
+    </row>
+    <row r="242" ht="18" customHeight="1">
+      <c r="I242" s="16" t="n"/>
+    </row>
+    <row r="243" ht="18" customHeight="1">
+      <c r="I243" s="16" t="n"/>
+    </row>
+    <row r="244" ht="18" customHeight="1">
+      <c r="I244" s="16" t="n"/>
+    </row>
+    <row r="245" ht="18" customHeight="1">
+      <c r="I245" s="16" t="n"/>
+    </row>
+    <row r="246" ht="18" customHeight="1">
+      <c r="I246" s="16" t="n"/>
+    </row>
+    <row r="247" ht="18" customHeight="1">
+      <c r="I247" s="16" t="n"/>
+    </row>
+    <row r="248" ht="18" customHeight="1">
+      <c r="I248" s="16" t="n"/>
+    </row>
+    <row r="249" ht="18" customHeight="1">
+      <c r="I249" s="16" t="n"/>
+    </row>
+    <row r="250" ht="18" customHeight="1">
+      <c r="I250" s="16" t="n"/>
+    </row>
+    <row r="251" ht="18" customHeight="1">
+      <c r="I251" s="16" t="n"/>
+    </row>
+    <row r="252" ht="18" customHeight="1">
+      <c r="I252" s="16" t="n"/>
+    </row>
+    <row r="253" ht="18" customHeight="1">
+      <c r="I253" s="16" t="n"/>
+    </row>
+    <row r="254" ht="18" customHeight="1">
+      <c r="I254" s="16" t="n"/>
+    </row>
+    <row r="255" ht="18" customHeight="1">
+      <c r="I255" s="16" t="n"/>
+    </row>
+    <row r="256" ht="18" customHeight="1">
+      <c r="I256" s="16" t="n"/>
+    </row>
+    <row r="257" ht="18" customHeight="1">
+      <c r="I257" s="16" t="n"/>
+    </row>
+    <row r="258" ht="18" customHeight="1">
+      <c r="I258" s="16" t="n"/>
+    </row>
+    <row r="259" ht="18" customHeight="1">
+      <c r="I259" s="16" t="n"/>
+    </row>
+    <row r="260" ht="18" customHeight="1">
+      <c r="I260" s="16" t="n"/>
+    </row>
+    <row r="261" ht="18" customHeight="1">
+      <c r="I261" s="16" t="n"/>
+    </row>
+    <row r="262" ht="18" customHeight="1">
+      <c r="I262" s="16" t="n"/>
+    </row>
+    <row r="263" ht="18" customHeight="1">
+      <c r="I263" s="16" t="n"/>
+    </row>
+    <row r="264" ht="18" customHeight="1">
+      <c r="I264" s="16" t="n"/>
+    </row>
+    <row r="265" ht="18" customHeight="1">
+      <c r="I265" s="16" t="n"/>
+    </row>
+    <row r="266" ht="18" customHeight="1">
+      <c r="I266" s="16" t="n"/>
+    </row>
+    <row r="267" ht="18" customHeight="1">
+      <c r="I267" s="16" t="n"/>
+    </row>
+    <row r="268" ht="18" customHeight="1">
+      <c r="I268" s="16" t="n"/>
+    </row>
+    <row r="269" ht="18" customHeight="1">
+      <c r="I269" s="16" t="n"/>
+    </row>
+    <row r="270" ht="18" customHeight="1">
+      <c r="I270" s="16" t="n"/>
+    </row>
+    <row r="271" ht="18" customHeight="1">
+      <c r="I271" s="16" t="n"/>
+    </row>
+    <row r="272" ht="18" customHeight="1">
+      <c r="I272" s="16" t="n"/>
+    </row>
+    <row r="273" ht="18" customHeight="1">
+      <c r="I273" s="16" t="n"/>
+    </row>
+    <row r="274" ht="18" customHeight="1">
+      <c r="I274" s="16" t="n"/>
+    </row>
+    <row r="275" ht="18" customHeight="1">
+      <c r="I275" s="16" t="n"/>
+    </row>
+    <row r="276" ht="18" customHeight="1">
+      <c r="I276" s="16" t="n"/>
+    </row>
+    <row r="277" ht="18" customHeight="1">
+      <c r="I277" s="16" t="n"/>
+    </row>
+    <row r="278" ht="18" customHeight="1">
+      <c r="I278" s="16" t="n"/>
+    </row>
+    <row r="279" ht="18" customHeight="1">
+      <c r="I279" s="16" t="n"/>
+    </row>
+    <row r="280" ht="18" customHeight="1">
+      <c r="I280" s="16" t="n"/>
+    </row>
+    <row r="281" ht="18" customHeight="1">
+      <c r="I281" s="16" t="n"/>
+    </row>
+    <row r="282" ht="18" customHeight="1">
+      <c r="I282" s="16" t="n"/>
+    </row>
+    <row r="283" ht="18" customHeight="1">
+      <c r="I283" s="16" t="n"/>
+    </row>
+    <row r="284" ht="18" customHeight="1">
+      <c r="I284" s="16" t="n"/>
+    </row>
+    <row r="285" ht="18" customHeight="1">
+      <c r="I285" s="16" t="n"/>
+    </row>
+    <row r="286" ht="18" customHeight="1">
+      <c r="I286" s="16" t="n"/>
+    </row>
+    <row r="287" ht="18" customHeight="1">
+      <c r="I287" s="16" t="n"/>
+    </row>
+    <row r="288" ht="18" customHeight="1">
+      <c r="I288" s="16" t="n"/>
+    </row>
+    <row r="289" ht="18" customHeight="1">
+      <c r="I289" s="16" t="n"/>
+    </row>
+    <row r="290" ht="18" customHeight="1">
+      <c r="I290" s="16" t="n"/>
+    </row>
+    <row r="291" ht="18" customHeight="1">
+      <c r="I291" s="16" t="n"/>
+    </row>
+    <row r="292" ht="18" customHeight="1">
+      <c r="I292" s="16" t="n"/>
+    </row>
+    <row r="293" ht="18" customHeight="1">
+      <c r="I293" s="16" t="n"/>
+    </row>
+    <row r="294" ht="18" customHeight="1">
+      <c r="I294" s="16" t="n"/>
+    </row>
+    <row r="295" ht="18" customHeight="1">
+      <c r="I295" s="16" t="n"/>
+    </row>
+    <row r="296" ht="18" customHeight="1">
+      <c r="I296" s="16" t="n"/>
+    </row>
+    <row r="297" ht="18" customHeight="1">
+      <c r="I297" s="16" t="n"/>
+    </row>
+    <row r="298" ht="18" customHeight="1">
+      <c r="I298" s="16" t="n"/>
+    </row>
+    <row r="299" ht="18" customHeight="1">
+      <c r="I299" s="16" t="n"/>
+    </row>
+    <row r="300" ht="18" customHeight="1">
+      <c r="I300" s="16" t="n"/>
+    </row>
+    <row r="301" ht="18" customHeight="1">
+      <c r="I301" s="16" t="n"/>
+    </row>
+    <row r="302" ht="18" customHeight="1">
+      <c r="I302" s="16" t="n"/>
+    </row>
+    <row r="303" ht="18" customHeight="1">
+      <c r="I303" s="16" t="n"/>
+    </row>
+    <row r="304" ht="18" customHeight="1">
+      <c r="I304" s="16" t="n"/>
+    </row>
+    <row r="305" ht="18" customHeight="1">
+      <c r="I305" s="16" t="n"/>
+    </row>
+    <row r="306" ht="18" customHeight="1">
+      <c r="I306" s="16" t="n"/>
+    </row>
+    <row r="307" ht="18" customHeight="1">
+      <c r="I307" s="16" t="n"/>
+    </row>
+    <row r="308" ht="18" customHeight="1">
+      <c r="I308" s="16" t="n"/>
+    </row>
+    <row r="309" ht="18" customHeight="1">
+      <c r="I309" s="16" t="n"/>
+    </row>
+    <row r="310" ht="18" customHeight="1">
+      <c r="I310" s="16" t="n"/>
+    </row>
+    <row r="311" ht="18" customHeight="1">
+      <c r="I311" s="16" t="n"/>
+    </row>
+    <row r="312" ht="18" customHeight="1">
+      <c r="I312" s="16" t="n"/>
+    </row>
+    <row r="313" ht="18" customHeight="1">
+      <c r="I313" s="16" t="n"/>
+    </row>
+    <row r="314" ht="18" customHeight="1">
+      <c r="I314" s="16" t="n"/>
+    </row>
+    <row r="315" ht="18" customHeight="1">
+      <c r="I315" s="16" t="n"/>
+    </row>
+    <row r="316" ht="18" customHeight="1">
+      <c r="I316" s="16" t="n"/>
+    </row>
+    <row r="317" ht="18" customHeight="1">
+      <c r="I317" s="16" t="n"/>
+    </row>
+    <row r="318" ht="18" customHeight="1">
+      <c r="I318" s="16" t="n"/>
+    </row>
+    <row r="319" ht="18" customHeight="1">
+      <c r="I319" s="16" t="n"/>
+    </row>
+    <row r="320" ht="18" customHeight="1">
+      <c r="I320" s="16" t="n"/>
+    </row>
+    <row r="321" ht="18" customHeight="1">
+      <c r="I321" s="16" t="n"/>
+    </row>
+    <row r="322" ht="18" customHeight="1">
+      <c r="I322" s="16" t="n"/>
+    </row>
+    <row r="323" ht="18" customHeight="1">
+      <c r="I323" s="16" t="n"/>
+    </row>
+    <row r="324" ht="18" customHeight="1">
+      <c r="I324" s="16" t="n"/>
+    </row>
+    <row r="325" ht="18" customHeight="1">
+      <c r="I325" s="16" t="n"/>
+    </row>
+    <row r="326" ht="18" customHeight="1">
+      <c r="I326" s="16" t="n"/>
+    </row>
+    <row r="327" ht="18" customHeight="1">
+      <c r="I327" s="16" t="n"/>
+    </row>
+    <row r="328" ht="18" customHeight="1">
+      <c r="I328" s="16" t="n"/>
+    </row>
+    <row r="329" ht="18" customHeight="1">
+      <c r="I329" s="16" t="n"/>
+    </row>
+    <row r="330" ht="18" customHeight="1">
+      <c r="I330" s="16" t="n"/>
+    </row>
+    <row r="331" ht="18" customHeight="1">
+      <c r="I331" s="16" t="n"/>
+    </row>
+    <row r="332" ht="18" customHeight="1">
+      <c r="I332" s="16" t="n"/>
+    </row>
+    <row r="333" ht="18" customHeight="1">
+      <c r="I333" s="16" t="n"/>
+    </row>
+    <row r="334" ht="18" customHeight="1">
+      <c r="I334" s="16" t="n"/>
+    </row>
+    <row r="335" ht="18" customHeight="1">
+      <c r="I335" s="16" t="n"/>
+    </row>
+    <row r="336" ht="18" customHeight="1">
+      <c r="I336" s="16" t="n"/>
+    </row>
+    <row r="337" ht="18" customHeight="1">
+      <c r="I337" s="16" t="n"/>
+    </row>
+    <row r="338" ht="18" customHeight="1">
+      <c r="I338" s="16" t="n"/>
+    </row>
+    <row r="339" ht="18" customHeight="1">
+      <c r="I339" s="16" t="n"/>
+    </row>
+    <row r="340" ht="18" customHeight="1">
+      <c r="I340" s="16" t="n"/>
+    </row>
+    <row r="341" ht="18" customHeight="1">
+      <c r="I341" s="16" t="n"/>
+    </row>
+    <row r="342" ht="18" customHeight="1">
+      <c r="I342" s="16" t="n"/>
+    </row>
+    <row r="343" ht="18" customHeight="1">
+      <c r="I343" s="16" t="n"/>
+    </row>
+    <row r="344" ht="18" customHeight="1">
+      <c r="I344" s="16" t="n"/>
+    </row>
+    <row r="345" ht="18" customHeight="1">
+      <c r="I345" s="16" t="n"/>
+    </row>
+    <row r="346" ht="18" customHeight="1">
+      <c r="I346" s="16" t="n"/>
+    </row>
+    <row r="347" ht="18" customHeight="1">
+      <c r="I347" s="16" t="n"/>
+    </row>
+    <row r="348" ht="18" customHeight="1">
+      <c r="I348" s="16" t="n"/>
+    </row>
+    <row r="349" ht="18" customHeight="1">
+      <c r="I349" s="16" t="n"/>
+    </row>
+    <row r="350" ht="18" customHeight="1">
+      <c r="I350" s="16" t="n"/>
+    </row>
+    <row r="351" ht="18" customHeight="1">
+      <c r="I351" s="16" t="n"/>
+    </row>
+    <row r="352" ht="18" customHeight="1">
+      <c r="I352" s="16" t="n"/>
+    </row>
+    <row r="353" ht="18" customHeight="1">
+      <c r="I353" s="16" t="n"/>
+    </row>
+    <row r="354" ht="18" customHeight="1">
+      <c r="I354" s="16" t="n"/>
+    </row>
+    <row r="355" ht="18" customHeight="1">
+      <c r="I355" s="16" t="n"/>
+    </row>
+    <row r="356" ht="18" customHeight="1">
+      <c r="I356" s="16" t="n"/>
+    </row>
+    <row r="357" ht="18" customHeight="1">
+      <c r="I357" s="16" t="n"/>
+    </row>
+    <row r="358" ht="18" customHeight="1">
+      <c r="I358" s="16" t="n"/>
+    </row>
+    <row r="359" ht="18" customHeight="1">
+      <c r="I359" s="16" t="n"/>
+    </row>
+    <row r="360" ht="18" customHeight="1">
+      <c r="I360" s="16" t="n"/>
+    </row>
+    <row r="361" ht="18" customHeight="1">
+      <c r="I361" s="16" t="n"/>
+    </row>
+    <row r="362" ht="18" customHeight="1">
+      <c r="I362" s="16" t="n"/>
+    </row>
+    <row r="363" ht="18" customHeight="1">
+      <c r="I363" s="16" t="n"/>
+    </row>
+    <row r="364" ht="18" customHeight="1">
+      <c r="I364" s="16" t="n"/>
+    </row>
+    <row r="365" ht="18" customHeight="1">
+      <c r="I365" s="16" t="n"/>
+    </row>
+    <row r="366" ht="18" customHeight="1">
+      <c r="I366" s="16" t="n"/>
+    </row>
+    <row r="367" ht="18" customHeight="1">
+      <c r="I367" s="16" t="n"/>
+    </row>
+    <row r="368" ht="18" customHeight="1">
+      <c r="I368" s="16" t="n"/>
+    </row>
+    <row r="369" ht="18" customHeight="1">
+      <c r="I369" s="16" t="n"/>
+    </row>
+    <row r="370" ht="18" customHeight="1">
+      <c r="I370" s="16" t="n"/>
+    </row>
+    <row r="371" ht="18" customHeight="1">
+      <c r="I371" s="16" t="n"/>
+    </row>
+    <row r="372" ht="18" customHeight="1">
+      <c r="I372" s="16" t="n"/>
+    </row>
+    <row r="373" ht="18" customHeight="1">
+      <c r="I373" s="16" t="n"/>
+    </row>
+    <row r="374" ht="18" customHeight="1">
+      <c r="I374" s="16" t="n"/>
+    </row>
+    <row r="375" ht="18" customHeight="1">
+      <c r="I375" s="16" t="n"/>
+    </row>
+    <row r="376" ht="18" customHeight="1">
+      <c r="I376" s="16" t="n"/>
+    </row>
+    <row r="377" ht="18" customHeight="1">
+      <c r="I377" s="16" t="n"/>
+    </row>
+    <row r="378" ht="18" customHeight="1">
+      <c r="I378" s="16" t="n"/>
+    </row>
+    <row r="379" ht="18" customHeight="1">
+      <c r="I379" s="16" t="n"/>
+    </row>
+    <row r="380" ht="18" customHeight="1">
+      <c r="I380" s="16" t="n"/>
+    </row>
+    <row r="381" ht="18" customHeight="1">
+      <c r="I381" s="16" t="n"/>
+    </row>
+    <row r="382" ht="18" customHeight="1">
+      <c r="I382" s="16" t="n"/>
+    </row>
+    <row r="383" ht="18" customHeight="1">
+      <c r="I383" s="16" t="n"/>
+    </row>
+    <row r="384" ht="18" customHeight="1">
+      <c r="I384" s="16" t="n"/>
+    </row>
+    <row r="385" ht="18" customHeight="1">
+      <c r="I385" s="16" t="n"/>
+    </row>
+    <row r="386" ht="18" customHeight="1">
+      <c r="I386" s="16" t="n"/>
+    </row>
+    <row r="387" ht="18" customHeight="1">
+      <c r="I387" s="16" t="n"/>
+    </row>
+    <row r="388" ht="18" customHeight="1">
+      <c r="I388" s="16" t="n"/>
+    </row>
+    <row r="389" ht="18" customHeight="1">
+      <c r="I389" s="16" t="n"/>
+    </row>
+    <row r="390" ht="18" customHeight="1">
+      <c r="I390" s="16" t="n"/>
+    </row>
+    <row r="391" ht="18" customHeight="1">
+      <c r="I391" s="16" t="n"/>
+    </row>
+    <row r="392" ht="18" customHeight="1">
+      <c r="I392" s="16" t="n"/>
+    </row>
+    <row r="393" ht="18" customHeight="1">
+      <c r="I393" s="16" t="n"/>
+    </row>
+    <row r="394" ht="18" customHeight="1">
+      <c r="I394" s="16" t="n"/>
+    </row>
+    <row r="395" ht="18" customHeight="1">
+      <c r="I395" s="16" t="n"/>
+    </row>
+    <row r="396" ht="18" customHeight="1">
+      <c r="I396" s="16" t="n"/>
+    </row>
+    <row r="397" ht="18" customHeight="1">
+      <c r="I397" s="16" t="n"/>
+    </row>
+    <row r="398" ht="18" customHeight="1">
+      <c r="I398" s="16" t="n"/>
+    </row>
+    <row r="399" ht="18" customHeight="1">
+      <c r="I399" s="16" t="n"/>
+    </row>
+    <row r="400" ht="18" customHeight="1">
+      <c r="I400" s="16" t="n"/>
+    </row>
+    <row r="401" ht="18" customHeight="1">
+      <c r="I401" s="16" t="n"/>
+    </row>
+    <row r="402" ht="18" customHeight="1">
+      <c r="I402" s="16" t="n"/>
+    </row>
+    <row r="403" ht="18" customHeight="1">
+      <c r="I403" s="16" t="n"/>
+    </row>
+    <row r="404" ht="18" customHeight="1">
+      <c r="I404" s="16" t="n"/>
+    </row>
+    <row r="405" ht="18" customHeight="1">
+      <c r="I405" s="16" t="n"/>
+    </row>
+    <row r="406" ht="18" customHeight="1">
+      <c r="I406" s="16" t="n"/>
+    </row>
+    <row r="407" ht="18" customHeight="1">
+      <c r="I407" s="16" t="n"/>
+    </row>
+    <row r="408" ht="18" customHeight="1">
+      <c r="I408" s="16" t="n"/>
+    </row>
+    <row r="409" ht="18" customHeight="1">
+      <c r="I409" s="16" t="n"/>
+    </row>
+    <row r="410" ht="18" customHeight="1">
+      <c r="I410" s="16" t="n"/>
+    </row>
+    <row r="411" ht="18" customHeight="1">
+      <c r="I411" s="16" t="n"/>
+    </row>
+    <row r="412" ht="18" customHeight="1">
+      <c r="I412" s="16" t="n"/>
+    </row>
+    <row r="413" ht="18" customHeight="1">
+      <c r="I413" s="16" t="n"/>
+    </row>
+    <row r="414" ht="18" customHeight="1">
+      <c r="I414" s="16" t="n"/>
+    </row>
+    <row r="415" ht="18" customHeight="1">
+      <c r="I415" s="16" t="n"/>
+    </row>
+    <row r="416" ht="18" customHeight="1">
+      <c r="I416" s="16" t="n"/>
+    </row>
+    <row r="417" ht="18" customHeight="1">
+      <c r="I417" s="16" t="n"/>
+    </row>
+    <row r="418" ht="18" customHeight="1">
+      <c r="I418" s="16" t="n"/>
+    </row>
+    <row r="419" ht="18" customHeight="1">
+      <c r="I419" s="16" t="n"/>
+    </row>
+    <row r="420" ht="18" customHeight="1">
+      <c r="I420" s="16" t="n"/>
+    </row>
+    <row r="421" ht="18" customHeight="1">
+      <c r="I421" s="16" t="n"/>
+    </row>
+    <row r="422" ht="18" customHeight="1">
+      <c r="I422" s="16" t="n"/>
+    </row>
+    <row r="423" ht="18" customHeight="1">
+      <c r="I423" s="16" t="n"/>
+    </row>
+    <row r="424" ht="18" customHeight="1">
+      <c r="I424" s="16" t="n"/>
+    </row>
+    <row r="425" ht="18" customHeight="1">
+      <c r="I425" s="16" t="n"/>
+    </row>
+    <row r="426" ht="18" customHeight="1">
+      <c r="I426" s="16" t="n"/>
+    </row>
+    <row r="427" ht="18" customHeight="1">
+      <c r="I427" s="16" t="n"/>
+    </row>
+    <row r="428" ht="18" customHeight="1">
+      <c r="I428" s="16" t="n"/>
+    </row>
+    <row r="429" ht="18" customHeight="1">
+      <c r="I429" s="16" t="n"/>
+    </row>
+    <row r="430" ht="18" customHeight="1">
+      <c r="I430" s="16" t="n"/>
+    </row>
+    <row r="431" ht="18" customHeight="1">
+      <c r="I431" s="16" t="n"/>
+    </row>
+    <row r="432" ht="18" customHeight="1">
+      <c r="I432" s="16" t="n"/>
+    </row>
+    <row r="433" ht="18" customHeight="1">
+      <c r="I433" s="16" t="n"/>
+    </row>
+    <row r="434" ht="18" customHeight="1">
+      <c r="I434" s="16" t="n"/>
+    </row>
+    <row r="435" ht="18" customHeight="1">
+      <c r="I435" s="16" t="n"/>
+    </row>
+    <row r="436" ht="18" customHeight="1">
+      <c r="I436" s="16" t="n"/>
+    </row>
+    <row r="437" ht="18" customHeight="1">
+      <c r="I437" s="16" t="n"/>
+    </row>
+    <row r="438" ht="18" customHeight="1">
+      <c r="I438" s="16" t="n"/>
+    </row>
+    <row r="439" ht="18" customHeight="1">
+      <c r="I439" s="16" t="n"/>
+    </row>
+    <row r="440" ht="18" customHeight="1">
+      <c r="I440" s="16" t="n"/>
+    </row>
+    <row r="441" ht="18" customHeight="1">
+      <c r="I441" s="16" t="n"/>
+    </row>
+    <row r="442" ht="18" customHeight="1">
+      <c r="I442" s="16" t="n"/>
+    </row>
+    <row r="443" ht="18" customHeight="1">
+      <c r="I443" s="16" t="n"/>
+    </row>
+    <row r="444" ht="18" customHeight="1">
+      <c r="I444" s="16" t="n"/>
+    </row>
+    <row r="445" ht="18" customHeight="1">
+      <c r="I445" s="16" t="n"/>
+    </row>
+    <row r="446" ht="18" customHeight="1">
+      <c r="I446" s="16" t="n"/>
+    </row>
+    <row r="447" ht="18" customHeight="1">
+      <c r="I447" s="16" t="n"/>
+    </row>
+    <row r="448" ht="18" customHeight="1">
+      <c r="I448" s="16" t="n"/>
+    </row>
+    <row r="449" ht="18" customHeight="1">
+      <c r="I449" s="16" t="n"/>
+    </row>
+    <row r="450" ht="18" customHeight="1">
+      <c r="I450" s="16" t="n"/>
+    </row>
+    <row r="451" ht="18" customHeight="1">
+      <c r="I451" s="16" t="n"/>
+    </row>
+    <row r="452" ht="18" customHeight="1">
+      <c r="I452" s="16" t="n"/>
+    </row>
+    <row r="453" ht="18" customHeight="1">
+      <c r="I453" s="16" t="n"/>
+    </row>
+    <row r="454" ht="18" customHeight="1">
+      <c r="I454" s="16" t="n"/>
+    </row>
+    <row r="455" ht="18" customHeight="1">
+      <c r="I455" s="16" t="n"/>
+    </row>
+    <row r="456" ht="18" customHeight="1">
+      <c r="I456" s="16" t="n"/>
+    </row>
+    <row r="457" ht="18" customHeight="1">
+      <c r="I457" s="16" t="n"/>
+    </row>
+    <row r="458" ht="18" customHeight="1">
+      <c r="I458" s="16" t="n"/>
+    </row>
+    <row r="459" ht="18" customHeight="1">
+      <c r="I459" s="16" t="n"/>
+    </row>
+    <row r="460" ht="18" customHeight="1">
+      <c r="I460" s="16" t="n"/>
+    </row>
+    <row r="461" ht="18" customHeight="1">
+      <c r="I461" s="16" t="n"/>
+    </row>
+    <row r="462" ht="18" customHeight="1">
+      <c r="I462" s="16" t="n"/>
+    </row>
+    <row r="463" ht="18" customHeight="1">
+      <c r="I463" s="16" t="n"/>
+    </row>
+    <row r="464" ht="18" customHeight="1">
+      <c r="I464" s="16" t="n"/>
+    </row>
+    <row r="465" ht="18" customHeight="1">
+      <c r="I465" s="16" t="n"/>
+    </row>
+    <row r="466" ht="18" customHeight="1">
+      <c r="I466" s="16" t="n"/>
+    </row>
+    <row r="467" ht="18" customHeight="1">
+      <c r="I467" s="16" t="n"/>
+    </row>
+    <row r="468" ht="18" customHeight="1">
+      <c r="I468" s="16" t="n"/>
+    </row>
+    <row r="469" ht="18" customHeight="1">
+      <c r="I469" s="16" t="n"/>
+    </row>
+    <row r="470" ht="18" customHeight="1">
+      <c r="I470" s="16" t="n"/>
+    </row>
+    <row r="471" ht="18" customHeight="1">
+      <c r="I471" s="16" t="n"/>
+    </row>
+    <row r="472" ht="18" customHeight="1">
+      <c r="I472" s="16" t="n"/>
+    </row>
+    <row r="473" ht="18" customHeight="1">
+      <c r="I473" s="16" t="n"/>
+    </row>
+    <row r="474" ht="18" customHeight="1">
+      <c r="I474" s="16" t="n"/>
+    </row>
+    <row r="475" ht="18" customHeight="1">
+      <c r="I475" s="16" t="n"/>
+    </row>
+    <row r="476" ht="18" customHeight="1">
+      <c r="I476" s="16" t="n"/>
+    </row>
+    <row r="477" ht="18" customHeight="1">
+      <c r="I477" s="16" t="n"/>
+    </row>
+    <row r="478" ht="18" customHeight="1">
+      <c r="I478" s="16" t="n"/>
+    </row>
+    <row r="479" ht="18" customHeight="1">
+      <c r="I479" s="16" t="n"/>
+    </row>
+    <row r="480" ht="18" customHeight="1">
+      <c r="I480" s="16" t="n"/>
+    </row>
+    <row r="481" ht="18" customHeight="1">
+      <c r="I481" s="16" t="n"/>
+    </row>
+    <row r="482" ht="18" customHeight="1">
+      <c r="I482" s="16" t="n"/>
+    </row>
+    <row r="483" ht="18" customHeight="1">
+      <c r="I483" s="16" t="n"/>
+    </row>
+    <row r="484" ht="18" customHeight="1">
+      <c r="I484" s="16" t="n"/>
+    </row>
+    <row r="485" ht="18" customHeight="1">
+      <c r="I485" s="16" t="n"/>
+    </row>
+    <row r="486" ht="18" customHeight="1">
+      <c r="I486" s="16" t="n"/>
+    </row>
+    <row r="487" ht="18" customHeight="1">
+      <c r="I487" s="16" t="n"/>
+    </row>
+    <row r="488" ht="18" customHeight="1">
+      <c r="I488" s="16" t="n"/>
+    </row>
+    <row r="489" ht="18" customHeight="1">
+      <c r="I489" s="16" t="n"/>
+    </row>
+    <row r="490" ht="18" customHeight="1">
+      <c r="I490" s="16" t="n"/>
+    </row>
+    <row r="491" ht="18" customHeight="1">
+      <c r="I491" s="16" t="n"/>
+    </row>
+    <row r="492" ht="18" customHeight="1">
+      <c r="I492" s="16" t="n"/>
+    </row>
+    <row r="493" ht="18" customHeight="1">
+      <c r="I493" s="16" t="n"/>
+    </row>
+    <row r="494" ht="18" customHeight="1">
+      <c r="I494" s="16" t="n"/>
+    </row>
+    <row r="495" ht="18" customHeight="1">
+      <c r="I495" s="16" t="n"/>
+    </row>
+    <row r="496" ht="18" customHeight="1">
+      <c r="I496" s="16" t="n"/>
+    </row>
+    <row r="497" ht="18" customHeight="1">
+      <c r="I497" s="16" t="n"/>
+    </row>
+    <row r="498" ht="18" customHeight="1">
+      <c r="I498" s="16" t="n"/>
+    </row>
+    <row r="499" ht="18" customHeight="1">
+      <c r="I499" s="16" t="n"/>
+    </row>
+    <row r="500" ht="18" customHeight="1">
+      <c r="I500" s="16" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -797,7 +2291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -950,6 +2444,1497 @@
       </c>
       <c r="I3" s="11" t="inlineStr"/>
       <c r="J3" s="11" t="inlineStr"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="I4" s="16" t="n"/>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="I5" s="16" t="n"/>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="I6" s="16" t="n"/>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="I7" s="16" t="n"/>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="I8" s="16" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="I9" s="16" t="n"/>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="I10" s="16" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="I11" s="16" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="I12" s="16" t="n"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="I13" s="16" t="n"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="I14" s="16" t="n"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="I15" s="16" t="n"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="I16" s="16" t="n"/>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="I17" s="16" t="n"/>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="I18" s="16" t="n"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="I19" s="16" t="n"/>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="I20" s="16" t="n"/>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="I21" s="16" t="n"/>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="I22" s="16" t="n"/>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="I23" s="16" t="n"/>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="I24" s="16" t="n"/>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="I25" s="16" t="n"/>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="I26" s="16" t="n"/>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="I27" s="16" t="n"/>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="I28" s="16" t="n"/>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="I29" s="16" t="n"/>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="I30" s="16" t="n"/>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="I31" s="16" t="n"/>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="I32" s="16" t="n"/>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="I33" s="16" t="n"/>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="I34" s="16" t="n"/>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="I35" s="16" t="n"/>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="I36" s="16" t="n"/>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="I37" s="16" t="n"/>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="I38" s="16" t="n"/>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="I39" s="16" t="n"/>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="I40" s="16" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="I41" s="16" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="I42" s="16" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="I43" s="16" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="I44" s="16" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="I45" s="16" t="n"/>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="I46" s="16" t="n"/>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="I47" s="16" t="n"/>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="I48" s="16" t="n"/>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="I49" s="16" t="n"/>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="I50" s="16" t="n"/>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="I51" s="16" t="n"/>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="I52" s="16" t="n"/>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="I53" s="16" t="n"/>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="I54" s="16" t="n"/>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="I55" s="16" t="n"/>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="I56" s="16" t="n"/>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="I57" s="16" t="n"/>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="I58" s="16" t="n"/>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="I59" s="16" t="n"/>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="I60" s="16" t="n"/>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="I61" s="16" t="n"/>
+    </row>
+    <row r="62" ht="18" customHeight="1">
+      <c r="I62" s="16" t="n"/>
+    </row>
+    <row r="63" ht="18" customHeight="1">
+      <c r="I63" s="16" t="n"/>
+    </row>
+    <row r="64" ht="18" customHeight="1">
+      <c r="I64" s="16" t="n"/>
+    </row>
+    <row r="65" ht="18" customHeight="1">
+      <c r="I65" s="16" t="n"/>
+    </row>
+    <row r="66" ht="18" customHeight="1">
+      <c r="I66" s="16" t="n"/>
+    </row>
+    <row r="67" ht="18" customHeight="1">
+      <c r="I67" s="16" t="n"/>
+    </row>
+    <row r="68" ht="18" customHeight="1">
+      <c r="I68" s="16" t="n"/>
+    </row>
+    <row r="69" ht="18" customHeight="1">
+      <c r="I69" s="16" t="n"/>
+    </row>
+    <row r="70" ht="18" customHeight="1">
+      <c r="I70" s="16" t="n"/>
+    </row>
+    <row r="71" ht="18" customHeight="1">
+      <c r="I71" s="16" t="n"/>
+    </row>
+    <row r="72" ht="18" customHeight="1">
+      <c r="I72" s="16" t="n"/>
+    </row>
+    <row r="73" ht="18" customHeight="1">
+      <c r="I73" s="16" t="n"/>
+    </row>
+    <row r="74" ht="18" customHeight="1">
+      <c r="I74" s="16" t="n"/>
+    </row>
+    <row r="75" ht="18" customHeight="1">
+      <c r="I75" s="16" t="n"/>
+    </row>
+    <row r="76" ht="18" customHeight="1">
+      <c r="I76" s="16" t="n"/>
+    </row>
+    <row r="77" ht="18" customHeight="1">
+      <c r="I77" s="16" t="n"/>
+    </row>
+    <row r="78" ht="18" customHeight="1">
+      <c r="I78" s="16" t="n"/>
+    </row>
+    <row r="79" ht="18" customHeight="1">
+      <c r="I79" s="16" t="n"/>
+    </row>
+    <row r="80" ht="18" customHeight="1">
+      <c r="I80" s="16" t="n"/>
+    </row>
+    <row r="81" ht="18" customHeight="1">
+      <c r="I81" s="16" t="n"/>
+    </row>
+    <row r="82" ht="18" customHeight="1">
+      <c r="I82" s="16" t="n"/>
+    </row>
+    <row r="83" ht="18" customHeight="1">
+      <c r="I83" s="16" t="n"/>
+    </row>
+    <row r="84" ht="18" customHeight="1">
+      <c r="I84" s="16" t="n"/>
+    </row>
+    <row r="85" ht="18" customHeight="1">
+      <c r="I85" s="16" t="n"/>
+    </row>
+    <row r="86" ht="18" customHeight="1">
+      <c r="I86" s="16" t="n"/>
+    </row>
+    <row r="87" ht="18" customHeight="1">
+      <c r="I87" s="16" t="n"/>
+    </row>
+    <row r="88" ht="18" customHeight="1">
+      <c r="I88" s="16" t="n"/>
+    </row>
+    <row r="89" ht="18" customHeight="1">
+      <c r="I89" s="16" t="n"/>
+    </row>
+    <row r="90" ht="18" customHeight="1">
+      <c r="I90" s="16" t="n"/>
+    </row>
+    <row r="91" ht="18" customHeight="1">
+      <c r="I91" s="16" t="n"/>
+    </row>
+    <row r="92" ht="18" customHeight="1">
+      <c r="I92" s="16" t="n"/>
+    </row>
+    <row r="93" ht="18" customHeight="1">
+      <c r="I93" s="16" t="n"/>
+    </row>
+    <row r="94" ht="18" customHeight="1">
+      <c r="I94" s="16" t="n"/>
+    </row>
+    <row r="95" ht="18" customHeight="1">
+      <c r="I95" s="16" t="n"/>
+    </row>
+    <row r="96" ht="18" customHeight="1">
+      <c r="I96" s="16" t="n"/>
+    </row>
+    <row r="97" ht="18" customHeight="1">
+      <c r="I97" s="16" t="n"/>
+    </row>
+    <row r="98" ht="18" customHeight="1">
+      <c r="I98" s="16" t="n"/>
+    </row>
+    <row r="99" ht="18" customHeight="1">
+      <c r="I99" s="16" t="n"/>
+    </row>
+    <row r="100" ht="18" customHeight="1">
+      <c r="I100" s="16" t="n"/>
+    </row>
+    <row r="101" ht="18" customHeight="1">
+      <c r="I101" s="16" t="n"/>
+    </row>
+    <row r="102" ht="18" customHeight="1">
+      <c r="I102" s="16" t="n"/>
+    </row>
+    <row r="103" ht="18" customHeight="1">
+      <c r="I103" s="16" t="n"/>
+    </row>
+    <row r="104" ht="18" customHeight="1">
+      <c r="I104" s="16" t="n"/>
+    </row>
+    <row r="105" ht="18" customHeight="1">
+      <c r="I105" s="16" t="n"/>
+    </row>
+    <row r="106" ht="18" customHeight="1">
+      <c r="I106" s="16" t="n"/>
+    </row>
+    <row r="107" ht="18" customHeight="1">
+      <c r="I107" s="16" t="n"/>
+    </row>
+    <row r="108" ht="18" customHeight="1">
+      <c r="I108" s="16" t="n"/>
+    </row>
+    <row r="109" ht="18" customHeight="1">
+      <c r="I109" s="16" t="n"/>
+    </row>
+    <row r="110" ht="18" customHeight="1">
+      <c r="I110" s="16" t="n"/>
+    </row>
+    <row r="111" ht="18" customHeight="1">
+      <c r="I111" s="16" t="n"/>
+    </row>
+    <row r="112" ht="18" customHeight="1">
+      <c r="I112" s="16" t="n"/>
+    </row>
+    <row r="113" ht="18" customHeight="1">
+      <c r="I113" s="16" t="n"/>
+    </row>
+    <row r="114" ht="18" customHeight="1">
+      <c r="I114" s="16" t="n"/>
+    </row>
+    <row r="115" ht="18" customHeight="1">
+      <c r="I115" s="16" t="n"/>
+    </row>
+    <row r="116" ht="18" customHeight="1">
+      <c r="I116" s="16" t="n"/>
+    </row>
+    <row r="117" ht="18" customHeight="1">
+      <c r="I117" s="16" t="n"/>
+    </row>
+    <row r="118" ht="18" customHeight="1">
+      <c r="I118" s="16" t="n"/>
+    </row>
+    <row r="119" ht="18" customHeight="1">
+      <c r="I119" s="16" t="n"/>
+    </row>
+    <row r="120" ht="18" customHeight="1">
+      <c r="I120" s="16" t="n"/>
+    </row>
+    <row r="121" ht="18" customHeight="1">
+      <c r="I121" s="16" t="n"/>
+    </row>
+    <row r="122" ht="18" customHeight="1">
+      <c r="I122" s="16" t="n"/>
+    </row>
+    <row r="123" ht="18" customHeight="1">
+      <c r="I123" s="16" t="n"/>
+    </row>
+    <row r="124" ht="18" customHeight="1">
+      <c r="I124" s="16" t="n"/>
+    </row>
+    <row r="125" ht="18" customHeight="1">
+      <c r="I125" s="16" t="n"/>
+    </row>
+    <row r="126" ht="18" customHeight="1">
+      <c r="I126" s="16" t="n"/>
+    </row>
+    <row r="127" ht="18" customHeight="1">
+      <c r="I127" s="16" t="n"/>
+    </row>
+    <row r="128" ht="18" customHeight="1">
+      <c r="I128" s="16" t="n"/>
+    </row>
+    <row r="129" ht="18" customHeight="1">
+      <c r="I129" s="16" t="n"/>
+    </row>
+    <row r="130" ht="18" customHeight="1">
+      <c r="I130" s="16" t="n"/>
+    </row>
+    <row r="131" ht="18" customHeight="1">
+      <c r="I131" s="16" t="n"/>
+    </row>
+    <row r="132" ht="18" customHeight="1">
+      <c r="I132" s="16" t="n"/>
+    </row>
+    <row r="133" ht="18" customHeight="1">
+      <c r="I133" s="16" t="n"/>
+    </row>
+    <row r="134" ht="18" customHeight="1">
+      <c r="I134" s="16" t="n"/>
+    </row>
+    <row r="135" ht="18" customHeight="1">
+      <c r="I135" s="16" t="n"/>
+    </row>
+    <row r="136" ht="18" customHeight="1">
+      <c r="I136" s="16" t="n"/>
+    </row>
+    <row r="137" ht="18" customHeight="1">
+      <c r="I137" s="16" t="n"/>
+    </row>
+    <row r="138" ht="18" customHeight="1">
+      <c r="I138" s="16" t="n"/>
+    </row>
+    <row r="139" ht="18" customHeight="1">
+      <c r="I139" s="16" t="n"/>
+    </row>
+    <row r="140" ht="18" customHeight="1">
+      <c r="I140" s="16" t="n"/>
+    </row>
+    <row r="141" ht="18" customHeight="1">
+      <c r="I141" s="16" t="n"/>
+    </row>
+    <row r="142" ht="18" customHeight="1">
+      <c r="I142" s="16" t="n"/>
+    </row>
+    <row r="143" ht="18" customHeight="1">
+      <c r="I143" s="16" t="n"/>
+    </row>
+    <row r="144" ht="18" customHeight="1">
+      <c r="I144" s="16" t="n"/>
+    </row>
+    <row r="145" ht="18" customHeight="1">
+      <c r="I145" s="16" t="n"/>
+    </row>
+    <row r="146" ht="18" customHeight="1">
+      <c r="I146" s="16" t="n"/>
+    </row>
+    <row r="147" ht="18" customHeight="1">
+      <c r="I147" s="16" t="n"/>
+    </row>
+    <row r="148" ht="18" customHeight="1">
+      <c r="I148" s="16" t="n"/>
+    </row>
+    <row r="149" ht="18" customHeight="1">
+      <c r="I149" s="16" t="n"/>
+    </row>
+    <row r="150" ht="18" customHeight="1">
+      <c r="I150" s="16" t="n"/>
+    </row>
+    <row r="151" ht="18" customHeight="1">
+      <c r="I151" s="16" t="n"/>
+    </row>
+    <row r="152" ht="18" customHeight="1">
+      <c r="I152" s="16" t="n"/>
+    </row>
+    <row r="153" ht="18" customHeight="1">
+      <c r="I153" s="16" t="n"/>
+    </row>
+    <row r="154" ht="18" customHeight="1">
+      <c r="I154" s="16" t="n"/>
+    </row>
+    <row r="155" ht="18" customHeight="1">
+      <c r="I155" s="16" t="n"/>
+    </row>
+    <row r="156" ht="18" customHeight="1">
+      <c r="I156" s="16" t="n"/>
+    </row>
+    <row r="157" ht="18" customHeight="1">
+      <c r="I157" s="16" t="n"/>
+    </row>
+    <row r="158" ht="18" customHeight="1">
+      <c r="I158" s="16" t="n"/>
+    </row>
+    <row r="159" ht="18" customHeight="1">
+      <c r="I159" s="16" t="n"/>
+    </row>
+    <row r="160" ht="18" customHeight="1">
+      <c r="I160" s="16" t="n"/>
+    </row>
+    <row r="161" ht="18" customHeight="1">
+      <c r="I161" s="16" t="n"/>
+    </row>
+    <row r="162" ht="18" customHeight="1">
+      <c r="I162" s="16" t="n"/>
+    </row>
+    <row r="163" ht="18" customHeight="1">
+      <c r="I163" s="16" t="n"/>
+    </row>
+    <row r="164" ht="18" customHeight="1">
+      <c r="I164" s="16" t="n"/>
+    </row>
+    <row r="165" ht="18" customHeight="1">
+      <c r="I165" s="16" t="n"/>
+    </row>
+    <row r="166" ht="18" customHeight="1">
+      <c r="I166" s="16" t="n"/>
+    </row>
+    <row r="167" ht="18" customHeight="1">
+      <c r="I167" s="16" t="n"/>
+    </row>
+    <row r="168" ht="18" customHeight="1">
+      <c r="I168" s="16" t="n"/>
+    </row>
+    <row r="169" ht="18" customHeight="1">
+      <c r="I169" s="16" t="n"/>
+    </row>
+    <row r="170" ht="18" customHeight="1">
+      <c r="I170" s="16" t="n"/>
+    </row>
+    <row r="171" ht="18" customHeight="1">
+      <c r="I171" s="16" t="n"/>
+    </row>
+    <row r="172" ht="18" customHeight="1">
+      <c r="I172" s="16" t="n"/>
+    </row>
+    <row r="173" ht="18" customHeight="1">
+      <c r="I173" s="16" t="n"/>
+    </row>
+    <row r="174" ht="18" customHeight="1">
+      <c r="I174" s="16" t="n"/>
+    </row>
+    <row r="175" ht="18" customHeight="1">
+      <c r="I175" s="16" t="n"/>
+    </row>
+    <row r="176" ht="18" customHeight="1">
+      <c r="I176" s="16" t="n"/>
+    </row>
+    <row r="177" ht="18" customHeight="1">
+      <c r="I177" s="16" t="n"/>
+    </row>
+    <row r="178" ht="18" customHeight="1">
+      <c r="I178" s="16" t="n"/>
+    </row>
+    <row r="179" ht="18" customHeight="1">
+      <c r="I179" s="16" t="n"/>
+    </row>
+    <row r="180" ht="18" customHeight="1">
+      <c r="I180" s="16" t="n"/>
+    </row>
+    <row r="181" ht="18" customHeight="1">
+      <c r="I181" s="16" t="n"/>
+    </row>
+    <row r="182" ht="18" customHeight="1">
+      <c r="I182" s="16" t="n"/>
+    </row>
+    <row r="183" ht="18" customHeight="1">
+      <c r="I183" s="16" t="n"/>
+    </row>
+    <row r="184" ht="18" customHeight="1">
+      <c r="I184" s="16" t="n"/>
+    </row>
+    <row r="185" ht="18" customHeight="1">
+      <c r="I185" s="16" t="n"/>
+    </row>
+    <row r="186" ht="18" customHeight="1">
+      <c r="I186" s="16" t="n"/>
+    </row>
+    <row r="187" ht="18" customHeight="1">
+      <c r="I187" s="16" t="n"/>
+    </row>
+    <row r="188" ht="18" customHeight="1">
+      <c r="I188" s="16" t="n"/>
+    </row>
+    <row r="189" ht="18" customHeight="1">
+      <c r="I189" s="16" t="n"/>
+    </row>
+    <row r="190" ht="18" customHeight="1">
+      <c r="I190" s="16" t="n"/>
+    </row>
+    <row r="191" ht="18" customHeight="1">
+      <c r="I191" s="16" t="n"/>
+    </row>
+    <row r="192" ht="18" customHeight="1">
+      <c r="I192" s="16" t="n"/>
+    </row>
+    <row r="193" ht="18" customHeight="1">
+      <c r="I193" s="16" t="n"/>
+    </row>
+    <row r="194" ht="18" customHeight="1">
+      <c r="I194" s="16" t="n"/>
+    </row>
+    <row r="195" ht="18" customHeight="1">
+      <c r="I195" s="16" t="n"/>
+    </row>
+    <row r="196" ht="18" customHeight="1">
+      <c r="I196" s="16" t="n"/>
+    </row>
+    <row r="197" ht="18" customHeight="1">
+      <c r="I197" s="16" t="n"/>
+    </row>
+    <row r="198" ht="18" customHeight="1">
+      <c r="I198" s="16" t="n"/>
+    </row>
+    <row r="199" ht="18" customHeight="1">
+      <c r="I199" s="16" t="n"/>
+    </row>
+    <row r="200" ht="18" customHeight="1">
+      <c r="I200" s="16" t="n"/>
+    </row>
+    <row r="201" ht="18" customHeight="1">
+      <c r="I201" s="16" t="n"/>
+    </row>
+    <row r="202" ht="18" customHeight="1">
+      <c r="I202" s="16" t="n"/>
+    </row>
+    <row r="203" ht="18" customHeight="1">
+      <c r="I203" s="16" t="n"/>
+    </row>
+    <row r="204" ht="18" customHeight="1">
+      <c r="I204" s="16" t="n"/>
+    </row>
+    <row r="205" ht="18" customHeight="1">
+      <c r="I205" s="16" t="n"/>
+    </row>
+    <row r="206" ht="18" customHeight="1">
+      <c r="I206" s="16" t="n"/>
+    </row>
+    <row r="207" ht="18" customHeight="1">
+      <c r="I207" s="16" t="n"/>
+    </row>
+    <row r="208" ht="18" customHeight="1">
+      <c r="I208" s="16" t="n"/>
+    </row>
+    <row r="209" ht="18" customHeight="1">
+      <c r="I209" s="16" t="n"/>
+    </row>
+    <row r="210" ht="18" customHeight="1">
+      <c r="I210" s="16" t="n"/>
+    </row>
+    <row r="211" ht="18" customHeight="1">
+      <c r="I211" s="16" t="n"/>
+    </row>
+    <row r="212" ht="18" customHeight="1">
+      <c r="I212" s="16" t="n"/>
+    </row>
+    <row r="213" ht="18" customHeight="1">
+      <c r="I213" s="16" t="n"/>
+    </row>
+    <row r="214" ht="18" customHeight="1">
+      <c r="I214" s="16" t="n"/>
+    </row>
+    <row r="215" ht="18" customHeight="1">
+      <c r="I215" s="16" t="n"/>
+    </row>
+    <row r="216" ht="18" customHeight="1">
+      <c r="I216" s="16" t="n"/>
+    </row>
+    <row r="217" ht="18" customHeight="1">
+      <c r="I217" s="16" t="n"/>
+    </row>
+    <row r="218" ht="18" customHeight="1">
+      <c r="I218" s="16" t="n"/>
+    </row>
+    <row r="219" ht="18" customHeight="1">
+      <c r="I219" s="16" t="n"/>
+    </row>
+    <row r="220" ht="18" customHeight="1">
+      <c r="I220" s="16" t="n"/>
+    </row>
+    <row r="221" ht="18" customHeight="1">
+      <c r="I221" s="16" t="n"/>
+    </row>
+    <row r="222" ht="18" customHeight="1">
+      <c r="I222" s="16" t="n"/>
+    </row>
+    <row r="223" ht="18" customHeight="1">
+      <c r="I223" s="16" t="n"/>
+    </row>
+    <row r="224" ht="18" customHeight="1">
+      <c r="I224" s="16" t="n"/>
+    </row>
+    <row r="225" ht="18" customHeight="1">
+      <c r="I225" s="16" t="n"/>
+    </row>
+    <row r="226" ht="18" customHeight="1">
+      <c r="I226" s="16" t="n"/>
+    </row>
+    <row r="227" ht="18" customHeight="1">
+      <c r="I227" s="16" t="n"/>
+    </row>
+    <row r="228" ht="18" customHeight="1">
+      <c r="I228" s="16" t="n"/>
+    </row>
+    <row r="229" ht="18" customHeight="1">
+      <c r="I229" s="16" t="n"/>
+    </row>
+    <row r="230" ht="18" customHeight="1">
+      <c r="I230" s="16" t="n"/>
+    </row>
+    <row r="231" ht="18" customHeight="1">
+      <c r="I231" s="16" t="n"/>
+    </row>
+    <row r="232" ht="18" customHeight="1">
+      <c r="I232" s="16" t="n"/>
+    </row>
+    <row r="233" ht="18" customHeight="1">
+      <c r="I233" s="16" t="n"/>
+    </row>
+    <row r="234" ht="18" customHeight="1">
+      <c r="I234" s="16" t="n"/>
+    </row>
+    <row r="235" ht="18" customHeight="1">
+      <c r="I235" s="16" t="n"/>
+    </row>
+    <row r="236" ht="18" customHeight="1">
+      <c r="I236" s="16" t="n"/>
+    </row>
+    <row r="237" ht="18" customHeight="1">
+      <c r="I237" s="16" t="n"/>
+    </row>
+    <row r="238" ht="18" customHeight="1">
+      <c r="I238" s="16" t="n"/>
+    </row>
+    <row r="239" ht="18" customHeight="1">
+      <c r="I239" s="16" t="n"/>
+    </row>
+    <row r="240" ht="18" customHeight="1">
+      <c r="I240" s="16" t="n"/>
+    </row>
+    <row r="241" ht="18" customHeight="1">
+      <c r="I241" s="16" t="n"/>
+    </row>
+    <row r="242" ht="18" customHeight="1">
+      <c r="I242" s="16" t="n"/>
+    </row>
+    <row r="243" ht="18" customHeight="1">
+      <c r="I243" s="16" t="n"/>
+    </row>
+    <row r="244" ht="18" customHeight="1">
+      <c r="I244" s="16" t="n"/>
+    </row>
+    <row r="245" ht="18" customHeight="1">
+      <c r="I245" s="16" t="n"/>
+    </row>
+    <row r="246" ht="18" customHeight="1">
+      <c r="I246" s="16" t="n"/>
+    </row>
+    <row r="247" ht="18" customHeight="1">
+      <c r="I247" s="16" t="n"/>
+    </row>
+    <row r="248" ht="18" customHeight="1">
+      <c r="I248" s="16" t="n"/>
+    </row>
+    <row r="249" ht="18" customHeight="1">
+      <c r="I249" s="16" t="n"/>
+    </row>
+    <row r="250" ht="18" customHeight="1">
+      <c r="I250" s="16" t="n"/>
+    </row>
+    <row r="251" ht="18" customHeight="1">
+      <c r="I251" s="16" t="n"/>
+    </row>
+    <row r="252" ht="18" customHeight="1">
+      <c r="I252" s="16" t="n"/>
+    </row>
+    <row r="253" ht="18" customHeight="1">
+      <c r="I253" s="16" t="n"/>
+    </row>
+    <row r="254" ht="18" customHeight="1">
+      <c r="I254" s="16" t="n"/>
+    </row>
+    <row r="255" ht="18" customHeight="1">
+      <c r="I255" s="16" t="n"/>
+    </row>
+    <row r="256" ht="18" customHeight="1">
+      <c r="I256" s="16" t="n"/>
+    </row>
+    <row r="257" ht="18" customHeight="1">
+      <c r="I257" s="16" t="n"/>
+    </row>
+    <row r="258" ht="18" customHeight="1">
+      <c r="I258" s="16" t="n"/>
+    </row>
+    <row r="259" ht="18" customHeight="1">
+      <c r="I259" s="16" t="n"/>
+    </row>
+    <row r="260" ht="18" customHeight="1">
+      <c r="I260" s="16" t="n"/>
+    </row>
+    <row r="261" ht="18" customHeight="1">
+      <c r="I261" s="16" t="n"/>
+    </row>
+    <row r="262" ht="18" customHeight="1">
+      <c r="I262" s="16" t="n"/>
+    </row>
+    <row r="263" ht="18" customHeight="1">
+      <c r="I263" s="16" t="n"/>
+    </row>
+    <row r="264" ht="18" customHeight="1">
+      <c r="I264" s="16" t="n"/>
+    </row>
+    <row r="265" ht="18" customHeight="1">
+      <c r="I265" s="16" t="n"/>
+    </row>
+    <row r="266" ht="18" customHeight="1">
+      <c r="I266" s="16" t="n"/>
+    </row>
+    <row r="267" ht="18" customHeight="1">
+      <c r="I267" s="16" t="n"/>
+    </row>
+    <row r="268" ht="18" customHeight="1">
+      <c r="I268" s="16" t="n"/>
+    </row>
+    <row r="269" ht="18" customHeight="1">
+      <c r="I269" s="16" t="n"/>
+    </row>
+    <row r="270" ht="18" customHeight="1">
+      <c r="I270" s="16" t="n"/>
+    </row>
+    <row r="271" ht="18" customHeight="1">
+      <c r="I271" s="16" t="n"/>
+    </row>
+    <row r="272" ht="18" customHeight="1">
+      <c r="I272" s="16" t="n"/>
+    </row>
+    <row r="273" ht="18" customHeight="1">
+      <c r="I273" s="16" t="n"/>
+    </row>
+    <row r="274" ht="18" customHeight="1">
+      <c r="I274" s="16" t="n"/>
+    </row>
+    <row r="275" ht="18" customHeight="1">
+      <c r="I275" s="16" t="n"/>
+    </row>
+    <row r="276" ht="18" customHeight="1">
+      <c r="I276" s="16" t="n"/>
+    </row>
+    <row r="277" ht="18" customHeight="1">
+      <c r="I277" s="16" t="n"/>
+    </row>
+    <row r="278" ht="18" customHeight="1">
+      <c r="I278" s="16" t="n"/>
+    </row>
+    <row r="279" ht="18" customHeight="1">
+      <c r="I279" s="16" t="n"/>
+    </row>
+    <row r="280" ht="18" customHeight="1">
+      <c r="I280" s="16" t="n"/>
+    </row>
+    <row r="281" ht="18" customHeight="1">
+      <c r="I281" s="16" t="n"/>
+    </row>
+    <row r="282" ht="18" customHeight="1">
+      <c r="I282" s="16" t="n"/>
+    </row>
+    <row r="283" ht="18" customHeight="1">
+      <c r="I283" s="16" t="n"/>
+    </row>
+    <row r="284" ht="18" customHeight="1">
+      <c r="I284" s="16" t="n"/>
+    </row>
+    <row r="285" ht="18" customHeight="1">
+      <c r="I285" s="16" t="n"/>
+    </row>
+    <row r="286" ht="18" customHeight="1">
+      <c r="I286" s="16" t="n"/>
+    </row>
+    <row r="287" ht="18" customHeight="1">
+      <c r="I287" s="16" t="n"/>
+    </row>
+    <row r="288" ht="18" customHeight="1">
+      <c r="I288" s="16" t="n"/>
+    </row>
+    <row r="289" ht="18" customHeight="1">
+      <c r="I289" s="16" t="n"/>
+    </row>
+    <row r="290" ht="18" customHeight="1">
+      <c r="I290" s="16" t="n"/>
+    </row>
+    <row r="291" ht="18" customHeight="1">
+      <c r="I291" s="16" t="n"/>
+    </row>
+    <row r="292" ht="18" customHeight="1">
+      <c r="I292" s="16" t="n"/>
+    </row>
+    <row r="293" ht="18" customHeight="1">
+      <c r="I293" s="16" t="n"/>
+    </row>
+    <row r="294" ht="18" customHeight="1">
+      <c r="I294" s="16" t="n"/>
+    </row>
+    <row r="295" ht="18" customHeight="1">
+      <c r="I295" s="16" t="n"/>
+    </row>
+    <row r="296" ht="18" customHeight="1">
+      <c r="I296" s="16" t="n"/>
+    </row>
+    <row r="297" ht="18" customHeight="1">
+      <c r="I297" s="16" t="n"/>
+    </row>
+    <row r="298" ht="18" customHeight="1">
+      <c r="I298" s="16" t="n"/>
+    </row>
+    <row r="299" ht="18" customHeight="1">
+      <c r="I299" s="16" t="n"/>
+    </row>
+    <row r="300" ht="18" customHeight="1">
+      <c r="I300" s="16" t="n"/>
+    </row>
+    <row r="301" ht="18" customHeight="1">
+      <c r="I301" s="16" t="n"/>
+    </row>
+    <row r="302" ht="18" customHeight="1">
+      <c r="I302" s="16" t="n"/>
+    </row>
+    <row r="303" ht="18" customHeight="1">
+      <c r="I303" s="16" t="n"/>
+    </row>
+    <row r="304" ht="18" customHeight="1">
+      <c r="I304" s="16" t="n"/>
+    </row>
+    <row r="305" ht="18" customHeight="1">
+      <c r="I305" s="16" t="n"/>
+    </row>
+    <row r="306" ht="18" customHeight="1">
+      <c r="I306" s="16" t="n"/>
+    </row>
+    <row r="307" ht="18" customHeight="1">
+      <c r="I307" s="16" t="n"/>
+    </row>
+    <row r="308" ht="18" customHeight="1">
+      <c r="I308" s="16" t="n"/>
+    </row>
+    <row r="309" ht="18" customHeight="1">
+      <c r="I309" s="16" t="n"/>
+    </row>
+    <row r="310" ht="18" customHeight="1">
+      <c r="I310" s="16" t="n"/>
+    </row>
+    <row r="311" ht="18" customHeight="1">
+      <c r="I311" s="16" t="n"/>
+    </row>
+    <row r="312" ht="18" customHeight="1">
+      <c r="I312" s="16" t="n"/>
+    </row>
+    <row r="313" ht="18" customHeight="1">
+      <c r="I313" s="16" t="n"/>
+    </row>
+    <row r="314" ht="18" customHeight="1">
+      <c r="I314" s="16" t="n"/>
+    </row>
+    <row r="315" ht="18" customHeight="1">
+      <c r="I315" s="16" t="n"/>
+    </row>
+    <row r="316" ht="18" customHeight="1">
+      <c r="I316" s="16" t="n"/>
+    </row>
+    <row r="317" ht="18" customHeight="1">
+      <c r="I317" s="16" t="n"/>
+    </row>
+    <row r="318" ht="18" customHeight="1">
+      <c r="I318" s="16" t="n"/>
+    </row>
+    <row r="319" ht="18" customHeight="1">
+      <c r="I319" s="16" t="n"/>
+    </row>
+    <row r="320" ht="18" customHeight="1">
+      <c r="I320" s="16" t="n"/>
+    </row>
+    <row r="321" ht="18" customHeight="1">
+      <c r="I321" s="16" t="n"/>
+    </row>
+    <row r="322" ht="18" customHeight="1">
+      <c r="I322" s="16" t="n"/>
+    </row>
+    <row r="323" ht="18" customHeight="1">
+      <c r="I323" s="16" t="n"/>
+    </row>
+    <row r="324" ht="18" customHeight="1">
+      <c r="I324" s="16" t="n"/>
+    </row>
+    <row r="325" ht="18" customHeight="1">
+      <c r="I325" s="16" t="n"/>
+    </row>
+    <row r="326" ht="18" customHeight="1">
+      <c r="I326" s="16" t="n"/>
+    </row>
+    <row r="327" ht="18" customHeight="1">
+      <c r="I327" s="16" t="n"/>
+    </row>
+    <row r="328" ht="18" customHeight="1">
+      <c r="I328" s="16" t="n"/>
+    </row>
+    <row r="329" ht="18" customHeight="1">
+      <c r="I329" s="16" t="n"/>
+    </row>
+    <row r="330" ht="18" customHeight="1">
+      <c r="I330" s="16" t="n"/>
+    </row>
+    <row r="331" ht="18" customHeight="1">
+      <c r="I331" s="16" t="n"/>
+    </row>
+    <row r="332" ht="18" customHeight="1">
+      <c r="I332" s="16" t="n"/>
+    </row>
+    <row r="333" ht="18" customHeight="1">
+      <c r="I333" s="16" t="n"/>
+    </row>
+    <row r="334" ht="18" customHeight="1">
+      <c r="I334" s="16" t="n"/>
+    </row>
+    <row r="335" ht="18" customHeight="1">
+      <c r="I335" s="16" t="n"/>
+    </row>
+    <row r="336" ht="18" customHeight="1">
+      <c r="I336" s="16" t="n"/>
+    </row>
+    <row r="337" ht="18" customHeight="1">
+      <c r="I337" s="16" t="n"/>
+    </row>
+    <row r="338" ht="18" customHeight="1">
+      <c r="I338" s="16" t="n"/>
+    </row>
+    <row r="339" ht="18" customHeight="1">
+      <c r="I339" s="16" t="n"/>
+    </row>
+    <row r="340" ht="18" customHeight="1">
+      <c r="I340" s="16" t="n"/>
+    </row>
+    <row r="341" ht="18" customHeight="1">
+      <c r="I341" s="16" t="n"/>
+    </row>
+    <row r="342" ht="18" customHeight="1">
+      <c r="I342" s="16" t="n"/>
+    </row>
+    <row r="343" ht="18" customHeight="1">
+      <c r="I343" s="16" t="n"/>
+    </row>
+    <row r="344" ht="18" customHeight="1">
+      <c r="I344" s="16" t="n"/>
+    </row>
+    <row r="345" ht="18" customHeight="1">
+      <c r="I345" s="16" t="n"/>
+    </row>
+    <row r="346" ht="18" customHeight="1">
+      <c r="I346" s="16" t="n"/>
+    </row>
+    <row r="347" ht="18" customHeight="1">
+      <c r="I347" s="16" t="n"/>
+    </row>
+    <row r="348" ht="18" customHeight="1">
+      <c r="I348" s="16" t="n"/>
+    </row>
+    <row r="349" ht="18" customHeight="1">
+      <c r="I349" s="16" t="n"/>
+    </row>
+    <row r="350" ht="18" customHeight="1">
+      <c r="I350" s="16" t="n"/>
+    </row>
+    <row r="351" ht="18" customHeight="1">
+      <c r="I351" s="16" t="n"/>
+    </row>
+    <row r="352" ht="18" customHeight="1">
+      <c r="I352" s="16" t="n"/>
+    </row>
+    <row r="353" ht="18" customHeight="1">
+      <c r="I353" s="16" t="n"/>
+    </row>
+    <row r="354" ht="18" customHeight="1">
+      <c r="I354" s="16" t="n"/>
+    </row>
+    <row r="355" ht="18" customHeight="1">
+      <c r="I355" s="16" t="n"/>
+    </row>
+    <row r="356" ht="18" customHeight="1">
+      <c r="I356" s="16" t="n"/>
+    </row>
+    <row r="357" ht="18" customHeight="1">
+      <c r="I357" s="16" t="n"/>
+    </row>
+    <row r="358" ht="18" customHeight="1">
+      <c r="I358" s="16" t="n"/>
+    </row>
+    <row r="359" ht="18" customHeight="1">
+      <c r="I359" s="16" t="n"/>
+    </row>
+    <row r="360" ht="18" customHeight="1">
+      <c r="I360" s="16" t="n"/>
+    </row>
+    <row r="361" ht="18" customHeight="1">
+      <c r="I361" s="16" t="n"/>
+    </row>
+    <row r="362" ht="18" customHeight="1">
+      <c r="I362" s="16" t="n"/>
+    </row>
+    <row r="363" ht="18" customHeight="1">
+      <c r="I363" s="16" t="n"/>
+    </row>
+    <row r="364" ht="18" customHeight="1">
+      <c r="I364" s="16" t="n"/>
+    </row>
+    <row r="365" ht="18" customHeight="1">
+      <c r="I365" s="16" t="n"/>
+    </row>
+    <row r="366" ht="18" customHeight="1">
+      <c r="I366" s="16" t="n"/>
+    </row>
+    <row r="367" ht="18" customHeight="1">
+      <c r="I367" s="16" t="n"/>
+    </row>
+    <row r="368" ht="18" customHeight="1">
+      <c r="I368" s="16" t="n"/>
+    </row>
+    <row r="369" ht="18" customHeight="1">
+      <c r="I369" s="16" t="n"/>
+    </row>
+    <row r="370" ht="18" customHeight="1">
+      <c r="I370" s="16" t="n"/>
+    </row>
+    <row r="371" ht="18" customHeight="1">
+      <c r="I371" s="16" t="n"/>
+    </row>
+    <row r="372" ht="18" customHeight="1">
+      <c r="I372" s="16" t="n"/>
+    </row>
+    <row r="373" ht="18" customHeight="1">
+      <c r="I373" s="16" t="n"/>
+    </row>
+    <row r="374" ht="18" customHeight="1">
+      <c r="I374" s="16" t="n"/>
+    </row>
+    <row r="375" ht="18" customHeight="1">
+      <c r="I375" s="16" t="n"/>
+    </row>
+    <row r="376" ht="18" customHeight="1">
+      <c r="I376" s="16" t="n"/>
+    </row>
+    <row r="377" ht="18" customHeight="1">
+      <c r="I377" s="16" t="n"/>
+    </row>
+    <row r="378" ht="18" customHeight="1">
+      <c r="I378" s="16" t="n"/>
+    </row>
+    <row r="379" ht="18" customHeight="1">
+      <c r="I379" s="16" t="n"/>
+    </row>
+    <row r="380" ht="18" customHeight="1">
+      <c r="I380" s="16" t="n"/>
+    </row>
+    <row r="381" ht="18" customHeight="1">
+      <c r="I381" s="16" t="n"/>
+    </row>
+    <row r="382" ht="18" customHeight="1">
+      <c r="I382" s="16" t="n"/>
+    </row>
+    <row r="383" ht="18" customHeight="1">
+      <c r="I383" s="16" t="n"/>
+    </row>
+    <row r="384" ht="18" customHeight="1">
+      <c r="I384" s="16" t="n"/>
+    </row>
+    <row r="385" ht="18" customHeight="1">
+      <c r="I385" s="16" t="n"/>
+    </row>
+    <row r="386" ht="18" customHeight="1">
+      <c r="I386" s="16" t="n"/>
+    </row>
+    <row r="387" ht="18" customHeight="1">
+      <c r="I387" s="16" t="n"/>
+    </row>
+    <row r="388" ht="18" customHeight="1">
+      <c r="I388" s="16" t="n"/>
+    </row>
+    <row r="389" ht="18" customHeight="1">
+      <c r="I389" s="16" t="n"/>
+    </row>
+    <row r="390" ht="18" customHeight="1">
+      <c r="I390" s="16" t="n"/>
+    </row>
+    <row r="391" ht="18" customHeight="1">
+      <c r="I391" s="16" t="n"/>
+    </row>
+    <row r="392" ht="18" customHeight="1">
+      <c r="I392" s="16" t="n"/>
+    </row>
+    <row r="393" ht="18" customHeight="1">
+      <c r="I393" s="16" t="n"/>
+    </row>
+    <row r="394" ht="18" customHeight="1">
+      <c r="I394" s="16" t="n"/>
+    </row>
+    <row r="395" ht="18" customHeight="1">
+      <c r="I395" s="16" t="n"/>
+    </row>
+    <row r="396" ht="18" customHeight="1">
+      <c r="I396" s="16" t="n"/>
+    </row>
+    <row r="397" ht="18" customHeight="1">
+      <c r="I397" s="16" t="n"/>
+    </row>
+    <row r="398" ht="18" customHeight="1">
+      <c r="I398" s="16" t="n"/>
+    </row>
+    <row r="399" ht="18" customHeight="1">
+      <c r="I399" s="16" t="n"/>
+    </row>
+    <row r="400" ht="18" customHeight="1">
+      <c r="I400" s="16" t="n"/>
+    </row>
+    <row r="401" ht="18" customHeight="1">
+      <c r="I401" s="16" t="n"/>
+    </row>
+    <row r="402" ht="18" customHeight="1">
+      <c r="I402" s="16" t="n"/>
+    </row>
+    <row r="403" ht="18" customHeight="1">
+      <c r="I403" s="16" t="n"/>
+    </row>
+    <row r="404" ht="18" customHeight="1">
+      <c r="I404" s="16" t="n"/>
+    </row>
+    <row r="405" ht="18" customHeight="1">
+      <c r="I405" s="16" t="n"/>
+    </row>
+    <row r="406" ht="18" customHeight="1">
+      <c r="I406" s="16" t="n"/>
+    </row>
+    <row r="407" ht="18" customHeight="1">
+      <c r="I407" s="16" t="n"/>
+    </row>
+    <row r="408" ht="18" customHeight="1">
+      <c r="I408" s="16" t="n"/>
+    </row>
+    <row r="409" ht="18" customHeight="1">
+      <c r="I409" s="16" t="n"/>
+    </row>
+    <row r="410" ht="18" customHeight="1">
+      <c r="I410" s="16" t="n"/>
+    </row>
+    <row r="411" ht="18" customHeight="1">
+      <c r="I411" s="16" t="n"/>
+    </row>
+    <row r="412" ht="18" customHeight="1">
+      <c r="I412" s="16" t="n"/>
+    </row>
+    <row r="413" ht="18" customHeight="1">
+      <c r="I413" s="16" t="n"/>
+    </row>
+    <row r="414" ht="18" customHeight="1">
+      <c r="I414" s="16" t="n"/>
+    </row>
+    <row r="415" ht="18" customHeight="1">
+      <c r="I415" s="16" t="n"/>
+    </row>
+    <row r="416" ht="18" customHeight="1">
+      <c r="I416" s="16" t="n"/>
+    </row>
+    <row r="417" ht="18" customHeight="1">
+      <c r="I417" s="16" t="n"/>
+    </row>
+    <row r="418" ht="18" customHeight="1">
+      <c r="I418" s="16" t="n"/>
+    </row>
+    <row r="419" ht="18" customHeight="1">
+      <c r="I419" s="16" t="n"/>
+    </row>
+    <row r="420" ht="18" customHeight="1">
+      <c r="I420" s="16" t="n"/>
+    </row>
+    <row r="421" ht="18" customHeight="1">
+      <c r="I421" s="16" t="n"/>
+    </row>
+    <row r="422" ht="18" customHeight="1">
+      <c r="I422" s="16" t="n"/>
+    </row>
+    <row r="423" ht="18" customHeight="1">
+      <c r="I423" s="16" t="n"/>
+    </row>
+    <row r="424" ht="18" customHeight="1">
+      <c r="I424" s="16" t="n"/>
+    </row>
+    <row r="425" ht="18" customHeight="1">
+      <c r="I425" s="16" t="n"/>
+    </row>
+    <row r="426" ht="18" customHeight="1">
+      <c r="I426" s="16" t="n"/>
+    </row>
+    <row r="427" ht="18" customHeight="1">
+      <c r="I427" s="16" t="n"/>
+    </row>
+    <row r="428" ht="18" customHeight="1">
+      <c r="I428" s="16" t="n"/>
+    </row>
+    <row r="429" ht="18" customHeight="1">
+      <c r="I429" s="16" t="n"/>
+    </row>
+    <row r="430" ht="18" customHeight="1">
+      <c r="I430" s="16" t="n"/>
+    </row>
+    <row r="431" ht="18" customHeight="1">
+      <c r="I431" s="16" t="n"/>
+    </row>
+    <row r="432" ht="18" customHeight="1">
+      <c r="I432" s="16" t="n"/>
+    </row>
+    <row r="433" ht="18" customHeight="1">
+      <c r="I433" s="16" t="n"/>
+    </row>
+    <row r="434" ht="18" customHeight="1">
+      <c r="I434" s="16" t="n"/>
+    </row>
+    <row r="435" ht="18" customHeight="1">
+      <c r="I435" s="16" t="n"/>
+    </row>
+    <row r="436" ht="18" customHeight="1">
+      <c r="I436" s="16" t="n"/>
+    </row>
+    <row r="437" ht="18" customHeight="1">
+      <c r="I437" s="16" t="n"/>
+    </row>
+    <row r="438" ht="18" customHeight="1">
+      <c r="I438" s="16" t="n"/>
+    </row>
+    <row r="439" ht="18" customHeight="1">
+      <c r="I439" s="16" t="n"/>
+    </row>
+    <row r="440" ht="18" customHeight="1">
+      <c r="I440" s="16" t="n"/>
+    </row>
+    <row r="441" ht="18" customHeight="1">
+      <c r="I441" s="16" t="n"/>
+    </row>
+    <row r="442" ht="18" customHeight="1">
+      <c r="I442" s="16" t="n"/>
+    </row>
+    <row r="443" ht="18" customHeight="1">
+      <c r="I443" s="16" t="n"/>
+    </row>
+    <row r="444" ht="18" customHeight="1">
+      <c r="I444" s="16" t="n"/>
+    </row>
+    <row r="445" ht="18" customHeight="1">
+      <c r="I445" s="16" t="n"/>
+    </row>
+    <row r="446" ht="18" customHeight="1">
+      <c r="I446" s="16" t="n"/>
+    </row>
+    <row r="447" ht="18" customHeight="1">
+      <c r="I447" s="16" t="n"/>
+    </row>
+    <row r="448" ht="18" customHeight="1">
+      <c r="I448" s="16" t="n"/>
+    </row>
+    <row r="449" ht="18" customHeight="1">
+      <c r="I449" s="16" t="n"/>
+    </row>
+    <row r="450" ht="18" customHeight="1">
+      <c r="I450" s="16" t="n"/>
+    </row>
+    <row r="451" ht="18" customHeight="1">
+      <c r="I451" s="16" t="n"/>
+    </row>
+    <row r="452" ht="18" customHeight="1">
+      <c r="I452" s="16" t="n"/>
+    </row>
+    <row r="453" ht="18" customHeight="1">
+      <c r="I453" s="16" t="n"/>
+    </row>
+    <row r="454" ht="18" customHeight="1">
+      <c r="I454" s="16" t="n"/>
+    </row>
+    <row r="455" ht="18" customHeight="1">
+      <c r="I455" s="16" t="n"/>
+    </row>
+    <row r="456" ht="18" customHeight="1">
+      <c r="I456" s="16" t="n"/>
+    </row>
+    <row r="457" ht="18" customHeight="1">
+      <c r="I457" s="16" t="n"/>
+    </row>
+    <row r="458" ht="18" customHeight="1">
+      <c r="I458" s="16" t="n"/>
+    </row>
+    <row r="459" ht="18" customHeight="1">
+      <c r="I459" s="16" t="n"/>
+    </row>
+    <row r="460" ht="18" customHeight="1">
+      <c r="I460" s="16" t="n"/>
+    </row>
+    <row r="461" ht="18" customHeight="1">
+      <c r="I461" s="16" t="n"/>
+    </row>
+    <row r="462" ht="18" customHeight="1">
+      <c r="I462" s="16" t="n"/>
+    </row>
+    <row r="463" ht="18" customHeight="1">
+      <c r="I463" s="16" t="n"/>
+    </row>
+    <row r="464" ht="18" customHeight="1">
+      <c r="I464" s="16" t="n"/>
+    </row>
+    <row r="465" ht="18" customHeight="1">
+      <c r="I465" s="16" t="n"/>
+    </row>
+    <row r="466" ht="18" customHeight="1">
+      <c r="I466" s="16" t="n"/>
+    </row>
+    <row r="467" ht="18" customHeight="1">
+      <c r="I467" s="16" t="n"/>
+    </row>
+    <row r="468" ht="18" customHeight="1">
+      <c r="I468" s="16" t="n"/>
+    </row>
+    <row r="469" ht="18" customHeight="1">
+      <c r="I469" s="16" t="n"/>
+    </row>
+    <row r="470" ht="18" customHeight="1">
+      <c r="I470" s="16" t="n"/>
+    </row>
+    <row r="471" ht="18" customHeight="1">
+      <c r="I471" s="16" t="n"/>
+    </row>
+    <row r="472" ht="18" customHeight="1">
+      <c r="I472" s="16" t="n"/>
+    </row>
+    <row r="473" ht="18" customHeight="1">
+      <c r="I473" s="16" t="n"/>
+    </row>
+    <row r="474" ht="18" customHeight="1">
+      <c r="I474" s="16" t="n"/>
+    </row>
+    <row r="475" ht="18" customHeight="1">
+      <c r="I475" s="16" t="n"/>
+    </row>
+    <row r="476" ht="18" customHeight="1">
+      <c r="I476" s="16" t="n"/>
+    </row>
+    <row r="477" ht="18" customHeight="1">
+      <c r="I477" s="16" t="n"/>
+    </row>
+    <row r="478" ht="18" customHeight="1">
+      <c r="I478" s="16" t="n"/>
+    </row>
+    <row r="479" ht="18" customHeight="1">
+      <c r="I479" s="16" t="n"/>
+    </row>
+    <row r="480" ht="18" customHeight="1">
+      <c r="I480" s="16" t="n"/>
+    </row>
+    <row r="481" ht="18" customHeight="1">
+      <c r="I481" s="16" t="n"/>
+    </row>
+    <row r="482" ht="18" customHeight="1">
+      <c r="I482" s="16" t="n"/>
+    </row>
+    <row r="483" ht="18" customHeight="1">
+      <c r="I483" s="16" t="n"/>
+    </row>
+    <row r="484" ht="18" customHeight="1">
+      <c r="I484" s="16" t="n"/>
+    </row>
+    <row r="485" ht="18" customHeight="1">
+      <c r="I485" s="16" t="n"/>
+    </row>
+    <row r="486" ht="18" customHeight="1">
+      <c r="I486" s="16" t="n"/>
+    </row>
+    <row r="487" ht="18" customHeight="1">
+      <c r="I487" s="16" t="n"/>
+    </row>
+    <row r="488" ht="18" customHeight="1">
+      <c r="I488" s="16" t="n"/>
+    </row>
+    <row r="489" ht="18" customHeight="1">
+      <c r="I489" s="16" t="n"/>
+    </row>
+    <row r="490" ht="18" customHeight="1">
+      <c r="I490" s="16" t="n"/>
+    </row>
+    <row r="491" ht="18" customHeight="1">
+      <c r="I491" s="16" t="n"/>
+    </row>
+    <row r="492" ht="18" customHeight="1">
+      <c r="I492" s="16" t="n"/>
+    </row>
+    <row r="493" ht="18" customHeight="1">
+      <c r="I493" s="16" t="n"/>
+    </row>
+    <row r="494" ht="18" customHeight="1">
+      <c r="I494" s="16" t="n"/>
+    </row>
+    <row r="495" ht="18" customHeight="1">
+      <c r="I495" s="16" t="n"/>
+    </row>
+    <row r="496" ht="18" customHeight="1">
+      <c r="I496" s="16" t="n"/>
+    </row>
+    <row r="497" ht="18" customHeight="1">
+      <c r="I497" s="16" t="n"/>
+    </row>
+    <row r="498" ht="18" customHeight="1">
+      <c r="I498" s="16" t="n"/>
+    </row>
+    <row r="499" ht="18" customHeight="1">
+      <c r="I499" s="16" t="n"/>
+    </row>
+    <row r="500" ht="18" customHeight="1">
+      <c r="I500" s="16" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -972,7 +3957,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1126,6 +4111,1497 @@
       <c r="I3" s="11" t="inlineStr"/>
       <c r="J3" s="11" t="inlineStr"/>
     </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="I4" s="16" t="n"/>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="I5" s="16" t="n"/>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="I6" s="16" t="n"/>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="I7" s="16" t="n"/>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="I8" s="16" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="I9" s="16" t="n"/>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="I10" s="16" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="I11" s="16" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="I12" s="16" t="n"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="I13" s="16" t="n"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="I14" s="16" t="n"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="I15" s="16" t="n"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="I16" s="16" t="n"/>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="I17" s="16" t="n"/>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="I18" s="16" t="n"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="I19" s="16" t="n"/>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="I20" s="16" t="n"/>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="I21" s="16" t="n"/>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="I22" s="16" t="n"/>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="I23" s="16" t="n"/>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="I24" s="16" t="n"/>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="I25" s="16" t="n"/>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="I26" s="16" t="n"/>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="I27" s="16" t="n"/>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="I28" s="16" t="n"/>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="I29" s="16" t="n"/>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="I30" s="16" t="n"/>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="I31" s="16" t="n"/>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="I32" s="16" t="n"/>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="I33" s="16" t="n"/>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="I34" s="16" t="n"/>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="I35" s="16" t="n"/>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="I36" s="16" t="n"/>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="I37" s="16" t="n"/>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="I38" s="16" t="n"/>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="I39" s="16" t="n"/>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="I40" s="16" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="I41" s="16" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="I42" s="16" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="I43" s="16" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="I44" s="16" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="I45" s="16" t="n"/>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="I46" s="16" t="n"/>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="I47" s="16" t="n"/>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="I48" s="16" t="n"/>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="I49" s="16" t="n"/>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="I50" s="16" t="n"/>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="I51" s="16" t="n"/>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="I52" s="16" t="n"/>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="I53" s="16" t="n"/>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="I54" s="16" t="n"/>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="I55" s="16" t="n"/>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="I56" s="16" t="n"/>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="I57" s="16" t="n"/>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="I58" s="16" t="n"/>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="I59" s="16" t="n"/>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="I60" s="16" t="n"/>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="I61" s="16" t="n"/>
+    </row>
+    <row r="62" ht="18" customHeight="1">
+      <c r="I62" s="16" t="n"/>
+    </row>
+    <row r="63" ht="18" customHeight="1">
+      <c r="I63" s="16" t="n"/>
+    </row>
+    <row r="64" ht="18" customHeight="1">
+      <c r="I64" s="16" t="n"/>
+    </row>
+    <row r="65" ht="18" customHeight="1">
+      <c r="I65" s="16" t="n"/>
+    </row>
+    <row r="66" ht="18" customHeight="1">
+      <c r="I66" s="16" t="n"/>
+    </row>
+    <row r="67" ht="18" customHeight="1">
+      <c r="I67" s="16" t="n"/>
+    </row>
+    <row r="68" ht="18" customHeight="1">
+      <c r="I68" s="16" t="n"/>
+    </row>
+    <row r="69" ht="18" customHeight="1">
+      <c r="I69" s="16" t="n"/>
+    </row>
+    <row r="70" ht="18" customHeight="1">
+      <c r="I70" s="16" t="n"/>
+    </row>
+    <row r="71" ht="18" customHeight="1">
+      <c r="I71" s="16" t="n"/>
+    </row>
+    <row r="72" ht="18" customHeight="1">
+      <c r="I72" s="16" t="n"/>
+    </row>
+    <row r="73" ht="18" customHeight="1">
+      <c r="I73" s="16" t="n"/>
+    </row>
+    <row r="74" ht="18" customHeight="1">
+      <c r="I74" s="16" t="n"/>
+    </row>
+    <row r="75" ht="18" customHeight="1">
+      <c r="I75" s="16" t="n"/>
+    </row>
+    <row r="76" ht="18" customHeight="1">
+      <c r="I76" s="16" t="n"/>
+    </row>
+    <row r="77" ht="18" customHeight="1">
+      <c r="I77" s="16" t="n"/>
+    </row>
+    <row r="78" ht="18" customHeight="1">
+      <c r="I78" s="16" t="n"/>
+    </row>
+    <row r="79" ht="18" customHeight="1">
+      <c r="I79" s="16" t="n"/>
+    </row>
+    <row r="80" ht="18" customHeight="1">
+      <c r="I80" s="16" t="n"/>
+    </row>
+    <row r="81" ht="18" customHeight="1">
+      <c r="I81" s="16" t="n"/>
+    </row>
+    <row r="82" ht="18" customHeight="1">
+      <c r="I82" s="16" t="n"/>
+    </row>
+    <row r="83" ht="18" customHeight="1">
+      <c r="I83" s="16" t="n"/>
+    </row>
+    <row r="84" ht="18" customHeight="1">
+      <c r="I84" s="16" t="n"/>
+    </row>
+    <row r="85" ht="18" customHeight="1">
+      <c r="I85" s="16" t="n"/>
+    </row>
+    <row r="86" ht="18" customHeight="1">
+      <c r="I86" s="16" t="n"/>
+    </row>
+    <row r="87" ht="18" customHeight="1">
+      <c r="I87" s="16" t="n"/>
+    </row>
+    <row r="88" ht="18" customHeight="1">
+      <c r="I88" s="16" t="n"/>
+    </row>
+    <row r="89" ht="18" customHeight="1">
+      <c r="I89" s="16" t="n"/>
+    </row>
+    <row r="90" ht="18" customHeight="1">
+      <c r="I90" s="16" t="n"/>
+    </row>
+    <row r="91" ht="18" customHeight="1">
+      <c r="I91" s="16" t="n"/>
+    </row>
+    <row r="92" ht="18" customHeight="1">
+      <c r="I92" s="16" t="n"/>
+    </row>
+    <row r="93" ht="18" customHeight="1">
+      <c r="I93" s="16" t="n"/>
+    </row>
+    <row r="94" ht="18" customHeight="1">
+      <c r="I94" s="16" t="n"/>
+    </row>
+    <row r="95" ht="18" customHeight="1">
+      <c r="I95" s="16" t="n"/>
+    </row>
+    <row r="96" ht="18" customHeight="1">
+      <c r="I96" s="16" t="n"/>
+    </row>
+    <row r="97" ht="18" customHeight="1">
+      <c r="I97" s="16" t="n"/>
+    </row>
+    <row r="98" ht="18" customHeight="1">
+      <c r="I98" s="16" t="n"/>
+    </row>
+    <row r="99" ht="18" customHeight="1">
+      <c r="I99" s="16" t="n"/>
+    </row>
+    <row r="100" ht="18" customHeight="1">
+      <c r="I100" s="16" t="n"/>
+    </row>
+    <row r="101" ht="18" customHeight="1">
+      <c r="I101" s="16" t="n"/>
+    </row>
+    <row r="102" ht="18" customHeight="1">
+      <c r="I102" s="16" t="n"/>
+    </row>
+    <row r="103" ht="18" customHeight="1">
+      <c r="I103" s="16" t="n"/>
+    </row>
+    <row r="104" ht="18" customHeight="1">
+      <c r="I104" s="16" t="n"/>
+    </row>
+    <row r="105" ht="18" customHeight="1">
+      <c r="I105" s="16" t="n"/>
+    </row>
+    <row r="106" ht="18" customHeight="1">
+      <c r="I106" s="16" t="n"/>
+    </row>
+    <row r="107" ht="18" customHeight="1">
+      <c r="I107" s="16" t="n"/>
+    </row>
+    <row r="108" ht="18" customHeight="1">
+      <c r="I108" s="16" t="n"/>
+    </row>
+    <row r="109" ht="18" customHeight="1">
+      <c r="I109" s="16" t="n"/>
+    </row>
+    <row r="110" ht="18" customHeight="1">
+      <c r="I110" s="16" t="n"/>
+    </row>
+    <row r="111" ht="18" customHeight="1">
+      <c r="I111" s="16" t="n"/>
+    </row>
+    <row r="112" ht="18" customHeight="1">
+      <c r="I112" s="16" t="n"/>
+    </row>
+    <row r="113" ht="18" customHeight="1">
+      <c r="I113" s="16" t="n"/>
+    </row>
+    <row r="114" ht="18" customHeight="1">
+      <c r="I114" s="16" t="n"/>
+    </row>
+    <row r="115" ht="18" customHeight="1">
+      <c r="I115" s="16" t="n"/>
+    </row>
+    <row r="116" ht="18" customHeight="1">
+      <c r="I116" s="16" t="n"/>
+    </row>
+    <row r="117" ht="18" customHeight="1">
+      <c r="I117" s="16" t="n"/>
+    </row>
+    <row r="118" ht="18" customHeight="1">
+      <c r="I118" s="16" t="n"/>
+    </row>
+    <row r="119" ht="18" customHeight="1">
+      <c r="I119" s="16" t="n"/>
+    </row>
+    <row r="120" ht="18" customHeight="1">
+      <c r="I120" s="16" t="n"/>
+    </row>
+    <row r="121" ht="18" customHeight="1">
+      <c r="I121" s="16" t="n"/>
+    </row>
+    <row r="122" ht="18" customHeight="1">
+      <c r="I122" s="16" t="n"/>
+    </row>
+    <row r="123" ht="18" customHeight="1">
+      <c r="I123" s="16" t="n"/>
+    </row>
+    <row r="124" ht="18" customHeight="1">
+      <c r="I124" s="16" t="n"/>
+    </row>
+    <row r="125" ht="18" customHeight="1">
+      <c r="I125" s="16" t="n"/>
+    </row>
+    <row r="126" ht="18" customHeight="1">
+      <c r="I126" s="16" t="n"/>
+    </row>
+    <row r="127" ht="18" customHeight="1">
+      <c r="I127" s="16" t="n"/>
+    </row>
+    <row r="128" ht="18" customHeight="1">
+      <c r="I128" s="16" t="n"/>
+    </row>
+    <row r="129" ht="18" customHeight="1">
+      <c r="I129" s="16" t="n"/>
+    </row>
+    <row r="130" ht="18" customHeight="1">
+      <c r="I130" s="16" t="n"/>
+    </row>
+    <row r="131" ht="18" customHeight="1">
+      <c r="I131" s="16" t="n"/>
+    </row>
+    <row r="132" ht="18" customHeight="1">
+      <c r="I132" s="16" t="n"/>
+    </row>
+    <row r="133" ht="18" customHeight="1">
+      <c r="I133" s="16" t="n"/>
+    </row>
+    <row r="134" ht="18" customHeight="1">
+      <c r="I134" s="16" t="n"/>
+    </row>
+    <row r="135" ht="18" customHeight="1">
+      <c r="I135" s="16" t="n"/>
+    </row>
+    <row r="136" ht="18" customHeight="1">
+      <c r="I136" s="16" t="n"/>
+    </row>
+    <row r="137" ht="18" customHeight="1">
+      <c r="I137" s="16" t="n"/>
+    </row>
+    <row r="138" ht="18" customHeight="1">
+      <c r="I138" s="16" t="n"/>
+    </row>
+    <row r="139" ht="18" customHeight="1">
+      <c r="I139" s="16" t="n"/>
+    </row>
+    <row r="140" ht="18" customHeight="1">
+      <c r="I140" s="16" t="n"/>
+    </row>
+    <row r="141" ht="18" customHeight="1">
+      <c r="I141" s="16" t="n"/>
+    </row>
+    <row r="142" ht="18" customHeight="1">
+      <c r="I142" s="16" t="n"/>
+    </row>
+    <row r="143" ht="18" customHeight="1">
+      <c r="I143" s="16" t="n"/>
+    </row>
+    <row r="144" ht="18" customHeight="1">
+      <c r="I144" s="16" t="n"/>
+    </row>
+    <row r="145" ht="18" customHeight="1">
+      <c r="I145" s="16" t="n"/>
+    </row>
+    <row r="146" ht="18" customHeight="1">
+      <c r="I146" s="16" t="n"/>
+    </row>
+    <row r="147" ht="18" customHeight="1">
+      <c r="I147" s="16" t="n"/>
+    </row>
+    <row r="148" ht="18" customHeight="1">
+      <c r="I148" s="16" t="n"/>
+    </row>
+    <row r="149" ht="18" customHeight="1">
+      <c r="I149" s="16" t="n"/>
+    </row>
+    <row r="150" ht="18" customHeight="1">
+      <c r="I150" s="16" t="n"/>
+    </row>
+    <row r="151" ht="18" customHeight="1">
+      <c r="I151" s="16" t="n"/>
+    </row>
+    <row r="152" ht="18" customHeight="1">
+      <c r="I152" s="16" t="n"/>
+    </row>
+    <row r="153" ht="18" customHeight="1">
+      <c r="I153" s="16" t="n"/>
+    </row>
+    <row r="154" ht="18" customHeight="1">
+      <c r="I154" s="16" t="n"/>
+    </row>
+    <row r="155" ht="18" customHeight="1">
+      <c r="I155" s="16" t="n"/>
+    </row>
+    <row r="156" ht="18" customHeight="1">
+      <c r="I156" s="16" t="n"/>
+    </row>
+    <row r="157" ht="18" customHeight="1">
+      <c r="I157" s="16" t="n"/>
+    </row>
+    <row r="158" ht="18" customHeight="1">
+      <c r="I158" s="16" t="n"/>
+    </row>
+    <row r="159" ht="18" customHeight="1">
+      <c r="I159" s="16" t="n"/>
+    </row>
+    <row r="160" ht="18" customHeight="1">
+      <c r="I160" s="16" t="n"/>
+    </row>
+    <row r="161" ht="18" customHeight="1">
+      <c r="I161" s="16" t="n"/>
+    </row>
+    <row r="162" ht="18" customHeight="1">
+      <c r="I162" s="16" t="n"/>
+    </row>
+    <row r="163" ht="18" customHeight="1">
+      <c r="I163" s="16" t="n"/>
+    </row>
+    <row r="164" ht="18" customHeight="1">
+      <c r="I164" s="16" t="n"/>
+    </row>
+    <row r="165" ht="18" customHeight="1">
+      <c r="I165" s="16" t="n"/>
+    </row>
+    <row r="166" ht="18" customHeight="1">
+      <c r="I166" s="16" t="n"/>
+    </row>
+    <row r="167" ht="18" customHeight="1">
+      <c r="I167" s="16" t="n"/>
+    </row>
+    <row r="168" ht="18" customHeight="1">
+      <c r="I168" s="16" t="n"/>
+    </row>
+    <row r="169" ht="18" customHeight="1">
+      <c r="I169" s="16" t="n"/>
+    </row>
+    <row r="170" ht="18" customHeight="1">
+      <c r="I170" s="16" t="n"/>
+    </row>
+    <row r="171" ht="18" customHeight="1">
+      <c r="I171" s="16" t="n"/>
+    </row>
+    <row r="172" ht="18" customHeight="1">
+      <c r="I172" s="16" t="n"/>
+    </row>
+    <row r="173" ht="18" customHeight="1">
+      <c r="I173" s="16" t="n"/>
+    </row>
+    <row r="174" ht="18" customHeight="1">
+      <c r="I174" s="16" t="n"/>
+    </row>
+    <row r="175" ht="18" customHeight="1">
+      <c r="I175" s="16" t="n"/>
+    </row>
+    <row r="176" ht="18" customHeight="1">
+      <c r="I176" s="16" t="n"/>
+    </row>
+    <row r="177" ht="18" customHeight="1">
+      <c r="I177" s="16" t="n"/>
+    </row>
+    <row r="178" ht="18" customHeight="1">
+      <c r="I178" s="16" t="n"/>
+    </row>
+    <row r="179" ht="18" customHeight="1">
+      <c r="I179" s="16" t="n"/>
+    </row>
+    <row r="180" ht="18" customHeight="1">
+      <c r="I180" s="16" t="n"/>
+    </row>
+    <row r="181" ht="18" customHeight="1">
+      <c r="I181" s="16" t="n"/>
+    </row>
+    <row r="182" ht="18" customHeight="1">
+      <c r="I182" s="16" t="n"/>
+    </row>
+    <row r="183" ht="18" customHeight="1">
+      <c r="I183" s="16" t="n"/>
+    </row>
+    <row r="184" ht="18" customHeight="1">
+      <c r="I184" s="16" t="n"/>
+    </row>
+    <row r="185" ht="18" customHeight="1">
+      <c r="I185" s="16" t="n"/>
+    </row>
+    <row r="186" ht="18" customHeight="1">
+      <c r="I186" s="16" t="n"/>
+    </row>
+    <row r="187" ht="18" customHeight="1">
+      <c r="I187" s="16" t="n"/>
+    </row>
+    <row r="188" ht="18" customHeight="1">
+      <c r="I188" s="16" t="n"/>
+    </row>
+    <row r="189" ht="18" customHeight="1">
+      <c r="I189" s="16" t="n"/>
+    </row>
+    <row r="190" ht="18" customHeight="1">
+      <c r="I190" s="16" t="n"/>
+    </row>
+    <row r="191" ht="18" customHeight="1">
+      <c r="I191" s="16" t="n"/>
+    </row>
+    <row r="192" ht="18" customHeight="1">
+      <c r="I192" s="16" t="n"/>
+    </row>
+    <row r="193" ht="18" customHeight="1">
+      <c r="I193" s="16" t="n"/>
+    </row>
+    <row r="194" ht="18" customHeight="1">
+      <c r="I194" s="16" t="n"/>
+    </row>
+    <row r="195" ht="18" customHeight="1">
+      <c r="I195" s="16" t="n"/>
+    </row>
+    <row r="196" ht="18" customHeight="1">
+      <c r="I196" s="16" t="n"/>
+    </row>
+    <row r="197" ht="18" customHeight="1">
+      <c r="I197" s="16" t="n"/>
+    </row>
+    <row r="198" ht="18" customHeight="1">
+      <c r="I198" s="16" t="n"/>
+    </row>
+    <row r="199" ht="18" customHeight="1">
+      <c r="I199" s="16" t="n"/>
+    </row>
+    <row r="200" ht="18" customHeight="1">
+      <c r="I200" s="16" t="n"/>
+    </row>
+    <row r="201" ht="18" customHeight="1">
+      <c r="I201" s="16" t="n"/>
+    </row>
+    <row r="202" ht="18" customHeight="1">
+      <c r="I202" s="16" t="n"/>
+    </row>
+    <row r="203" ht="18" customHeight="1">
+      <c r="I203" s="16" t="n"/>
+    </row>
+    <row r="204" ht="18" customHeight="1">
+      <c r="I204" s="16" t="n"/>
+    </row>
+    <row r="205" ht="18" customHeight="1">
+      <c r="I205" s="16" t="n"/>
+    </row>
+    <row r="206" ht="18" customHeight="1">
+      <c r="I206" s="16" t="n"/>
+    </row>
+    <row r="207" ht="18" customHeight="1">
+      <c r="I207" s="16" t="n"/>
+    </row>
+    <row r="208" ht="18" customHeight="1">
+      <c r="I208" s="16" t="n"/>
+    </row>
+    <row r="209" ht="18" customHeight="1">
+      <c r="I209" s="16" t="n"/>
+    </row>
+    <row r="210" ht="18" customHeight="1">
+      <c r="I210" s="16" t="n"/>
+    </row>
+    <row r="211" ht="18" customHeight="1">
+      <c r="I211" s="16" t="n"/>
+    </row>
+    <row r="212" ht="18" customHeight="1">
+      <c r="I212" s="16" t="n"/>
+    </row>
+    <row r="213" ht="18" customHeight="1">
+      <c r="I213" s="16" t="n"/>
+    </row>
+    <row r="214" ht="18" customHeight="1">
+      <c r="I214" s="16" t="n"/>
+    </row>
+    <row r="215" ht="18" customHeight="1">
+      <c r="I215" s="16" t="n"/>
+    </row>
+    <row r="216" ht="18" customHeight="1">
+      <c r="I216" s="16" t="n"/>
+    </row>
+    <row r="217" ht="18" customHeight="1">
+      <c r="I217" s="16" t="n"/>
+    </row>
+    <row r="218" ht="18" customHeight="1">
+      <c r="I218" s="16" t="n"/>
+    </row>
+    <row r="219" ht="18" customHeight="1">
+      <c r="I219" s="16" t="n"/>
+    </row>
+    <row r="220" ht="18" customHeight="1">
+      <c r="I220" s="16" t="n"/>
+    </row>
+    <row r="221" ht="18" customHeight="1">
+      <c r="I221" s="16" t="n"/>
+    </row>
+    <row r="222" ht="18" customHeight="1">
+      <c r="I222" s="16" t="n"/>
+    </row>
+    <row r="223" ht="18" customHeight="1">
+      <c r="I223" s="16" t="n"/>
+    </row>
+    <row r="224" ht="18" customHeight="1">
+      <c r="I224" s="16" t="n"/>
+    </row>
+    <row r="225" ht="18" customHeight="1">
+      <c r="I225" s="16" t="n"/>
+    </row>
+    <row r="226" ht="18" customHeight="1">
+      <c r="I226" s="16" t="n"/>
+    </row>
+    <row r="227" ht="18" customHeight="1">
+      <c r="I227" s="16" t="n"/>
+    </row>
+    <row r="228" ht="18" customHeight="1">
+      <c r="I228" s="16" t="n"/>
+    </row>
+    <row r="229" ht="18" customHeight="1">
+      <c r="I229" s="16" t="n"/>
+    </row>
+    <row r="230" ht="18" customHeight="1">
+      <c r="I230" s="16" t="n"/>
+    </row>
+    <row r="231" ht="18" customHeight="1">
+      <c r="I231" s="16" t="n"/>
+    </row>
+    <row r="232" ht="18" customHeight="1">
+      <c r="I232" s="16" t="n"/>
+    </row>
+    <row r="233" ht="18" customHeight="1">
+      <c r="I233" s="16" t="n"/>
+    </row>
+    <row r="234" ht="18" customHeight="1">
+      <c r="I234" s="16" t="n"/>
+    </row>
+    <row r="235" ht="18" customHeight="1">
+      <c r="I235" s="16" t="n"/>
+    </row>
+    <row r="236" ht="18" customHeight="1">
+      <c r="I236" s="16" t="n"/>
+    </row>
+    <row r="237" ht="18" customHeight="1">
+      <c r="I237" s="16" t="n"/>
+    </row>
+    <row r="238" ht="18" customHeight="1">
+      <c r="I238" s="16" t="n"/>
+    </row>
+    <row r="239" ht="18" customHeight="1">
+      <c r="I239" s="16" t="n"/>
+    </row>
+    <row r="240" ht="18" customHeight="1">
+      <c r="I240" s="16" t="n"/>
+    </row>
+    <row r="241" ht="18" customHeight="1">
+      <c r="I241" s="16" t="n"/>
+    </row>
+    <row r="242" ht="18" customHeight="1">
+      <c r="I242" s="16" t="n"/>
+    </row>
+    <row r="243" ht="18" customHeight="1">
+      <c r="I243" s="16" t="n"/>
+    </row>
+    <row r="244" ht="18" customHeight="1">
+      <c r="I244" s="16" t="n"/>
+    </row>
+    <row r="245" ht="18" customHeight="1">
+      <c r="I245" s="16" t="n"/>
+    </row>
+    <row r="246" ht="18" customHeight="1">
+      <c r="I246" s="16" t="n"/>
+    </row>
+    <row r="247" ht="18" customHeight="1">
+      <c r="I247" s="16" t="n"/>
+    </row>
+    <row r="248" ht="18" customHeight="1">
+      <c r="I248" s="16" t="n"/>
+    </row>
+    <row r="249" ht="18" customHeight="1">
+      <c r="I249" s="16" t="n"/>
+    </row>
+    <row r="250" ht="18" customHeight="1">
+      <c r="I250" s="16" t="n"/>
+    </row>
+    <row r="251" ht="18" customHeight="1">
+      <c r="I251" s="16" t="n"/>
+    </row>
+    <row r="252" ht="18" customHeight="1">
+      <c r="I252" s="16" t="n"/>
+    </row>
+    <row r="253" ht="18" customHeight="1">
+      <c r="I253" s="16" t="n"/>
+    </row>
+    <row r="254" ht="18" customHeight="1">
+      <c r="I254" s="16" t="n"/>
+    </row>
+    <row r="255" ht="18" customHeight="1">
+      <c r="I255" s="16" t="n"/>
+    </row>
+    <row r="256" ht="18" customHeight="1">
+      <c r="I256" s="16" t="n"/>
+    </row>
+    <row r="257" ht="18" customHeight="1">
+      <c r="I257" s="16" t="n"/>
+    </row>
+    <row r="258" ht="18" customHeight="1">
+      <c r="I258" s="16" t="n"/>
+    </row>
+    <row r="259" ht="18" customHeight="1">
+      <c r="I259" s="16" t="n"/>
+    </row>
+    <row r="260" ht="18" customHeight="1">
+      <c r="I260" s="16" t="n"/>
+    </row>
+    <row r="261" ht="18" customHeight="1">
+      <c r="I261" s="16" t="n"/>
+    </row>
+    <row r="262" ht="18" customHeight="1">
+      <c r="I262" s="16" t="n"/>
+    </row>
+    <row r="263" ht="18" customHeight="1">
+      <c r="I263" s="16" t="n"/>
+    </row>
+    <row r="264" ht="18" customHeight="1">
+      <c r="I264" s="16" t="n"/>
+    </row>
+    <row r="265" ht="18" customHeight="1">
+      <c r="I265" s="16" t="n"/>
+    </row>
+    <row r="266" ht="18" customHeight="1">
+      <c r="I266" s="16" t="n"/>
+    </row>
+    <row r="267" ht="18" customHeight="1">
+      <c r="I267" s="16" t="n"/>
+    </row>
+    <row r="268" ht="18" customHeight="1">
+      <c r="I268" s="16" t="n"/>
+    </row>
+    <row r="269" ht="18" customHeight="1">
+      <c r="I269" s="16" t="n"/>
+    </row>
+    <row r="270" ht="18" customHeight="1">
+      <c r="I270" s="16" t="n"/>
+    </row>
+    <row r="271" ht="18" customHeight="1">
+      <c r="I271" s="16" t="n"/>
+    </row>
+    <row r="272" ht="18" customHeight="1">
+      <c r="I272" s="16" t="n"/>
+    </row>
+    <row r="273" ht="18" customHeight="1">
+      <c r="I273" s="16" t="n"/>
+    </row>
+    <row r="274" ht="18" customHeight="1">
+      <c r="I274" s="16" t="n"/>
+    </row>
+    <row r="275" ht="18" customHeight="1">
+      <c r="I275" s="16" t="n"/>
+    </row>
+    <row r="276" ht="18" customHeight="1">
+      <c r="I276" s="16" t="n"/>
+    </row>
+    <row r="277" ht="18" customHeight="1">
+      <c r="I277" s="16" t="n"/>
+    </row>
+    <row r="278" ht="18" customHeight="1">
+      <c r="I278" s="16" t="n"/>
+    </row>
+    <row r="279" ht="18" customHeight="1">
+      <c r="I279" s="16" t="n"/>
+    </row>
+    <row r="280" ht="18" customHeight="1">
+      <c r="I280" s="16" t="n"/>
+    </row>
+    <row r="281" ht="18" customHeight="1">
+      <c r="I281" s="16" t="n"/>
+    </row>
+    <row r="282" ht="18" customHeight="1">
+      <c r="I282" s="16" t="n"/>
+    </row>
+    <row r="283" ht="18" customHeight="1">
+      <c r="I283" s="16" t="n"/>
+    </row>
+    <row r="284" ht="18" customHeight="1">
+      <c r="I284" s="16" t="n"/>
+    </row>
+    <row r="285" ht="18" customHeight="1">
+      <c r="I285" s="16" t="n"/>
+    </row>
+    <row r="286" ht="18" customHeight="1">
+      <c r="I286" s="16" t="n"/>
+    </row>
+    <row r="287" ht="18" customHeight="1">
+      <c r="I287" s="16" t="n"/>
+    </row>
+    <row r="288" ht="18" customHeight="1">
+      <c r="I288" s="16" t="n"/>
+    </row>
+    <row r="289" ht="18" customHeight="1">
+      <c r="I289" s="16" t="n"/>
+    </row>
+    <row r="290" ht="18" customHeight="1">
+      <c r="I290" s="16" t="n"/>
+    </row>
+    <row r="291" ht="18" customHeight="1">
+      <c r="I291" s="16" t="n"/>
+    </row>
+    <row r="292" ht="18" customHeight="1">
+      <c r="I292" s="16" t="n"/>
+    </row>
+    <row r="293" ht="18" customHeight="1">
+      <c r="I293" s="16" t="n"/>
+    </row>
+    <row r="294" ht="18" customHeight="1">
+      <c r="I294" s="16" t="n"/>
+    </row>
+    <row r="295" ht="18" customHeight="1">
+      <c r="I295" s="16" t="n"/>
+    </row>
+    <row r="296" ht="18" customHeight="1">
+      <c r="I296" s="16" t="n"/>
+    </row>
+    <row r="297" ht="18" customHeight="1">
+      <c r="I297" s="16" t="n"/>
+    </row>
+    <row r="298" ht="18" customHeight="1">
+      <c r="I298" s="16" t="n"/>
+    </row>
+    <row r="299" ht="18" customHeight="1">
+      <c r="I299" s="16" t="n"/>
+    </row>
+    <row r="300" ht="18" customHeight="1">
+      <c r="I300" s="16" t="n"/>
+    </row>
+    <row r="301" ht="18" customHeight="1">
+      <c r="I301" s="16" t="n"/>
+    </row>
+    <row r="302" ht="18" customHeight="1">
+      <c r="I302" s="16" t="n"/>
+    </row>
+    <row r="303" ht="18" customHeight="1">
+      <c r="I303" s="16" t="n"/>
+    </row>
+    <row r="304" ht="18" customHeight="1">
+      <c r="I304" s="16" t="n"/>
+    </row>
+    <row r="305" ht="18" customHeight="1">
+      <c r="I305" s="16" t="n"/>
+    </row>
+    <row r="306" ht="18" customHeight="1">
+      <c r="I306" s="16" t="n"/>
+    </row>
+    <row r="307" ht="18" customHeight="1">
+      <c r="I307" s="16" t="n"/>
+    </row>
+    <row r="308" ht="18" customHeight="1">
+      <c r="I308" s="16" t="n"/>
+    </row>
+    <row r="309" ht="18" customHeight="1">
+      <c r="I309" s="16" t="n"/>
+    </row>
+    <row r="310" ht="18" customHeight="1">
+      <c r="I310" s="16" t="n"/>
+    </row>
+    <row r="311" ht="18" customHeight="1">
+      <c r="I311" s="16" t="n"/>
+    </row>
+    <row r="312" ht="18" customHeight="1">
+      <c r="I312" s="16" t="n"/>
+    </row>
+    <row r="313" ht="18" customHeight="1">
+      <c r="I313" s="16" t="n"/>
+    </row>
+    <row r="314" ht="18" customHeight="1">
+      <c r="I314" s="16" t="n"/>
+    </row>
+    <row r="315" ht="18" customHeight="1">
+      <c r="I315" s="16" t="n"/>
+    </row>
+    <row r="316" ht="18" customHeight="1">
+      <c r="I316" s="16" t="n"/>
+    </row>
+    <row r="317" ht="18" customHeight="1">
+      <c r="I317" s="16" t="n"/>
+    </row>
+    <row r="318" ht="18" customHeight="1">
+      <c r="I318" s="16" t="n"/>
+    </row>
+    <row r="319" ht="18" customHeight="1">
+      <c r="I319" s="16" t="n"/>
+    </row>
+    <row r="320" ht="18" customHeight="1">
+      <c r="I320" s="16" t="n"/>
+    </row>
+    <row r="321" ht="18" customHeight="1">
+      <c r="I321" s="16" t="n"/>
+    </row>
+    <row r="322" ht="18" customHeight="1">
+      <c r="I322" s="16" t="n"/>
+    </row>
+    <row r="323" ht="18" customHeight="1">
+      <c r="I323" s="16" t="n"/>
+    </row>
+    <row r="324" ht="18" customHeight="1">
+      <c r="I324" s="16" t="n"/>
+    </row>
+    <row r="325" ht="18" customHeight="1">
+      <c r="I325" s="16" t="n"/>
+    </row>
+    <row r="326" ht="18" customHeight="1">
+      <c r="I326" s="16" t="n"/>
+    </row>
+    <row r="327" ht="18" customHeight="1">
+      <c r="I327" s="16" t="n"/>
+    </row>
+    <row r="328" ht="18" customHeight="1">
+      <c r="I328" s="16" t="n"/>
+    </row>
+    <row r="329" ht="18" customHeight="1">
+      <c r="I329" s="16" t="n"/>
+    </row>
+    <row r="330" ht="18" customHeight="1">
+      <c r="I330" s="16" t="n"/>
+    </row>
+    <row r="331" ht="18" customHeight="1">
+      <c r="I331" s="16" t="n"/>
+    </row>
+    <row r="332" ht="18" customHeight="1">
+      <c r="I332" s="16" t="n"/>
+    </row>
+    <row r="333" ht="18" customHeight="1">
+      <c r="I333" s="16" t="n"/>
+    </row>
+    <row r="334" ht="18" customHeight="1">
+      <c r="I334" s="16" t="n"/>
+    </row>
+    <row r="335" ht="18" customHeight="1">
+      <c r="I335" s="16" t="n"/>
+    </row>
+    <row r="336" ht="18" customHeight="1">
+      <c r="I336" s="16" t="n"/>
+    </row>
+    <row r="337" ht="18" customHeight="1">
+      <c r="I337" s="16" t="n"/>
+    </row>
+    <row r="338" ht="18" customHeight="1">
+      <c r="I338" s="16" t="n"/>
+    </row>
+    <row r="339" ht="18" customHeight="1">
+      <c r="I339" s="16" t="n"/>
+    </row>
+    <row r="340" ht="18" customHeight="1">
+      <c r="I340" s="16" t="n"/>
+    </row>
+    <row r="341" ht="18" customHeight="1">
+      <c r="I341" s="16" t="n"/>
+    </row>
+    <row r="342" ht="18" customHeight="1">
+      <c r="I342" s="16" t="n"/>
+    </row>
+    <row r="343" ht="18" customHeight="1">
+      <c r="I343" s="16" t="n"/>
+    </row>
+    <row r="344" ht="18" customHeight="1">
+      <c r="I344" s="16" t="n"/>
+    </row>
+    <row r="345" ht="18" customHeight="1">
+      <c r="I345" s="16" t="n"/>
+    </row>
+    <row r="346" ht="18" customHeight="1">
+      <c r="I346" s="16" t="n"/>
+    </row>
+    <row r="347" ht="18" customHeight="1">
+      <c r="I347" s="16" t="n"/>
+    </row>
+    <row r="348" ht="18" customHeight="1">
+      <c r="I348" s="16" t="n"/>
+    </row>
+    <row r="349" ht="18" customHeight="1">
+      <c r="I349" s="16" t="n"/>
+    </row>
+    <row r="350" ht="18" customHeight="1">
+      <c r="I350" s="16" t="n"/>
+    </row>
+    <row r="351" ht="18" customHeight="1">
+      <c r="I351" s="16" t="n"/>
+    </row>
+    <row r="352" ht="18" customHeight="1">
+      <c r="I352" s="16" t="n"/>
+    </row>
+    <row r="353" ht="18" customHeight="1">
+      <c r="I353" s="16" t="n"/>
+    </row>
+    <row r="354" ht="18" customHeight="1">
+      <c r="I354" s="16" t="n"/>
+    </row>
+    <row r="355" ht="18" customHeight="1">
+      <c r="I355" s="16" t="n"/>
+    </row>
+    <row r="356" ht="18" customHeight="1">
+      <c r="I356" s="16" t="n"/>
+    </row>
+    <row r="357" ht="18" customHeight="1">
+      <c r="I357" s="16" t="n"/>
+    </row>
+    <row r="358" ht="18" customHeight="1">
+      <c r="I358" s="16" t="n"/>
+    </row>
+    <row r="359" ht="18" customHeight="1">
+      <c r="I359" s="16" t="n"/>
+    </row>
+    <row r="360" ht="18" customHeight="1">
+      <c r="I360" s="16" t="n"/>
+    </row>
+    <row r="361" ht="18" customHeight="1">
+      <c r="I361" s="16" t="n"/>
+    </row>
+    <row r="362" ht="18" customHeight="1">
+      <c r="I362" s="16" t="n"/>
+    </row>
+    <row r="363" ht="18" customHeight="1">
+      <c r="I363" s="16" t="n"/>
+    </row>
+    <row r="364" ht="18" customHeight="1">
+      <c r="I364" s="16" t="n"/>
+    </row>
+    <row r="365" ht="18" customHeight="1">
+      <c r="I365" s="16" t="n"/>
+    </row>
+    <row r="366" ht="18" customHeight="1">
+      <c r="I366" s="16" t="n"/>
+    </row>
+    <row r="367" ht="18" customHeight="1">
+      <c r="I367" s="16" t="n"/>
+    </row>
+    <row r="368" ht="18" customHeight="1">
+      <c r="I368" s="16" t="n"/>
+    </row>
+    <row r="369" ht="18" customHeight="1">
+      <c r="I369" s="16" t="n"/>
+    </row>
+    <row r="370" ht="18" customHeight="1">
+      <c r="I370" s="16" t="n"/>
+    </row>
+    <row r="371" ht="18" customHeight="1">
+      <c r="I371" s="16" t="n"/>
+    </row>
+    <row r="372" ht="18" customHeight="1">
+      <c r="I372" s="16" t="n"/>
+    </row>
+    <row r="373" ht="18" customHeight="1">
+      <c r="I373" s="16" t="n"/>
+    </row>
+    <row r="374" ht="18" customHeight="1">
+      <c r="I374" s="16" t="n"/>
+    </row>
+    <row r="375" ht="18" customHeight="1">
+      <c r="I375" s="16" t="n"/>
+    </row>
+    <row r="376" ht="18" customHeight="1">
+      <c r="I376" s="16" t="n"/>
+    </row>
+    <row r="377" ht="18" customHeight="1">
+      <c r="I377" s="16" t="n"/>
+    </row>
+    <row r="378" ht="18" customHeight="1">
+      <c r="I378" s="16" t="n"/>
+    </row>
+    <row r="379" ht="18" customHeight="1">
+      <c r="I379" s="16" t="n"/>
+    </row>
+    <row r="380" ht="18" customHeight="1">
+      <c r="I380" s="16" t="n"/>
+    </row>
+    <row r="381" ht="18" customHeight="1">
+      <c r="I381" s="16" t="n"/>
+    </row>
+    <row r="382" ht="18" customHeight="1">
+      <c r="I382" s="16" t="n"/>
+    </row>
+    <row r="383" ht="18" customHeight="1">
+      <c r="I383" s="16" t="n"/>
+    </row>
+    <row r="384" ht="18" customHeight="1">
+      <c r="I384" s="16" t="n"/>
+    </row>
+    <row r="385" ht="18" customHeight="1">
+      <c r="I385" s="16" t="n"/>
+    </row>
+    <row r="386" ht="18" customHeight="1">
+      <c r="I386" s="16" t="n"/>
+    </row>
+    <row r="387" ht="18" customHeight="1">
+      <c r="I387" s="16" t="n"/>
+    </row>
+    <row r="388" ht="18" customHeight="1">
+      <c r="I388" s="16" t="n"/>
+    </row>
+    <row r="389" ht="18" customHeight="1">
+      <c r="I389" s="16" t="n"/>
+    </row>
+    <row r="390" ht="18" customHeight="1">
+      <c r="I390" s="16" t="n"/>
+    </row>
+    <row r="391" ht="18" customHeight="1">
+      <c r="I391" s="16" t="n"/>
+    </row>
+    <row r="392" ht="18" customHeight="1">
+      <c r="I392" s="16" t="n"/>
+    </row>
+    <row r="393" ht="18" customHeight="1">
+      <c r="I393" s="16" t="n"/>
+    </row>
+    <row r="394" ht="18" customHeight="1">
+      <c r="I394" s="16" t="n"/>
+    </row>
+    <row r="395" ht="18" customHeight="1">
+      <c r="I395" s="16" t="n"/>
+    </row>
+    <row r="396" ht="18" customHeight="1">
+      <c r="I396" s="16" t="n"/>
+    </row>
+    <row r="397" ht="18" customHeight="1">
+      <c r="I397" s="16" t="n"/>
+    </row>
+    <row r="398" ht="18" customHeight="1">
+      <c r="I398" s="16" t="n"/>
+    </row>
+    <row r="399" ht="18" customHeight="1">
+      <c r="I399" s="16" t="n"/>
+    </row>
+    <row r="400" ht="18" customHeight="1">
+      <c r="I400" s="16" t="n"/>
+    </row>
+    <row r="401" ht="18" customHeight="1">
+      <c r="I401" s="16" t="n"/>
+    </row>
+    <row r="402" ht="18" customHeight="1">
+      <c r="I402" s="16" t="n"/>
+    </row>
+    <row r="403" ht="18" customHeight="1">
+      <c r="I403" s="16" t="n"/>
+    </row>
+    <row r="404" ht="18" customHeight="1">
+      <c r="I404" s="16" t="n"/>
+    </row>
+    <row r="405" ht="18" customHeight="1">
+      <c r="I405" s="16" t="n"/>
+    </row>
+    <row r="406" ht="18" customHeight="1">
+      <c r="I406" s="16" t="n"/>
+    </row>
+    <row r="407" ht="18" customHeight="1">
+      <c r="I407" s="16" t="n"/>
+    </row>
+    <row r="408" ht="18" customHeight="1">
+      <c r="I408" s="16" t="n"/>
+    </row>
+    <row r="409" ht="18" customHeight="1">
+      <c r="I409" s="16" t="n"/>
+    </row>
+    <row r="410" ht="18" customHeight="1">
+      <c r="I410" s="16" t="n"/>
+    </row>
+    <row r="411" ht="18" customHeight="1">
+      <c r="I411" s="16" t="n"/>
+    </row>
+    <row r="412" ht="18" customHeight="1">
+      <c r="I412" s="16" t="n"/>
+    </row>
+    <row r="413" ht="18" customHeight="1">
+      <c r="I413" s="16" t="n"/>
+    </row>
+    <row r="414" ht="18" customHeight="1">
+      <c r="I414" s="16" t="n"/>
+    </row>
+    <row r="415" ht="18" customHeight="1">
+      <c r="I415" s="16" t="n"/>
+    </row>
+    <row r="416" ht="18" customHeight="1">
+      <c r="I416" s="16" t="n"/>
+    </row>
+    <row r="417" ht="18" customHeight="1">
+      <c r="I417" s="16" t="n"/>
+    </row>
+    <row r="418" ht="18" customHeight="1">
+      <c r="I418" s="16" t="n"/>
+    </row>
+    <row r="419" ht="18" customHeight="1">
+      <c r="I419" s="16" t="n"/>
+    </row>
+    <row r="420" ht="18" customHeight="1">
+      <c r="I420" s="16" t="n"/>
+    </row>
+    <row r="421" ht="18" customHeight="1">
+      <c r="I421" s="16" t="n"/>
+    </row>
+    <row r="422" ht="18" customHeight="1">
+      <c r="I422" s="16" t="n"/>
+    </row>
+    <row r="423" ht="18" customHeight="1">
+      <c r="I423" s="16" t="n"/>
+    </row>
+    <row r="424" ht="18" customHeight="1">
+      <c r="I424" s="16" t="n"/>
+    </row>
+    <row r="425" ht="18" customHeight="1">
+      <c r="I425" s="16" t="n"/>
+    </row>
+    <row r="426" ht="18" customHeight="1">
+      <c r="I426" s="16" t="n"/>
+    </row>
+    <row r="427" ht="18" customHeight="1">
+      <c r="I427" s="16" t="n"/>
+    </row>
+    <row r="428" ht="18" customHeight="1">
+      <c r="I428" s="16" t="n"/>
+    </row>
+    <row r="429" ht="18" customHeight="1">
+      <c r="I429" s="16" t="n"/>
+    </row>
+    <row r="430" ht="18" customHeight="1">
+      <c r="I430" s="16" t="n"/>
+    </row>
+    <row r="431" ht="18" customHeight="1">
+      <c r="I431" s="16" t="n"/>
+    </row>
+    <row r="432" ht="18" customHeight="1">
+      <c r="I432" s="16" t="n"/>
+    </row>
+    <row r="433" ht="18" customHeight="1">
+      <c r="I433" s="16" t="n"/>
+    </row>
+    <row r="434" ht="18" customHeight="1">
+      <c r="I434" s="16" t="n"/>
+    </row>
+    <row r="435" ht="18" customHeight="1">
+      <c r="I435" s="16" t="n"/>
+    </row>
+    <row r="436" ht="18" customHeight="1">
+      <c r="I436" s="16" t="n"/>
+    </row>
+    <row r="437" ht="18" customHeight="1">
+      <c r="I437" s="16" t="n"/>
+    </row>
+    <row r="438" ht="18" customHeight="1">
+      <c r="I438" s="16" t="n"/>
+    </row>
+    <row r="439" ht="18" customHeight="1">
+      <c r="I439" s="16" t="n"/>
+    </row>
+    <row r="440" ht="18" customHeight="1">
+      <c r="I440" s="16" t="n"/>
+    </row>
+    <row r="441" ht="18" customHeight="1">
+      <c r="I441" s="16" t="n"/>
+    </row>
+    <row r="442" ht="18" customHeight="1">
+      <c r="I442" s="16" t="n"/>
+    </row>
+    <row r="443" ht="18" customHeight="1">
+      <c r="I443" s="16" t="n"/>
+    </row>
+    <row r="444" ht="18" customHeight="1">
+      <c r="I444" s="16" t="n"/>
+    </row>
+    <row r="445" ht="18" customHeight="1">
+      <c r="I445" s="16" t="n"/>
+    </row>
+    <row r="446" ht="18" customHeight="1">
+      <c r="I446" s="16" t="n"/>
+    </row>
+    <row r="447" ht="18" customHeight="1">
+      <c r="I447" s="16" t="n"/>
+    </row>
+    <row r="448" ht="18" customHeight="1">
+      <c r="I448" s="16" t="n"/>
+    </row>
+    <row r="449" ht="18" customHeight="1">
+      <c r="I449" s="16" t="n"/>
+    </row>
+    <row r="450" ht="18" customHeight="1">
+      <c r="I450" s="16" t="n"/>
+    </row>
+    <row r="451" ht="18" customHeight="1">
+      <c r="I451" s="16" t="n"/>
+    </row>
+    <row r="452" ht="18" customHeight="1">
+      <c r="I452" s="16" t="n"/>
+    </row>
+    <row r="453" ht="18" customHeight="1">
+      <c r="I453" s="16" t="n"/>
+    </row>
+    <row r="454" ht="18" customHeight="1">
+      <c r="I454" s="16" t="n"/>
+    </row>
+    <row r="455" ht="18" customHeight="1">
+      <c r="I455" s="16" t="n"/>
+    </row>
+    <row r="456" ht="18" customHeight="1">
+      <c r="I456" s="16" t="n"/>
+    </row>
+    <row r="457" ht="18" customHeight="1">
+      <c r="I457" s="16" t="n"/>
+    </row>
+    <row r="458" ht="18" customHeight="1">
+      <c r="I458" s="16" t="n"/>
+    </row>
+    <row r="459" ht="18" customHeight="1">
+      <c r="I459" s="16" t="n"/>
+    </row>
+    <row r="460" ht="18" customHeight="1">
+      <c r="I460" s="16" t="n"/>
+    </row>
+    <row r="461" ht="18" customHeight="1">
+      <c r="I461" s="16" t="n"/>
+    </row>
+    <row r="462" ht="18" customHeight="1">
+      <c r="I462" s="16" t="n"/>
+    </row>
+    <row r="463" ht="18" customHeight="1">
+      <c r="I463" s="16" t="n"/>
+    </row>
+    <row r="464" ht="18" customHeight="1">
+      <c r="I464" s="16" t="n"/>
+    </row>
+    <row r="465" ht="18" customHeight="1">
+      <c r="I465" s="16" t="n"/>
+    </row>
+    <row r="466" ht="18" customHeight="1">
+      <c r="I466" s="16" t="n"/>
+    </row>
+    <row r="467" ht="18" customHeight="1">
+      <c r="I467" s="16" t="n"/>
+    </row>
+    <row r="468" ht="18" customHeight="1">
+      <c r="I468" s="16" t="n"/>
+    </row>
+    <row r="469" ht="18" customHeight="1">
+      <c r="I469" s="16" t="n"/>
+    </row>
+    <row r="470" ht="18" customHeight="1">
+      <c r="I470" s="16" t="n"/>
+    </row>
+    <row r="471" ht="18" customHeight="1">
+      <c r="I471" s="16" t="n"/>
+    </row>
+    <row r="472" ht="18" customHeight="1">
+      <c r="I472" s="16" t="n"/>
+    </row>
+    <row r="473" ht="18" customHeight="1">
+      <c r="I473" s="16" t="n"/>
+    </row>
+    <row r="474" ht="18" customHeight="1">
+      <c r="I474" s="16" t="n"/>
+    </row>
+    <row r="475" ht="18" customHeight="1">
+      <c r="I475" s="16" t="n"/>
+    </row>
+    <row r="476" ht="18" customHeight="1">
+      <c r="I476" s="16" t="n"/>
+    </row>
+    <row r="477" ht="18" customHeight="1">
+      <c r="I477" s="16" t="n"/>
+    </row>
+    <row r="478" ht="18" customHeight="1">
+      <c r="I478" s="16" t="n"/>
+    </row>
+    <row r="479" ht="18" customHeight="1">
+      <c r="I479" s="16" t="n"/>
+    </row>
+    <row r="480" ht="18" customHeight="1">
+      <c r="I480" s="16" t="n"/>
+    </row>
+    <row r="481" ht="18" customHeight="1">
+      <c r="I481" s="16" t="n"/>
+    </row>
+    <row r="482" ht="18" customHeight="1">
+      <c r="I482" s="16" t="n"/>
+    </row>
+    <row r="483" ht="18" customHeight="1">
+      <c r="I483" s="16" t="n"/>
+    </row>
+    <row r="484" ht="18" customHeight="1">
+      <c r="I484" s="16" t="n"/>
+    </row>
+    <row r="485" ht="18" customHeight="1">
+      <c r="I485" s="16" t="n"/>
+    </row>
+    <row r="486" ht="18" customHeight="1">
+      <c r="I486" s="16" t="n"/>
+    </row>
+    <row r="487" ht="18" customHeight="1">
+      <c r="I487" s="16" t="n"/>
+    </row>
+    <row r="488" ht="18" customHeight="1">
+      <c r="I488" s="16" t="n"/>
+    </row>
+    <row r="489" ht="18" customHeight="1">
+      <c r="I489" s="16" t="n"/>
+    </row>
+    <row r="490" ht="18" customHeight="1">
+      <c r="I490" s="16" t="n"/>
+    </row>
+    <row r="491" ht="18" customHeight="1">
+      <c r="I491" s="16" t="n"/>
+    </row>
+    <row r="492" ht="18" customHeight="1">
+      <c r="I492" s="16" t="n"/>
+    </row>
+    <row r="493" ht="18" customHeight="1">
+      <c r="I493" s="16" t="n"/>
+    </row>
+    <row r="494" ht="18" customHeight="1">
+      <c r="I494" s="16" t="n"/>
+    </row>
+    <row r="495" ht="18" customHeight="1">
+      <c r="I495" s="16" t="n"/>
+    </row>
+    <row r="496" ht="18" customHeight="1">
+      <c r="I496" s="16" t="n"/>
+    </row>
+    <row r="497" ht="18" customHeight="1">
+      <c r="I497" s="16" t="n"/>
+    </row>
+    <row r="498" ht="18" customHeight="1">
+      <c r="I498" s="16" t="n"/>
+    </row>
+    <row r="499" ht="18" customHeight="1">
+      <c r="I499" s="16" t="n"/>
+    </row>
+    <row r="500" ht="18" customHeight="1">
+      <c r="I500" s="16" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="C1:D1"/>

--- a/4_pagos/efectivo/inputs/mesa_5.xlsx
+++ b/4_pagos/efectivo/inputs/mesa_5.xlsx
@@ -60,6 +60,12 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="00880E4F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <color rgb="001D4ED8"/>
       <sz val="10"/>
     </font>
@@ -89,20 +95,14 @@
     </font>
     <font>
       <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="009CA3AF"/>
+      <b val="1"/>
+      <color rgb="00880E4F"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00880E4F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00880E4F"/>
+      <i val="1"/>
+      <color rgb="009CA3AF"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -144,7 +144,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -166,55 +166,11 @@
         <color rgb="00FFFFFF"/>
       </bottom>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00FFFFFF"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00FFFFFF"/>
-      </right>
-      <top style="thin">
-        <color rgb="00FFFFFF"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00FFFFFF"/>
-      </right>
-      <top style="thin">
-        <color rgb="00FFFFFF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00FFFFFF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00FFFFFF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00FFFFFF"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -231,31 +187,29 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -647,21 +601,16 @@
           <t>¿Quién cobró?</t>
         </is>
       </c>
-      <c r="B1" s="12" t="n"/>
       <c r="C1" s="2" t="inlineStr">
         <is>
           <t>¿Dónde vive?</t>
         </is>
       </c>
-      <c r="D1" s="12" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
           <t>¿Cuánto y cuándo?</t>
         </is>
       </c>
-      <c r="F1" s="13" t="n"/>
-      <c r="G1" s="13" t="n"/>
-      <c r="H1" s="12" t="n"/>
       <c r="I1" s="4" t="inlineStr">
         <is>
           <t>¿Alguna nota?</t>
@@ -672,1603 +621,1604 @@
           <t>¿Qué tipo?</t>
         </is>
       </c>
-      <c r="K1" s="14" t="inlineStr">
+      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>¿Qué pasó?</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>COBRADOR</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>FECHA_REGISTRO</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>MZ</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>LT</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="E2" s="9" t="inlineStr">
         <is>
           <t>MONTO</t>
         </is>
       </c>
-      <c r="F2" s="8" t="inlineStr">
+      <c r="F2" s="9" t="inlineStr">
         <is>
           <t>MONTO_EFECTIVO</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="G2" s="9" t="inlineStr">
         <is>
           <t>MONTO_YAPE</t>
         </is>
       </c>
-      <c r="H2" s="8" t="inlineStr">
+      <c r="H2" s="9" t="inlineStr">
         <is>
           <t>FECHA</t>
         </is>
       </c>
-      <c r="I2" s="9" t="inlineStr">
+      <c r="I2" s="10" t="inlineStr">
         <is>
           <t>COMENTARIO</t>
         </is>
       </c>
-      <c r="J2" s="10" t="inlineStr">
+      <c r="J2" s="11" t="inlineStr">
         <is>
           <t>CONCEPTO</t>
         </is>
       </c>
-      <c r="K2" s="15" t="inlineStr">
+      <c r="K2" s="12" t="inlineStr">
         <is>
           <t>CATEGORIA</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>María García</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>8C</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>38.00</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>20.00</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>18.00</t>
         </is>
       </c>
-      <c r="H3" s="11" t="inlineStr">
+      <c r="H3" s="13" t="inlineStr">
         <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="I3" s="11" t="inlineStr"/>
-      <c r="J3" s="11" t="inlineStr"/>
+      <c r="I3" s="13" t="inlineStr"/>
+      <c r="J3" s="13" t="inlineStr"/>
+      <c r="K3" s="13" t="inlineStr"/>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="I4" s="16" t="n"/>
+      <c r="I4" s="14" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="I5" s="16" t="n"/>
+      <c r="I5" s="14" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="I6" s="16" t="n"/>
+      <c r="I6" s="14" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="I7" s="16" t="n"/>
+      <c r="I7" s="14" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="I8" s="16" t="n"/>
+      <c r="I8" s="14" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="I9" s="16" t="n"/>
+      <c r="I9" s="14" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="I10" s="16" t="n"/>
+      <c r="I10" s="14" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="I11" s="16" t="n"/>
+      <c r="I11" s="14" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="I12" s="16" t="n"/>
+      <c r="I12" s="14" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="I13" s="16" t="n"/>
+      <c r="I13" s="14" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="I14" s="16" t="n"/>
+      <c r="I14" s="14" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="I15" s="16" t="n"/>
+      <c r="I15" s="14" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="I16" s="16" t="n"/>
+      <c r="I16" s="14" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="I17" s="16" t="n"/>
+      <c r="I17" s="14" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="I18" s="16" t="n"/>
+      <c r="I18" s="14" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="I19" s="16" t="n"/>
+      <c r="I19" s="14" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="I20" s="16" t="n"/>
+      <c r="I20" s="14" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="I21" s="16" t="n"/>
+      <c r="I21" s="14" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="I22" s="16" t="n"/>
+      <c r="I22" s="14" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="I23" s="16" t="n"/>
+      <c r="I23" s="14" t="n"/>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="I24" s="16" t="n"/>
+      <c r="I24" s="14" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="I25" s="16" t="n"/>
+      <c r="I25" s="14" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="I26" s="16" t="n"/>
+      <c r="I26" s="14" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="I27" s="16" t="n"/>
+      <c r="I27" s="14" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="I28" s="16" t="n"/>
+      <c r="I28" s="14" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="I29" s="16" t="n"/>
+      <c r="I29" s="14" t="n"/>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="I30" s="16" t="n"/>
+      <c r="I30" s="14" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="I31" s="16" t="n"/>
+      <c r="I31" s="14" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="I32" s="16" t="n"/>
+      <c r="I32" s="14" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="I33" s="16" t="n"/>
+      <c r="I33" s="14" t="n"/>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="I34" s="16" t="n"/>
+      <c r="I34" s="14" t="n"/>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="I35" s="16" t="n"/>
+      <c r="I35" s="14" t="n"/>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="I36" s="16" t="n"/>
+      <c r="I36" s="14" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1">
-      <c r="I37" s="16" t="n"/>
+      <c r="I37" s="14" t="n"/>
     </row>
     <row r="38" ht="18" customHeight="1">
-      <c r="I38" s="16" t="n"/>
+      <c r="I38" s="14" t="n"/>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="I39" s="16" t="n"/>
+      <c r="I39" s="14" t="n"/>
     </row>
     <row r="40" ht="18" customHeight="1">
-      <c r="I40" s="16" t="n"/>
+      <c r="I40" s="14" t="n"/>
     </row>
     <row r="41" ht="18" customHeight="1">
-      <c r="I41" s="16" t="n"/>
+      <c r="I41" s="14" t="n"/>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="I42" s="16" t="n"/>
+      <c r="I42" s="14" t="n"/>
     </row>
     <row r="43" ht="18" customHeight="1">
-      <c r="I43" s="16" t="n"/>
+      <c r="I43" s="14" t="n"/>
     </row>
     <row r="44" ht="18" customHeight="1">
-      <c r="I44" s="16" t="n"/>
+      <c r="I44" s="14" t="n"/>
     </row>
     <row r="45" ht="18" customHeight="1">
-      <c r="I45" s="16" t="n"/>
+      <c r="I45" s="14" t="n"/>
     </row>
     <row r="46" ht="18" customHeight="1">
-      <c r="I46" s="16" t="n"/>
+      <c r="I46" s="14" t="n"/>
     </row>
     <row r="47" ht="18" customHeight="1">
-      <c r="I47" s="16" t="n"/>
+      <c r="I47" s="14" t="n"/>
     </row>
     <row r="48" ht="18" customHeight="1">
-      <c r="I48" s="16" t="n"/>
+      <c r="I48" s="14" t="n"/>
     </row>
     <row r="49" ht="18" customHeight="1">
-      <c r="I49" s="16" t="n"/>
+      <c r="I49" s="14" t="n"/>
     </row>
     <row r="50" ht="18" customHeight="1">
-      <c r="I50" s="16" t="n"/>
+      <c r="I50" s="14" t="n"/>
     </row>
     <row r="51" ht="18" customHeight="1">
-      <c r="I51" s="16" t="n"/>
+      <c r="I51" s="14" t="n"/>
     </row>
     <row r="52" ht="18" customHeight="1">
-      <c r="I52" s="16" t="n"/>
+      <c r="I52" s="14" t="n"/>
     </row>
     <row r="53" ht="18" customHeight="1">
-      <c r="I53" s="16" t="n"/>
+      <c r="I53" s="14" t="n"/>
     </row>
     <row r="54" ht="18" customHeight="1">
-      <c r="I54" s="16" t="n"/>
+      <c r="I54" s="14" t="n"/>
     </row>
     <row r="55" ht="18" customHeight="1">
-      <c r="I55" s="16" t="n"/>
+      <c r="I55" s="14" t="n"/>
     </row>
     <row r="56" ht="18" customHeight="1">
-      <c r="I56" s="16" t="n"/>
+      <c r="I56" s="14" t="n"/>
     </row>
     <row r="57" ht="18" customHeight="1">
-      <c r="I57" s="16" t="n"/>
+      <c r="I57" s="14" t="n"/>
     </row>
     <row r="58" ht="18" customHeight="1">
-      <c r="I58" s="16" t="n"/>
+      <c r="I58" s="14" t="n"/>
     </row>
     <row r="59" ht="18" customHeight="1">
-      <c r="I59" s="16" t="n"/>
+      <c r="I59" s="14" t="n"/>
     </row>
     <row r="60" ht="18" customHeight="1">
-      <c r="I60" s="16" t="n"/>
+      <c r="I60" s="14" t="n"/>
     </row>
     <row r="61" ht="18" customHeight="1">
-      <c r="I61" s="16" t="n"/>
+      <c r="I61" s="14" t="n"/>
     </row>
     <row r="62" ht="18" customHeight="1">
-      <c r="I62" s="16" t="n"/>
+      <c r="I62" s="14" t="n"/>
     </row>
     <row r="63" ht="18" customHeight="1">
-      <c r="I63" s="16" t="n"/>
+      <c r="I63" s="14" t="n"/>
     </row>
     <row r="64" ht="18" customHeight="1">
-      <c r="I64" s="16" t="n"/>
+      <c r="I64" s="14" t="n"/>
     </row>
     <row r="65" ht="18" customHeight="1">
-      <c r="I65" s="16" t="n"/>
+      <c r="I65" s="14" t="n"/>
     </row>
     <row r="66" ht="18" customHeight="1">
-      <c r="I66" s="16" t="n"/>
+      <c r="I66" s="14" t="n"/>
     </row>
     <row r="67" ht="18" customHeight="1">
-      <c r="I67" s="16" t="n"/>
+      <c r="I67" s="14" t="n"/>
     </row>
     <row r="68" ht="18" customHeight="1">
-      <c r="I68" s="16" t="n"/>
+      <c r="I68" s="14" t="n"/>
     </row>
     <row r="69" ht="18" customHeight="1">
-      <c r="I69" s="16" t="n"/>
+      <c r="I69" s="14" t="n"/>
     </row>
     <row r="70" ht="18" customHeight="1">
-      <c r="I70" s="16" t="n"/>
+      <c r="I70" s="14" t="n"/>
     </row>
     <row r="71" ht="18" customHeight="1">
-      <c r="I71" s="16" t="n"/>
+      <c r="I71" s="14" t="n"/>
     </row>
     <row r="72" ht="18" customHeight="1">
-      <c r="I72" s="16" t="n"/>
+      <c r="I72" s="14" t="n"/>
     </row>
     <row r="73" ht="18" customHeight="1">
-      <c r="I73" s="16" t="n"/>
+      <c r="I73" s="14" t="n"/>
     </row>
     <row r="74" ht="18" customHeight="1">
-      <c r="I74" s="16" t="n"/>
+      <c r="I74" s="14" t="n"/>
     </row>
     <row r="75" ht="18" customHeight="1">
-      <c r="I75" s="16" t="n"/>
+      <c r="I75" s="14" t="n"/>
     </row>
     <row r="76" ht="18" customHeight="1">
-      <c r="I76" s="16" t="n"/>
+      <c r="I76" s="14" t="n"/>
     </row>
     <row r="77" ht="18" customHeight="1">
-      <c r="I77" s="16" t="n"/>
+      <c r="I77" s="14" t="n"/>
     </row>
     <row r="78" ht="18" customHeight="1">
-      <c r="I78" s="16" t="n"/>
+      <c r="I78" s="14" t="n"/>
     </row>
     <row r="79" ht="18" customHeight="1">
-      <c r="I79" s="16" t="n"/>
+      <c r="I79" s="14" t="n"/>
     </row>
     <row r="80" ht="18" customHeight="1">
-      <c r="I80" s="16" t="n"/>
+      <c r="I80" s="14" t="n"/>
     </row>
     <row r="81" ht="18" customHeight="1">
-      <c r="I81" s="16" t="n"/>
+      <c r="I81" s="14" t="n"/>
     </row>
     <row r="82" ht="18" customHeight="1">
-      <c r="I82" s="16" t="n"/>
+      <c r="I82" s="14" t="n"/>
     </row>
     <row r="83" ht="18" customHeight="1">
-      <c r="I83" s="16" t="n"/>
+      <c r="I83" s="14" t="n"/>
     </row>
     <row r="84" ht="18" customHeight="1">
-      <c r="I84" s="16" t="n"/>
+      <c r="I84" s="14" t="n"/>
     </row>
     <row r="85" ht="18" customHeight="1">
-      <c r="I85" s="16" t="n"/>
+      <c r="I85" s="14" t="n"/>
     </row>
     <row r="86" ht="18" customHeight="1">
-      <c r="I86" s="16" t="n"/>
+      <c r="I86" s="14" t="n"/>
     </row>
     <row r="87" ht="18" customHeight="1">
-      <c r="I87" s="16" t="n"/>
+      <c r="I87" s="14" t="n"/>
     </row>
     <row r="88" ht="18" customHeight="1">
-      <c r="I88" s="16" t="n"/>
+      <c r="I88" s="14" t="n"/>
     </row>
     <row r="89" ht="18" customHeight="1">
-      <c r="I89" s="16" t="n"/>
+      <c r="I89" s="14" t="n"/>
     </row>
     <row r="90" ht="18" customHeight="1">
-      <c r="I90" s="16" t="n"/>
+      <c r="I90" s="14" t="n"/>
     </row>
     <row r="91" ht="18" customHeight="1">
-      <c r="I91" s="16" t="n"/>
+      <c r="I91" s="14" t="n"/>
     </row>
     <row r="92" ht="18" customHeight="1">
-      <c r="I92" s="16" t="n"/>
+      <c r="I92" s="14" t="n"/>
     </row>
     <row r="93" ht="18" customHeight="1">
-      <c r="I93" s="16" t="n"/>
+      <c r="I93" s="14" t="n"/>
     </row>
     <row r="94" ht="18" customHeight="1">
-      <c r="I94" s="16" t="n"/>
+      <c r="I94" s="14" t="n"/>
     </row>
     <row r="95" ht="18" customHeight="1">
-      <c r="I95" s="16" t="n"/>
+      <c r="I95" s="14" t="n"/>
     </row>
     <row r="96" ht="18" customHeight="1">
-      <c r="I96" s="16" t="n"/>
+      <c r="I96" s="14" t="n"/>
     </row>
     <row r="97" ht="18" customHeight="1">
-      <c r="I97" s="16" t="n"/>
+      <c r="I97" s="14" t="n"/>
     </row>
     <row r="98" ht="18" customHeight="1">
-      <c r="I98" s="16" t="n"/>
+      <c r="I98" s="14" t="n"/>
     </row>
     <row r="99" ht="18" customHeight="1">
-      <c r="I99" s="16" t="n"/>
+      <c r="I99" s="14" t="n"/>
     </row>
     <row r="100" ht="18" customHeight="1">
-      <c r="I100" s="16" t="n"/>
+      <c r="I100" s="14" t="n"/>
     </row>
     <row r="101" ht="18" customHeight="1">
-      <c r="I101" s="16" t="n"/>
+      <c r="I101" s="14" t="n"/>
     </row>
     <row r="102" ht="18" customHeight="1">
-      <c r="I102" s="16" t="n"/>
+      <c r="I102" s="14" t="n"/>
     </row>
     <row r="103" ht="18" customHeight="1">
-      <c r="I103" s="16" t="n"/>
+      <c r="I103" s="14" t="n"/>
     </row>
     <row r="104" ht="18" customHeight="1">
-      <c r="I104" s="16" t="n"/>
+      <c r="I104" s="14" t="n"/>
     </row>
     <row r="105" ht="18" customHeight="1">
-      <c r="I105" s="16" t="n"/>
+      <c r="I105" s="14" t="n"/>
     </row>
     <row r="106" ht="18" customHeight="1">
-      <c r="I106" s="16" t="n"/>
+      <c r="I106" s="14" t="n"/>
     </row>
     <row r="107" ht="18" customHeight="1">
-      <c r="I107" s="16" t="n"/>
+      <c r="I107" s="14" t="n"/>
     </row>
     <row r="108" ht="18" customHeight="1">
-      <c r="I108" s="16" t="n"/>
+      <c r="I108" s="14" t="n"/>
     </row>
     <row r="109" ht="18" customHeight="1">
-      <c r="I109" s="16" t="n"/>
+      <c r="I109" s="14" t="n"/>
     </row>
     <row r="110" ht="18" customHeight="1">
-      <c r="I110" s="16" t="n"/>
+      <c r="I110" s="14" t="n"/>
     </row>
     <row r="111" ht="18" customHeight="1">
-      <c r="I111" s="16" t="n"/>
+      <c r="I111" s="14" t="n"/>
     </row>
     <row r="112" ht="18" customHeight="1">
-      <c r="I112" s="16" t="n"/>
+      <c r="I112" s="14" t="n"/>
     </row>
     <row r="113" ht="18" customHeight="1">
-      <c r="I113" s="16" t="n"/>
+      <c r="I113" s="14" t="n"/>
     </row>
     <row r="114" ht="18" customHeight="1">
-      <c r="I114" s="16" t="n"/>
+      <c r="I114" s="14" t="n"/>
     </row>
     <row r="115" ht="18" customHeight="1">
-      <c r="I115" s="16" t="n"/>
+      <c r="I115" s="14" t="n"/>
     </row>
     <row r="116" ht="18" customHeight="1">
-      <c r="I116" s="16" t="n"/>
+      <c r="I116" s="14" t="n"/>
     </row>
     <row r="117" ht="18" customHeight="1">
-      <c r="I117" s="16" t="n"/>
+      <c r="I117" s="14" t="n"/>
     </row>
     <row r="118" ht="18" customHeight="1">
-      <c r="I118" s="16" t="n"/>
+      <c r="I118" s="14" t="n"/>
     </row>
     <row r="119" ht="18" customHeight="1">
-      <c r="I119" s="16" t="n"/>
+      <c r="I119" s="14" t="n"/>
     </row>
     <row r="120" ht="18" customHeight="1">
-      <c r="I120" s="16" t="n"/>
+      <c r="I120" s="14" t="n"/>
     </row>
     <row r="121" ht="18" customHeight="1">
-      <c r="I121" s="16" t="n"/>
+      <c r="I121" s="14" t="n"/>
     </row>
     <row r="122" ht="18" customHeight="1">
-      <c r="I122" s="16" t="n"/>
+      <c r="I122" s="14" t="n"/>
     </row>
     <row r="123" ht="18" customHeight="1">
-      <c r="I123" s="16" t="n"/>
+      <c r="I123" s="14" t="n"/>
     </row>
     <row r="124" ht="18" customHeight="1">
-      <c r="I124" s="16" t="n"/>
+      <c r="I124" s="14" t="n"/>
     </row>
     <row r="125" ht="18" customHeight="1">
-      <c r="I125" s="16" t="n"/>
+      <c r="I125" s="14" t="n"/>
     </row>
     <row r="126" ht="18" customHeight="1">
-      <c r="I126" s="16" t="n"/>
+      <c r="I126" s="14" t="n"/>
     </row>
     <row r="127" ht="18" customHeight="1">
-      <c r="I127" s="16" t="n"/>
+      <c r="I127" s="14" t="n"/>
     </row>
     <row r="128" ht="18" customHeight="1">
-      <c r="I128" s="16" t="n"/>
+      <c r="I128" s="14" t="n"/>
     </row>
     <row r="129" ht="18" customHeight="1">
-      <c r="I129" s="16" t="n"/>
+      <c r="I129" s="14" t="n"/>
     </row>
     <row r="130" ht="18" customHeight="1">
-      <c r="I130" s="16" t="n"/>
+      <c r="I130" s="14" t="n"/>
     </row>
     <row r="131" ht="18" customHeight="1">
-      <c r="I131" s="16" t="n"/>
+      <c r="I131" s="14" t="n"/>
     </row>
     <row r="132" ht="18" customHeight="1">
-      <c r="I132" s="16" t="n"/>
+      <c r="I132" s="14" t="n"/>
     </row>
     <row r="133" ht="18" customHeight="1">
-      <c r="I133" s="16" t="n"/>
+      <c r="I133" s="14" t="n"/>
     </row>
     <row r="134" ht="18" customHeight="1">
-      <c r="I134" s="16" t="n"/>
+      <c r="I134" s="14" t="n"/>
     </row>
     <row r="135" ht="18" customHeight="1">
-      <c r="I135" s="16" t="n"/>
+      <c r="I135" s="14" t="n"/>
     </row>
     <row r="136" ht="18" customHeight="1">
-      <c r="I136" s="16" t="n"/>
+      <c r="I136" s="14" t="n"/>
     </row>
     <row r="137" ht="18" customHeight="1">
-      <c r="I137" s="16" t="n"/>
+      <c r="I137" s="14" t="n"/>
     </row>
     <row r="138" ht="18" customHeight="1">
-      <c r="I138" s="16" t="n"/>
+      <c r="I138" s="14" t="n"/>
     </row>
     <row r="139" ht="18" customHeight="1">
-      <c r="I139" s="16" t="n"/>
+      <c r="I139" s="14" t="n"/>
     </row>
     <row r="140" ht="18" customHeight="1">
-      <c r="I140" s="16" t="n"/>
+      <c r="I140" s="14" t="n"/>
     </row>
     <row r="141" ht="18" customHeight="1">
-      <c r="I141" s="16" t="n"/>
+      <c r="I141" s="14" t="n"/>
     </row>
     <row r="142" ht="18" customHeight="1">
-      <c r="I142" s="16" t="n"/>
+      <c r="I142" s="14" t="n"/>
     </row>
     <row r="143" ht="18" customHeight="1">
-      <c r="I143" s="16" t="n"/>
+      <c r="I143" s="14" t="n"/>
     </row>
     <row r="144" ht="18" customHeight="1">
-      <c r="I144" s="16" t="n"/>
+      <c r="I144" s="14" t="n"/>
     </row>
     <row r="145" ht="18" customHeight="1">
-      <c r="I145" s="16" t="n"/>
+      <c r="I145" s="14" t="n"/>
     </row>
     <row r="146" ht="18" customHeight="1">
-      <c r="I146" s="16" t="n"/>
+      <c r="I146" s="14" t="n"/>
     </row>
     <row r="147" ht="18" customHeight="1">
-      <c r="I147" s="16" t="n"/>
+      <c r="I147" s="14" t="n"/>
     </row>
     <row r="148" ht="18" customHeight="1">
-      <c r="I148" s="16" t="n"/>
+      <c r="I148" s="14" t="n"/>
     </row>
     <row r="149" ht="18" customHeight="1">
-      <c r="I149" s="16" t="n"/>
+      <c r="I149" s="14" t="n"/>
     </row>
     <row r="150" ht="18" customHeight="1">
-      <c r="I150" s="16" t="n"/>
+      <c r="I150" s="14" t="n"/>
     </row>
     <row r="151" ht="18" customHeight="1">
-      <c r="I151" s="16" t="n"/>
+      <c r="I151" s="14" t="n"/>
     </row>
     <row r="152" ht="18" customHeight="1">
-      <c r="I152" s="16" t="n"/>
+      <c r="I152" s="14" t="n"/>
     </row>
     <row r="153" ht="18" customHeight="1">
-      <c r="I153" s="16" t="n"/>
+      <c r="I153" s="14" t="n"/>
     </row>
     <row r="154" ht="18" customHeight="1">
-      <c r="I154" s="16" t="n"/>
+      <c r="I154" s="14" t="n"/>
     </row>
     <row r="155" ht="18" customHeight="1">
-      <c r="I155" s="16" t="n"/>
+      <c r="I155" s="14" t="n"/>
     </row>
     <row r="156" ht="18" customHeight="1">
-      <c r="I156" s="16" t="n"/>
+      <c r="I156" s="14" t="n"/>
     </row>
     <row r="157" ht="18" customHeight="1">
-      <c r="I157" s="16" t="n"/>
+      <c r="I157" s="14" t="n"/>
     </row>
     <row r="158" ht="18" customHeight="1">
-      <c r="I158" s="16" t="n"/>
+      <c r="I158" s="14" t="n"/>
     </row>
     <row r="159" ht="18" customHeight="1">
-      <c r="I159" s="16" t="n"/>
+      <c r="I159" s="14" t="n"/>
     </row>
     <row r="160" ht="18" customHeight="1">
-      <c r="I160" s="16" t="n"/>
+      <c r="I160" s="14" t="n"/>
     </row>
     <row r="161" ht="18" customHeight="1">
-      <c r="I161" s="16" t="n"/>
+      <c r="I161" s="14" t="n"/>
     </row>
     <row r="162" ht="18" customHeight="1">
-      <c r="I162" s="16" t="n"/>
+      <c r="I162" s="14" t="n"/>
     </row>
     <row r="163" ht="18" customHeight="1">
-      <c r="I163" s="16" t="n"/>
+      <c r="I163" s="14" t="n"/>
     </row>
     <row r="164" ht="18" customHeight="1">
-      <c r="I164" s="16" t="n"/>
+      <c r="I164" s="14" t="n"/>
     </row>
     <row r="165" ht="18" customHeight="1">
-      <c r="I165" s="16" t="n"/>
+      <c r="I165" s="14" t="n"/>
     </row>
     <row r="166" ht="18" customHeight="1">
-      <c r="I166" s="16" t="n"/>
+      <c r="I166" s="14" t="n"/>
     </row>
     <row r="167" ht="18" customHeight="1">
-      <c r="I167" s="16" t="n"/>
+      <c r="I167" s="14" t="n"/>
     </row>
     <row r="168" ht="18" customHeight="1">
-      <c r="I168" s="16" t="n"/>
+      <c r="I168" s="14" t="n"/>
     </row>
     <row r="169" ht="18" customHeight="1">
-      <c r="I169" s="16" t="n"/>
+      <c r="I169" s="14" t="n"/>
     </row>
     <row r="170" ht="18" customHeight="1">
-      <c r="I170" s="16" t="n"/>
+      <c r="I170" s="14" t="n"/>
     </row>
     <row r="171" ht="18" customHeight="1">
-      <c r="I171" s="16" t="n"/>
+      <c r="I171" s="14" t="n"/>
     </row>
     <row r="172" ht="18" customHeight="1">
-      <c r="I172" s="16" t="n"/>
+      <c r="I172" s="14" t="n"/>
     </row>
     <row r="173" ht="18" customHeight="1">
-      <c r="I173" s="16" t="n"/>
+      <c r="I173" s="14" t="n"/>
     </row>
     <row r="174" ht="18" customHeight="1">
-      <c r="I174" s="16" t="n"/>
+      <c r="I174" s="14" t="n"/>
     </row>
     <row r="175" ht="18" customHeight="1">
-      <c r="I175" s="16" t="n"/>
+      <c r="I175" s="14" t="n"/>
     </row>
     <row r="176" ht="18" customHeight="1">
-      <c r="I176" s="16" t="n"/>
+      <c r="I176" s="14" t="n"/>
     </row>
     <row r="177" ht="18" customHeight="1">
-      <c r="I177" s="16" t="n"/>
+      <c r="I177" s="14" t="n"/>
     </row>
     <row r="178" ht="18" customHeight="1">
-      <c r="I178" s="16" t="n"/>
+      <c r="I178" s="14" t="n"/>
     </row>
     <row r="179" ht="18" customHeight="1">
-      <c r="I179" s="16" t="n"/>
+      <c r="I179" s="14" t="n"/>
     </row>
     <row r="180" ht="18" customHeight="1">
-      <c r="I180" s="16" t="n"/>
+      <c r="I180" s="14" t="n"/>
     </row>
     <row r="181" ht="18" customHeight="1">
-      <c r="I181" s="16" t="n"/>
+      <c r="I181" s="14" t="n"/>
     </row>
     <row r="182" ht="18" customHeight="1">
-      <c r="I182" s="16" t="n"/>
+      <c r="I182" s="14" t="n"/>
     </row>
     <row r="183" ht="18" customHeight="1">
-      <c r="I183" s="16" t="n"/>
+      <c r="I183" s="14" t="n"/>
     </row>
     <row r="184" ht="18" customHeight="1">
-      <c r="I184" s="16" t="n"/>
+      <c r="I184" s="14" t="n"/>
     </row>
     <row r="185" ht="18" customHeight="1">
-      <c r="I185" s="16" t="n"/>
+      <c r="I185" s="14" t="n"/>
     </row>
     <row r="186" ht="18" customHeight="1">
-      <c r="I186" s="16" t="n"/>
+      <c r="I186" s="14" t="n"/>
     </row>
     <row r="187" ht="18" customHeight="1">
-      <c r="I187" s="16" t="n"/>
+      <c r="I187" s="14" t="n"/>
     </row>
     <row r="188" ht="18" customHeight="1">
-      <c r="I188" s="16" t="n"/>
+      <c r="I188" s="14" t="n"/>
     </row>
     <row r="189" ht="18" customHeight="1">
-      <c r="I189" s="16" t="n"/>
+      <c r="I189" s="14" t="n"/>
     </row>
     <row r="190" ht="18" customHeight="1">
-      <c r="I190" s="16" t="n"/>
+      <c r="I190" s="14" t="n"/>
     </row>
     <row r="191" ht="18" customHeight="1">
-      <c r="I191" s="16" t="n"/>
+      <c r="I191" s="14" t="n"/>
     </row>
     <row r="192" ht="18" customHeight="1">
-      <c r="I192" s="16" t="n"/>
+      <c r="I192" s="14" t="n"/>
     </row>
     <row r="193" ht="18" customHeight="1">
-      <c r="I193" s="16" t="n"/>
+      <c r="I193" s="14" t="n"/>
     </row>
     <row r="194" ht="18" customHeight="1">
-      <c r="I194" s="16" t="n"/>
+      <c r="I194" s="14" t="n"/>
     </row>
     <row r="195" ht="18" customHeight="1">
-      <c r="I195" s="16" t="n"/>
+      <c r="I195" s="14" t="n"/>
     </row>
     <row r="196" ht="18" customHeight="1">
-      <c r="I196" s="16" t="n"/>
+      <c r="I196" s="14" t="n"/>
     </row>
     <row r="197" ht="18" customHeight="1">
-      <c r="I197" s="16" t="n"/>
+      <c r="I197" s="14" t="n"/>
     </row>
     <row r="198" ht="18" customHeight="1">
-      <c r="I198" s="16" t="n"/>
+      <c r="I198" s="14" t="n"/>
     </row>
     <row r="199" ht="18" customHeight="1">
-      <c r="I199" s="16" t="n"/>
+      <c r="I199" s="14" t="n"/>
     </row>
     <row r="200" ht="18" customHeight="1">
-      <c r="I200" s="16" t="n"/>
+      <c r="I200" s="14" t="n"/>
     </row>
     <row r="201" ht="18" customHeight="1">
-      <c r="I201" s="16" t="n"/>
+      <c r="I201" s="14" t="n"/>
     </row>
     <row r="202" ht="18" customHeight="1">
-      <c r="I202" s="16" t="n"/>
+      <c r="I202" s="14" t="n"/>
     </row>
     <row r="203" ht="18" customHeight="1">
-      <c r="I203" s="16" t="n"/>
+      <c r="I203" s="14" t="n"/>
     </row>
     <row r="204" ht="18" customHeight="1">
-      <c r="I204" s="16" t="n"/>
+      <c r="I204" s="14" t="n"/>
     </row>
     <row r="205" ht="18" customHeight="1">
-      <c r="I205" s="16" t="n"/>
+      <c r="I205" s="14" t="n"/>
     </row>
     <row r="206" ht="18" customHeight="1">
-      <c r="I206" s="16" t="n"/>
+      <c r="I206" s="14" t="n"/>
     </row>
     <row r="207" ht="18" customHeight="1">
-      <c r="I207" s="16" t="n"/>
+      <c r="I207" s="14" t="n"/>
     </row>
     <row r="208" ht="18" customHeight="1">
-      <c r="I208" s="16" t="n"/>
+      <c r="I208" s="14" t="n"/>
     </row>
     <row r="209" ht="18" customHeight="1">
-      <c r="I209" s="16" t="n"/>
+      <c r="I209" s="14" t="n"/>
     </row>
     <row r="210" ht="18" customHeight="1">
-      <c r="I210" s="16" t="n"/>
+      <c r="I210" s="14" t="n"/>
     </row>
     <row r="211" ht="18" customHeight="1">
-      <c r="I211" s="16" t="n"/>
+      <c r="I211" s="14" t="n"/>
     </row>
     <row r="212" ht="18" customHeight="1">
-      <c r="I212" s="16" t="n"/>
+      <c r="I212" s="14" t="n"/>
     </row>
     <row r="213" ht="18" customHeight="1">
-      <c r="I213" s="16" t="n"/>
+      <c r="I213" s="14" t="n"/>
     </row>
     <row r="214" ht="18" customHeight="1">
-      <c r="I214" s="16" t="n"/>
+      <c r="I214" s="14" t="n"/>
     </row>
     <row r="215" ht="18" customHeight="1">
-      <c r="I215" s="16" t="n"/>
+      <c r="I215" s="14" t="n"/>
     </row>
     <row r="216" ht="18" customHeight="1">
-      <c r="I216" s="16" t="n"/>
+      <c r="I216" s="14" t="n"/>
     </row>
     <row r="217" ht="18" customHeight="1">
-      <c r="I217" s="16" t="n"/>
+      <c r="I217" s="14" t="n"/>
     </row>
     <row r="218" ht="18" customHeight="1">
-      <c r="I218" s="16" t="n"/>
+      <c r="I218" s="14" t="n"/>
     </row>
     <row r="219" ht="18" customHeight="1">
-      <c r="I219" s="16" t="n"/>
+      <c r="I219" s="14" t="n"/>
     </row>
     <row r="220" ht="18" customHeight="1">
-      <c r="I220" s="16" t="n"/>
+      <c r="I220" s="14" t="n"/>
     </row>
     <row r="221" ht="18" customHeight="1">
-      <c r="I221" s="16" t="n"/>
+      <c r="I221" s="14" t="n"/>
     </row>
     <row r="222" ht="18" customHeight="1">
-      <c r="I222" s="16" t="n"/>
+      <c r="I222" s="14" t="n"/>
     </row>
     <row r="223" ht="18" customHeight="1">
-      <c r="I223" s="16" t="n"/>
+      <c r="I223" s="14" t="n"/>
     </row>
     <row r="224" ht="18" customHeight="1">
-      <c r="I224" s="16" t="n"/>
+      <c r="I224" s="14" t="n"/>
     </row>
     <row r="225" ht="18" customHeight="1">
-      <c r="I225" s="16" t="n"/>
+      <c r="I225" s="14" t="n"/>
     </row>
     <row r="226" ht="18" customHeight="1">
-      <c r="I226" s="16" t="n"/>
+      <c r="I226" s="14" t="n"/>
     </row>
     <row r="227" ht="18" customHeight="1">
-      <c r="I227" s="16" t="n"/>
+      <c r="I227" s="14" t="n"/>
     </row>
     <row r="228" ht="18" customHeight="1">
-      <c r="I228" s="16" t="n"/>
+      <c r="I228" s="14" t="n"/>
     </row>
     <row r="229" ht="18" customHeight="1">
-      <c r="I229" s="16" t="n"/>
+      <c r="I229" s="14" t="n"/>
     </row>
     <row r="230" ht="18" customHeight="1">
-      <c r="I230" s="16" t="n"/>
+      <c r="I230" s="14" t="n"/>
     </row>
     <row r="231" ht="18" customHeight="1">
-      <c r="I231" s="16" t="n"/>
+      <c r="I231" s="14" t="n"/>
     </row>
     <row r="232" ht="18" customHeight="1">
-      <c r="I232" s="16" t="n"/>
+      <c r="I232" s="14" t="n"/>
     </row>
     <row r="233" ht="18" customHeight="1">
-      <c r="I233" s="16" t="n"/>
+      <c r="I233" s="14" t="n"/>
     </row>
     <row r="234" ht="18" customHeight="1">
-      <c r="I234" s="16" t="n"/>
+      <c r="I234" s="14" t="n"/>
     </row>
     <row r="235" ht="18" customHeight="1">
-      <c r="I235" s="16" t="n"/>
+      <c r="I235" s="14" t="n"/>
     </row>
     <row r="236" ht="18" customHeight="1">
-      <c r="I236" s="16" t="n"/>
+      <c r="I236" s="14" t="n"/>
     </row>
     <row r="237" ht="18" customHeight="1">
-      <c r="I237" s="16" t="n"/>
+      <c r="I237" s="14" t="n"/>
     </row>
     <row r="238" ht="18" customHeight="1">
-      <c r="I238" s="16" t="n"/>
+      <c r="I238" s="14" t="n"/>
     </row>
     <row r="239" ht="18" customHeight="1">
-      <c r="I239" s="16" t="n"/>
+      <c r="I239" s="14" t="n"/>
     </row>
     <row r="240" ht="18" customHeight="1">
-      <c r="I240" s="16" t="n"/>
+      <c r="I240" s="14" t="n"/>
     </row>
     <row r="241" ht="18" customHeight="1">
-      <c r="I241" s="16" t="n"/>
+      <c r="I241" s="14" t="n"/>
     </row>
     <row r="242" ht="18" customHeight="1">
-      <c r="I242" s="16" t="n"/>
+      <c r="I242" s="14" t="n"/>
     </row>
     <row r="243" ht="18" customHeight="1">
-      <c r="I243" s="16" t="n"/>
+      <c r="I243" s="14" t="n"/>
     </row>
     <row r="244" ht="18" customHeight="1">
-      <c r="I244" s="16" t="n"/>
+      <c r="I244" s="14" t="n"/>
     </row>
     <row r="245" ht="18" customHeight="1">
-      <c r="I245" s="16" t="n"/>
+      <c r="I245" s="14" t="n"/>
     </row>
     <row r="246" ht="18" customHeight="1">
-      <c r="I246" s="16" t="n"/>
+      <c r="I246" s="14" t="n"/>
     </row>
     <row r="247" ht="18" customHeight="1">
-      <c r="I247" s="16" t="n"/>
+      <c r="I247" s="14" t="n"/>
     </row>
     <row r="248" ht="18" customHeight="1">
-      <c r="I248" s="16" t="n"/>
+      <c r="I248" s="14" t="n"/>
     </row>
     <row r="249" ht="18" customHeight="1">
-      <c r="I249" s="16" t="n"/>
+      <c r="I249" s="14" t="n"/>
     </row>
     <row r="250" ht="18" customHeight="1">
-      <c r="I250" s="16" t="n"/>
+      <c r="I250" s="14" t="n"/>
     </row>
     <row r="251" ht="18" customHeight="1">
-      <c r="I251" s="16" t="n"/>
+      <c r="I251" s="14" t="n"/>
     </row>
     <row r="252" ht="18" customHeight="1">
-      <c r="I252" s="16" t="n"/>
+      <c r="I252" s="14" t="n"/>
     </row>
     <row r="253" ht="18" customHeight="1">
-      <c r="I253" s="16" t="n"/>
+      <c r="I253" s="14" t="n"/>
     </row>
     <row r="254" ht="18" customHeight="1">
-      <c r="I254" s="16" t="n"/>
+      <c r="I254" s="14" t="n"/>
     </row>
     <row r="255" ht="18" customHeight="1">
-      <c r="I255" s="16" t="n"/>
+      <c r="I255" s="14" t="n"/>
     </row>
     <row r="256" ht="18" customHeight="1">
-      <c r="I256" s="16" t="n"/>
+      <c r="I256" s="14" t="n"/>
     </row>
     <row r="257" ht="18" customHeight="1">
-      <c r="I257" s="16" t="n"/>
+      <c r="I257" s="14" t="n"/>
     </row>
     <row r="258" ht="18" customHeight="1">
-      <c r="I258" s="16" t="n"/>
+      <c r="I258" s="14" t="n"/>
     </row>
     <row r="259" ht="18" customHeight="1">
-      <c r="I259" s="16" t="n"/>
+      <c r="I259" s="14" t="n"/>
     </row>
     <row r="260" ht="18" customHeight="1">
-      <c r="I260" s="16" t="n"/>
+      <c r="I260" s="14" t="n"/>
     </row>
     <row r="261" ht="18" customHeight="1">
-      <c r="I261" s="16" t="n"/>
+      <c r="I261" s="14" t="n"/>
     </row>
     <row r="262" ht="18" customHeight="1">
-      <c r="I262" s="16" t="n"/>
+      <c r="I262" s="14" t="n"/>
     </row>
     <row r="263" ht="18" customHeight="1">
-      <c r="I263" s="16" t="n"/>
+      <c r="I263" s="14" t="n"/>
     </row>
     <row r="264" ht="18" customHeight="1">
-      <c r="I264" s="16" t="n"/>
+      <c r="I264" s="14" t="n"/>
     </row>
     <row r="265" ht="18" customHeight="1">
-      <c r="I265" s="16" t="n"/>
+      <c r="I265" s="14" t="n"/>
     </row>
     <row r="266" ht="18" customHeight="1">
-      <c r="I266" s="16" t="n"/>
+      <c r="I266" s="14" t="n"/>
     </row>
     <row r="267" ht="18" customHeight="1">
-      <c r="I267" s="16" t="n"/>
+      <c r="I267" s="14" t="n"/>
     </row>
     <row r="268" ht="18" customHeight="1">
-      <c r="I268" s="16" t="n"/>
+      <c r="I268" s="14" t="n"/>
     </row>
     <row r="269" ht="18" customHeight="1">
-      <c r="I269" s="16" t="n"/>
+      <c r="I269" s="14" t="n"/>
     </row>
     <row r="270" ht="18" customHeight="1">
-      <c r="I270" s="16" t="n"/>
+      <c r="I270" s="14" t="n"/>
     </row>
     <row r="271" ht="18" customHeight="1">
-      <c r="I271" s="16" t="n"/>
+      <c r="I271" s="14" t="n"/>
     </row>
     <row r="272" ht="18" customHeight="1">
-      <c r="I272" s="16" t="n"/>
+      <c r="I272" s="14" t="n"/>
     </row>
     <row r="273" ht="18" customHeight="1">
-      <c r="I273" s="16" t="n"/>
+      <c r="I273" s="14" t="n"/>
     </row>
     <row r="274" ht="18" customHeight="1">
-      <c r="I274" s="16" t="n"/>
+      <c r="I274" s="14" t="n"/>
     </row>
     <row r="275" ht="18" customHeight="1">
-      <c r="I275" s="16" t="n"/>
+      <c r="I275" s="14" t="n"/>
     </row>
     <row r="276" ht="18" customHeight="1">
-      <c r="I276" s="16" t="n"/>
+      <c r="I276" s="14" t="n"/>
     </row>
     <row r="277" ht="18" customHeight="1">
-      <c r="I277" s="16" t="n"/>
+      <c r="I277" s="14" t="n"/>
     </row>
     <row r="278" ht="18" customHeight="1">
-      <c r="I278" s="16" t="n"/>
+      <c r="I278" s="14" t="n"/>
     </row>
     <row r="279" ht="18" customHeight="1">
-      <c r="I279" s="16" t="n"/>
+      <c r="I279" s="14" t="n"/>
     </row>
     <row r="280" ht="18" customHeight="1">
-      <c r="I280" s="16" t="n"/>
+      <c r="I280" s="14" t="n"/>
     </row>
     <row r="281" ht="18" customHeight="1">
-      <c r="I281" s="16" t="n"/>
+      <c r="I281" s="14" t="n"/>
     </row>
     <row r="282" ht="18" customHeight="1">
-      <c r="I282" s="16" t="n"/>
+      <c r="I282" s="14" t="n"/>
     </row>
     <row r="283" ht="18" customHeight="1">
-      <c r="I283" s="16" t="n"/>
+      <c r="I283" s="14" t="n"/>
     </row>
     <row r="284" ht="18" customHeight="1">
-      <c r="I284" s="16" t="n"/>
+      <c r="I284" s="14" t="n"/>
     </row>
     <row r="285" ht="18" customHeight="1">
-      <c r="I285" s="16" t="n"/>
+      <c r="I285" s="14" t="n"/>
     </row>
     <row r="286" ht="18" customHeight="1">
-      <c r="I286" s="16" t="n"/>
+      <c r="I286" s="14" t="n"/>
     </row>
     <row r="287" ht="18" customHeight="1">
-      <c r="I287" s="16" t="n"/>
+      <c r="I287" s="14" t="n"/>
     </row>
     <row r="288" ht="18" customHeight="1">
-      <c r="I288" s="16" t="n"/>
+      <c r="I288" s="14" t="n"/>
     </row>
     <row r="289" ht="18" customHeight="1">
-      <c r="I289" s="16" t="n"/>
+      <c r="I289" s="14" t="n"/>
     </row>
     <row r="290" ht="18" customHeight="1">
-      <c r="I290" s="16" t="n"/>
+      <c r="I290" s="14" t="n"/>
     </row>
     <row r="291" ht="18" customHeight="1">
-      <c r="I291" s="16" t="n"/>
+      <c r="I291" s="14" t="n"/>
     </row>
     <row r="292" ht="18" customHeight="1">
-      <c r="I292" s="16" t="n"/>
+      <c r="I292" s="14" t="n"/>
     </row>
     <row r="293" ht="18" customHeight="1">
-      <c r="I293" s="16" t="n"/>
+      <c r="I293" s="14" t="n"/>
     </row>
     <row r="294" ht="18" customHeight="1">
-      <c r="I294" s="16" t="n"/>
+      <c r="I294" s="14" t="n"/>
     </row>
     <row r="295" ht="18" customHeight="1">
-      <c r="I295" s="16" t="n"/>
+      <c r="I295" s="14" t="n"/>
     </row>
     <row r="296" ht="18" customHeight="1">
-      <c r="I296" s="16" t="n"/>
+      <c r="I296" s="14" t="n"/>
     </row>
     <row r="297" ht="18" customHeight="1">
-      <c r="I297" s="16" t="n"/>
+      <c r="I297" s="14" t="n"/>
     </row>
     <row r="298" ht="18" customHeight="1">
-      <c r="I298" s="16" t="n"/>
+      <c r="I298" s="14" t="n"/>
     </row>
     <row r="299" ht="18" customHeight="1">
-      <c r="I299" s="16" t="n"/>
+      <c r="I299" s="14" t="n"/>
     </row>
     <row r="300" ht="18" customHeight="1">
-      <c r="I300" s="16" t="n"/>
+      <c r="I300" s="14" t="n"/>
     </row>
     <row r="301" ht="18" customHeight="1">
-      <c r="I301" s="16" t="n"/>
+      <c r="I301" s="14" t="n"/>
     </row>
     <row r="302" ht="18" customHeight="1">
-      <c r="I302" s="16" t="n"/>
+      <c r="I302" s="14" t="n"/>
     </row>
     <row r="303" ht="18" customHeight="1">
-      <c r="I303" s="16" t="n"/>
+      <c r="I303" s="14" t="n"/>
     </row>
     <row r="304" ht="18" customHeight="1">
-      <c r="I304" s="16" t="n"/>
+      <c r="I304" s="14" t="n"/>
     </row>
     <row r="305" ht="18" customHeight="1">
-      <c r="I305" s="16" t="n"/>
+      <c r="I305" s="14" t="n"/>
     </row>
     <row r="306" ht="18" customHeight="1">
-      <c r="I306" s="16" t="n"/>
+      <c r="I306" s="14" t="n"/>
     </row>
     <row r="307" ht="18" customHeight="1">
-      <c r="I307" s="16" t="n"/>
+      <c r="I307" s="14" t="n"/>
     </row>
     <row r="308" ht="18" customHeight="1">
-      <c r="I308" s="16" t="n"/>
+      <c r="I308" s="14" t="n"/>
     </row>
     <row r="309" ht="18" customHeight="1">
-      <c r="I309" s="16" t="n"/>
+      <c r="I309" s="14" t="n"/>
     </row>
     <row r="310" ht="18" customHeight="1">
-      <c r="I310" s="16" t="n"/>
+      <c r="I310" s="14" t="n"/>
     </row>
     <row r="311" ht="18" customHeight="1">
-      <c r="I311" s="16" t="n"/>
+      <c r="I311" s="14" t="n"/>
     </row>
     <row r="312" ht="18" customHeight="1">
-      <c r="I312" s="16" t="n"/>
+      <c r="I312" s="14" t="n"/>
     </row>
     <row r="313" ht="18" customHeight="1">
-      <c r="I313" s="16" t="n"/>
+      <c r="I313" s="14" t="n"/>
     </row>
     <row r="314" ht="18" customHeight="1">
-      <c r="I314" s="16" t="n"/>
+      <c r="I314" s="14" t="n"/>
     </row>
     <row r="315" ht="18" customHeight="1">
-      <c r="I315" s="16" t="n"/>
+      <c r="I315" s="14" t="n"/>
     </row>
     <row r="316" ht="18" customHeight="1">
-      <c r="I316" s="16" t="n"/>
+      <c r="I316" s="14" t="n"/>
     </row>
     <row r="317" ht="18" customHeight="1">
-      <c r="I317" s="16" t="n"/>
+      <c r="I317" s="14" t="n"/>
     </row>
     <row r="318" ht="18" customHeight="1">
-      <c r="I318" s="16" t="n"/>
+      <c r="I318" s="14" t="n"/>
     </row>
     <row r="319" ht="18" customHeight="1">
-      <c r="I319" s="16" t="n"/>
+      <c r="I319" s="14" t="n"/>
     </row>
     <row r="320" ht="18" customHeight="1">
-      <c r="I320" s="16" t="n"/>
+      <c r="I320" s="14" t="n"/>
     </row>
     <row r="321" ht="18" customHeight="1">
-      <c r="I321" s="16" t="n"/>
+      <c r="I321" s="14" t="n"/>
     </row>
     <row r="322" ht="18" customHeight="1">
-      <c r="I322" s="16" t="n"/>
+      <c r="I322" s="14" t="n"/>
     </row>
     <row r="323" ht="18" customHeight="1">
-      <c r="I323" s="16" t="n"/>
+      <c r="I323" s="14" t="n"/>
     </row>
     <row r="324" ht="18" customHeight="1">
-      <c r="I324" s="16" t="n"/>
+      <c r="I324" s="14" t="n"/>
     </row>
     <row r="325" ht="18" customHeight="1">
-      <c r="I325" s="16" t="n"/>
+      <c r="I325" s="14" t="n"/>
     </row>
     <row r="326" ht="18" customHeight="1">
-      <c r="I326" s="16" t="n"/>
+      <c r="I326" s="14" t="n"/>
     </row>
     <row r="327" ht="18" customHeight="1">
-      <c r="I327" s="16" t="n"/>
+      <c r="I327" s="14" t="n"/>
     </row>
     <row r="328" ht="18" customHeight="1">
-      <c r="I328" s="16" t="n"/>
+      <c r="I328" s="14" t="n"/>
     </row>
     <row r="329" ht="18" customHeight="1">
-      <c r="I329" s="16" t="n"/>
+      <c r="I329" s="14" t="n"/>
     </row>
     <row r="330" ht="18" customHeight="1">
-      <c r="I330" s="16" t="n"/>
+      <c r="I330" s="14" t="n"/>
     </row>
     <row r="331" ht="18" customHeight="1">
-      <c r="I331" s="16" t="n"/>
+      <c r="I331" s="14" t="n"/>
     </row>
     <row r="332" ht="18" customHeight="1">
-      <c r="I332" s="16" t="n"/>
+      <c r="I332" s="14" t="n"/>
     </row>
     <row r="333" ht="18" customHeight="1">
-      <c r="I333" s="16" t="n"/>
+      <c r="I333" s="14" t="n"/>
     </row>
     <row r="334" ht="18" customHeight="1">
-      <c r="I334" s="16" t="n"/>
+      <c r="I334" s="14" t="n"/>
     </row>
     <row r="335" ht="18" customHeight="1">
-      <c r="I335" s="16" t="n"/>
+      <c r="I335" s="14" t="n"/>
     </row>
     <row r="336" ht="18" customHeight="1">
-      <c r="I336" s="16" t="n"/>
+      <c r="I336" s="14" t="n"/>
     </row>
     <row r="337" ht="18" customHeight="1">
-      <c r="I337" s="16" t="n"/>
+      <c r="I337" s="14" t="n"/>
     </row>
     <row r="338" ht="18" customHeight="1">
-      <c r="I338" s="16" t="n"/>
+      <c r="I338" s="14" t="n"/>
     </row>
     <row r="339" ht="18" customHeight="1">
-      <c r="I339" s="16" t="n"/>
+      <c r="I339" s="14" t="n"/>
     </row>
     <row r="340" ht="18" customHeight="1">
-      <c r="I340" s="16" t="n"/>
+      <c r="I340" s="14" t="n"/>
     </row>
     <row r="341" ht="18" customHeight="1">
-      <c r="I341" s="16" t="n"/>
+      <c r="I341" s="14" t="n"/>
     </row>
     <row r="342" ht="18" customHeight="1">
-      <c r="I342" s="16" t="n"/>
+      <c r="I342" s="14" t="n"/>
     </row>
     <row r="343" ht="18" customHeight="1">
-      <c r="I343" s="16" t="n"/>
+      <c r="I343" s="14" t="n"/>
     </row>
     <row r="344" ht="18" customHeight="1">
-      <c r="I344" s="16" t="n"/>
+      <c r="I344" s="14" t="n"/>
     </row>
     <row r="345" ht="18" customHeight="1">
-      <c r="I345" s="16" t="n"/>
+      <c r="I345" s="14" t="n"/>
     </row>
     <row r="346" ht="18" customHeight="1">
-      <c r="I346" s="16" t="n"/>
+      <c r="I346" s="14" t="n"/>
     </row>
     <row r="347" ht="18" customHeight="1">
-      <c r="I347" s="16" t="n"/>
+      <c r="I347" s="14" t="n"/>
     </row>
     <row r="348" ht="18" customHeight="1">
-      <c r="I348" s="16" t="n"/>
+      <c r="I348" s="14" t="n"/>
     </row>
     <row r="349" ht="18" customHeight="1">
-      <c r="I349" s="16" t="n"/>
+      <c r="I349" s="14" t="n"/>
     </row>
     <row r="350" ht="18" customHeight="1">
-      <c r="I350" s="16" t="n"/>
+      <c r="I350" s="14" t="n"/>
     </row>
     <row r="351" ht="18" customHeight="1">
-      <c r="I351" s="16" t="n"/>
+      <c r="I351" s="14" t="n"/>
     </row>
     <row r="352" ht="18" customHeight="1">
-      <c r="I352" s="16" t="n"/>
+      <c r="I352" s="14" t="n"/>
     </row>
     <row r="353" ht="18" customHeight="1">
-      <c r="I353" s="16" t="n"/>
+      <c r="I353" s="14" t="n"/>
     </row>
     <row r="354" ht="18" customHeight="1">
-      <c r="I354" s="16" t="n"/>
+      <c r="I354" s="14" t="n"/>
     </row>
     <row r="355" ht="18" customHeight="1">
-      <c r="I355" s="16" t="n"/>
+      <c r="I355" s="14" t="n"/>
     </row>
     <row r="356" ht="18" customHeight="1">
-      <c r="I356" s="16" t="n"/>
+      <c r="I356" s="14" t="n"/>
     </row>
     <row r="357" ht="18" customHeight="1">
-      <c r="I357" s="16" t="n"/>
+      <c r="I357" s="14" t="n"/>
     </row>
     <row r="358" ht="18" customHeight="1">
-      <c r="I358" s="16" t="n"/>
+      <c r="I358" s="14" t="n"/>
     </row>
     <row r="359" ht="18" customHeight="1">
-      <c r="I359" s="16" t="n"/>
+      <c r="I359" s="14" t="n"/>
     </row>
     <row r="360" ht="18" customHeight="1">
-      <c r="I360" s="16" t="n"/>
+      <c r="I360" s="14" t="n"/>
     </row>
     <row r="361" ht="18" customHeight="1">
-      <c r="I361" s="16" t="n"/>
+      <c r="I361" s="14" t="n"/>
     </row>
     <row r="362" ht="18" customHeight="1">
-      <c r="I362" s="16" t="n"/>
+      <c r="I362" s="14" t="n"/>
     </row>
     <row r="363" ht="18" customHeight="1">
-      <c r="I363" s="16" t="n"/>
+      <c r="I363" s="14" t="n"/>
     </row>
     <row r="364" ht="18" customHeight="1">
-      <c r="I364" s="16" t="n"/>
+      <c r="I364" s="14" t="n"/>
     </row>
     <row r="365" ht="18" customHeight="1">
-      <c r="I365" s="16" t="n"/>
+      <c r="I365" s="14" t="n"/>
     </row>
     <row r="366" ht="18" customHeight="1">
-      <c r="I366" s="16" t="n"/>
+      <c r="I366" s="14" t="n"/>
     </row>
     <row r="367" ht="18" customHeight="1">
-      <c r="I367" s="16" t="n"/>
+      <c r="I367" s="14" t="n"/>
     </row>
     <row r="368" ht="18" customHeight="1">
-      <c r="I368" s="16" t="n"/>
+      <c r="I368" s="14" t="n"/>
     </row>
     <row r="369" ht="18" customHeight="1">
-      <c r="I369" s="16" t="n"/>
+      <c r="I369" s="14" t="n"/>
     </row>
     <row r="370" ht="18" customHeight="1">
-      <c r="I370" s="16" t="n"/>
+      <c r="I370" s="14" t="n"/>
     </row>
     <row r="371" ht="18" customHeight="1">
-      <c r="I371" s="16" t="n"/>
+      <c r="I371" s="14" t="n"/>
     </row>
     <row r="372" ht="18" customHeight="1">
-      <c r="I372" s="16" t="n"/>
+      <c r="I372" s="14" t="n"/>
     </row>
     <row r="373" ht="18" customHeight="1">
-      <c r="I373" s="16" t="n"/>
+      <c r="I373" s="14" t="n"/>
     </row>
     <row r="374" ht="18" customHeight="1">
-      <c r="I374" s="16" t="n"/>
+      <c r="I374" s="14" t="n"/>
     </row>
     <row r="375" ht="18" customHeight="1">
-      <c r="I375" s="16" t="n"/>
+      <c r="I375" s="14" t="n"/>
     </row>
     <row r="376" ht="18" customHeight="1">
-      <c r="I376" s="16" t="n"/>
+      <c r="I376" s="14" t="n"/>
     </row>
     <row r="377" ht="18" customHeight="1">
-      <c r="I377" s="16" t="n"/>
+      <c r="I377" s="14" t="n"/>
     </row>
     <row r="378" ht="18" customHeight="1">
-      <c r="I378" s="16" t="n"/>
+      <c r="I378" s="14" t="n"/>
     </row>
     <row r="379" ht="18" customHeight="1">
-      <c r="I379" s="16" t="n"/>
+      <c r="I379" s="14" t="n"/>
     </row>
     <row r="380" ht="18" customHeight="1">
-      <c r="I380" s="16" t="n"/>
+      <c r="I380" s="14" t="n"/>
     </row>
     <row r="381" ht="18" customHeight="1">
-      <c r="I381" s="16" t="n"/>
+      <c r="I381" s="14" t="n"/>
     </row>
     <row r="382" ht="18" customHeight="1">
-      <c r="I382" s="16" t="n"/>
+      <c r="I382" s="14" t="n"/>
     </row>
     <row r="383" ht="18" customHeight="1">
-      <c r="I383" s="16" t="n"/>
+      <c r="I383" s="14" t="n"/>
     </row>
     <row r="384" ht="18" customHeight="1">
-      <c r="I384" s="16" t="n"/>
+      <c r="I384" s="14" t="n"/>
     </row>
     <row r="385" ht="18" customHeight="1">
-      <c r="I385" s="16" t="n"/>
+      <c r="I385" s="14" t="n"/>
     </row>
     <row r="386" ht="18" customHeight="1">
-      <c r="I386" s="16" t="n"/>
+      <c r="I386" s="14" t="n"/>
     </row>
     <row r="387" ht="18" customHeight="1">
-      <c r="I387" s="16" t="n"/>
+      <c r="I387" s="14" t="n"/>
     </row>
     <row r="388" ht="18" customHeight="1">
-      <c r="I388" s="16" t="n"/>
+      <c r="I388" s="14" t="n"/>
     </row>
     <row r="389" ht="18" customHeight="1">
-      <c r="I389" s="16" t="n"/>
+      <c r="I389" s="14" t="n"/>
     </row>
     <row r="390" ht="18" customHeight="1">
-      <c r="I390" s="16" t="n"/>
+      <c r="I390" s="14" t="n"/>
     </row>
     <row r="391" ht="18" customHeight="1">
-      <c r="I391" s="16" t="n"/>
+      <c r="I391" s="14" t="n"/>
     </row>
     <row r="392" ht="18" customHeight="1">
-      <c r="I392" s="16" t="n"/>
+      <c r="I392" s="14" t="n"/>
     </row>
     <row r="393" ht="18" customHeight="1">
-      <c r="I393" s="16" t="n"/>
+      <c r="I393" s="14" t="n"/>
     </row>
     <row r="394" ht="18" customHeight="1">
-      <c r="I394" s="16" t="n"/>
+      <c r="I394" s="14" t="n"/>
     </row>
     <row r="395" ht="18" customHeight="1">
-      <c r="I395" s="16" t="n"/>
+      <c r="I395" s="14" t="n"/>
     </row>
     <row r="396" ht="18" customHeight="1">
-      <c r="I396" s="16" t="n"/>
+      <c r="I396" s="14" t="n"/>
     </row>
     <row r="397" ht="18" customHeight="1">
-      <c r="I397" s="16" t="n"/>
+      <c r="I397" s="14" t="n"/>
     </row>
     <row r="398" ht="18" customHeight="1">
-      <c r="I398" s="16" t="n"/>
+      <c r="I398" s="14" t="n"/>
     </row>
     <row r="399" ht="18" customHeight="1">
-      <c r="I399" s="16" t="n"/>
+      <c r="I399" s="14" t="n"/>
     </row>
     <row r="400" ht="18" customHeight="1">
-      <c r="I400" s="16" t="n"/>
+      <c r="I400" s="14" t="n"/>
     </row>
     <row r="401" ht="18" customHeight="1">
-      <c r="I401" s="16" t="n"/>
+      <c r="I401" s="14" t="n"/>
     </row>
     <row r="402" ht="18" customHeight="1">
-      <c r="I402" s="16" t="n"/>
+      <c r="I402" s="14" t="n"/>
     </row>
     <row r="403" ht="18" customHeight="1">
-      <c r="I403" s="16" t="n"/>
+      <c r="I403" s="14" t="n"/>
     </row>
     <row r="404" ht="18" customHeight="1">
-      <c r="I404" s="16" t="n"/>
+      <c r="I404" s="14" t="n"/>
     </row>
     <row r="405" ht="18" customHeight="1">
-      <c r="I405" s="16" t="n"/>
+      <c r="I405" s="14" t="n"/>
     </row>
     <row r="406" ht="18" customHeight="1">
-      <c r="I406" s="16" t="n"/>
+      <c r="I406" s="14" t="n"/>
     </row>
     <row r="407" ht="18" customHeight="1">
-      <c r="I407" s="16" t="n"/>
+      <c r="I407" s="14" t="n"/>
     </row>
     <row r="408" ht="18" customHeight="1">
-      <c r="I408" s="16" t="n"/>
+      <c r="I408" s="14" t="n"/>
     </row>
     <row r="409" ht="18" customHeight="1">
-      <c r="I409" s="16" t="n"/>
+      <c r="I409" s="14" t="n"/>
     </row>
     <row r="410" ht="18" customHeight="1">
-      <c r="I410" s="16" t="n"/>
+      <c r="I410" s="14" t="n"/>
     </row>
     <row r="411" ht="18" customHeight="1">
-      <c r="I411" s="16" t="n"/>
+      <c r="I411" s="14" t="n"/>
     </row>
     <row r="412" ht="18" customHeight="1">
-      <c r="I412" s="16" t="n"/>
+      <c r="I412" s="14" t="n"/>
     </row>
     <row r="413" ht="18" customHeight="1">
-      <c r="I413" s="16" t="n"/>
+      <c r="I413" s="14" t="n"/>
     </row>
     <row r="414" ht="18" customHeight="1">
-      <c r="I414" s="16" t="n"/>
+      <c r="I414" s="14" t="n"/>
     </row>
     <row r="415" ht="18" customHeight="1">
-      <c r="I415" s="16" t="n"/>
+      <c r="I415" s="14" t="n"/>
     </row>
     <row r="416" ht="18" customHeight="1">
-      <c r="I416" s="16" t="n"/>
+      <c r="I416" s="14" t="n"/>
     </row>
     <row r="417" ht="18" customHeight="1">
-      <c r="I417" s="16" t="n"/>
+      <c r="I417" s="14" t="n"/>
     </row>
     <row r="418" ht="18" customHeight="1">
-      <c r="I418" s="16" t="n"/>
+      <c r="I418" s="14" t="n"/>
     </row>
     <row r="419" ht="18" customHeight="1">
-      <c r="I419" s="16" t="n"/>
+      <c r="I419" s="14" t="n"/>
     </row>
     <row r="420" ht="18" customHeight="1">
-      <c r="I420" s="16" t="n"/>
+      <c r="I420" s="14" t="n"/>
     </row>
     <row r="421" ht="18" customHeight="1">
-      <c r="I421" s="16" t="n"/>
+      <c r="I421" s="14" t="n"/>
     </row>
     <row r="422" ht="18" customHeight="1">
-      <c r="I422" s="16" t="n"/>
+      <c r="I422" s="14" t="n"/>
     </row>
     <row r="423" ht="18" customHeight="1">
-      <c r="I423" s="16" t="n"/>
+      <c r="I423" s="14" t="n"/>
     </row>
     <row r="424" ht="18" customHeight="1">
-      <c r="I424" s="16" t="n"/>
+      <c r="I424" s="14" t="n"/>
     </row>
     <row r="425" ht="18" customHeight="1">
-      <c r="I425" s="16" t="n"/>
+      <c r="I425" s="14" t="n"/>
     </row>
     <row r="426" ht="18" customHeight="1">
-      <c r="I426" s="16" t="n"/>
+      <c r="I426" s="14" t="n"/>
     </row>
     <row r="427" ht="18" customHeight="1">
-      <c r="I427" s="16" t="n"/>
+      <c r="I427" s="14" t="n"/>
     </row>
     <row r="428" ht="18" customHeight="1">
-      <c r="I428" s="16" t="n"/>
+      <c r="I428" s="14" t="n"/>
     </row>
     <row r="429" ht="18" customHeight="1">
-      <c r="I429" s="16" t="n"/>
+      <c r="I429" s="14" t="n"/>
     </row>
     <row r="430" ht="18" customHeight="1">
-      <c r="I430" s="16" t="n"/>
+      <c r="I430" s="14" t="n"/>
     </row>
     <row r="431" ht="18" customHeight="1">
-      <c r="I431" s="16" t="n"/>
+      <c r="I431" s="14" t="n"/>
     </row>
     <row r="432" ht="18" customHeight="1">
-      <c r="I432" s="16" t="n"/>
+      <c r="I432" s="14" t="n"/>
     </row>
     <row r="433" ht="18" customHeight="1">
-      <c r="I433" s="16" t="n"/>
+      <c r="I433" s="14" t="n"/>
     </row>
     <row r="434" ht="18" customHeight="1">
-      <c r="I434" s="16" t="n"/>
+      <c r="I434" s="14" t="n"/>
     </row>
     <row r="435" ht="18" customHeight="1">
-      <c r="I435" s="16" t="n"/>
+      <c r="I435" s="14" t="n"/>
     </row>
     <row r="436" ht="18" customHeight="1">
-      <c r="I436" s="16" t="n"/>
+      <c r="I436" s="14" t="n"/>
     </row>
     <row r="437" ht="18" customHeight="1">
-      <c r="I437" s="16" t="n"/>
+      <c r="I437" s="14" t="n"/>
     </row>
     <row r="438" ht="18" customHeight="1">
-      <c r="I438" s="16" t="n"/>
+      <c r="I438" s="14" t="n"/>
     </row>
     <row r="439" ht="18" customHeight="1">
-      <c r="I439" s="16" t="n"/>
+      <c r="I439" s="14" t="n"/>
     </row>
     <row r="440" ht="18" customHeight="1">
-      <c r="I440" s="16" t="n"/>
+      <c r="I440" s="14" t="n"/>
     </row>
     <row r="441" ht="18" customHeight="1">
-      <c r="I441" s="16" t="n"/>
+      <c r="I441" s="14" t="n"/>
     </row>
     <row r="442" ht="18" customHeight="1">
-      <c r="I442" s="16" t="n"/>
+      <c r="I442" s="14" t="n"/>
     </row>
     <row r="443" ht="18" customHeight="1">
-      <c r="I443" s="16" t="n"/>
+      <c r="I443" s="14" t="n"/>
     </row>
     <row r="444" ht="18" customHeight="1">
-      <c r="I444" s="16" t="n"/>
+      <c r="I444" s="14" t="n"/>
     </row>
     <row r="445" ht="18" customHeight="1">
-      <c r="I445" s="16" t="n"/>
+      <c r="I445" s="14" t="n"/>
     </row>
     <row r="446" ht="18" customHeight="1">
-      <c r="I446" s="16" t="n"/>
+      <c r="I446" s="14" t="n"/>
     </row>
     <row r="447" ht="18" customHeight="1">
-      <c r="I447" s="16" t="n"/>
+      <c r="I447" s="14" t="n"/>
     </row>
     <row r="448" ht="18" customHeight="1">
-      <c r="I448" s="16" t="n"/>
+      <c r="I448" s="14" t="n"/>
     </row>
     <row r="449" ht="18" customHeight="1">
-      <c r="I449" s="16" t="n"/>
+      <c r="I449" s="14" t="n"/>
     </row>
     <row r="450" ht="18" customHeight="1">
-      <c r="I450" s="16" t="n"/>
+      <c r="I450" s="14" t="n"/>
     </row>
     <row r="451" ht="18" customHeight="1">
-      <c r="I451" s="16" t="n"/>
+      <c r="I451" s="14" t="n"/>
     </row>
     <row r="452" ht="18" customHeight="1">
-      <c r="I452" s="16" t="n"/>
+      <c r="I452" s="14" t="n"/>
     </row>
     <row r="453" ht="18" customHeight="1">
-      <c r="I453" s="16" t="n"/>
+      <c r="I453" s="14" t="n"/>
     </row>
     <row r="454" ht="18" customHeight="1">
-      <c r="I454" s="16" t="n"/>
+      <c r="I454" s="14" t="n"/>
     </row>
     <row r="455" ht="18" customHeight="1">
-      <c r="I455" s="16" t="n"/>
+      <c r="I455" s="14" t="n"/>
     </row>
     <row r="456" ht="18" customHeight="1">
-      <c r="I456" s="16" t="n"/>
+      <c r="I456" s="14" t="n"/>
     </row>
     <row r="457" ht="18" customHeight="1">
-      <c r="I457" s="16" t="n"/>
+      <c r="I457" s="14" t="n"/>
     </row>
     <row r="458" ht="18" customHeight="1">
-      <c r="I458" s="16" t="n"/>
+      <c r="I458" s="14" t="n"/>
     </row>
     <row r="459" ht="18" customHeight="1">
-      <c r="I459" s="16" t="n"/>
+      <c r="I459" s="14" t="n"/>
     </row>
     <row r="460" ht="18" customHeight="1">
-      <c r="I460" s="16" t="n"/>
+      <c r="I460" s="14" t="n"/>
     </row>
     <row r="461" ht="18" customHeight="1">
-      <c r="I461" s="16" t="n"/>
+      <c r="I461" s="14" t="n"/>
     </row>
     <row r="462" ht="18" customHeight="1">
-      <c r="I462" s="16" t="n"/>
+      <c r="I462" s="14" t="n"/>
     </row>
     <row r="463" ht="18" customHeight="1">
-      <c r="I463" s="16" t="n"/>
+      <c r="I463" s="14" t="n"/>
     </row>
     <row r="464" ht="18" customHeight="1">
-      <c r="I464" s="16" t="n"/>
+      <c r="I464" s="14" t="n"/>
     </row>
     <row r="465" ht="18" customHeight="1">
-      <c r="I465" s="16" t="n"/>
+      <c r="I465" s="14" t="n"/>
     </row>
     <row r="466" ht="18" customHeight="1">
-      <c r="I466" s="16" t="n"/>
+      <c r="I466" s="14" t="n"/>
     </row>
     <row r="467" ht="18" customHeight="1">
-      <c r="I467" s="16" t="n"/>
+      <c r="I467" s="14" t="n"/>
     </row>
     <row r="468" ht="18" customHeight="1">
-      <c r="I468" s="16" t="n"/>
+      <c r="I468" s="14" t="n"/>
     </row>
     <row r="469" ht="18" customHeight="1">
-      <c r="I469" s="16" t="n"/>
+      <c r="I469" s="14" t="n"/>
     </row>
     <row r="470" ht="18" customHeight="1">
-      <c r="I470" s="16" t="n"/>
+      <c r="I470" s="14" t="n"/>
     </row>
     <row r="471" ht="18" customHeight="1">
-      <c r="I471" s="16" t="n"/>
+      <c r="I471" s="14" t="n"/>
     </row>
     <row r="472" ht="18" customHeight="1">
-      <c r="I472" s="16" t="n"/>
+      <c r="I472" s="14" t="n"/>
     </row>
     <row r="473" ht="18" customHeight="1">
-      <c r="I473" s="16" t="n"/>
+      <c r="I473" s="14" t="n"/>
     </row>
     <row r="474" ht="18" customHeight="1">
-      <c r="I474" s="16" t="n"/>
+      <c r="I474" s="14" t="n"/>
     </row>
     <row r="475" ht="18" customHeight="1">
-      <c r="I475" s="16" t="n"/>
+      <c r="I475" s="14" t="n"/>
     </row>
     <row r="476" ht="18" customHeight="1">
-      <c r="I476" s="16" t="n"/>
+      <c r="I476" s="14" t="n"/>
     </row>
     <row r="477" ht="18" customHeight="1">
-      <c r="I477" s="16" t="n"/>
+      <c r="I477" s="14" t="n"/>
     </row>
     <row r="478" ht="18" customHeight="1">
-      <c r="I478" s="16" t="n"/>
+      <c r="I478" s="14" t="n"/>
     </row>
     <row r="479" ht="18" customHeight="1">
-      <c r="I479" s="16" t="n"/>
+      <c r="I479" s="14" t="n"/>
     </row>
     <row r="480" ht="18" customHeight="1">
-      <c r="I480" s="16" t="n"/>
+      <c r="I480" s="14" t="n"/>
     </row>
     <row r="481" ht="18" customHeight="1">
-      <c r="I481" s="16" t="n"/>
+      <c r="I481" s="14" t="n"/>
     </row>
     <row r="482" ht="18" customHeight="1">
-      <c r="I482" s="16" t="n"/>
+      <c r="I482" s="14" t="n"/>
     </row>
     <row r="483" ht="18" customHeight="1">
-      <c r="I483" s="16" t="n"/>
+      <c r="I483" s="14" t="n"/>
     </row>
     <row r="484" ht="18" customHeight="1">
-      <c r="I484" s="16" t="n"/>
+      <c r="I484" s="14" t="n"/>
     </row>
     <row r="485" ht="18" customHeight="1">
-      <c r="I485" s="16" t="n"/>
+      <c r="I485" s="14" t="n"/>
     </row>
     <row r="486" ht="18" customHeight="1">
-      <c r="I486" s="16" t="n"/>
+      <c r="I486" s="14" t="n"/>
     </row>
     <row r="487" ht="18" customHeight="1">
-      <c r="I487" s="16" t="n"/>
+      <c r="I487" s="14" t="n"/>
     </row>
     <row r="488" ht="18" customHeight="1">
-      <c r="I488" s="16" t="n"/>
+      <c r="I488" s="14" t="n"/>
     </row>
     <row r="489" ht="18" customHeight="1">
-      <c r="I489" s="16" t="n"/>
+      <c r="I489" s="14" t="n"/>
     </row>
     <row r="490" ht="18" customHeight="1">
-      <c r="I490" s="16" t="n"/>
+      <c r="I490" s="14" t="n"/>
     </row>
     <row r="491" ht="18" customHeight="1">
-      <c r="I491" s="16" t="n"/>
+      <c r="I491" s="14" t="n"/>
     </row>
     <row r="492" ht="18" customHeight="1">
-      <c r="I492" s="16" t="n"/>
+      <c r="I492" s="14" t="n"/>
     </row>
     <row r="493" ht="18" customHeight="1">
-      <c r="I493" s="16" t="n"/>
+      <c r="I493" s="14" t="n"/>
     </row>
     <row r="494" ht="18" customHeight="1">
-      <c r="I494" s="16" t="n"/>
+      <c r="I494" s="14" t="n"/>
     </row>
     <row r="495" ht="18" customHeight="1">
-      <c r="I495" s="16" t="n"/>
+      <c r="I495" s="14" t="n"/>
     </row>
     <row r="496" ht="18" customHeight="1">
-      <c r="I496" s="16" t="n"/>
+      <c r="I496" s="14" t="n"/>
     </row>
     <row r="497" ht="18" customHeight="1">
-      <c r="I497" s="16" t="n"/>
+      <c r="I497" s="14" t="n"/>
     </row>
     <row r="498" ht="18" customHeight="1">
-      <c r="I498" s="16" t="n"/>
+      <c r="I498" s="14" t="n"/>
     </row>
     <row r="499" ht="18" customHeight="1">
-      <c r="I499" s="16" t="n"/>
+      <c r="I499" s="14" t="n"/>
     </row>
     <row r="500" ht="18" customHeight="1">
-      <c r="I500" s="16" t="n"/>
+      <c r="I500" s="14" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2277,8 +2227,8 @@
     <mergeCell ref="E1:H1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="K4:K500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="CATEGORIA inválida" error="Valores: reclamo, compromiso, otros — o dejar vacío (pago normal)." type="list">
-      <formula1>"reclamo,compromiso,otros"</formula1>
+    <dataValidation sqref="K4:K500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="CATEGORIA inválida" error="Valores: reclamo, compromiso, exoneracion, otros — o dejar vacío (pago normal)." type="list">
+      <formula1>"reclamo,compromiso,exoneracion,otros"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2313,21 +2263,16 @@
           <t>¿Quién cobró?</t>
         </is>
       </c>
-      <c r="B1" s="12" t="n"/>
       <c r="C1" s="2" t="inlineStr">
         <is>
           <t>¿Dónde vive?</t>
         </is>
       </c>
-      <c r="D1" s="12" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
           <t>¿Cuánto y cuándo?</t>
         </is>
       </c>
-      <c r="F1" s="13" t="n"/>
-      <c r="G1" s="13" t="n"/>
-      <c r="H1" s="12" t="n"/>
       <c r="I1" s="4" t="inlineStr">
         <is>
           <t>¿Alguna nota?</t>
@@ -2338,1603 +2283,1604 @@
           <t>¿Qué tipo?</t>
         </is>
       </c>
-      <c r="K1" s="14" t="inlineStr">
+      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>¿Qué pasó?</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>COBRADOR</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>FECHA_REGISTRO</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>MZ</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>LT</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="E2" s="9" t="inlineStr">
         <is>
           <t>MONTO</t>
         </is>
       </c>
-      <c r="F2" s="8" t="inlineStr">
+      <c r="F2" s="9" t="inlineStr">
         <is>
           <t>MONTO_EFECTIVO</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="G2" s="9" t="inlineStr">
         <is>
           <t>MONTO_YAPE</t>
         </is>
       </c>
-      <c r="H2" s="8" t="inlineStr">
+      <c r="H2" s="9" t="inlineStr">
         <is>
           <t>FECHA</t>
         </is>
       </c>
-      <c r="I2" s="9" t="inlineStr">
+      <c r="I2" s="10" t="inlineStr">
         <is>
           <t>COMENTARIO</t>
         </is>
       </c>
-      <c r="J2" s="10" t="inlineStr">
+      <c r="J2" s="11" t="inlineStr">
         <is>
           <t>CONCEPTO</t>
         </is>
       </c>
-      <c r="K2" s="15" t="inlineStr">
+      <c r="K2" s="12" t="inlineStr">
         <is>
           <t>CATEGORIA</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>María García</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>8C</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>38.00</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>20.00</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>18.00</t>
         </is>
       </c>
-      <c r="H3" s="11" t="inlineStr">
+      <c r="H3" s="13" t="inlineStr">
         <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="I3" s="11" t="inlineStr"/>
-      <c r="J3" s="11" t="inlineStr"/>
+      <c r="I3" s="13" t="inlineStr"/>
+      <c r="J3" s="13" t="inlineStr"/>
+      <c r="K3" s="13" t="inlineStr"/>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="I4" s="16" t="n"/>
+      <c r="I4" s="14" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="I5" s="16" t="n"/>
+      <c r="I5" s="14" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="I6" s="16" t="n"/>
+      <c r="I6" s="14" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="I7" s="16" t="n"/>
+      <c r="I7" s="14" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="I8" s="16" t="n"/>
+      <c r="I8" s="14" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="I9" s="16" t="n"/>
+      <c r="I9" s="14" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="I10" s="16" t="n"/>
+      <c r="I10" s="14" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="I11" s="16" t="n"/>
+      <c r="I11" s="14" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="I12" s="16" t="n"/>
+      <c r="I12" s="14" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="I13" s="16" t="n"/>
+      <c r="I13" s="14" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="I14" s="16" t="n"/>
+      <c r="I14" s="14" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="I15" s="16" t="n"/>
+      <c r="I15" s="14" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="I16" s="16" t="n"/>
+      <c r="I16" s="14" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="I17" s="16" t="n"/>
+      <c r="I17" s="14" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="I18" s="16" t="n"/>
+      <c r="I18" s="14" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="I19" s="16" t="n"/>
+      <c r="I19" s="14" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="I20" s="16" t="n"/>
+      <c r="I20" s="14" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="I21" s="16" t="n"/>
+      <c r="I21" s="14" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="I22" s="16" t="n"/>
+      <c r="I22" s="14" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="I23" s="16" t="n"/>
+      <c r="I23" s="14" t="n"/>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="I24" s="16" t="n"/>
+      <c r="I24" s="14" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="I25" s="16" t="n"/>
+      <c r="I25" s="14" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="I26" s="16" t="n"/>
+      <c r="I26" s="14" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="I27" s="16" t="n"/>
+      <c r="I27" s="14" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="I28" s="16" t="n"/>
+      <c r="I28" s="14" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="I29" s="16" t="n"/>
+      <c r="I29" s="14" t="n"/>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="I30" s="16" t="n"/>
+      <c r="I30" s="14" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="I31" s="16" t="n"/>
+      <c r="I31" s="14" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="I32" s="16" t="n"/>
+      <c r="I32" s="14" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="I33" s="16" t="n"/>
+      <c r="I33" s="14" t="n"/>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="I34" s="16" t="n"/>
+      <c r="I34" s="14" t="n"/>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="I35" s="16" t="n"/>
+      <c r="I35" s="14" t="n"/>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="I36" s="16" t="n"/>
+      <c r="I36" s="14" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1">
-      <c r="I37" s="16" t="n"/>
+      <c r="I37" s="14" t="n"/>
     </row>
     <row r="38" ht="18" customHeight="1">
-      <c r="I38" s="16" t="n"/>
+      <c r="I38" s="14" t="n"/>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="I39" s="16" t="n"/>
+      <c r="I39" s="14" t="n"/>
     </row>
     <row r="40" ht="18" customHeight="1">
-      <c r="I40" s="16" t="n"/>
+      <c r="I40" s="14" t="n"/>
     </row>
     <row r="41" ht="18" customHeight="1">
-      <c r="I41" s="16" t="n"/>
+      <c r="I41" s="14" t="n"/>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="I42" s="16" t="n"/>
+      <c r="I42" s="14" t="n"/>
     </row>
     <row r="43" ht="18" customHeight="1">
-      <c r="I43" s="16" t="n"/>
+      <c r="I43" s="14" t="n"/>
     </row>
     <row r="44" ht="18" customHeight="1">
-      <c r="I44" s="16" t="n"/>
+      <c r="I44" s="14" t="n"/>
     </row>
     <row r="45" ht="18" customHeight="1">
-      <c r="I45" s="16" t="n"/>
+      <c r="I45" s="14" t="n"/>
     </row>
     <row r="46" ht="18" customHeight="1">
-      <c r="I46" s="16" t="n"/>
+      <c r="I46" s="14" t="n"/>
     </row>
     <row r="47" ht="18" customHeight="1">
-      <c r="I47" s="16" t="n"/>
+      <c r="I47" s="14" t="n"/>
     </row>
     <row r="48" ht="18" customHeight="1">
-      <c r="I48" s="16" t="n"/>
+      <c r="I48" s="14" t="n"/>
     </row>
     <row r="49" ht="18" customHeight="1">
-      <c r="I49" s="16" t="n"/>
+      <c r="I49" s="14" t="n"/>
     </row>
     <row r="50" ht="18" customHeight="1">
-      <c r="I50" s="16" t="n"/>
+      <c r="I50" s="14" t="n"/>
     </row>
     <row r="51" ht="18" customHeight="1">
-      <c r="I51" s="16" t="n"/>
+      <c r="I51" s="14" t="n"/>
     </row>
     <row r="52" ht="18" customHeight="1">
-      <c r="I52" s="16" t="n"/>
+      <c r="I52" s="14" t="n"/>
     </row>
     <row r="53" ht="18" customHeight="1">
-      <c r="I53" s="16" t="n"/>
+      <c r="I53" s="14" t="n"/>
     </row>
     <row r="54" ht="18" customHeight="1">
-      <c r="I54" s="16" t="n"/>
+      <c r="I54" s="14" t="n"/>
     </row>
     <row r="55" ht="18" customHeight="1">
-      <c r="I55" s="16" t="n"/>
+      <c r="I55" s="14" t="n"/>
     </row>
     <row r="56" ht="18" customHeight="1">
-      <c r="I56" s="16" t="n"/>
+      <c r="I56" s="14" t="n"/>
     </row>
     <row r="57" ht="18" customHeight="1">
-      <c r="I57" s="16" t="n"/>
+      <c r="I57" s="14" t="n"/>
     </row>
     <row r="58" ht="18" customHeight="1">
-      <c r="I58" s="16" t="n"/>
+      <c r="I58" s="14" t="n"/>
     </row>
     <row r="59" ht="18" customHeight="1">
-      <c r="I59" s="16" t="n"/>
+      <c r="I59" s="14" t="n"/>
     </row>
     <row r="60" ht="18" customHeight="1">
-      <c r="I60" s="16" t="n"/>
+      <c r="I60" s="14" t="n"/>
     </row>
     <row r="61" ht="18" customHeight="1">
-      <c r="I61" s="16" t="n"/>
+      <c r="I61" s="14" t="n"/>
     </row>
     <row r="62" ht="18" customHeight="1">
-      <c r="I62" s="16" t="n"/>
+      <c r="I62" s="14" t="n"/>
     </row>
     <row r="63" ht="18" customHeight="1">
-      <c r="I63" s="16" t="n"/>
+      <c r="I63" s="14" t="n"/>
     </row>
     <row r="64" ht="18" customHeight="1">
-      <c r="I64" s="16" t="n"/>
+      <c r="I64" s="14" t="n"/>
     </row>
     <row r="65" ht="18" customHeight="1">
-      <c r="I65" s="16" t="n"/>
+      <c r="I65" s="14" t="n"/>
     </row>
     <row r="66" ht="18" customHeight="1">
-      <c r="I66" s="16" t="n"/>
+      <c r="I66" s="14" t="n"/>
     </row>
     <row r="67" ht="18" customHeight="1">
-      <c r="I67" s="16" t="n"/>
+      <c r="I67" s="14" t="n"/>
     </row>
     <row r="68" ht="18" customHeight="1">
-      <c r="I68" s="16" t="n"/>
+      <c r="I68" s="14" t="n"/>
     </row>
     <row r="69" ht="18" customHeight="1">
-      <c r="I69" s="16" t="n"/>
+      <c r="I69" s="14" t="n"/>
     </row>
     <row r="70" ht="18" customHeight="1">
-      <c r="I70" s="16" t="n"/>
+      <c r="I70" s="14" t="n"/>
     </row>
     <row r="71" ht="18" customHeight="1">
-      <c r="I71" s="16" t="n"/>
+      <c r="I71" s="14" t="n"/>
     </row>
     <row r="72" ht="18" customHeight="1">
-      <c r="I72" s="16" t="n"/>
+      <c r="I72" s="14" t="n"/>
     </row>
     <row r="73" ht="18" customHeight="1">
-      <c r="I73" s="16" t="n"/>
+      <c r="I73" s="14" t="n"/>
     </row>
     <row r="74" ht="18" customHeight="1">
-      <c r="I74" s="16" t="n"/>
+      <c r="I74" s="14" t="n"/>
     </row>
     <row r="75" ht="18" customHeight="1">
-      <c r="I75" s="16" t="n"/>
+      <c r="I75" s="14" t="n"/>
     </row>
     <row r="76" ht="18" customHeight="1">
-      <c r="I76" s="16" t="n"/>
+      <c r="I76" s="14" t="n"/>
     </row>
     <row r="77" ht="18" customHeight="1">
-      <c r="I77" s="16" t="n"/>
+      <c r="I77" s="14" t="n"/>
     </row>
     <row r="78" ht="18" customHeight="1">
-      <c r="I78" s="16" t="n"/>
+      <c r="I78" s="14" t="n"/>
     </row>
     <row r="79" ht="18" customHeight="1">
-      <c r="I79" s="16" t="n"/>
+      <c r="I79" s="14" t="n"/>
     </row>
     <row r="80" ht="18" customHeight="1">
-      <c r="I80" s="16" t="n"/>
+      <c r="I80" s="14" t="n"/>
     </row>
     <row r="81" ht="18" customHeight="1">
-      <c r="I81" s="16" t="n"/>
+      <c r="I81" s="14" t="n"/>
     </row>
     <row r="82" ht="18" customHeight="1">
-      <c r="I82" s="16" t="n"/>
+      <c r="I82" s="14" t="n"/>
     </row>
     <row r="83" ht="18" customHeight="1">
-      <c r="I83" s="16" t="n"/>
+      <c r="I83" s="14" t="n"/>
     </row>
     <row r="84" ht="18" customHeight="1">
-      <c r="I84" s="16" t="n"/>
+      <c r="I84" s="14" t="n"/>
     </row>
     <row r="85" ht="18" customHeight="1">
-      <c r="I85" s="16" t="n"/>
+      <c r="I85" s="14" t="n"/>
     </row>
     <row r="86" ht="18" customHeight="1">
-      <c r="I86" s="16" t="n"/>
+      <c r="I86" s="14" t="n"/>
     </row>
     <row r="87" ht="18" customHeight="1">
-      <c r="I87" s="16" t="n"/>
+      <c r="I87" s="14" t="n"/>
     </row>
     <row r="88" ht="18" customHeight="1">
-      <c r="I88" s="16" t="n"/>
+      <c r="I88" s="14" t="n"/>
     </row>
     <row r="89" ht="18" customHeight="1">
-      <c r="I89" s="16" t="n"/>
+      <c r="I89" s="14" t="n"/>
     </row>
     <row r="90" ht="18" customHeight="1">
-      <c r="I90" s="16" t="n"/>
+      <c r="I90" s="14" t="n"/>
     </row>
     <row r="91" ht="18" customHeight="1">
-      <c r="I91" s="16" t="n"/>
+      <c r="I91" s="14" t="n"/>
     </row>
     <row r="92" ht="18" customHeight="1">
-      <c r="I92" s="16" t="n"/>
+      <c r="I92" s="14" t="n"/>
     </row>
     <row r="93" ht="18" customHeight="1">
-      <c r="I93" s="16" t="n"/>
+      <c r="I93" s="14" t="n"/>
     </row>
     <row r="94" ht="18" customHeight="1">
-      <c r="I94" s="16" t="n"/>
+      <c r="I94" s="14" t="n"/>
     </row>
     <row r="95" ht="18" customHeight="1">
-      <c r="I95" s="16" t="n"/>
+      <c r="I95" s="14" t="n"/>
     </row>
     <row r="96" ht="18" customHeight="1">
-      <c r="I96" s="16" t="n"/>
+      <c r="I96" s="14" t="n"/>
     </row>
     <row r="97" ht="18" customHeight="1">
-      <c r="I97" s="16" t="n"/>
+      <c r="I97" s="14" t="n"/>
     </row>
     <row r="98" ht="18" customHeight="1">
-      <c r="I98" s="16" t="n"/>
+      <c r="I98" s="14" t="n"/>
     </row>
     <row r="99" ht="18" customHeight="1">
-      <c r="I99" s="16" t="n"/>
+      <c r="I99" s="14" t="n"/>
     </row>
     <row r="100" ht="18" customHeight="1">
-      <c r="I100" s="16" t="n"/>
+      <c r="I100" s="14" t="n"/>
     </row>
     <row r="101" ht="18" customHeight="1">
-      <c r="I101" s="16" t="n"/>
+      <c r="I101" s="14" t="n"/>
     </row>
     <row r="102" ht="18" customHeight="1">
-      <c r="I102" s="16" t="n"/>
+      <c r="I102" s="14" t="n"/>
     </row>
     <row r="103" ht="18" customHeight="1">
-      <c r="I103" s="16" t="n"/>
+      <c r="I103" s="14" t="n"/>
     </row>
     <row r="104" ht="18" customHeight="1">
-      <c r="I104" s="16" t="n"/>
+      <c r="I104" s="14" t="n"/>
     </row>
     <row r="105" ht="18" customHeight="1">
-      <c r="I105" s="16" t="n"/>
+      <c r="I105" s="14" t="n"/>
     </row>
     <row r="106" ht="18" customHeight="1">
-      <c r="I106" s="16" t="n"/>
+      <c r="I106" s="14" t="n"/>
     </row>
     <row r="107" ht="18" customHeight="1">
-      <c r="I107" s="16" t="n"/>
+      <c r="I107" s="14" t="n"/>
     </row>
     <row r="108" ht="18" customHeight="1">
-      <c r="I108" s="16" t="n"/>
+      <c r="I108" s="14" t="n"/>
     </row>
     <row r="109" ht="18" customHeight="1">
-      <c r="I109" s="16" t="n"/>
+      <c r="I109" s="14" t="n"/>
     </row>
     <row r="110" ht="18" customHeight="1">
-      <c r="I110" s="16" t="n"/>
+      <c r="I110" s="14" t="n"/>
     </row>
     <row r="111" ht="18" customHeight="1">
-      <c r="I111" s="16" t="n"/>
+      <c r="I111" s="14" t="n"/>
     </row>
     <row r="112" ht="18" customHeight="1">
-      <c r="I112" s="16" t="n"/>
+      <c r="I112" s="14" t="n"/>
     </row>
     <row r="113" ht="18" customHeight="1">
-      <c r="I113" s="16" t="n"/>
+      <c r="I113" s="14" t="n"/>
     </row>
     <row r="114" ht="18" customHeight="1">
-      <c r="I114" s="16" t="n"/>
+      <c r="I114" s="14" t="n"/>
     </row>
     <row r="115" ht="18" customHeight="1">
-      <c r="I115" s="16" t="n"/>
+      <c r="I115" s="14" t="n"/>
     </row>
     <row r="116" ht="18" customHeight="1">
-      <c r="I116" s="16" t="n"/>
+      <c r="I116" s="14" t="n"/>
     </row>
     <row r="117" ht="18" customHeight="1">
-      <c r="I117" s="16" t="n"/>
+      <c r="I117" s="14" t="n"/>
     </row>
     <row r="118" ht="18" customHeight="1">
-      <c r="I118" s="16" t="n"/>
+      <c r="I118" s="14" t="n"/>
     </row>
     <row r="119" ht="18" customHeight="1">
-      <c r="I119" s="16" t="n"/>
+      <c r="I119" s="14" t="n"/>
     </row>
     <row r="120" ht="18" customHeight="1">
-      <c r="I120" s="16" t="n"/>
+      <c r="I120" s="14" t="n"/>
     </row>
     <row r="121" ht="18" customHeight="1">
-      <c r="I121" s="16" t="n"/>
+      <c r="I121" s="14" t="n"/>
     </row>
     <row r="122" ht="18" customHeight="1">
-      <c r="I122" s="16" t="n"/>
+      <c r="I122" s="14" t="n"/>
     </row>
     <row r="123" ht="18" customHeight="1">
-      <c r="I123" s="16" t="n"/>
+      <c r="I123" s="14" t="n"/>
     </row>
     <row r="124" ht="18" customHeight="1">
-      <c r="I124" s="16" t="n"/>
+      <c r="I124" s="14" t="n"/>
     </row>
     <row r="125" ht="18" customHeight="1">
-      <c r="I125" s="16" t="n"/>
+      <c r="I125" s="14" t="n"/>
     </row>
     <row r="126" ht="18" customHeight="1">
-      <c r="I126" s="16" t="n"/>
+      <c r="I126" s="14" t="n"/>
     </row>
     <row r="127" ht="18" customHeight="1">
-      <c r="I127" s="16" t="n"/>
+      <c r="I127" s="14" t="n"/>
     </row>
     <row r="128" ht="18" customHeight="1">
-      <c r="I128" s="16" t="n"/>
+      <c r="I128" s="14" t="n"/>
     </row>
     <row r="129" ht="18" customHeight="1">
-      <c r="I129" s="16" t="n"/>
+      <c r="I129" s="14" t="n"/>
     </row>
     <row r="130" ht="18" customHeight="1">
-      <c r="I130" s="16" t="n"/>
+      <c r="I130" s="14" t="n"/>
     </row>
     <row r="131" ht="18" customHeight="1">
-      <c r="I131" s="16" t="n"/>
+      <c r="I131" s="14" t="n"/>
     </row>
     <row r="132" ht="18" customHeight="1">
-      <c r="I132" s="16" t="n"/>
+      <c r="I132" s="14" t="n"/>
     </row>
     <row r="133" ht="18" customHeight="1">
-      <c r="I133" s="16" t="n"/>
+      <c r="I133" s="14" t="n"/>
     </row>
     <row r="134" ht="18" customHeight="1">
-      <c r="I134" s="16" t="n"/>
+      <c r="I134" s="14" t="n"/>
     </row>
     <row r="135" ht="18" customHeight="1">
-      <c r="I135" s="16" t="n"/>
+      <c r="I135" s="14" t="n"/>
     </row>
     <row r="136" ht="18" customHeight="1">
-      <c r="I136" s="16" t="n"/>
+      <c r="I136" s="14" t="n"/>
     </row>
     <row r="137" ht="18" customHeight="1">
-      <c r="I137" s="16" t="n"/>
+      <c r="I137" s="14" t="n"/>
     </row>
     <row r="138" ht="18" customHeight="1">
-      <c r="I138" s="16" t="n"/>
+      <c r="I138" s="14" t="n"/>
     </row>
     <row r="139" ht="18" customHeight="1">
-      <c r="I139" s="16" t="n"/>
+      <c r="I139" s="14" t="n"/>
     </row>
     <row r="140" ht="18" customHeight="1">
-      <c r="I140" s="16" t="n"/>
+      <c r="I140" s="14" t="n"/>
     </row>
     <row r="141" ht="18" customHeight="1">
-      <c r="I141" s="16" t="n"/>
+      <c r="I141" s="14" t="n"/>
     </row>
     <row r="142" ht="18" customHeight="1">
-      <c r="I142" s="16" t="n"/>
+      <c r="I142" s="14" t="n"/>
     </row>
     <row r="143" ht="18" customHeight="1">
-      <c r="I143" s="16" t="n"/>
+      <c r="I143" s="14" t="n"/>
     </row>
     <row r="144" ht="18" customHeight="1">
-      <c r="I144" s="16" t="n"/>
+      <c r="I144" s="14" t="n"/>
     </row>
     <row r="145" ht="18" customHeight="1">
-      <c r="I145" s="16" t="n"/>
+      <c r="I145" s="14" t="n"/>
     </row>
     <row r="146" ht="18" customHeight="1">
-      <c r="I146" s="16" t="n"/>
+      <c r="I146" s="14" t="n"/>
     </row>
     <row r="147" ht="18" customHeight="1">
-      <c r="I147" s="16" t="n"/>
+      <c r="I147" s="14" t="n"/>
     </row>
     <row r="148" ht="18" customHeight="1">
-      <c r="I148" s="16" t="n"/>
+      <c r="I148" s="14" t="n"/>
     </row>
     <row r="149" ht="18" customHeight="1">
-      <c r="I149" s="16" t="n"/>
+      <c r="I149" s="14" t="n"/>
     </row>
     <row r="150" ht="18" customHeight="1">
-      <c r="I150" s="16" t="n"/>
+      <c r="I150" s="14" t="n"/>
     </row>
     <row r="151" ht="18" customHeight="1">
-      <c r="I151" s="16" t="n"/>
+      <c r="I151" s="14" t="n"/>
     </row>
     <row r="152" ht="18" customHeight="1">
-      <c r="I152" s="16" t="n"/>
+      <c r="I152" s="14" t="n"/>
     </row>
     <row r="153" ht="18" customHeight="1">
-      <c r="I153" s="16" t="n"/>
+      <c r="I153" s="14" t="n"/>
     </row>
     <row r="154" ht="18" customHeight="1">
-      <c r="I154" s="16" t="n"/>
+      <c r="I154" s="14" t="n"/>
     </row>
     <row r="155" ht="18" customHeight="1">
-      <c r="I155" s="16" t="n"/>
+      <c r="I155" s="14" t="n"/>
     </row>
     <row r="156" ht="18" customHeight="1">
-      <c r="I156" s="16" t="n"/>
+      <c r="I156" s="14" t="n"/>
     </row>
     <row r="157" ht="18" customHeight="1">
-      <c r="I157" s="16" t="n"/>
+      <c r="I157" s="14" t="n"/>
     </row>
     <row r="158" ht="18" customHeight="1">
-      <c r="I158" s="16" t="n"/>
+      <c r="I158" s="14" t="n"/>
     </row>
     <row r="159" ht="18" customHeight="1">
-      <c r="I159" s="16" t="n"/>
+      <c r="I159" s="14" t="n"/>
     </row>
     <row r="160" ht="18" customHeight="1">
-      <c r="I160" s="16" t="n"/>
+      <c r="I160" s="14" t="n"/>
     </row>
     <row r="161" ht="18" customHeight="1">
-      <c r="I161" s="16" t="n"/>
+      <c r="I161" s="14" t="n"/>
     </row>
     <row r="162" ht="18" customHeight="1">
-      <c r="I162" s="16" t="n"/>
+      <c r="I162" s="14" t="n"/>
     </row>
     <row r="163" ht="18" customHeight="1">
-      <c r="I163" s="16" t="n"/>
+      <c r="I163" s="14" t="n"/>
     </row>
     <row r="164" ht="18" customHeight="1">
-      <c r="I164" s="16" t="n"/>
+      <c r="I164" s="14" t="n"/>
     </row>
     <row r="165" ht="18" customHeight="1">
-      <c r="I165" s="16" t="n"/>
+      <c r="I165" s="14" t="n"/>
     </row>
     <row r="166" ht="18" customHeight="1">
-      <c r="I166" s="16" t="n"/>
+      <c r="I166" s="14" t="n"/>
     </row>
     <row r="167" ht="18" customHeight="1">
-      <c r="I167" s="16" t="n"/>
+      <c r="I167" s="14" t="n"/>
     </row>
     <row r="168" ht="18" customHeight="1">
-      <c r="I168" s="16" t="n"/>
+      <c r="I168" s="14" t="n"/>
     </row>
     <row r="169" ht="18" customHeight="1">
-      <c r="I169" s="16" t="n"/>
+      <c r="I169" s="14" t="n"/>
     </row>
     <row r="170" ht="18" customHeight="1">
-      <c r="I170" s="16" t="n"/>
+      <c r="I170" s="14" t="n"/>
     </row>
     <row r="171" ht="18" customHeight="1">
-      <c r="I171" s="16" t="n"/>
+      <c r="I171" s="14" t="n"/>
     </row>
     <row r="172" ht="18" customHeight="1">
-      <c r="I172" s="16" t="n"/>
+      <c r="I172" s="14" t="n"/>
     </row>
     <row r="173" ht="18" customHeight="1">
-      <c r="I173" s="16" t="n"/>
+      <c r="I173" s="14" t="n"/>
     </row>
     <row r="174" ht="18" customHeight="1">
-      <c r="I174" s="16" t="n"/>
+      <c r="I174" s="14" t="n"/>
     </row>
     <row r="175" ht="18" customHeight="1">
-      <c r="I175" s="16" t="n"/>
+      <c r="I175" s="14" t="n"/>
     </row>
     <row r="176" ht="18" customHeight="1">
-      <c r="I176" s="16" t="n"/>
+      <c r="I176" s="14" t="n"/>
     </row>
     <row r="177" ht="18" customHeight="1">
-      <c r="I177" s="16" t="n"/>
+      <c r="I177" s="14" t="n"/>
     </row>
     <row r="178" ht="18" customHeight="1">
-      <c r="I178" s="16" t="n"/>
+      <c r="I178" s="14" t="n"/>
     </row>
     <row r="179" ht="18" customHeight="1">
-      <c r="I179" s="16" t="n"/>
+      <c r="I179" s="14" t="n"/>
     </row>
     <row r="180" ht="18" customHeight="1">
-      <c r="I180" s="16" t="n"/>
+      <c r="I180" s="14" t="n"/>
     </row>
     <row r="181" ht="18" customHeight="1">
-      <c r="I181" s="16" t="n"/>
+      <c r="I181" s="14" t="n"/>
     </row>
     <row r="182" ht="18" customHeight="1">
-      <c r="I182" s="16" t="n"/>
+      <c r="I182" s="14" t="n"/>
     </row>
     <row r="183" ht="18" customHeight="1">
-      <c r="I183" s="16" t="n"/>
+      <c r="I183" s="14" t="n"/>
     </row>
     <row r="184" ht="18" customHeight="1">
-      <c r="I184" s="16" t="n"/>
+      <c r="I184" s="14" t="n"/>
     </row>
     <row r="185" ht="18" customHeight="1">
-      <c r="I185" s="16" t="n"/>
+      <c r="I185" s="14" t="n"/>
     </row>
     <row r="186" ht="18" customHeight="1">
-      <c r="I186" s="16" t="n"/>
+      <c r="I186" s="14" t="n"/>
     </row>
     <row r="187" ht="18" customHeight="1">
-      <c r="I187" s="16" t="n"/>
+      <c r="I187" s="14" t="n"/>
     </row>
     <row r="188" ht="18" customHeight="1">
-      <c r="I188" s="16" t="n"/>
+      <c r="I188" s="14" t="n"/>
     </row>
     <row r="189" ht="18" customHeight="1">
-      <c r="I189" s="16" t="n"/>
+      <c r="I189" s="14" t="n"/>
     </row>
     <row r="190" ht="18" customHeight="1">
-      <c r="I190" s="16" t="n"/>
+      <c r="I190" s="14" t="n"/>
     </row>
     <row r="191" ht="18" customHeight="1">
-      <c r="I191" s="16" t="n"/>
+      <c r="I191" s="14" t="n"/>
     </row>
     <row r="192" ht="18" customHeight="1">
-      <c r="I192" s="16" t="n"/>
+      <c r="I192" s="14" t="n"/>
     </row>
     <row r="193" ht="18" customHeight="1">
-      <c r="I193" s="16" t="n"/>
+      <c r="I193" s="14" t="n"/>
     </row>
     <row r="194" ht="18" customHeight="1">
-      <c r="I194" s="16" t="n"/>
+      <c r="I194" s="14" t="n"/>
     </row>
     <row r="195" ht="18" customHeight="1">
-      <c r="I195" s="16" t="n"/>
+      <c r="I195" s="14" t="n"/>
     </row>
     <row r="196" ht="18" customHeight="1">
-      <c r="I196" s="16" t="n"/>
+      <c r="I196" s="14" t="n"/>
     </row>
     <row r="197" ht="18" customHeight="1">
-      <c r="I197" s="16" t="n"/>
+      <c r="I197" s="14" t="n"/>
     </row>
     <row r="198" ht="18" customHeight="1">
-      <c r="I198" s="16" t="n"/>
+      <c r="I198" s="14" t="n"/>
     </row>
     <row r="199" ht="18" customHeight="1">
-      <c r="I199" s="16" t="n"/>
+      <c r="I199" s="14" t="n"/>
     </row>
     <row r="200" ht="18" customHeight="1">
-      <c r="I200" s="16" t="n"/>
+      <c r="I200" s="14" t="n"/>
     </row>
     <row r="201" ht="18" customHeight="1">
-      <c r="I201" s="16" t="n"/>
+      <c r="I201" s="14" t="n"/>
     </row>
     <row r="202" ht="18" customHeight="1">
-      <c r="I202" s="16" t="n"/>
+      <c r="I202" s="14" t="n"/>
     </row>
     <row r="203" ht="18" customHeight="1">
-      <c r="I203" s="16" t="n"/>
+      <c r="I203" s="14" t="n"/>
     </row>
     <row r="204" ht="18" customHeight="1">
-      <c r="I204" s="16" t="n"/>
+      <c r="I204" s="14" t="n"/>
     </row>
     <row r="205" ht="18" customHeight="1">
-      <c r="I205" s="16" t="n"/>
+      <c r="I205" s="14" t="n"/>
     </row>
     <row r="206" ht="18" customHeight="1">
-      <c r="I206" s="16" t="n"/>
+      <c r="I206" s="14" t="n"/>
     </row>
     <row r="207" ht="18" customHeight="1">
-      <c r="I207" s="16" t="n"/>
+      <c r="I207" s="14" t="n"/>
     </row>
     <row r="208" ht="18" customHeight="1">
-      <c r="I208" s="16" t="n"/>
+      <c r="I208" s="14" t="n"/>
     </row>
     <row r="209" ht="18" customHeight="1">
-      <c r="I209" s="16" t="n"/>
+      <c r="I209" s="14" t="n"/>
     </row>
     <row r="210" ht="18" customHeight="1">
-      <c r="I210" s="16" t="n"/>
+      <c r="I210" s="14" t="n"/>
     </row>
     <row r="211" ht="18" customHeight="1">
-      <c r="I211" s="16" t="n"/>
+      <c r="I211" s="14" t="n"/>
     </row>
     <row r="212" ht="18" customHeight="1">
-      <c r="I212" s="16" t="n"/>
+      <c r="I212" s="14" t="n"/>
     </row>
     <row r="213" ht="18" customHeight="1">
-      <c r="I213" s="16" t="n"/>
+      <c r="I213" s="14" t="n"/>
     </row>
     <row r="214" ht="18" customHeight="1">
-      <c r="I214" s="16" t="n"/>
+      <c r="I214" s="14" t="n"/>
     </row>
     <row r="215" ht="18" customHeight="1">
-      <c r="I215" s="16" t="n"/>
+      <c r="I215" s="14" t="n"/>
     </row>
     <row r="216" ht="18" customHeight="1">
-      <c r="I216" s="16" t="n"/>
+      <c r="I216" s="14" t="n"/>
     </row>
     <row r="217" ht="18" customHeight="1">
-      <c r="I217" s="16" t="n"/>
+      <c r="I217" s="14" t="n"/>
     </row>
     <row r="218" ht="18" customHeight="1">
-      <c r="I218" s="16" t="n"/>
+      <c r="I218" s="14" t="n"/>
     </row>
     <row r="219" ht="18" customHeight="1">
-      <c r="I219" s="16" t="n"/>
+      <c r="I219" s="14" t="n"/>
     </row>
     <row r="220" ht="18" customHeight="1">
-      <c r="I220" s="16" t="n"/>
+      <c r="I220" s="14" t="n"/>
     </row>
     <row r="221" ht="18" customHeight="1">
-      <c r="I221" s="16" t="n"/>
+      <c r="I221" s="14" t="n"/>
     </row>
     <row r="222" ht="18" customHeight="1">
-      <c r="I222" s="16" t="n"/>
+      <c r="I222" s="14" t="n"/>
     </row>
     <row r="223" ht="18" customHeight="1">
-      <c r="I223" s="16" t="n"/>
+      <c r="I223" s="14" t="n"/>
     </row>
     <row r="224" ht="18" customHeight="1">
-      <c r="I224" s="16" t="n"/>
+      <c r="I224" s="14" t="n"/>
     </row>
     <row r="225" ht="18" customHeight="1">
-      <c r="I225" s="16" t="n"/>
+      <c r="I225" s="14" t="n"/>
     </row>
     <row r="226" ht="18" customHeight="1">
-      <c r="I226" s="16" t="n"/>
+      <c r="I226" s="14" t="n"/>
     </row>
     <row r="227" ht="18" customHeight="1">
-      <c r="I227" s="16" t="n"/>
+      <c r="I227" s="14" t="n"/>
     </row>
     <row r="228" ht="18" customHeight="1">
-      <c r="I228" s="16" t="n"/>
+      <c r="I228" s="14" t="n"/>
     </row>
     <row r="229" ht="18" customHeight="1">
-      <c r="I229" s="16" t="n"/>
+      <c r="I229" s="14" t="n"/>
     </row>
     <row r="230" ht="18" customHeight="1">
-      <c r="I230" s="16" t="n"/>
+      <c r="I230" s="14" t="n"/>
     </row>
     <row r="231" ht="18" customHeight="1">
-      <c r="I231" s="16" t="n"/>
+      <c r="I231" s="14" t="n"/>
     </row>
     <row r="232" ht="18" customHeight="1">
-      <c r="I232" s="16" t="n"/>
+      <c r="I232" s="14" t="n"/>
     </row>
     <row r="233" ht="18" customHeight="1">
-      <c r="I233" s="16" t="n"/>
+      <c r="I233" s="14" t="n"/>
     </row>
     <row r="234" ht="18" customHeight="1">
-      <c r="I234" s="16" t="n"/>
+      <c r="I234" s="14" t="n"/>
     </row>
     <row r="235" ht="18" customHeight="1">
-      <c r="I235" s="16" t="n"/>
+      <c r="I235" s="14" t="n"/>
     </row>
     <row r="236" ht="18" customHeight="1">
-      <c r="I236" s="16" t="n"/>
+      <c r="I236" s="14" t="n"/>
     </row>
     <row r="237" ht="18" customHeight="1">
-      <c r="I237" s="16" t="n"/>
+      <c r="I237" s="14" t="n"/>
     </row>
     <row r="238" ht="18" customHeight="1">
-      <c r="I238" s="16" t="n"/>
+      <c r="I238" s="14" t="n"/>
     </row>
     <row r="239" ht="18" customHeight="1">
-      <c r="I239" s="16" t="n"/>
+      <c r="I239" s="14" t="n"/>
     </row>
     <row r="240" ht="18" customHeight="1">
-      <c r="I240" s="16" t="n"/>
+      <c r="I240" s="14" t="n"/>
     </row>
     <row r="241" ht="18" customHeight="1">
-      <c r="I241" s="16" t="n"/>
+      <c r="I241" s="14" t="n"/>
     </row>
     <row r="242" ht="18" customHeight="1">
-      <c r="I242" s="16" t="n"/>
+      <c r="I242" s="14" t="n"/>
     </row>
     <row r="243" ht="18" customHeight="1">
-      <c r="I243" s="16" t="n"/>
+      <c r="I243" s="14" t="n"/>
     </row>
     <row r="244" ht="18" customHeight="1">
-      <c r="I244" s="16" t="n"/>
+      <c r="I244" s="14" t="n"/>
     </row>
     <row r="245" ht="18" customHeight="1">
-      <c r="I245" s="16" t="n"/>
+      <c r="I245" s="14" t="n"/>
     </row>
     <row r="246" ht="18" customHeight="1">
-      <c r="I246" s="16" t="n"/>
+      <c r="I246" s="14" t="n"/>
     </row>
     <row r="247" ht="18" customHeight="1">
-      <c r="I247" s="16" t="n"/>
+      <c r="I247" s="14" t="n"/>
     </row>
     <row r="248" ht="18" customHeight="1">
-      <c r="I248" s="16" t="n"/>
+      <c r="I248" s="14" t="n"/>
     </row>
     <row r="249" ht="18" customHeight="1">
-      <c r="I249" s="16" t="n"/>
+      <c r="I249" s="14" t="n"/>
     </row>
     <row r="250" ht="18" customHeight="1">
-      <c r="I250" s="16" t="n"/>
+      <c r="I250" s="14" t="n"/>
     </row>
     <row r="251" ht="18" customHeight="1">
-      <c r="I251" s="16" t="n"/>
+      <c r="I251" s="14" t="n"/>
     </row>
     <row r="252" ht="18" customHeight="1">
-      <c r="I252" s="16" t="n"/>
+      <c r="I252" s="14" t="n"/>
     </row>
     <row r="253" ht="18" customHeight="1">
-      <c r="I253" s="16" t="n"/>
+      <c r="I253" s="14" t="n"/>
     </row>
     <row r="254" ht="18" customHeight="1">
-      <c r="I254" s="16" t="n"/>
+      <c r="I254" s="14" t="n"/>
     </row>
     <row r="255" ht="18" customHeight="1">
-      <c r="I255" s="16" t="n"/>
+      <c r="I255" s="14" t="n"/>
     </row>
     <row r="256" ht="18" customHeight="1">
-      <c r="I256" s="16" t="n"/>
+      <c r="I256" s="14" t="n"/>
     </row>
     <row r="257" ht="18" customHeight="1">
-      <c r="I257" s="16" t="n"/>
+      <c r="I257" s="14" t="n"/>
     </row>
     <row r="258" ht="18" customHeight="1">
-      <c r="I258" s="16" t="n"/>
+      <c r="I258" s="14" t="n"/>
     </row>
     <row r="259" ht="18" customHeight="1">
-      <c r="I259" s="16" t="n"/>
+      <c r="I259" s="14" t="n"/>
     </row>
     <row r="260" ht="18" customHeight="1">
-      <c r="I260" s="16" t="n"/>
+      <c r="I260" s="14" t="n"/>
     </row>
     <row r="261" ht="18" customHeight="1">
-      <c r="I261" s="16" t="n"/>
+      <c r="I261" s="14" t="n"/>
     </row>
     <row r="262" ht="18" customHeight="1">
-      <c r="I262" s="16" t="n"/>
+      <c r="I262" s="14" t="n"/>
     </row>
     <row r="263" ht="18" customHeight="1">
-      <c r="I263" s="16" t="n"/>
+      <c r="I263" s="14" t="n"/>
     </row>
     <row r="264" ht="18" customHeight="1">
-      <c r="I264" s="16" t="n"/>
+      <c r="I264" s="14" t="n"/>
     </row>
     <row r="265" ht="18" customHeight="1">
-      <c r="I265" s="16" t="n"/>
+      <c r="I265" s="14" t="n"/>
     </row>
     <row r="266" ht="18" customHeight="1">
-      <c r="I266" s="16" t="n"/>
+      <c r="I266" s="14" t="n"/>
     </row>
     <row r="267" ht="18" customHeight="1">
-      <c r="I267" s="16" t="n"/>
+      <c r="I267" s="14" t="n"/>
     </row>
     <row r="268" ht="18" customHeight="1">
-      <c r="I268" s="16" t="n"/>
+      <c r="I268" s="14" t="n"/>
     </row>
     <row r="269" ht="18" customHeight="1">
-      <c r="I269" s="16" t="n"/>
+      <c r="I269" s="14" t="n"/>
     </row>
     <row r="270" ht="18" customHeight="1">
-      <c r="I270" s="16" t="n"/>
+      <c r="I270" s="14" t="n"/>
     </row>
     <row r="271" ht="18" customHeight="1">
-      <c r="I271" s="16" t="n"/>
+      <c r="I271" s="14" t="n"/>
     </row>
     <row r="272" ht="18" customHeight="1">
-      <c r="I272" s="16" t="n"/>
+      <c r="I272" s="14" t="n"/>
     </row>
     <row r="273" ht="18" customHeight="1">
-      <c r="I273" s="16" t="n"/>
+      <c r="I273" s="14" t="n"/>
     </row>
     <row r="274" ht="18" customHeight="1">
-      <c r="I274" s="16" t="n"/>
+      <c r="I274" s="14" t="n"/>
     </row>
     <row r="275" ht="18" customHeight="1">
-      <c r="I275" s="16" t="n"/>
+      <c r="I275" s="14" t="n"/>
     </row>
     <row r="276" ht="18" customHeight="1">
-      <c r="I276" s="16" t="n"/>
+      <c r="I276" s="14" t="n"/>
     </row>
     <row r="277" ht="18" customHeight="1">
-      <c r="I277" s="16" t="n"/>
+      <c r="I277" s="14" t="n"/>
     </row>
     <row r="278" ht="18" customHeight="1">
-      <c r="I278" s="16" t="n"/>
+      <c r="I278" s="14" t="n"/>
     </row>
     <row r="279" ht="18" customHeight="1">
-      <c r="I279" s="16" t="n"/>
+      <c r="I279" s="14" t="n"/>
     </row>
     <row r="280" ht="18" customHeight="1">
-      <c r="I280" s="16" t="n"/>
+      <c r="I280" s="14" t="n"/>
     </row>
     <row r="281" ht="18" customHeight="1">
-      <c r="I281" s="16" t="n"/>
+      <c r="I281" s="14" t="n"/>
     </row>
     <row r="282" ht="18" customHeight="1">
-      <c r="I282" s="16" t="n"/>
+      <c r="I282" s="14" t="n"/>
     </row>
     <row r="283" ht="18" customHeight="1">
-      <c r="I283" s="16" t="n"/>
+      <c r="I283" s="14" t="n"/>
     </row>
     <row r="284" ht="18" customHeight="1">
-      <c r="I284" s="16" t="n"/>
+      <c r="I284" s="14" t="n"/>
     </row>
     <row r="285" ht="18" customHeight="1">
-      <c r="I285" s="16" t="n"/>
+      <c r="I285" s="14" t="n"/>
     </row>
     <row r="286" ht="18" customHeight="1">
-      <c r="I286" s="16" t="n"/>
+      <c r="I286" s="14" t="n"/>
     </row>
     <row r="287" ht="18" customHeight="1">
-      <c r="I287" s="16" t="n"/>
+      <c r="I287" s="14" t="n"/>
     </row>
     <row r="288" ht="18" customHeight="1">
-      <c r="I288" s="16" t="n"/>
+      <c r="I288" s="14" t="n"/>
     </row>
     <row r="289" ht="18" customHeight="1">
-      <c r="I289" s="16" t="n"/>
+      <c r="I289" s="14" t="n"/>
     </row>
     <row r="290" ht="18" customHeight="1">
-      <c r="I290" s="16" t="n"/>
+      <c r="I290" s="14" t="n"/>
     </row>
     <row r="291" ht="18" customHeight="1">
-      <c r="I291" s="16" t="n"/>
+      <c r="I291" s="14" t="n"/>
     </row>
     <row r="292" ht="18" customHeight="1">
-      <c r="I292" s="16" t="n"/>
+      <c r="I292" s="14" t="n"/>
     </row>
     <row r="293" ht="18" customHeight="1">
-      <c r="I293" s="16" t="n"/>
+      <c r="I293" s="14" t="n"/>
     </row>
     <row r="294" ht="18" customHeight="1">
-      <c r="I294" s="16" t="n"/>
+      <c r="I294" s="14" t="n"/>
     </row>
     <row r="295" ht="18" customHeight="1">
-      <c r="I295" s="16" t="n"/>
+      <c r="I295" s="14" t="n"/>
     </row>
     <row r="296" ht="18" customHeight="1">
-      <c r="I296" s="16" t="n"/>
+      <c r="I296" s="14" t="n"/>
     </row>
     <row r="297" ht="18" customHeight="1">
-      <c r="I297" s="16" t="n"/>
+      <c r="I297" s="14" t="n"/>
     </row>
     <row r="298" ht="18" customHeight="1">
-      <c r="I298" s="16" t="n"/>
+      <c r="I298" s="14" t="n"/>
     </row>
     <row r="299" ht="18" customHeight="1">
-      <c r="I299" s="16" t="n"/>
+      <c r="I299" s="14" t="n"/>
     </row>
     <row r="300" ht="18" customHeight="1">
-      <c r="I300" s="16" t="n"/>
+      <c r="I300" s="14" t="n"/>
     </row>
     <row r="301" ht="18" customHeight="1">
-      <c r="I301" s="16" t="n"/>
+      <c r="I301" s="14" t="n"/>
     </row>
     <row r="302" ht="18" customHeight="1">
-      <c r="I302" s="16" t="n"/>
+      <c r="I302" s="14" t="n"/>
     </row>
     <row r="303" ht="18" customHeight="1">
-      <c r="I303" s="16" t="n"/>
+      <c r="I303" s="14" t="n"/>
     </row>
     <row r="304" ht="18" customHeight="1">
-      <c r="I304" s="16" t="n"/>
+      <c r="I304" s="14" t="n"/>
     </row>
     <row r="305" ht="18" customHeight="1">
-      <c r="I305" s="16" t="n"/>
+      <c r="I305" s="14" t="n"/>
     </row>
     <row r="306" ht="18" customHeight="1">
-      <c r="I306" s="16" t="n"/>
+      <c r="I306" s="14" t="n"/>
     </row>
     <row r="307" ht="18" customHeight="1">
-      <c r="I307" s="16" t="n"/>
+      <c r="I307" s="14" t="n"/>
     </row>
     <row r="308" ht="18" customHeight="1">
-      <c r="I308" s="16" t="n"/>
+      <c r="I308" s="14" t="n"/>
     </row>
     <row r="309" ht="18" customHeight="1">
-      <c r="I309" s="16" t="n"/>
+      <c r="I309" s="14" t="n"/>
     </row>
     <row r="310" ht="18" customHeight="1">
-      <c r="I310" s="16" t="n"/>
+      <c r="I310" s="14" t="n"/>
     </row>
     <row r="311" ht="18" customHeight="1">
-      <c r="I311" s="16" t="n"/>
+      <c r="I311" s="14" t="n"/>
     </row>
     <row r="312" ht="18" customHeight="1">
-      <c r="I312" s="16" t="n"/>
+      <c r="I312" s="14" t="n"/>
     </row>
     <row r="313" ht="18" customHeight="1">
-      <c r="I313" s="16" t="n"/>
+      <c r="I313" s="14" t="n"/>
     </row>
     <row r="314" ht="18" customHeight="1">
-      <c r="I314" s="16" t="n"/>
+      <c r="I314" s="14" t="n"/>
     </row>
     <row r="315" ht="18" customHeight="1">
-      <c r="I315" s="16" t="n"/>
+      <c r="I315" s="14" t="n"/>
     </row>
     <row r="316" ht="18" customHeight="1">
-      <c r="I316" s="16" t="n"/>
+      <c r="I316" s="14" t="n"/>
     </row>
     <row r="317" ht="18" customHeight="1">
-      <c r="I317" s="16" t="n"/>
+      <c r="I317" s="14" t="n"/>
     </row>
     <row r="318" ht="18" customHeight="1">
-      <c r="I318" s="16" t="n"/>
+      <c r="I318" s="14" t="n"/>
     </row>
     <row r="319" ht="18" customHeight="1">
-      <c r="I319" s="16" t="n"/>
+      <c r="I319" s="14" t="n"/>
     </row>
     <row r="320" ht="18" customHeight="1">
-      <c r="I320" s="16" t="n"/>
+      <c r="I320" s="14" t="n"/>
     </row>
     <row r="321" ht="18" customHeight="1">
-      <c r="I321" s="16" t="n"/>
+      <c r="I321" s="14" t="n"/>
     </row>
     <row r="322" ht="18" customHeight="1">
-      <c r="I322" s="16" t="n"/>
+      <c r="I322" s="14" t="n"/>
     </row>
     <row r="323" ht="18" customHeight="1">
-      <c r="I323" s="16" t="n"/>
+      <c r="I323" s="14" t="n"/>
     </row>
     <row r="324" ht="18" customHeight="1">
-      <c r="I324" s="16" t="n"/>
+      <c r="I324" s="14" t="n"/>
     </row>
     <row r="325" ht="18" customHeight="1">
-      <c r="I325" s="16" t="n"/>
+      <c r="I325" s="14" t="n"/>
     </row>
     <row r="326" ht="18" customHeight="1">
-      <c r="I326" s="16" t="n"/>
+      <c r="I326" s="14" t="n"/>
     </row>
     <row r="327" ht="18" customHeight="1">
-      <c r="I327" s="16" t="n"/>
+      <c r="I327" s="14" t="n"/>
     </row>
     <row r="328" ht="18" customHeight="1">
-      <c r="I328" s="16" t="n"/>
+      <c r="I328" s="14" t="n"/>
     </row>
     <row r="329" ht="18" customHeight="1">
-      <c r="I329" s="16" t="n"/>
+      <c r="I329" s="14" t="n"/>
     </row>
     <row r="330" ht="18" customHeight="1">
-      <c r="I330" s="16" t="n"/>
+      <c r="I330" s="14" t="n"/>
     </row>
     <row r="331" ht="18" customHeight="1">
-      <c r="I331" s="16" t="n"/>
+      <c r="I331" s="14" t="n"/>
     </row>
     <row r="332" ht="18" customHeight="1">
-      <c r="I332" s="16" t="n"/>
+      <c r="I332" s="14" t="n"/>
     </row>
     <row r="333" ht="18" customHeight="1">
-      <c r="I333" s="16" t="n"/>
+      <c r="I333" s="14" t="n"/>
     </row>
     <row r="334" ht="18" customHeight="1">
-      <c r="I334" s="16" t="n"/>
+      <c r="I334" s="14" t="n"/>
     </row>
     <row r="335" ht="18" customHeight="1">
-      <c r="I335" s="16" t="n"/>
+      <c r="I335" s="14" t="n"/>
     </row>
     <row r="336" ht="18" customHeight="1">
-      <c r="I336" s="16" t="n"/>
+      <c r="I336" s="14" t="n"/>
     </row>
     <row r="337" ht="18" customHeight="1">
-      <c r="I337" s="16" t="n"/>
+      <c r="I337" s="14" t="n"/>
     </row>
     <row r="338" ht="18" customHeight="1">
-      <c r="I338" s="16" t="n"/>
+      <c r="I338" s="14" t="n"/>
     </row>
     <row r="339" ht="18" customHeight="1">
-      <c r="I339" s="16" t="n"/>
+      <c r="I339" s="14" t="n"/>
     </row>
     <row r="340" ht="18" customHeight="1">
-      <c r="I340" s="16" t="n"/>
+      <c r="I340" s="14" t="n"/>
     </row>
     <row r="341" ht="18" customHeight="1">
-      <c r="I341" s="16" t="n"/>
+      <c r="I341" s="14" t="n"/>
     </row>
     <row r="342" ht="18" customHeight="1">
-      <c r="I342" s="16" t="n"/>
+      <c r="I342" s="14" t="n"/>
     </row>
     <row r="343" ht="18" customHeight="1">
-      <c r="I343" s="16" t="n"/>
+      <c r="I343" s="14" t="n"/>
     </row>
     <row r="344" ht="18" customHeight="1">
-      <c r="I344" s="16" t="n"/>
+      <c r="I344" s="14" t="n"/>
     </row>
     <row r="345" ht="18" customHeight="1">
-      <c r="I345" s="16" t="n"/>
+      <c r="I345" s="14" t="n"/>
     </row>
     <row r="346" ht="18" customHeight="1">
-      <c r="I346" s="16" t="n"/>
+      <c r="I346" s="14" t="n"/>
     </row>
     <row r="347" ht="18" customHeight="1">
-      <c r="I347" s="16" t="n"/>
+      <c r="I347" s="14" t="n"/>
     </row>
     <row r="348" ht="18" customHeight="1">
-      <c r="I348" s="16" t="n"/>
+      <c r="I348" s="14" t="n"/>
     </row>
     <row r="349" ht="18" customHeight="1">
-      <c r="I349" s="16" t="n"/>
+      <c r="I349" s="14" t="n"/>
     </row>
     <row r="350" ht="18" customHeight="1">
-      <c r="I350" s="16" t="n"/>
+      <c r="I350" s="14" t="n"/>
     </row>
     <row r="351" ht="18" customHeight="1">
-      <c r="I351" s="16" t="n"/>
+      <c r="I351" s="14" t="n"/>
     </row>
     <row r="352" ht="18" customHeight="1">
-      <c r="I352" s="16" t="n"/>
+      <c r="I352" s="14" t="n"/>
     </row>
     <row r="353" ht="18" customHeight="1">
-      <c r="I353" s="16" t="n"/>
+      <c r="I353" s="14" t="n"/>
     </row>
     <row r="354" ht="18" customHeight="1">
-      <c r="I354" s="16" t="n"/>
+      <c r="I354" s="14" t="n"/>
     </row>
     <row r="355" ht="18" customHeight="1">
-      <c r="I355" s="16" t="n"/>
+      <c r="I355" s="14" t="n"/>
     </row>
     <row r="356" ht="18" customHeight="1">
-      <c r="I356" s="16" t="n"/>
+      <c r="I356" s="14" t="n"/>
     </row>
     <row r="357" ht="18" customHeight="1">
-      <c r="I357" s="16" t="n"/>
+      <c r="I357" s="14" t="n"/>
     </row>
     <row r="358" ht="18" customHeight="1">
-      <c r="I358" s="16" t="n"/>
+      <c r="I358" s="14" t="n"/>
     </row>
     <row r="359" ht="18" customHeight="1">
-      <c r="I359" s="16" t="n"/>
+      <c r="I359" s="14" t="n"/>
     </row>
     <row r="360" ht="18" customHeight="1">
-      <c r="I360" s="16" t="n"/>
+      <c r="I360" s="14" t="n"/>
     </row>
     <row r="361" ht="18" customHeight="1">
-      <c r="I361" s="16" t="n"/>
+      <c r="I361" s="14" t="n"/>
     </row>
     <row r="362" ht="18" customHeight="1">
-      <c r="I362" s="16" t="n"/>
+      <c r="I362" s="14" t="n"/>
     </row>
     <row r="363" ht="18" customHeight="1">
-      <c r="I363" s="16" t="n"/>
+      <c r="I363" s="14" t="n"/>
     </row>
     <row r="364" ht="18" customHeight="1">
-      <c r="I364" s="16" t="n"/>
+      <c r="I364" s="14" t="n"/>
     </row>
     <row r="365" ht="18" customHeight="1">
-      <c r="I365" s="16" t="n"/>
+      <c r="I365" s="14" t="n"/>
     </row>
     <row r="366" ht="18" customHeight="1">
-      <c r="I366" s="16" t="n"/>
+      <c r="I366" s="14" t="n"/>
     </row>
     <row r="367" ht="18" customHeight="1">
-      <c r="I367" s="16" t="n"/>
+      <c r="I367" s="14" t="n"/>
     </row>
     <row r="368" ht="18" customHeight="1">
-      <c r="I368" s="16" t="n"/>
+      <c r="I368" s="14" t="n"/>
     </row>
     <row r="369" ht="18" customHeight="1">
-      <c r="I369" s="16" t="n"/>
+      <c r="I369" s="14" t="n"/>
     </row>
     <row r="370" ht="18" customHeight="1">
-      <c r="I370" s="16" t="n"/>
+      <c r="I370" s="14" t="n"/>
     </row>
     <row r="371" ht="18" customHeight="1">
-      <c r="I371" s="16" t="n"/>
+      <c r="I371" s="14" t="n"/>
     </row>
     <row r="372" ht="18" customHeight="1">
-      <c r="I372" s="16" t="n"/>
+      <c r="I372" s="14" t="n"/>
     </row>
     <row r="373" ht="18" customHeight="1">
-      <c r="I373" s="16" t="n"/>
+      <c r="I373" s="14" t="n"/>
     </row>
     <row r="374" ht="18" customHeight="1">
-      <c r="I374" s="16" t="n"/>
+      <c r="I374" s="14" t="n"/>
     </row>
     <row r="375" ht="18" customHeight="1">
-      <c r="I375" s="16" t="n"/>
+      <c r="I375" s="14" t="n"/>
     </row>
     <row r="376" ht="18" customHeight="1">
-      <c r="I376" s="16" t="n"/>
+      <c r="I376" s="14" t="n"/>
     </row>
     <row r="377" ht="18" customHeight="1">
-      <c r="I377" s="16" t="n"/>
+      <c r="I377" s="14" t="n"/>
     </row>
     <row r="378" ht="18" customHeight="1">
-      <c r="I378" s="16" t="n"/>
+      <c r="I378" s="14" t="n"/>
     </row>
     <row r="379" ht="18" customHeight="1">
-      <c r="I379" s="16" t="n"/>
+      <c r="I379" s="14" t="n"/>
     </row>
     <row r="380" ht="18" customHeight="1">
-      <c r="I380" s="16" t="n"/>
+      <c r="I380" s="14" t="n"/>
     </row>
     <row r="381" ht="18" customHeight="1">
-      <c r="I381" s="16" t="n"/>
+      <c r="I381" s="14" t="n"/>
     </row>
     <row r="382" ht="18" customHeight="1">
-      <c r="I382" s="16" t="n"/>
+      <c r="I382" s="14" t="n"/>
     </row>
     <row r="383" ht="18" customHeight="1">
-      <c r="I383" s="16" t="n"/>
+      <c r="I383" s="14" t="n"/>
     </row>
     <row r="384" ht="18" customHeight="1">
-      <c r="I384" s="16" t="n"/>
+      <c r="I384" s="14" t="n"/>
     </row>
     <row r="385" ht="18" customHeight="1">
-      <c r="I385" s="16" t="n"/>
+      <c r="I385" s="14" t="n"/>
     </row>
     <row r="386" ht="18" customHeight="1">
-      <c r="I386" s="16" t="n"/>
+      <c r="I386" s="14" t="n"/>
     </row>
     <row r="387" ht="18" customHeight="1">
-      <c r="I387" s="16" t="n"/>
+      <c r="I387" s="14" t="n"/>
     </row>
     <row r="388" ht="18" customHeight="1">
-      <c r="I388" s="16" t="n"/>
+      <c r="I388" s="14" t="n"/>
     </row>
     <row r="389" ht="18" customHeight="1">
-      <c r="I389" s="16" t="n"/>
+      <c r="I389" s="14" t="n"/>
     </row>
     <row r="390" ht="18" customHeight="1">
-      <c r="I390" s="16" t="n"/>
+      <c r="I390" s="14" t="n"/>
     </row>
     <row r="391" ht="18" customHeight="1">
-      <c r="I391" s="16" t="n"/>
+      <c r="I391" s="14" t="n"/>
     </row>
     <row r="392" ht="18" customHeight="1">
-      <c r="I392" s="16" t="n"/>
+      <c r="I392" s="14" t="n"/>
     </row>
     <row r="393" ht="18" customHeight="1">
-      <c r="I393" s="16" t="n"/>
+      <c r="I393" s="14" t="n"/>
     </row>
     <row r="394" ht="18" customHeight="1">
-      <c r="I394" s="16" t="n"/>
+      <c r="I394" s="14" t="n"/>
     </row>
     <row r="395" ht="18" customHeight="1">
-      <c r="I395" s="16" t="n"/>
+      <c r="I395" s="14" t="n"/>
     </row>
     <row r="396" ht="18" customHeight="1">
-      <c r="I396" s="16" t="n"/>
+      <c r="I396" s="14" t="n"/>
     </row>
     <row r="397" ht="18" customHeight="1">
-      <c r="I397" s="16" t="n"/>
+      <c r="I397" s="14" t="n"/>
     </row>
     <row r="398" ht="18" customHeight="1">
-      <c r="I398" s="16" t="n"/>
+      <c r="I398" s="14" t="n"/>
     </row>
     <row r="399" ht="18" customHeight="1">
-      <c r="I399" s="16" t="n"/>
+      <c r="I399" s="14" t="n"/>
     </row>
     <row r="400" ht="18" customHeight="1">
-      <c r="I400" s="16" t="n"/>
+      <c r="I400" s="14" t="n"/>
     </row>
     <row r="401" ht="18" customHeight="1">
-      <c r="I401" s="16" t="n"/>
+      <c r="I401" s="14" t="n"/>
     </row>
     <row r="402" ht="18" customHeight="1">
-      <c r="I402" s="16" t="n"/>
+      <c r="I402" s="14" t="n"/>
     </row>
     <row r="403" ht="18" customHeight="1">
-      <c r="I403" s="16" t="n"/>
+      <c r="I403" s="14" t="n"/>
     </row>
     <row r="404" ht="18" customHeight="1">
-      <c r="I404" s="16" t="n"/>
+      <c r="I404" s="14" t="n"/>
     </row>
     <row r="405" ht="18" customHeight="1">
-      <c r="I405" s="16" t="n"/>
+      <c r="I405" s="14" t="n"/>
     </row>
     <row r="406" ht="18" customHeight="1">
-      <c r="I406" s="16" t="n"/>
+      <c r="I406" s="14" t="n"/>
     </row>
     <row r="407" ht="18" customHeight="1">
-      <c r="I407" s="16" t="n"/>
+      <c r="I407" s="14" t="n"/>
     </row>
     <row r="408" ht="18" customHeight="1">
-      <c r="I408" s="16" t="n"/>
+      <c r="I408" s="14" t="n"/>
     </row>
     <row r="409" ht="18" customHeight="1">
-      <c r="I409" s="16" t="n"/>
+      <c r="I409" s="14" t="n"/>
     </row>
     <row r="410" ht="18" customHeight="1">
-      <c r="I410" s="16" t="n"/>
+      <c r="I410" s="14" t="n"/>
     </row>
     <row r="411" ht="18" customHeight="1">
-      <c r="I411" s="16" t="n"/>
+      <c r="I411" s="14" t="n"/>
     </row>
     <row r="412" ht="18" customHeight="1">
-      <c r="I412" s="16" t="n"/>
+      <c r="I412" s="14" t="n"/>
     </row>
     <row r="413" ht="18" customHeight="1">
-      <c r="I413" s="16" t="n"/>
+      <c r="I413" s="14" t="n"/>
     </row>
     <row r="414" ht="18" customHeight="1">
-      <c r="I414" s="16" t="n"/>
+      <c r="I414" s="14" t="n"/>
     </row>
     <row r="415" ht="18" customHeight="1">
-      <c r="I415" s="16" t="n"/>
+      <c r="I415" s="14" t="n"/>
     </row>
     <row r="416" ht="18" customHeight="1">
-      <c r="I416" s="16" t="n"/>
+      <c r="I416" s="14" t="n"/>
     </row>
     <row r="417" ht="18" customHeight="1">
-      <c r="I417" s="16" t="n"/>
+      <c r="I417" s="14" t="n"/>
     </row>
     <row r="418" ht="18" customHeight="1">
-      <c r="I418" s="16" t="n"/>
+      <c r="I418" s="14" t="n"/>
     </row>
     <row r="419" ht="18" customHeight="1">
-      <c r="I419" s="16" t="n"/>
+      <c r="I419" s="14" t="n"/>
     </row>
     <row r="420" ht="18" customHeight="1">
-      <c r="I420" s="16" t="n"/>
+      <c r="I420" s="14" t="n"/>
     </row>
     <row r="421" ht="18" customHeight="1">
-      <c r="I421" s="16" t="n"/>
+      <c r="I421" s="14" t="n"/>
     </row>
     <row r="422" ht="18" customHeight="1">
-      <c r="I422" s="16" t="n"/>
+      <c r="I422" s="14" t="n"/>
     </row>
     <row r="423" ht="18" customHeight="1">
-      <c r="I423" s="16" t="n"/>
+      <c r="I423" s="14" t="n"/>
     </row>
     <row r="424" ht="18" customHeight="1">
-      <c r="I424" s="16" t="n"/>
+      <c r="I424" s="14" t="n"/>
     </row>
     <row r="425" ht="18" customHeight="1">
-      <c r="I425" s="16" t="n"/>
+      <c r="I425" s="14" t="n"/>
     </row>
     <row r="426" ht="18" customHeight="1">
-      <c r="I426" s="16" t="n"/>
+      <c r="I426" s="14" t="n"/>
     </row>
     <row r="427" ht="18" customHeight="1">
-      <c r="I427" s="16" t="n"/>
+      <c r="I427" s="14" t="n"/>
     </row>
     <row r="428" ht="18" customHeight="1">
-      <c r="I428" s="16" t="n"/>
+      <c r="I428" s="14" t="n"/>
     </row>
     <row r="429" ht="18" customHeight="1">
-      <c r="I429" s="16" t="n"/>
+      <c r="I429" s="14" t="n"/>
     </row>
     <row r="430" ht="18" customHeight="1">
-      <c r="I430" s="16" t="n"/>
+      <c r="I430" s="14" t="n"/>
     </row>
     <row r="431" ht="18" customHeight="1">
-      <c r="I431" s="16" t="n"/>
+      <c r="I431" s="14" t="n"/>
     </row>
     <row r="432" ht="18" customHeight="1">
-      <c r="I432" s="16" t="n"/>
+      <c r="I432" s="14" t="n"/>
     </row>
     <row r="433" ht="18" customHeight="1">
-      <c r="I433" s="16" t="n"/>
+      <c r="I433" s="14" t="n"/>
     </row>
     <row r="434" ht="18" customHeight="1">
-      <c r="I434" s="16" t="n"/>
+      <c r="I434" s="14" t="n"/>
     </row>
     <row r="435" ht="18" customHeight="1">
-      <c r="I435" s="16" t="n"/>
+      <c r="I435" s="14" t="n"/>
     </row>
     <row r="436" ht="18" customHeight="1">
-      <c r="I436" s="16" t="n"/>
+      <c r="I436" s="14" t="n"/>
     </row>
     <row r="437" ht="18" customHeight="1">
-      <c r="I437" s="16" t="n"/>
+      <c r="I437" s="14" t="n"/>
     </row>
     <row r="438" ht="18" customHeight="1">
-      <c r="I438" s="16" t="n"/>
+      <c r="I438" s="14" t="n"/>
     </row>
     <row r="439" ht="18" customHeight="1">
-      <c r="I439" s="16" t="n"/>
+      <c r="I439" s="14" t="n"/>
     </row>
     <row r="440" ht="18" customHeight="1">
-      <c r="I440" s="16" t="n"/>
+      <c r="I440" s="14" t="n"/>
     </row>
     <row r="441" ht="18" customHeight="1">
-      <c r="I441" s="16" t="n"/>
+      <c r="I441" s="14" t="n"/>
     </row>
     <row r="442" ht="18" customHeight="1">
-      <c r="I442" s="16" t="n"/>
+      <c r="I442" s="14" t="n"/>
     </row>
     <row r="443" ht="18" customHeight="1">
-      <c r="I443" s="16" t="n"/>
+      <c r="I443" s="14" t="n"/>
     </row>
     <row r="444" ht="18" customHeight="1">
-      <c r="I444" s="16" t="n"/>
+      <c r="I444" s="14" t="n"/>
     </row>
     <row r="445" ht="18" customHeight="1">
-      <c r="I445" s="16" t="n"/>
+      <c r="I445" s="14" t="n"/>
     </row>
     <row r="446" ht="18" customHeight="1">
-      <c r="I446" s="16" t="n"/>
+      <c r="I446" s="14" t="n"/>
     </row>
     <row r="447" ht="18" customHeight="1">
-      <c r="I447" s="16" t="n"/>
+      <c r="I447" s="14" t="n"/>
     </row>
     <row r="448" ht="18" customHeight="1">
-      <c r="I448" s="16" t="n"/>
+      <c r="I448" s="14" t="n"/>
     </row>
     <row r="449" ht="18" customHeight="1">
-      <c r="I449" s="16" t="n"/>
+      <c r="I449" s="14" t="n"/>
     </row>
     <row r="450" ht="18" customHeight="1">
-      <c r="I450" s="16" t="n"/>
+      <c r="I450" s="14" t="n"/>
     </row>
     <row r="451" ht="18" customHeight="1">
-      <c r="I451" s="16" t="n"/>
+      <c r="I451" s="14" t="n"/>
     </row>
     <row r="452" ht="18" customHeight="1">
-      <c r="I452" s="16" t="n"/>
+      <c r="I452" s="14" t="n"/>
     </row>
     <row r="453" ht="18" customHeight="1">
-      <c r="I453" s="16" t="n"/>
+      <c r="I453" s="14" t="n"/>
     </row>
     <row r="454" ht="18" customHeight="1">
-      <c r="I454" s="16" t="n"/>
+      <c r="I454" s="14" t="n"/>
     </row>
     <row r="455" ht="18" customHeight="1">
-      <c r="I455" s="16" t="n"/>
+      <c r="I455" s="14" t="n"/>
     </row>
     <row r="456" ht="18" customHeight="1">
-      <c r="I456" s="16" t="n"/>
+      <c r="I456" s="14" t="n"/>
     </row>
     <row r="457" ht="18" customHeight="1">
-      <c r="I457" s="16" t="n"/>
+      <c r="I457" s="14" t="n"/>
     </row>
     <row r="458" ht="18" customHeight="1">
-      <c r="I458" s="16" t="n"/>
+      <c r="I458" s="14" t="n"/>
     </row>
     <row r="459" ht="18" customHeight="1">
-      <c r="I459" s="16" t="n"/>
+      <c r="I459" s="14" t="n"/>
     </row>
     <row r="460" ht="18" customHeight="1">
-      <c r="I460" s="16" t="n"/>
+      <c r="I460" s="14" t="n"/>
     </row>
     <row r="461" ht="18" customHeight="1">
-      <c r="I461" s="16" t="n"/>
+      <c r="I461" s="14" t="n"/>
     </row>
     <row r="462" ht="18" customHeight="1">
-      <c r="I462" s="16" t="n"/>
+      <c r="I462" s="14" t="n"/>
     </row>
     <row r="463" ht="18" customHeight="1">
-      <c r="I463" s="16" t="n"/>
+      <c r="I463" s="14" t="n"/>
     </row>
     <row r="464" ht="18" customHeight="1">
-      <c r="I464" s="16" t="n"/>
+      <c r="I464" s="14" t="n"/>
     </row>
     <row r="465" ht="18" customHeight="1">
-      <c r="I465" s="16" t="n"/>
+      <c r="I465" s="14" t="n"/>
     </row>
     <row r="466" ht="18" customHeight="1">
-      <c r="I466" s="16" t="n"/>
+      <c r="I466" s="14" t="n"/>
     </row>
     <row r="467" ht="18" customHeight="1">
-      <c r="I467" s="16" t="n"/>
+      <c r="I467" s="14" t="n"/>
     </row>
     <row r="468" ht="18" customHeight="1">
-      <c r="I468" s="16" t="n"/>
+      <c r="I468" s="14" t="n"/>
     </row>
     <row r="469" ht="18" customHeight="1">
-      <c r="I469" s="16" t="n"/>
+      <c r="I469" s="14" t="n"/>
     </row>
     <row r="470" ht="18" customHeight="1">
-      <c r="I470" s="16" t="n"/>
+      <c r="I470" s="14" t="n"/>
     </row>
     <row r="471" ht="18" customHeight="1">
-      <c r="I471" s="16" t="n"/>
+      <c r="I471" s="14" t="n"/>
     </row>
     <row r="472" ht="18" customHeight="1">
-      <c r="I472" s="16" t="n"/>
+      <c r="I472" s="14" t="n"/>
     </row>
     <row r="473" ht="18" customHeight="1">
-      <c r="I473" s="16" t="n"/>
+      <c r="I473" s="14" t="n"/>
     </row>
     <row r="474" ht="18" customHeight="1">
-      <c r="I474" s="16" t="n"/>
+      <c r="I474" s="14" t="n"/>
     </row>
     <row r="475" ht="18" customHeight="1">
-      <c r="I475" s="16" t="n"/>
+      <c r="I475" s="14" t="n"/>
     </row>
     <row r="476" ht="18" customHeight="1">
-      <c r="I476" s="16" t="n"/>
+      <c r="I476" s="14" t="n"/>
     </row>
     <row r="477" ht="18" customHeight="1">
-      <c r="I477" s="16" t="n"/>
+      <c r="I477" s="14" t="n"/>
     </row>
     <row r="478" ht="18" customHeight="1">
-      <c r="I478" s="16" t="n"/>
+      <c r="I478" s="14" t="n"/>
     </row>
     <row r="479" ht="18" customHeight="1">
-      <c r="I479" s="16" t="n"/>
+      <c r="I479" s="14" t="n"/>
     </row>
     <row r="480" ht="18" customHeight="1">
-      <c r="I480" s="16" t="n"/>
+      <c r="I480" s="14" t="n"/>
     </row>
     <row r="481" ht="18" customHeight="1">
-      <c r="I481" s="16" t="n"/>
+      <c r="I481" s="14" t="n"/>
     </row>
     <row r="482" ht="18" customHeight="1">
-      <c r="I482" s="16" t="n"/>
+      <c r="I482" s="14" t="n"/>
     </row>
     <row r="483" ht="18" customHeight="1">
-      <c r="I483" s="16" t="n"/>
+      <c r="I483" s="14" t="n"/>
     </row>
     <row r="484" ht="18" customHeight="1">
-      <c r="I484" s="16" t="n"/>
+      <c r="I484" s="14" t="n"/>
     </row>
     <row r="485" ht="18" customHeight="1">
-      <c r="I485" s="16" t="n"/>
+      <c r="I485" s="14" t="n"/>
     </row>
     <row r="486" ht="18" customHeight="1">
-      <c r="I486" s="16" t="n"/>
+      <c r="I486" s="14" t="n"/>
     </row>
     <row r="487" ht="18" customHeight="1">
-      <c r="I487" s="16" t="n"/>
+      <c r="I487" s="14" t="n"/>
     </row>
     <row r="488" ht="18" customHeight="1">
-      <c r="I488" s="16" t="n"/>
+      <c r="I488" s="14" t="n"/>
     </row>
     <row r="489" ht="18" customHeight="1">
-      <c r="I489" s="16" t="n"/>
+      <c r="I489" s="14" t="n"/>
     </row>
     <row r="490" ht="18" customHeight="1">
-      <c r="I490" s="16" t="n"/>
+      <c r="I490" s="14" t="n"/>
     </row>
     <row r="491" ht="18" customHeight="1">
-      <c r="I491" s="16" t="n"/>
+      <c r="I491" s="14" t="n"/>
     </row>
     <row r="492" ht="18" customHeight="1">
-      <c r="I492" s="16" t="n"/>
+      <c r="I492" s="14" t="n"/>
     </row>
     <row r="493" ht="18" customHeight="1">
-      <c r="I493" s="16" t="n"/>
+      <c r="I493" s="14" t="n"/>
     </row>
     <row r="494" ht="18" customHeight="1">
-      <c r="I494" s="16" t="n"/>
+      <c r="I494" s="14" t="n"/>
     </row>
     <row r="495" ht="18" customHeight="1">
-      <c r="I495" s="16" t="n"/>
+      <c r="I495" s="14" t="n"/>
     </row>
     <row r="496" ht="18" customHeight="1">
-      <c r="I496" s="16" t="n"/>
+      <c r="I496" s="14" t="n"/>
     </row>
     <row r="497" ht="18" customHeight="1">
-      <c r="I497" s="16" t="n"/>
+      <c r="I497" s="14" t="n"/>
     </row>
     <row r="498" ht="18" customHeight="1">
-      <c r="I498" s="16" t="n"/>
+      <c r="I498" s="14" t="n"/>
     </row>
     <row r="499" ht="18" customHeight="1">
-      <c r="I499" s="16" t="n"/>
+      <c r="I499" s="14" t="n"/>
     </row>
     <row r="500" ht="18" customHeight="1">
-      <c r="I500" s="16" t="n"/>
+      <c r="I500" s="14" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3943,8 +3889,8 @@
     <mergeCell ref="E1:H1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="K4:K500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="CATEGORIA inválida" error="Valores: reclamo, compromiso, otros — o dejar vacío (pago normal)." type="list">
-      <formula1>"reclamo,compromiso,otros"</formula1>
+    <dataValidation sqref="K4:K500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="CATEGORIA inválida" error="Valores: reclamo, compromiso, exoneracion, otros — o dejar vacío (pago normal)." type="list">
+      <formula1>"reclamo,compromiso,exoneracion,otros"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3979,21 +3925,16 @@
           <t>¿Quién cobró?</t>
         </is>
       </c>
-      <c r="B1" s="12" t="n"/>
       <c r="C1" s="2" t="inlineStr">
         <is>
           <t>¿Dónde vive?</t>
         </is>
       </c>
-      <c r="D1" s="12" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
           <t>¿Cuánto y cuándo?</t>
         </is>
       </c>
-      <c r="F1" s="13" t="n"/>
-      <c r="G1" s="13" t="n"/>
-      <c r="H1" s="12" t="n"/>
       <c r="I1" s="4" t="inlineStr">
         <is>
           <t>¿Alguna nota?</t>
@@ -4004,1603 +3945,1604 @@
           <t>¿Qué tipo?</t>
         </is>
       </c>
-      <c r="K1" s="14" t="inlineStr">
+      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>¿Qué pasó?</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>COBRADOR</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>FECHA_REGISTRO</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>MZ</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>LT</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="E2" s="9" t="inlineStr">
         <is>
           <t>MONTO</t>
         </is>
       </c>
-      <c r="F2" s="8" t="inlineStr">
+      <c r="F2" s="9" t="inlineStr">
         <is>
           <t>MONTO_EFECTIVO</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="G2" s="9" t="inlineStr">
         <is>
           <t>MONTO_YAPE</t>
         </is>
       </c>
-      <c r="H2" s="8" t="inlineStr">
+      <c r="H2" s="9" t="inlineStr">
         <is>
           <t>FECHA</t>
         </is>
       </c>
-      <c r="I2" s="9" t="inlineStr">
+      <c r="I2" s="10" t="inlineStr">
         <is>
           <t>COMENTARIO</t>
         </is>
       </c>
-      <c r="J2" s="10" t="inlineStr">
+      <c r="J2" s="11" t="inlineStr">
         <is>
           <t>CONCEPTO</t>
         </is>
       </c>
-      <c r="K2" s="15" t="inlineStr">
+      <c r="K2" s="12" t="inlineStr">
         <is>
           <t>CATEGORIA</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>María García</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>8C</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>38.00</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>20.00</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>18.00</t>
         </is>
       </c>
-      <c r="H3" s="11" t="inlineStr">
+      <c r="H3" s="13" t="inlineStr">
         <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="I3" s="11" t="inlineStr"/>
-      <c r="J3" s="11" t="inlineStr"/>
+      <c r="I3" s="13" t="inlineStr"/>
+      <c r="J3" s="13" t="inlineStr"/>
+      <c r="K3" s="13" t="inlineStr"/>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="I4" s="16" t="n"/>
+      <c r="I4" s="14" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="I5" s="16" t="n"/>
+      <c r="I5" s="14" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="I6" s="16" t="n"/>
+      <c r="I6" s="14" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="I7" s="16" t="n"/>
+      <c r="I7" s="14" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="I8" s="16" t="n"/>
+      <c r="I8" s="14" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="I9" s="16" t="n"/>
+      <c r="I9" s="14" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="I10" s="16" t="n"/>
+      <c r="I10" s="14" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="I11" s="16" t="n"/>
+      <c r="I11" s="14" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="I12" s="16" t="n"/>
+      <c r="I12" s="14" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="I13" s="16" t="n"/>
+      <c r="I13" s="14" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="I14" s="16" t="n"/>
+      <c r="I14" s="14" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="I15" s="16" t="n"/>
+      <c r="I15" s="14" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="I16" s="16" t="n"/>
+      <c r="I16" s="14" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="I17" s="16" t="n"/>
+      <c r="I17" s="14" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="I18" s="16" t="n"/>
+      <c r="I18" s="14" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="I19" s="16" t="n"/>
+      <c r="I19" s="14" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="I20" s="16" t="n"/>
+      <c r="I20" s="14" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="I21" s="16" t="n"/>
+      <c r="I21" s="14" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="I22" s="16" t="n"/>
+      <c r="I22" s="14" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="I23" s="16" t="n"/>
+      <c r="I23" s="14" t="n"/>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="I24" s="16" t="n"/>
+      <c r="I24" s="14" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="I25" s="16" t="n"/>
+      <c r="I25" s="14" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="I26" s="16" t="n"/>
+      <c r="I26" s="14" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="I27" s="16" t="n"/>
+      <c r="I27" s="14" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="I28" s="16" t="n"/>
+      <c r="I28" s="14" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="I29" s="16" t="n"/>
+      <c r="I29" s="14" t="n"/>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="I30" s="16" t="n"/>
+      <c r="I30" s="14" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="I31" s="16" t="n"/>
+      <c r="I31" s="14" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="I32" s="16" t="n"/>
+      <c r="I32" s="14" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="I33" s="16" t="n"/>
+      <c r="I33" s="14" t="n"/>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="I34" s="16" t="n"/>
+      <c r="I34" s="14" t="n"/>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="I35" s="16" t="n"/>
+      <c r="I35" s="14" t="n"/>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="I36" s="16" t="n"/>
+      <c r="I36" s="14" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1">
-      <c r="I37" s="16" t="n"/>
+      <c r="I37" s="14" t="n"/>
     </row>
     <row r="38" ht="18" customHeight="1">
-      <c r="I38" s="16" t="n"/>
+      <c r="I38" s="14" t="n"/>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="I39" s="16" t="n"/>
+      <c r="I39" s="14" t="n"/>
     </row>
     <row r="40" ht="18" customHeight="1">
-      <c r="I40" s="16" t="n"/>
+      <c r="I40" s="14" t="n"/>
     </row>
     <row r="41" ht="18" customHeight="1">
-      <c r="I41" s="16" t="n"/>
+      <c r="I41" s="14" t="n"/>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="I42" s="16" t="n"/>
+      <c r="I42" s="14" t="n"/>
     </row>
     <row r="43" ht="18" customHeight="1">
-      <c r="I43" s="16" t="n"/>
+      <c r="I43" s="14" t="n"/>
     </row>
     <row r="44" ht="18" customHeight="1">
-      <c r="I44" s="16" t="n"/>
+      <c r="I44" s="14" t="n"/>
     </row>
     <row r="45" ht="18" customHeight="1">
-      <c r="I45" s="16" t="n"/>
+      <c r="I45" s="14" t="n"/>
     </row>
     <row r="46" ht="18" customHeight="1">
-      <c r="I46" s="16" t="n"/>
+      <c r="I46" s="14" t="n"/>
     </row>
     <row r="47" ht="18" customHeight="1">
-      <c r="I47" s="16" t="n"/>
+      <c r="I47" s="14" t="n"/>
     </row>
     <row r="48" ht="18" customHeight="1">
-      <c r="I48" s="16" t="n"/>
+      <c r="I48" s="14" t="n"/>
     </row>
     <row r="49" ht="18" customHeight="1">
-      <c r="I49" s="16" t="n"/>
+      <c r="I49" s="14" t="n"/>
     </row>
     <row r="50" ht="18" customHeight="1">
-      <c r="I50" s="16" t="n"/>
+      <c r="I50" s="14" t="n"/>
     </row>
     <row r="51" ht="18" customHeight="1">
-      <c r="I51" s="16" t="n"/>
+      <c r="I51" s="14" t="n"/>
     </row>
     <row r="52" ht="18" customHeight="1">
-      <c r="I52" s="16" t="n"/>
+      <c r="I52" s="14" t="n"/>
     </row>
     <row r="53" ht="18" customHeight="1">
-      <c r="I53" s="16" t="n"/>
+      <c r="I53" s="14" t="n"/>
     </row>
     <row r="54" ht="18" customHeight="1">
-      <c r="I54" s="16" t="n"/>
+      <c r="I54" s="14" t="n"/>
     </row>
     <row r="55" ht="18" customHeight="1">
-      <c r="I55" s="16" t="n"/>
+      <c r="I55" s="14" t="n"/>
     </row>
     <row r="56" ht="18" customHeight="1">
-      <c r="I56" s="16" t="n"/>
+      <c r="I56" s="14" t="n"/>
     </row>
     <row r="57" ht="18" customHeight="1">
-      <c r="I57" s="16" t="n"/>
+      <c r="I57" s="14" t="n"/>
     </row>
     <row r="58" ht="18" customHeight="1">
-      <c r="I58" s="16" t="n"/>
+      <c r="I58" s="14" t="n"/>
     </row>
     <row r="59" ht="18" customHeight="1">
-      <c r="I59" s="16" t="n"/>
+      <c r="I59" s="14" t="n"/>
     </row>
     <row r="60" ht="18" customHeight="1">
-      <c r="I60" s="16" t="n"/>
+      <c r="I60" s="14" t="n"/>
     </row>
     <row r="61" ht="18" customHeight="1">
-      <c r="I61" s="16" t="n"/>
+      <c r="I61" s="14" t="n"/>
     </row>
     <row r="62" ht="18" customHeight="1">
-      <c r="I62" s="16" t="n"/>
+      <c r="I62" s="14" t="n"/>
     </row>
     <row r="63" ht="18" customHeight="1">
-      <c r="I63" s="16" t="n"/>
+      <c r="I63" s="14" t="n"/>
     </row>
     <row r="64" ht="18" customHeight="1">
-      <c r="I64" s="16" t="n"/>
+      <c r="I64" s="14" t="n"/>
     </row>
     <row r="65" ht="18" customHeight="1">
-      <c r="I65" s="16" t="n"/>
+      <c r="I65" s="14" t="n"/>
     </row>
     <row r="66" ht="18" customHeight="1">
-      <c r="I66" s="16" t="n"/>
+      <c r="I66" s="14" t="n"/>
     </row>
     <row r="67" ht="18" customHeight="1">
-      <c r="I67" s="16" t="n"/>
+      <c r="I67" s="14" t="n"/>
     </row>
     <row r="68" ht="18" customHeight="1">
-      <c r="I68" s="16" t="n"/>
+      <c r="I68" s="14" t="n"/>
     </row>
     <row r="69" ht="18" customHeight="1">
-      <c r="I69" s="16" t="n"/>
+      <c r="I69" s="14" t="n"/>
     </row>
     <row r="70" ht="18" customHeight="1">
-      <c r="I70" s="16" t="n"/>
+      <c r="I70" s="14" t="n"/>
     </row>
     <row r="71" ht="18" customHeight="1">
-      <c r="I71" s="16" t="n"/>
+      <c r="I71" s="14" t="n"/>
     </row>
     <row r="72" ht="18" customHeight="1">
-      <c r="I72" s="16" t="n"/>
+      <c r="I72" s="14" t="n"/>
     </row>
     <row r="73" ht="18" customHeight="1">
-      <c r="I73" s="16" t="n"/>
+      <c r="I73" s="14" t="n"/>
     </row>
     <row r="74" ht="18" customHeight="1">
-      <c r="I74" s="16" t="n"/>
+      <c r="I74" s="14" t="n"/>
     </row>
     <row r="75" ht="18" customHeight="1">
-      <c r="I75" s="16" t="n"/>
+      <c r="I75" s="14" t="n"/>
     </row>
     <row r="76" ht="18" customHeight="1">
-      <c r="I76" s="16" t="n"/>
+      <c r="I76" s="14" t="n"/>
     </row>
     <row r="77" ht="18" customHeight="1">
-      <c r="I77" s="16" t="n"/>
+      <c r="I77" s="14" t="n"/>
     </row>
     <row r="78" ht="18" customHeight="1">
-      <c r="I78" s="16" t="n"/>
+      <c r="I78" s="14" t="n"/>
     </row>
     <row r="79" ht="18" customHeight="1">
-      <c r="I79" s="16" t="n"/>
+      <c r="I79" s="14" t="n"/>
     </row>
     <row r="80" ht="18" customHeight="1">
-      <c r="I80" s="16" t="n"/>
+      <c r="I80" s="14" t="n"/>
     </row>
     <row r="81" ht="18" customHeight="1">
-      <c r="I81" s="16" t="n"/>
+      <c r="I81" s="14" t="n"/>
     </row>
     <row r="82" ht="18" customHeight="1">
-      <c r="I82" s="16" t="n"/>
+      <c r="I82" s="14" t="n"/>
     </row>
     <row r="83" ht="18" customHeight="1">
-      <c r="I83" s="16" t="n"/>
+      <c r="I83" s="14" t="n"/>
     </row>
     <row r="84" ht="18" customHeight="1">
-      <c r="I84" s="16" t="n"/>
+      <c r="I84" s="14" t="n"/>
     </row>
     <row r="85" ht="18" customHeight="1">
-      <c r="I85" s="16" t="n"/>
+      <c r="I85" s="14" t="n"/>
     </row>
     <row r="86" ht="18" customHeight="1">
-      <c r="I86" s="16" t="n"/>
+      <c r="I86" s="14" t="n"/>
     </row>
     <row r="87" ht="18" customHeight="1">
-      <c r="I87" s="16" t="n"/>
+      <c r="I87" s="14" t="n"/>
     </row>
     <row r="88" ht="18" customHeight="1">
-      <c r="I88" s="16" t="n"/>
+      <c r="I88" s="14" t="n"/>
     </row>
     <row r="89" ht="18" customHeight="1">
-      <c r="I89" s="16" t="n"/>
+      <c r="I89" s="14" t="n"/>
     </row>
     <row r="90" ht="18" customHeight="1">
-      <c r="I90" s="16" t="n"/>
+      <c r="I90" s="14" t="n"/>
     </row>
     <row r="91" ht="18" customHeight="1">
-      <c r="I91" s="16" t="n"/>
+      <c r="I91" s="14" t="n"/>
     </row>
     <row r="92" ht="18" customHeight="1">
-      <c r="I92" s="16" t="n"/>
+      <c r="I92" s="14" t="n"/>
     </row>
     <row r="93" ht="18" customHeight="1">
-      <c r="I93" s="16" t="n"/>
+      <c r="I93" s="14" t="n"/>
     </row>
     <row r="94" ht="18" customHeight="1">
-      <c r="I94" s="16" t="n"/>
+      <c r="I94" s="14" t="n"/>
     </row>
     <row r="95" ht="18" customHeight="1">
-      <c r="I95" s="16" t="n"/>
+      <c r="I95" s="14" t="n"/>
     </row>
     <row r="96" ht="18" customHeight="1">
-      <c r="I96" s="16" t="n"/>
+      <c r="I96" s="14" t="n"/>
     </row>
     <row r="97" ht="18" customHeight="1">
-      <c r="I97" s="16" t="n"/>
+      <c r="I97" s="14" t="n"/>
     </row>
     <row r="98" ht="18" customHeight="1">
-      <c r="I98" s="16" t="n"/>
+      <c r="I98" s="14" t="n"/>
     </row>
     <row r="99" ht="18" customHeight="1">
-      <c r="I99" s="16" t="n"/>
+      <c r="I99" s="14" t="n"/>
     </row>
     <row r="100" ht="18" customHeight="1">
-      <c r="I100" s="16" t="n"/>
+      <c r="I100" s="14" t="n"/>
     </row>
     <row r="101" ht="18" customHeight="1">
-      <c r="I101" s="16" t="n"/>
+      <c r="I101" s="14" t="n"/>
     </row>
     <row r="102" ht="18" customHeight="1">
-      <c r="I102" s="16" t="n"/>
+      <c r="I102" s="14" t="n"/>
     </row>
     <row r="103" ht="18" customHeight="1">
-      <c r="I103" s="16" t="n"/>
+      <c r="I103" s="14" t="n"/>
     </row>
     <row r="104" ht="18" customHeight="1">
-      <c r="I104" s="16" t="n"/>
+      <c r="I104" s="14" t="n"/>
     </row>
     <row r="105" ht="18" customHeight="1">
-      <c r="I105" s="16" t="n"/>
+      <c r="I105" s="14" t="n"/>
     </row>
     <row r="106" ht="18" customHeight="1">
-      <c r="I106" s="16" t="n"/>
+      <c r="I106" s="14" t="n"/>
     </row>
     <row r="107" ht="18" customHeight="1">
-      <c r="I107" s="16" t="n"/>
+      <c r="I107" s="14" t="n"/>
     </row>
     <row r="108" ht="18" customHeight="1">
-      <c r="I108" s="16" t="n"/>
+      <c r="I108" s="14" t="n"/>
     </row>
     <row r="109" ht="18" customHeight="1">
-      <c r="I109" s="16" t="n"/>
+      <c r="I109" s="14" t="n"/>
     </row>
     <row r="110" ht="18" customHeight="1">
-      <c r="I110" s="16" t="n"/>
+      <c r="I110" s="14" t="n"/>
     </row>
     <row r="111" ht="18" customHeight="1">
-      <c r="I111" s="16" t="n"/>
+      <c r="I111" s="14" t="n"/>
     </row>
     <row r="112" ht="18" customHeight="1">
-      <c r="I112" s="16" t="n"/>
+      <c r="I112" s="14" t="n"/>
     </row>
     <row r="113" ht="18" customHeight="1">
-      <c r="I113" s="16" t="n"/>
+      <c r="I113" s="14" t="n"/>
     </row>
     <row r="114" ht="18" customHeight="1">
-      <c r="I114" s="16" t="n"/>
+      <c r="I114" s="14" t="n"/>
     </row>
     <row r="115" ht="18" customHeight="1">
-      <c r="I115" s="16" t="n"/>
+      <c r="I115" s="14" t="n"/>
     </row>
     <row r="116" ht="18" customHeight="1">
-      <c r="I116" s="16" t="n"/>
+      <c r="I116" s="14" t="n"/>
     </row>
     <row r="117" ht="18" customHeight="1">
-      <c r="I117" s="16" t="n"/>
+      <c r="I117" s="14" t="n"/>
     </row>
     <row r="118" ht="18" customHeight="1">
-      <c r="I118" s="16" t="n"/>
+      <c r="I118" s="14" t="n"/>
     </row>
     <row r="119" ht="18" customHeight="1">
-      <c r="I119" s="16" t="n"/>
+      <c r="I119" s="14" t="n"/>
     </row>
     <row r="120" ht="18" customHeight="1">
-      <c r="I120" s="16" t="n"/>
+      <c r="I120" s="14" t="n"/>
     </row>
     <row r="121" ht="18" customHeight="1">
-      <c r="I121" s="16" t="n"/>
+      <c r="I121" s="14" t="n"/>
     </row>
     <row r="122" ht="18" customHeight="1">
-      <c r="I122" s="16" t="n"/>
+      <c r="I122" s="14" t="n"/>
     </row>
     <row r="123" ht="18" customHeight="1">
-      <c r="I123" s="16" t="n"/>
+      <c r="I123" s="14" t="n"/>
     </row>
     <row r="124" ht="18" customHeight="1">
-      <c r="I124" s="16" t="n"/>
+      <c r="I124" s="14" t="n"/>
     </row>
     <row r="125" ht="18" customHeight="1">
-      <c r="I125" s="16" t="n"/>
+      <c r="I125" s="14" t="n"/>
     </row>
     <row r="126" ht="18" customHeight="1">
-      <c r="I126" s="16" t="n"/>
+      <c r="I126" s="14" t="n"/>
     </row>
     <row r="127" ht="18" customHeight="1">
-      <c r="I127" s="16" t="n"/>
+      <c r="I127" s="14" t="n"/>
     </row>
     <row r="128" ht="18" customHeight="1">
-      <c r="I128" s="16" t="n"/>
+      <c r="I128" s="14" t="n"/>
     </row>
     <row r="129" ht="18" customHeight="1">
-      <c r="I129" s="16" t="n"/>
+      <c r="I129" s="14" t="n"/>
     </row>
     <row r="130" ht="18" customHeight="1">
-      <c r="I130" s="16" t="n"/>
+      <c r="I130" s="14" t="n"/>
     </row>
     <row r="131" ht="18" customHeight="1">
-      <c r="I131" s="16" t="n"/>
+      <c r="I131" s="14" t="n"/>
     </row>
     <row r="132" ht="18" customHeight="1">
-      <c r="I132" s="16" t="n"/>
+      <c r="I132" s="14" t="n"/>
     </row>
     <row r="133" ht="18" customHeight="1">
-      <c r="I133" s="16" t="n"/>
+      <c r="I133" s="14" t="n"/>
     </row>
     <row r="134" ht="18" customHeight="1">
-      <c r="I134" s="16" t="n"/>
+      <c r="I134" s="14" t="n"/>
     </row>
     <row r="135" ht="18" customHeight="1">
-      <c r="I135" s="16" t="n"/>
+      <c r="I135" s="14" t="n"/>
     </row>
     <row r="136" ht="18" customHeight="1">
-      <c r="I136" s="16" t="n"/>
+      <c r="I136" s="14" t="n"/>
     </row>
     <row r="137" ht="18" customHeight="1">
-      <c r="I137" s="16" t="n"/>
+      <c r="I137" s="14" t="n"/>
     </row>
     <row r="138" ht="18" customHeight="1">
-      <c r="I138" s="16" t="n"/>
+      <c r="I138" s="14" t="n"/>
     </row>
     <row r="139" ht="18" customHeight="1">
-      <c r="I139" s="16" t="n"/>
+      <c r="I139" s="14" t="n"/>
     </row>
     <row r="140" ht="18" customHeight="1">
-      <c r="I140" s="16" t="n"/>
+      <c r="I140" s="14" t="n"/>
     </row>
     <row r="141" ht="18" customHeight="1">
-      <c r="I141" s="16" t="n"/>
+      <c r="I141" s="14" t="n"/>
     </row>
     <row r="142" ht="18" customHeight="1">
-      <c r="I142" s="16" t="n"/>
+      <c r="I142" s="14" t="n"/>
     </row>
     <row r="143" ht="18" customHeight="1">
-      <c r="I143" s="16" t="n"/>
+      <c r="I143" s="14" t="n"/>
     </row>
     <row r="144" ht="18" customHeight="1">
-      <c r="I144" s="16" t="n"/>
+      <c r="I144" s="14" t="n"/>
     </row>
     <row r="145" ht="18" customHeight="1">
-      <c r="I145" s="16" t="n"/>
+      <c r="I145" s="14" t="n"/>
     </row>
     <row r="146" ht="18" customHeight="1">
-      <c r="I146" s="16" t="n"/>
+      <c r="I146" s="14" t="n"/>
     </row>
     <row r="147" ht="18" customHeight="1">
-      <c r="I147" s="16" t="n"/>
+      <c r="I147" s="14" t="n"/>
     </row>
     <row r="148" ht="18" customHeight="1">
-      <c r="I148" s="16" t="n"/>
+      <c r="I148" s="14" t="n"/>
     </row>
     <row r="149" ht="18" customHeight="1">
-      <c r="I149" s="16" t="n"/>
+      <c r="I149" s="14" t="n"/>
     </row>
     <row r="150" ht="18" customHeight="1">
-      <c r="I150" s="16" t="n"/>
+      <c r="I150" s="14" t="n"/>
     </row>
     <row r="151" ht="18" customHeight="1">
-      <c r="I151" s="16" t="n"/>
+      <c r="I151" s="14" t="n"/>
     </row>
     <row r="152" ht="18" customHeight="1">
-      <c r="I152" s="16" t="n"/>
+      <c r="I152" s="14" t="n"/>
     </row>
     <row r="153" ht="18" customHeight="1">
-      <c r="I153" s="16" t="n"/>
+      <c r="I153" s="14" t="n"/>
     </row>
     <row r="154" ht="18" customHeight="1">
-      <c r="I154" s="16" t="n"/>
+      <c r="I154" s="14" t="n"/>
     </row>
     <row r="155" ht="18" customHeight="1">
-      <c r="I155" s="16" t="n"/>
+      <c r="I155" s="14" t="n"/>
     </row>
     <row r="156" ht="18" customHeight="1">
-      <c r="I156" s="16" t="n"/>
+      <c r="I156" s="14" t="n"/>
     </row>
     <row r="157" ht="18" customHeight="1">
-      <c r="I157" s="16" t="n"/>
+      <c r="I157" s="14" t="n"/>
     </row>
     <row r="158" ht="18" customHeight="1">
-      <c r="I158" s="16" t="n"/>
+      <c r="I158" s="14" t="n"/>
     </row>
     <row r="159" ht="18" customHeight="1">
-      <c r="I159" s="16" t="n"/>
+      <c r="I159" s="14" t="n"/>
     </row>
     <row r="160" ht="18" customHeight="1">
-      <c r="I160" s="16" t="n"/>
+      <c r="I160" s="14" t="n"/>
     </row>
     <row r="161" ht="18" customHeight="1">
-      <c r="I161" s="16" t="n"/>
+      <c r="I161" s="14" t="n"/>
     </row>
     <row r="162" ht="18" customHeight="1">
-      <c r="I162" s="16" t="n"/>
+      <c r="I162" s="14" t="n"/>
     </row>
     <row r="163" ht="18" customHeight="1">
-      <c r="I163" s="16" t="n"/>
+      <c r="I163" s="14" t="n"/>
     </row>
     <row r="164" ht="18" customHeight="1">
-      <c r="I164" s="16" t="n"/>
+      <c r="I164" s="14" t="n"/>
     </row>
     <row r="165" ht="18" customHeight="1">
-      <c r="I165" s="16" t="n"/>
+      <c r="I165" s="14" t="n"/>
     </row>
     <row r="166" ht="18" customHeight="1">
-      <c r="I166" s="16" t="n"/>
+      <c r="I166" s="14" t="n"/>
     </row>
     <row r="167" ht="18" customHeight="1">
-      <c r="I167" s="16" t="n"/>
+      <c r="I167" s="14" t="n"/>
     </row>
     <row r="168" ht="18" customHeight="1">
-      <c r="I168" s="16" t="n"/>
+      <c r="I168" s="14" t="n"/>
     </row>
     <row r="169" ht="18" customHeight="1">
-      <c r="I169" s="16" t="n"/>
+      <c r="I169" s="14" t="n"/>
     </row>
     <row r="170" ht="18" customHeight="1">
-      <c r="I170" s="16" t="n"/>
+      <c r="I170" s="14" t="n"/>
     </row>
     <row r="171" ht="18" customHeight="1">
-      <c r="I171" s="16" t="n"/>
+      <c r="I171" s="14" t="n"/>
     </row>
     <row r="172" ht="18" customHeight="1">
-      <c r="I172" s="16" t="n"/>
+      <c r="I172" s="14" t="n"/>
     </row>
     <row r="173" ht="18" customHeight="1">
-      <c r="I173" s="16" t="n"/>
+      <c r="I173" s="14" t="n"/>
     </row>
     <row r="174" ht="18" customHeight="1">
-      <c r="I174" s="16" t="n"/>
+      <c r="I174" s="14" t="n"/>
     </row>
     <row r="175" ht="18" customHeight="1">
-      <c r="I175" s="16" t="n"/>
+      <c r="I175" s="14" t="n"/>
     </row>
     <row r="176" ht="18" customHeight="1">
-      <c r="I176" s="16" t="n"/>
+      <c r="I176" s="14" t="n"/>
     </row>
     <row r="177" ht="18" customHeight="1">
-      <c r="I177" s="16" t="n"/>
+      <c r="I177" s="14" t="n"/>
     </row>
     <row r="178" ht="18" customHeight="1">
-      <c r="I178" s="16" t="n"/>
+      <c r="I178" s="14" t="n"/>
     </row>
     <row r="179" ht="18" customHeight="1">
-      <c r="I179" s="16" t="n"/>
+      <c r="I179" s="14" t="n"/>
     </row>
     <row r="180" ht="18" customHeight="1">
-      <c r="I180" s="16" t="n"/>
+      <c r="I180" s="14" t="n"/>
     </row>
     <row r="181" ht="18" customHeight="1">
-      <c r="I181" s="16" t="n"/>
+      <c r="I181" s="14" t="n"/>
     </row>
     <row r="182" ht="18" customHeight="1">
-      <c r="I182" s="16" t="n"/>
+      <c r="I182" s="14" t="n"/>
     </row>
     <row r="183" ht="18" customHeight="1">
-      <c r="I183" s="16" t="n"/>
+      <c r="I183" s="14" t="n"/>
     </row>
     <row r="184" ht="18" customHeight="1">
-      <c r="I184" s="16" t="n"/>
+      <c r="I184" s="14" t="n"/>
     </row>
     <row r="185" ht="18" customHeight="1">
-      <c r="I185" s="16" t="n"/>
+      <c r="I185" s="14" t="n"/>
     </row>
     <row r="186" ht="18" customHeight="1">
-      <c r="I186" s="16" t="n"/>
+      <c r="I186" s="14" t="n"/>
     </row>
     <row r="187" ht="18" customHeight="1">
-      <c r="I187" s="16" t="n"/>
+      <c r="I187" s="14" t="n"/>
     </row>
     <row r="188" ht="18" customHeight="1">
-      <c r="I188" s="16" t="n"/>
+      <c r="I188" s="14" t="n"/>
     </row>
     <row r="189" ht="18" customHeight="1">
-      <c r="I189" s="16" t="n"/>
+      <c r="I189" s="14" t="n"/>
     </row>
     <row r="190" ht="18" customHeight="1">
-      <c r="I190" s="16" t="n"/>
+      <c r="I190" s="14" t="n"/>
     </row>
     <row r="191" ht="18" customHeight="1">
-      <c r="I191" s="16" t="n"/>
+      <c r="I191" s="14" t="n"/>
     </row>
     <row r="192" ht="18" customHeight="1">
-      <c r="I192" s="16" t="n"/>
+      <c r="I192" s="14" t="n"/>
     </row>
     <row r="193" ht="18" customHeight="1">
-      <c r="I193" s="16" t="n"/>
+      <c r="I193" s="14" t="n"/>
     </row>
     <row r="194" ht="18" customHeight="1">
-      <c r="I194" s="16" t="n"/>
+      <c r="I194" s="14" t="n"/>
     </row>
     <row r="195" ht="18" customHeight="1">
-      <c r="I195" s="16" t="n"/>
+      <c r="I195" s="14" t="n"/>
     </row>
     <row r="196" ht="18" customHeight="1">
-      <c r="I196" s="16" t="n"/>
+      <c r="I196" s="14" t="n"/>
     </row>
     <row r="197" ht="18" customHeight="1">
-      <c r="I197" s="16" t="n"/>
+      <c r="I197" s="14" t="n"/>
     </row>
     <row r="198" ht="18" customHeight="1">
-      <c r="I198" s="16" t="n"/>
+      <c r="I198" s="14" t="n"/>
     </row>
     <row r="199" ht="18" customHeight="1">
-      <c r="I199" s="16" t="n"/>
+      <c r="I199" s="14" t="n"/>
     </row>
     <row r="200" ht="18" customHeight="1">
-      <c r="I200" s="16" t="n"/>
+      <c r="I200" s="14" t="n"/>
     </row>
     <row r="201" ht="18" customHeight="1">
-      <c r="I201" s="16" t="n"/>
+      <c r="I201" s="14" t="n"/>
     </row>
     <row r="202" ht="18" customHeight="1">
-      <c r="I202" s="16" t="n"/>
+      <c r="I202" s="14" t="n"/>
     </row>
     <row r="203" ht="18" customHeight="1">
-      <c r="I203" s="16" t="n"/>
+      <c r="I203" s="14" t="n"/>
     </row>
     <row r="204" ht="18" customHeight="1">
-      <c r="I204" s="16" t="n"/>
+      <c r="I204" s="14" t="n"/>
     </row>
     <row r="205" ht="18" customHeight="1">
-      <c r="I205" s="16" t="n"/>
+      <c r="I205" s="14" t="n"/>
     </row>
     <row r="206" ht="18" customHeight="1">
-      <c r="I206" s="16" t="n"/>
+      <c r="I206" s="14" t="n"/>
     </row>
     <row r="207" ht="18" customHeight="1">
-      <c r="I207" s="16" t="n"/>
+      <c r="I207" s="14" t="n"/>
     </row>
     <row r="208" ht="18" customHeight="1">
-      <c r="I208" s="16" t="n"/>
+      <c r="I208" s="14" t="n"/>
     </row>
     <row r="209" ht="18" customHeight="1">
-      <c r="I209" s="16" t="n"/>
+      <c r="I209" s="14" t="n"/>
     </row>
     <row r="210" ht="18" customHeight="1">
-      <c r="I210" s="16" t="n"/>
+      <c r="I210" s="14" t="n"/>
     </row>
     <row r="211" ht="18" customHeight="1">
-      <c r="I211" s="16" t="n"/>
+      <c r="I211" s="14" t="n"/>
     </row>
     <row r="212" ht="18" customHeight="1">
-      <c r="I212" s="16" t="n"/>
+      <c r="I212" s="14" t="n"/>
     </row>
     <row r="213" ht="18" customHeight="1">
-      <c r="I213" s="16" t="n"/>
+      <c r="I213" s="14" t="n"/>
     </row>
     <row r="214" ht="18" customHeight="1">
-      <c r="I214" s="16" t="n"/>
+      <c r="I214" s="14" t="n"/>
     </row>
     <row r="215" ht="18" customHeight="1">
-      <c r="I215" s="16" t="n"/>
+      <c r="I215" s="14" t="n"/>
     </row>
     <row r="216" ht="18" customHeight="1">
-      <c r="I216" s="16" t="n"/>
+      <c r="I216" s="14" t="n"/>
     </row>
     <row r="217" ht="18" customHeight="1">
-      <c r="I217" s="16" t="n"/>
+      <c r="I217" s="14" t="n"/>
     </row>
     <row r="218" ht="18" customHeight="1">
-      <c r="I218" s="16" t="n"/>
+      <c r="I218" s="14" t="n"/>
     </row>
     <row r="219" ht="18" customHeight="1">
-      <c r="I219" s="16" t="n"/>
+      <c r="I219" s="14" t="n"/>
     </row>
     <row r="220" ht="18" customHeight="1">
-      <c r="I220" s="16" t="n"/>
+      <c r="I220" s="14" t="n"/>
     </row>
     <row r="221" ht="18" customHeight="1">
-      <c r="I221" s="16" t="n"/>
+      <c r="I221" s="14" t="n"/>
     </row>
     <row r="222" ht="18" customHeight="1">
-      <c r="I222" s="16" t="n"/>
+      <c r="I222" s="14" t="n"/>
     </row>
     <row r="223" ht="18" customHeight="1">
-      <c r="I223" s="16" t="n"/>
+      <c r="I223" s="14" t="n"/>
     </row>
     <row r="224" ht="18" customHeight="1">
-      <c r="I224" s="16" t="n"/>
+      <c r="I224" s="14" t="n"/>
     </row>
     <row r="225" ht="18" customHeight="1">
-      <c r="I225" s="16" t="n"/>
+      <c r="I225" s="14" t="n"/>
     </row>
     <row r="226" ht="18" customHeight="1">
-      <c r="I226" s="16" t="n"/>
+      <c r="I226" s="14" t="n"/>
     </row>
     <row r="227" ht="18" customHeight="1">
-      <c r="I227" s="16" t="n"/>
+      <c r="I227" s="14" t="n"/>
     </row>
     <row r="228" ht="18" customHeight="1">
-      <c r="I228" s="16" t="n"/>
+      <c r="I228" s="14" t="n"/>
     </row>
     <row r="229" ht="18" customHeight="1">
-      <c r="I229" s="16" t="n"/>
+      <c r="I229" s="14" t="n"/>
     </row>
     <row r="230" ht="18" customHeight="1">
-      <c r="I230" s="16" t="n"/>
+      <c r="I230" s="14" t="n"/>
     </row>
     <row r="231" ht="18" customHeight="1">
-      <c r="I231" s="16" t="n"/>
+      <c r="I231" s="14" t="n"/>
     </row>
     <row r="232" ht="18" customHeight="1">
-      <c r="I232" s="16" t="n"/>
+      <c r="I232" s="14" t="n"/>
     </row>
     <row r="233" ht="18" customHeight="1">
-      <c r="I233" s="16" t="n"/>
+      <c r="I233" s="14" t="n"/>
     </row>
     <row r="234" ht="18" customHeight="1">
-      <c r="I234" s="16" t="n"/>
+      <c r="I234" s="14" t="n"/>
     </row>
     <row r="235" ht="18" customHeight="1">
-      <c r="I235" s="16" t="n"/>
+      <c r="I235" s="14" t="n"/>
     </row>
     <row r="236" ht="18" customHeight="1">
-      <c r="I236" s="16" t="n"/>
+      <c r="I236" s="14" t="n"/>
     </row>
     <row r="237" ht="18" customHeight="1">
-      <c r="I237" s="16" t="n"/>
+      <c r="I237" s="14" t="n"/>
     </row>
     <row r="238" ht="18" customHeight="1">
-      <c r="I238" s="16" t="n"/>
+      <c r="I238" s="14" t="n"/>
     </row>
     <row r="239" ht="18" customHeight="1">
-      <c r="I239" s="16" t="n"/>
+      <c r="I239" s="14" t="n"/>
     </row>
     <row r="240" ht="18" customHeight="1">
-      <c r="I240" s="16" t="n"/>
+      <c r="I240" s="14" t="n"/>
     </row>
     <row r="241" ht="18" customHeight="1">
-      <c r="I241" s="16" t="n"/>
+      <c r="I241" s="14" t="n"/>
     </row>
     <row r="242" ht="18" customHeight="1">
-      <c r="I242" s="16" t="n"/>
+      <c r="I242" s="14" t="n"/>
     </row>
     <row r="243" ht="18" customHeight="1">
-      <c r="I243" s="16" t="n"/>
+      <c r="I243" s="14" t="n"/>
     </row>
     <row r="244" ht="18" customHeight="1">
-      <c r="I244" s="16" t="n"/>
+      <c r="I244" s="14" t="n"/>
     </row>
     <row r="245" ht="18" customHeight="1">
-      <c r="I245" s="16" t="n"/>
+      <c r="I245" s="14" t="n"/>
     </row>
     <row r="246" ht="18" customHeight="1">
-      <c r="I246" s="16" t="n"/>
+      <c r="I246" s="14" t="n"/>
     </row>
     <row r="247" ht="18" customHeight="1">
-      <c r="I247" s="16" t="n"/>
+      <c r="I247" s="14" t="n"/>
     </row>
     <row r="248" ht="18" customHeight="1">
-      <c r="I248" s="16" t="n"/>
+      <c r="I248" s="14" t="n"/>
     </row>
     <row r="249" ht="18" customHeight="1">
-      <c r="I249" s="16" t="n"/>
+      <c r="I249" s="14" t="n"/>
     </row>
     <row r="250" ht="18" customHeight="1">
-      <c r="I250" s="16" t="n"/>
+      <c r="I250" s="14" t="n"/>
     </row>
     <row r="251" ht="18" customHeight="1">
-      <c r="I251" s="16" t="n"/>
+      <c r="I251" s="14" t="n"/>
     </row>
     <row r="252" ht="18" customHeight="1">
-      <c r="I252" s="16" t="n"/>
+      <c r="I252" s="14" t="n"/>
     </row>
     <row r="253" ht="18" customHeight="1">
-      <c r="I253" s="16" t="n"/>
+      <c r="I253" s="14" t="n"/>
     </row>
     <row r="254" ht="18" customHeight="1">
-      <c r="I254" s="16" t="n"/>
+      <c r="I254" s="14" t="n"/>
     </row>
     <row r="255" ht="18" customHeight="1">
-      <c r="I255" s="16" t="n"/>
+      <c r="I255" s="14" t="n"/>
     </row>
     <row r="256" ht="18" customHeight="1">
-      <c r="I256" s="16" t="n"/>
+      <c r="I256" s="14" t="n"/>
     </row>
     <row r="257" ht="18" customHeight="1">
-      <c r="I257" s="16" t="n"/>
+      <c r="I257" s="14" t="n"/>
     </row>
     <row r="258" ht="18" customHeight="1">
-      <c r="I258" s="16" t="n"/>
+      <c r="I258" s="14" t="n"/>
     </row>
     <row r="259" ht="18" customHeight="1">
-      <c r="I259" s="16" t="n"/>
+      <c r="I259" s="14" t="n"/>
     </row>
     <row r="260" ht="18" customHeight="1">
-      <c r="I260" s="16" t="n"/>
+      <c r="I260" s="14" t="n"/>
     </row>
     <row r="261" ht="18" customHeight="1">
-      <c r="I261" s="16" t="n"/>
+      <c r="I261" s="14" t="n"/>
     </row>
     <row r="262" ht="18" customHeight="1">
-      <c r="I262" s="16" t="n"/>
+      <c r="I262" s="14" t="n"/>
     </row>
     <row r="263" ht="18" customHeight="1">
-      <c r="I263" s="16" t="n"/>
+      <c r="I263" s="14" t="n"/>
     </row>
     <row r="264" ht="18" customHeight="1">
-      <c r="I264" s="16" t="n"/>
+      <c r="I264" s="14" t="n"/>
     </row>
     <row r="265" ht="18" customHeight="1">
-      <c r="I265" s="16" t="n"/>
+      <c r="I265" s="14" t="n"/>
     </row>
     <row r="266" ht="18" customHeight="1">
-      <c r="I266" s="16" t="n"/>
+      <c r="I266" s="14" t="n"/>
     </row>
     <row r="267" ht="18" customHeight="1">
-      <c r="I267" s="16" t="n"/>
+      <c r="I267" s="14" t="n"/>
     </row>
     <row r="268" ht="18" customHeight="1">
-      <c r="I268" s="16" t="n"/>
+      <c r="I268" s="14" t="n"/>
     </row>
     <row r="269" ht="18" customHeight="1">
-      <c r="I269" s="16" t="n"/>
+      <c r="I269" s="14" t="n"/>
     </row>
     <row r="270" ht="18" customHeight="1">
-      <c r="I270" s="16" t="n"/>
+      <c r="I270" s="14" t="n"/>
     </row>
     <row r="271" ht="18" customHeight="1">
-      <c r="I271" s="16" t="n"/>
+      <c r="I271" s="14" t="n"/>
     </row>
     <row r="272" ht="18" customHeight="1">
-      <c r="I272" s="16" t="n"/>
+      <c r="I272" s="14" t="n"/>
     </row>
     <row r="273" ht="18" customHeight="1">
-      <c r="I273" s="16" t="n"/>
+      <c r="I273" s="14" t="n"/>
     </row>
     <row r="274" ht="18" customHeight="1">
-      <c r="I274" s="16" t="n"/>
+      <c r="I274" s="14" t="n"/>
     </row>
     <row r="275" ht="18" customHeight="1">
-      <c r="I275" s="16" t="n"/>
+      <c r="I275" s="14" t="n"/>
     </row>
     <row r="276" ht="18" customHeight="1">
-      <c r="I276" s="16" t="n"/>
+      <c r="I276" s="14" t="n"/>
     </row>
     <row r="277" ht="18" customHeight="1">
-      <c r="I277" s="16" t="n"/>
+      <c r="I277" s="14" t="n"/>
     </row>
     <row r="278" ht="18" customHeight="1">
-      <c r="I278" s="16" t="n"/>
+      <c r="I278" s="14" t="n"/>
     </row>
     <row r="279" ht="18" customHeight="1">
-      <c r="I279" s="16" t="n"/>
+      <c r="I279" s="14" t="n"/>
     </row>
     <row r="280" ht="18" customHeight="1">
-      <c r="I280" s="16" t="n"/>
+      <c r="I280" s="14" t="n"/>
     </row>
     <row r="281" ht="18" customHeight="1">
-      <c r="I281" s="16" t="n"/>
+      <c r="I281" s="14" t="n"/>
     </row>
     <row r="282" ht="18" customHeight="1">
-      <c r="I282" s="16" t="n"/>
+      <c r="I282" s="14" t="n"/>
     </row>
     <row r="283" ht="18" customHeight="1">
-      <c r="I283" s="16" t="n"/>
+      <c r="I283" s="14" t="n"/>
     </row>
     <row r="284" ht="18" customHeight="1">
-      <c r="I284" s="16" t="n"/>
+      <c r="I284" s="14" t="n"/>
     </row>
     <row r="285" ht="18" customHeight="1">
-      <c r="I285" s="16" t="n"/>
+      <c r="I285" s="14" t="n"/>
     </row>
     <row r="286" ht="18" customHeight="1">
-      <c r="I286" s="16" t="n"/>
+      <c r="I286" s="14" t="n"/>
     </row>
     <row r="287" ht="18" customHeight="1">
-      <c r="I287" s="16" t="n"/>
+      <c r="I287" s="14" t="n"/>
     </row>
     <row r="288" ht="18" customHeight="1">
-      <c r="I288" s="16" t="n"/>
+      <c r="I288" s="14" t="n"/>
     </row>
     <row r="289" ht="18" customHeight="1">
-      <c r="I289" s="16" t="n"/>
+      <c r="I289" s="14" t="n"/>
     </row>
     <row r="290" ht="18" customHeight="1">
-      <c r="I290" s="16" t="n"/>
+      <c r="I290" s="14" t="n"/>
     </row>
     <row r="291" ht="18" customHeight="1">
-      <c r="I291" s="16" t="n"/>
+      <c r="I291" s="14" t="n"/>
     </row>
     <row r="292" ht="18" customHeight="1">
-      <c r="I292" s="16" t="n"/>
+      <c r="I292" s="14" t="n"/>
     </row>
     <row r="293" ht="18" customHeight="1">
-      <c r="I293" s="16" t="n"/>
+      <c r="I293" s="14" t="n"/>
     </row>
     <row r="294" ht="18" customHeight="1">
-      <c r="I294" s="16" t="n"/>
+      <c r="I294" s="14" t="n"/>
     </row>
     <row r="295" ht="18" customHeight="1">
-      <c r="I295" s="16" t="n"/>
+      <c r="I295" s="14" t="n"/>
     </row>
     <row r="296" ht="18" customHeight="1">
-      <c r="I296" s="16" t="n"/>
+      <c r="I296" s="14" t="n"/>
     </row>
     <row r="297" ht="18" customHeight="1">
-      <c r="I297" s="16" t="n"/>
+      <c r="I297" s="14" t="n"/>
     </row>
     <row r="298" ht="18" customHeight="1">
-      <c r="I298" s="16" t="n"/>
+      <c r="I298" s="14" t="n"/>
     </row>
     <row r="299" ht="18" customHeight="1">
-      <c r="I299" s="16" t="n"/>
+      <c r="I299" s="14" t="n"/>
     </row>
     <row r="300" ht="18" customHeight="1">
-      <c r="I300" s="16" t="n"/>
+      <c r="I300" s="14" t="n"/>
     </row>
     <row r="301" ht="18" customHeight="1">
-      <c r="I301" s="16" t="n"/>
+      <c r="I301" s="14" t="n"/>
     </row>
     <row r="302" ht="18" customHeight="1">
-      <c r="I302" s="16" t="n"/>
+      <c r="I302" s="14" t="n"/>
     </row>
     <row r="303" ht="18" customHeight="1">
-      <c r="I303" s="16" t="n"/>
+      <c r="I303" s="14" t="n"/>
     </row>
     <row r="304" ht="18" customHeight="1">
-      <c r="I304" s="16" t="n"/>
+      <c r="I304" s="14" t="n"/>
     </row>
     <row r="305" ht="18" customHeight="1">
-      <c r="I305" s="16" t="n"/>
+      <c r="I305" s="14" t="n"/>
     </row>
     <row r="306" ht="18" customHeight="1">
-      <c r="I306" s="16" t="n"/>
+      <c r="I306" s="14" t="n"/>
     </row>
     <row r="307" ht="18" customHeight="1">
-      <c r="I307" s="16" t="n"/>
+      <c r="I307" s="14" t="n"/>
     </row>
     <row r="308" ht="18" customHeight="1">
-      <c r="I308" s="16" t="n"/>
+      <c r="I308" s="14" t="n"/>
     </row>
     <row r="309" ht="18" customHeight="1">
-      <c r="I309" s="16" t="n"/>
+      <c r="I309" s="14" t="n"/>
     </row>
     <row r="310" ht="18" customHeight="1">
-      <c r="I310" s="16" t="n"/>
+      <c r="I310" s="14" t="n"/>
     </row>
     <row r="311" ht="18" customHeight="1">
-      <c r="I311" s="16" t="n"/>
+      <c r="I311" s="14" t="n"/>
     </row>
     <row r="312" ht="18" customHeight="1">
-      <c r="I312" s="16" t="n"/>
+      <c r="I312" s="14" t="n"/>
     </row>
     <row r="313" ht="18" customHeight="1">
-      <c r="I313" s="16" t="n"/>
+      <c r="I313" s="14" t="n"/>
     </row>
     <row r="314" ht="18" customHeight="1">
-      <c r="I314" s="16" t="n"/>
+      <c r="I314" s="14" t="n"/>
     </row>
     <row r="315" ht="18" customHeight="1">
-      <c r="I315" s="16" t="n"/>
+      <c r="I315" s="14" t="n"/>
     </row>
     <row r="316" ht="18" customHeight="1">
-      <c r="I316" s="16" t="n"/>
+      <c r="I316" s="14" t="n"/>
     </row>
     <row r="317" ht="18" customHeight="1">
-      <c r="I317" s="16" t="n"/>
+      <c r="I317" s="14" t="n"/>
     </row>
     <row r="318" ht="18" customHeight="1">
-      <c r="I318" s="16" t="n"/>
+      <c r="I318" s="14" t="n"/>
     </row>
     <row r="319" ht="18" customHeight="1">
-      <c r="I319" s="16" t="n"/>
+      <c r="I319" s="14" t="n"/>
     </row>
     <row r="320" ht="18" customHeight="1">
-      <c r="I320" s="16" t="n"/>
+      <c r="I320" s="14" t="n"/>
     </row>
     <row r="321" ht="18" customHeight="1">
-      <c r="I321" s="16" t="n"/>
+      <c r="I321" s="14" t="n"/>
     </row>
     <row r="322" ht="18" customHeight="1">
-      <c r="I322" s="16" t="n"/>
+      <c r="I322" s="14" t="n"/>
     </row>
     <row r="323" ht="18" customHeight="1">
-      <c r="I323" s="16" t="n"/>
+      <c r="I323" s="14" t="n"/>
     </row>
     <row r="324" ht="18" customHeight="1">
-      <c r="I324" s="16" t="n"/>
+      <c r="I324" s="14" t="n"/>
     </row>
     <row r="325" ht="18" customHeight="1">
-      <c r="I325" s="16" t="n"/>
+      <c r="I325" s="14" t="n"/>
     </row>
     <row r="326" ht="18" customHeight="1">
-      <c r="I326" s="16" t="n"/>
+      <c r="I326" s="14" t="n"/>
     </row>
     <row r="327" ht="18" customHeight="1">
-      <c r="I327" s="16" t="n"/>
+      <c r="I327" s="14" t="n"/>
     </row>
     <row r="328" ht="18" customHeight="1">
-      <c r="I328" s="16" t="n"/>
+      <c r="I328" s="14" t="n"/>
     </row>
     <row r="329" ht="18" customHeight="1">
-      <c r="I329" s="16" t="n"/>
+      <c r="I329" s="14" t="n"/>
     </row>
     <row r="330" ht="18" customHeight="1">
-      <c r="I330" s="16" t="n"/>
+      <c r="I330" s="14" t="n"/>
     </row>
     <row r="331" ht="18" customHeight="1">
-      <c r="I331" s="16" t="n"/>
+      <c r="I331" s="14" t="n"/>
     </row>
     <row r="332" ht="18" customHeight="1">
-      <c r="I332" s="16" t="n"/>
+      <c r="I332" s="14" t="n"/>
     </row>
     <row r="333" ht="18" customHeight="1">
-      <c r="I333" s="16" t="n"/>
+      <c r="I333" s="14" t="n"/>
     </row>
     <row r="334" ht="18" customHeight="1">
-      <c r="I334" s="16" t="n"/>
+      <c r="I334" s="14" t="n"/>
     </row>
     <row r="335" ht="18" customHeight="1">
-      <c r="I335" s="16" t="n"/>
+      <c r="I335" s="14" t="n"/>
     </row>
     <row r="336" ht="18" customHeight="1">
-      <c r="I336" s="16" t="n"/>
+      <c r="I336" s="14" t="n"/>
     </row>
     <row r="337" ht="18" customHeight="1">
-      <c r="I337" s="16" t="n"/>
+      <c r="I337" s="14" t="n"/>
     </row>
     <row r="338" ht="18" customHeight="1">
-      <c r="I338" s="16" t="n"/>
+      <c r="I338" s="14" t="n"/>
     </row>
     <row r="339" ht="18" customHeight="1">
-      <c r="I339" s="16" t="n"/>
+      <c r="I339" s="14" t="n"/>
     </row>
     <row r="340" ht="18" customHeight="1">
-      <c r="I340" s="16" t="n"/>
+      <c r="I340" s="14" t="n"/>
     </row>
     <row r="341" ht="18" customHeight="1">
-      <c r="I341" s="16" t="n"/>
+      <c r="I341" s="14" t="n"/>
     </row>
     <row r="342" ht="18" customHeight="1">
-      <c r="I342" s="16" t="n"/>
+      <c r="I342" s="14" t="n"/>
     </row>
     <row r="343" ht="18" customHeight="1">
-      <c r="I343" s="16" t="n"/>
+      <c r="I343" s="14" t="n"/>
     </row>
     <row r="344" ht="18" customHeight="1">
-      <c r="I344" s="16" t="n"/>
+      <c r="I344" s="14" t="n"/>
     </row>
     <row r="345" ht="18" customHeight="1">
-      <c r="I345" s="16" t="n"/>
+      <c r="I345" s="14" t="n"/>
     </row>
     <row r="346" ht="18" customHeight="1">
-      <c r="I346" s="16" t="n"/>
+      <c r="I346" s="14" t="n"/>
     </row>
     <row r="347" ht="18" customHeight="1">
-      <c r="I347" s="16" t="n"/>
+      <c r="I347" s="14" t="n"/>
     </row>
     <row r="348" ht="18" customHeight="1">
-      <c r="I348" s="16" t="n"/>
+      <c r="I348" s="14" t="n"/>
     </row>
     <row r="349" ht="18" customHeight="1">
-      <c r="I349" s="16" t="n"/>
+      <c r="I349" s="14" t="n"/>
     </row>
     <row r="350" ht="18" customHeight="1">
-      <c r="I350" s="16" t="n"/>
+      <c r="I350" s="14" t="n"/>
     </row>
     <row r="351" ht="18" customHeight="1">
-      <c r="I351" s="16" t="n"/>
+      <c r="I351" s="14" t="n"/>
     </row>
     <row r="352" ht="18" customHeight="1">
-      <c r="I352" s="16" t="n"/>
+      <c r="I352" s="14" t="n"/>
     </row>
     <row r="353" ht="18" customHeight="1">
-      <c r="I353" s="16" t="n"/>
+      <c r="I353" s="14" t="n"/>
     </row>
     <row r="354" ht="18" customHeight="1">
-      <c r="I354" s="16" t="n"/>
+      <c r="I354" s="14" t="n"/>
     </row>
     <row r="355" ht="18" customHeight="1">
-      <c r="I355" s="16" t="n"/>
+      <c r="I355" s="14" t="n"/>
     </row>
     <row r="356" ht="18" customHeight="1">
-      <c r="I356" s="16" t="n"/>
+      <c r="I356" s="14" t="n"/>
     </row>
     <row r="357" ht="18" customHeight="1">
-      <c r="I357" s="16" t="n"/>
+      <c r="I357" s="14" t="n"/>
     </row>
     <row r="358" ht="18" customHeight="1">
-      <c r="I358" s="16" t="n"/>
+      <c r="I358" s="14" t="n"/>
     </row>
     <row r="359" ht="18" customHeight="1">
-      <c r="I359" s="16" t="n"/>
+      <c r="I359" s="14" t="n"/>
     </row>
     <row r="360" ht="18" customHeight="1">
-      <c r="I360" s="16" t="n"/>
+      <c r="I360" s="14" t="n"/>
     </row>
     <row r="361" ht="18" customHeight="1">
-      <c r="I361" s="16" t="n"/>
+      <c r="I361" s="14" t="n"/>
     </row>
     <row r="362" ht="18" customHeight="1">
-      <c r="I362" s="16" t="n"/>
+      <c r="I362" s="14" t="n"/>
     </row>
     <row r="363" ht="18" customHeight="1">
-      <c r="I363" s="16" t="n"/>
+      <c r="I363" s="14" t="n"/>
     </row>
     <row r="364" ht="18" customHeight="1">
-      <c r="I364" s="16" t="n"/>
+      <c r="I364" s="14" t="n"/>
     </row>
     <row r="365" ht="18" customHeight="1">
-      <c r="I365" s="16" t="n"/>
+      <c r="I365" s="14" t="n"/>
     </row>
     <row r="366" ht="18" customHeight="1">
-      <c r="I366" s="16" t="n"/>
+      <c r="I366" s="14" t="n"/>
     </row>
     <row r="367" ht="18" customHeight="1">
-      <c r="I367" s="16" t="n"/>
+      <c r="I367" s="14" t="n"/>
     </row>
     <row r="368" ht="18" customHeight="1">
-      <c r="I368" s="16" t="n"/>
+      <c r="I368" s="14" t="n"/>
     </row>
     <row r="369" ht="18" customHeight="1">
-      <c r="I369" s="16" t="n"/>
+      <c r="I369" s="14" t="n"/>
     </row>
     <row r="370" ht="18" customHeight="1">
-      <c r="I370" s="16" t="n"/>
+      <c r="I370" s="14" t="n"/>
     </row>
     <row r="371" ht="18" customHeight="1">
-      <c r="I371" s="16" t="n"/>
+      <c r="I371" s="14" t="n"/>
     </row>
     <row r="372" ht="18" customHeight="1">
-      <c r="I372" s="16" t="n"/>
+      <c r="I372" s="14" t="n"/>
     </row>
     <row r="373" ht="18" customHeight="1">
-      <c r="I373" s="16" t="n"/>
+      <c r="I373" s="14" t="n"/>
     </row>
     <row r="374" ht="18" customHeight="1">
-      <c r="I374" s="16" t="n"/>
+      <c r="I374" s="14" t="n"/>
     </row>
     <row r="375" ht="18" customHeight="1">
-      <c r="I375" s="16" t="n"/>
+      <c r="I375" s="14" t="n"/>
     </row>
     <row r="376" ht="18" customHeight="1">
-      <c r="I376" s="16" t="n"/>
+      <c r="I376" s="14" t="n"/>
     </row>
     <row r="377" ht="18" customHeight="1">
-      <c r="I377" s="16" t="n"/>
+      <c r="I377" s="14" t="n"/>
     </row>
     <row r="378" ht="18" customHeight="1">
-      <c r="I378" s="16" t="n"/>
+      <c r="I378" s="14" t="n"/>
     </row>
     <row r="379" ht="18" customHeight="1">
-      <c r="I379" s="16" t="n"/>
+      <c r="I379" s="14" t="n"/>
     </row>
     <row r="380" ht="18" customHeight="1">
-      <c r="I380" s="16" t="n"/>
+      <c r="I380" s="14" t="n"/>
     </row>
     <row r="381" ht="18" customHeight="1">
-      <c r="I381" s="16" t="n"/>
+      <c r="I381" s="14" t="n"/>
     </row>
     <row r="382" ht="18" customHeight="1">
-      <c r="I382" s="16" t="n"/>
+      <c r="I382" s="14" t="n"/>
     </row>
     <row r="383" ht="18" customHeight="1">
-      <c r="I383" s="16" t="n"/>
+      <c r="I383" s="14" t="n"/>
     </row>
     <row r="384" ht="18" customHeight="1">
-      <c r="I384" s="16" t="n"/>
+      <c r="I384" s="14" t="n"/>
     </row>
     <row r="385" ht="18" customHeight="1">
-      <c r="I385" s="16" t="n"/>
+      <c r="I385" s="14" t="n"/>
     </row>
     <row r="386" ht="18" customHeight="1">
-      <c r="I386" s="16" t="n"/>
+      <c r="I386" s="14" t="n"/>
     </row>
     <row r="387" ht="18" customHeight="1">
-      <c r="I387" s="16" t="n"/>
+      <c r="I387" s="14" t="n"/>
     </row>
     <row r="388" ht="18" customHeight="1">
-      <c r="I388" s="16" t="n"/>
+      <c r="I388" s="14" t="n"/>
     </row>
     <row r="389" ht="18" customHeight="1">
-      <c r="I389" s="16" t="n"/>
+      <c r="I389" s="14" t="n"/>
     </row>
     <row r="390" ht="18" customHeight="1">
-      <c r="I390" s="16" t="n"/>
+      <c r="I390" s="14" t="n"/>
     </row>
     <row r="391" ht="18" customHeight="1">
-      <c r="I391" s="16" t="n"/>
+      <c r="I391" s="14" t="n"/>
     </row>
     <row r="392" ht="18" customHeight="1">
-      <c r="I392" s="16" t="n"/>
+      <c r="I392" s="14" t="n"/>
     </row>
     <row r="393" ht="18" customHeight="1">
-      <c r="I393" s="16" t="n"/>
+      <c r="I393" s="14" t="n"/>
     </row>
     <row r="394" ht="18" customHeight="1">
-      <c r="I394" s="16" t="n"/>
+      <c r="I394" s="14" t="n"/>
     </row>
     <row r="395" ht="18" customHeight="1">
-      <c r="I395" s="16" t="n"/>
+      <c r="I395" s="14" t="n"/>
     </row>
     <row r="396" ht="18" customHeight="1">
-      <c r="I396" s="16" t="n"/>
+      <c r="I396" s="14" t="n"/>
     </row>
     <row r="397" ht="18" customHeight="1">
-      <c r="I397" s="16" t="n"/>
+      <c r="I397" s="14" t="n"/>
     </row>
     <row r="398" ht="18" customHeight="1">
-      <c r="I398" s="16" t="n"/>
+      <c r="I398" s="14" t="n"/>
     </row>
     <row r="399" ht="18" customHeight="1">
-      <c r="I399" s="16" t="n"/>
+      <c r="I399" s="14" t="n"/>
     </row>
     <row r="400" ht="18" customHeight="1">
-      <c r="I400" s="16" t="n"/>
+      <c r="I400" s="14" t="n"/>
     </row>
     <row r="401" ht="18" customHeight="1">
-      <c r="I401" s="16" t="n"/>
+      <c r="I401" s="14" t="n"/>
     </row>
     <row r="402" ht="18" customHeight="1">
-      <c r="I402" s="16" t="n"/>
+      <c r="I402" s="14" t="n"/>
     </row>
     <row r="403" ht="18" customHeight="1">
-      <c r="I403" s="16" t="n"/>
+      <c r="I403" s="14" t="n"/>
     </row>
     <row r="404" ht="18" customHeight="1">
-      <c r="I404" s="16" t="n"/>
+      <c r="I404" s="14" t="n"/>
     </row>
     <row r="405" ht="18" customHeight="1">
-      <c r="I405" s="16" t="n"/>
+      <c r="I405" s="14" t="n"/>
     </row>
     <row r="406" ht="18" customHeight="1">
-      <c r="I406" s="16" t="n"/>
+      <c r="I406" s="14" t="n"/>
     </row>
     <row r="407" ht="18" customHeight="1">
-      <c r="I407" s="16" t="n"/>
+      <c r="I407" s="14" t="n"/>
     </row>
     <row r="408" ht="18" customHeight="1">
-      <c r="I408" s="16" t="n"/>
+      <c r="I408" s="14" t="n"/>
     </row>
     <row r="409" ht="18" customHeight="1">
-      <c r="I409" s="16" t="n"/>
+      <c r="I409" s="14" t="n"/>
     </row>
     <row r="410" ht="18" customHeight="1">
-      <c r="I410" s="16" t="n"/>
+      <c r="I410" s="14" t="n"/>
     </row>
     <row r="411" ht="18" customHeight="1">
-      <c r="I411" s="16" t="n"/>
+      <c r="I411" s="14" t="n"/>
     </row>
     <row r="412" ht="18" customHeight="1">
-      <c r="I412" s="16" t="n"/>
+      <c r="I412" s="14" t="n"/>
     </row>
     <row r="413" ht="18" customHeight="1">
-      <c r="I413" s="16" t="n"/>
+      <c r="I413" s="14" t="n"/>
     </row>
     <row r="414" ht="18" customHeight="1">
-      <c r="I414" s="16" t="n"/>
+      <c r="I414" s="14" t="n"/>
     </row>
     <row r="415" ht="18" customHeight="1">
-      <c r="I415" s="16" t="n"/>
+      <c r="I415" s="14" t="n"/>
     </row>
     <row r="416" ht="18" customHeight="1">
-      <c r="I416" s="16" t="n"/>
+      <c r="I416" s="14" t="n"/>
     </row>
     <row r="417" ht="18" customHeight="1">
-      <c r="I417" s="16" t="n"/>
+      <c r="I417" s="14" t="n"/>
     </row>
     <row r="418" ht="18" customHeight="1">
-      <c r="I418" s="16" t="n"/>
+      <c r="I418" s="14" t="n"/>
     </row>
     <row r="419" ht="18" customHeight="1">
-      <c r="I419" s="16" t="n"/>
+      <c r="I419" s="14" t="n"/>
     </row>
     <row r="420" ht="18" customHeight="1">
-      <c r="I420" s="16" t="n"/>
+      <c r="I420" s="14" t="n"/>
     </row>
     <row r="421" ht="18" customHeight="1">
-      <c r="I421" s="16" t="n"/>
+      <c r="I421" s="14" t="n"/>
     </row>
     <row r="422" ht="18" customHeight="1">
-      <c r="I422" s="16" t="n"/>
+      <c r="I422" s="14" t="n"/>
     </row>
     <row r="423" ht="18" customHeight="1">
-      <c r="I423" s="16" t="n"/>
+      <c r="I423" s="14" t="n"/>
     </row>
     <row r="424" ht="18" customHeight="1">
-      <c r="I424" s="16" t="n"/>
+      <c r="I424" s="14" t="n"/>
     </row>
     <row r="425" ht="18" customHeight="1">
-      <c r="I425" s="16" t="n"/>
+      <c r="I425" s="14" t="n"/>
     </row>
     <row r="426" ht="18" customHeight="1">
-      <c r="I426" s="16" t="n"/>
+      <c r="I426" s="14" t="n"/>
     </row>
     <row r="427" ht="18" customHeight="1">
-      <c r="I427" s="16" t="n"/>
+      <c r="I427" s="14" t="n"/>
     </row>
     <row r="428" ht="18" customHeight="1">
-      <c r="I428" s="16" t="n"/>
+      <c r="I428" s="14" t="n"/>
     </row>
     <row r="429" ht="18" customHeight="1">
-      <c r="I429" s="16" t="n"/>
+      <c r="I429" s="14" t="n"/>
     </row>
     <row r="430" ht="18" customHeight="1">
-      <c r="I430" s="16" t="n"/>
+      <c r="I430" s="14" t="n"/>
     </row>
     <row r="431" ht="18" customHeight="1">
-      <c r="I431" s="16" t="n"/>
+      <c r="I431" s="14" t="n"/>
     </row>
     <row r="432" ht="18" customHeight="1">
-      <c r="I432" s="16" t="n"/>
+      <c r="I432" s="14" t="n"/>
     </row>
     <row r="433" ht="18" customHeight="1">
-      <c r="I433" s="16" t="n"/>
+      <c r="I433" s="14" t="n"/>
     </row>
     <row r="434" ht="18" customHeight="1">
-      <c r="I434" s="16" t="n"/>
+      <c r="I434" s="14" t="n"/>
     </row>
     <row r="435" ht="18" customHeight="1">
-      <c r="I435" s="16" t="n"/>
+      <c r="I435" s="14" t="n"/>
     </row>
     <row r="436" ht="18" customHeight="1">
-      <c r="I436" s="16" t="n"/>
+      <c r="I436" s="14" t="n"/>
     </row>
     <row r="437" ht="18" customHeight="1">
-      <c r="I437" s="16" t="n"/>
+      <c r="I437" s="14" t="n"/>
     </row>
     <row r="438" ht="18" customHeight="1">
-      <c r="I438" s="16" t="n"/>
+      <c r="I438" s="14" t="n"/>
     </row>
     <row r="439" ht="18" customHeight="1">
-      <c r="I439" s="16" t="n"/>
+      <c r="I439" s="14" t="n"/>
     </row>
     <row r="440" ht="18" customHeight="1">
-      <c r="I440" s="16" t="n"/>
+      <c r="I440" s="14" t="n"/>
     </row>
     <row r="441" ht="18" customHeight="1">
-      <c r="I441" s="16" t="n"/>
+      <c r="I441" s="14" t="n"/>
     </row>
     <row r="442" ht="18" customHeight="1">
-      <c r="I442" s="16" t="n"/>
+      <c r="I442" s="14" t="n"/>
     </row>
     <row r="443" ht="18" customHeight="1">
-      <c r="I443" s="16" t="n"/>
+      <c r="I443" s="14" t="n"/>
     </row>
     <row r="444" ht="18" customHeight="1">
-      <c r="I444" s="16" t="n"/>
+      <c r="I444" s="14" t="n"/>
     </row>
     <row r="445" ht="18" customHeight="1">
-      <c r="I445" s="16" t="n"/>
+      <c r="I445" s="14" t="n"/>
     </row>
     <row r="446" ht="18" customHeight="1">
-      <c r="I446" s="16" t="n"/>
+      <c r="I446" s="14" t="n"/>
     </row>
     <row r="447" ht="18" customHeight="1">
-      <c r="I447" s="16" t="n"/>
+      <c r="I447" s="14" t="n"/>
     </row>
     <row r="448" ht="18" customHeight="1">
-      <c r="I448" s="16" t="n"/>
+      <c r="I448" s="14" t="n"/>
     </row>
     <row r="449" ht="18" customHeight="1">
-      <c r="I449" s="16" t="n"/>
+      <c r="I449" s="14" t="n"/>
     </row>
     <row r="450" ht="18" customHeight="1">
-      <c r="I450" s="16" t="n"/>
+      <c r="I450" s="14" t="n"/>
     </row>
     <row r="451" ht="18" customHeight="1">
-      <c r="I451" s="16" t="n"/>
+      <c r="I451" s="14" t="n"/>
     </row>
     <row r="452" ht="18" customHeight="1">
-      <c r="I452" s="16" t="n"/>
+      <c r="I452" s="14" t="n"/>
     </row>
     <row r="453" ht="18" customHeight="1">
-      <c r="I453" s="16" t="n"/>
+      <c r="I453" s="14" t="n"/>
     </row>
     <row r="454" ht="18" customHeight="1">
-      <c r="I454" s="16" t="n"/>
+      <c r="I454" s="14" t="n"/>
     </row>
     <row r="455" ht="18" customHeight="1">
-      <c r="I455" s="16" t="n"/>
+      <c r="I455" s="14" t="n"/>
     </row>
     <row r="456" ht="18" customHeight="1">
-      <c r="I456" s="16" t="n"/>
+      <c r="I456" s="14" t="n"/>
     </row>
     <row r="457" ht="18" customHeight="1">
-      <c r="I457" s="16" t="n"/>
+      <c r="I457" s="14" t="n"/>
     </row>
     <row r="458" ht="18" customHeight="1">
-      <c r="I458" s="16" t="n"/>
+      <c r="I458" s="14" t="n"/>
     </row>
     <row r="459" ht="18" customHeight="1">
-      <c r="I459" s="16" t="n"/>
+      <c r="I459" s="14" t="n"/>
     </row>
     <row r="460" ht="18" customHeight="1">
-      <c r="I460" s="16" t="n"/>
+      <c r="I460" s="14" t="n"/>
     </row>
     <row r="461" ht="18" customHeight="1">
-      <c r="I461" s="16" t="n"/>
+      <c r="I461" s="14" t="n"/>
     </row>
     <row r="462" ht="18" customHeight="1">
-      <c r="I462" s="16" t="n"/>
+      <c r="I462" s="14" t="n"/>
     </row>
     <row r="463" ht="18" customHeight="1">
-      <c r="I463" s="16" t="n"/>
+      <c r="I463" s="14" t="n"/>
     </row>
     <row r="464" ht="18" customHeight="1">
-      <c r="I464" s="16" t="n"/>
+      <c r="I464" s="14" t="n"/>
     </row>
     <row r="465" ht="18" customHeight="1">
-      <c r="I465" s="16" t="n"/>
+      <c r="I465" s="14" t="n"/>
     </row>
     <row r="466" ht="18" customHeight="1">
-      <c r="I466" s="16" t="n"/>
+      <c r="I466" s="14" t="n"/>
     </row>
     <row r="467" ht="18" customHeight="1">
-      <c r="I467" s="16" t="n"/>
+      <c r="I467" s="14" t="n"/>
     </row>
     <row r="468" ht="18" customHeight="1">
-      <c r="I468" s="16" t="n"/>
+      <c r="I468" s="14" t="n"/>
     </row>
     <row r="469" ht="18" customHeight="1">
-      <c r="I469" s="16" t="n"/>
+      <c r="I469" s="14" t="n"/>
     </row>
     <row r="470" ht="18" customHeight="1">
-      <c r="I470" s="16" t="n"/>
+      <c r="I470" s="14" t="n"/>
     </row>
     <row r="471" ht="18" customHeight="1">
-      <c r="I471" s="16" t="n"/>
+      <c r="I471" s="14" t="n"/>
     </row>
     <row r="472" ht="18" customHeight="1">
-      <c r="I472" s="16" t="n"/>
+      <c r="I472" s="14" t="n"/>
     </row>
     <row r="473" ht="18" customHeight="1">
-      <c r="I473" s="16" t="n"/>
+      <c r="I473" s="14" t="n"/>
     </row>
     <row r="474" ht="18" customHeight="1">
-      <c r="I474" s="16" t="n"/>
+      <c r="I474" s="14" t="n"/>
     </row>
     <row r="475" ht="18" customHeight="1">
-      <c r="I475" s="16" t="n"/>
+      <c r="I475" s="14" t="n"/>
     </row>
     <row r="476" ht="18" customHeight="1">
-      <c r="I476" s="16" t="n"/>
+      <c r="I476" s="14" t="n"/>
     </row>
     <row r="477" ht="18" customHeight="1">
-      <c r="I477" s="16" t="n"/>
+      <c r="I477" s="14" t="n"/>
     </row>
     <row r="478" ht="18" customHeight="1">
-      <c r="I478" s="16" t="n"/>
+      <c r="I478" s="14" t="n"/>
     </row>
     <row r="479" ht="18" customHeight="1">
-      <c r="I479" s="16" t="n"/>
+      <c r="I479" s="14" t="n"/>
     </row>
     <row r="480" ht="18" customHeight="1">
-      <c r="I480" s="16" t="n"/>
+      <c r="I480" s="14" t="n"/>
     </row>
     <row r="481" ht="18" customHeight="1">
-      <c r="I481" s="16" t="n"/>
+      <c r="I481" s="14" t="n"/>
     </row>
     <row r="482" ht="18" customHeight="1">
-      <c r="I482" s="16" t="n"/>
+      <c r="I482" s="14" t="n"/>
     </row>
     <row r="483" ht="18" customHeight="1">
-      <c r="I483" s="16" t="n"/>
+      <c r="I483" s="14" t="n"/>
     </row>
     <row r="484" ht="18" customHeight="1">
-      <c r="I484" s="16" t="n"/>
+      <c r="I484" s="14" t="n"/>
     </row>
     <row r="485" ht="18" customHeight="1">
-      <c r="I485" s="16" t="n"/>
+      <c r="I485" s="14" t="n"/>
     </row>
     <row r="486" ht="18" customHeight="1">
-      <c r="I486" s="16" t="n"/>
+      <c r="I486" s="14" t="n"/>
     </row>
     <row r="487" ht="18" customHeight="1">
-      <c r="I487" s="16" t="n"/>
+      <c r="I487" s="14" t="n"/>
     </row>
     <row r="488" ht="18" customHeight="1">
-      <c r="I488" s="16" t="n"/>
+      <c r="I488" s="14" t="n"/>
     </row>
     <row r="489" ht="18" customHeight="1">
-      <c r="I489" s="16" t="n"/>
+      <c r="I489" s="14" t="n"/>
     </row>
     <row r="490" ht="18" customHeight="1">
-      <c r="I490" s="16" t="n"/>
+      <c r="I490" s="14" t="n"/>
     </row>
     <row r="491" ht="18" customHeight="1">
-      <c r="I491" s="16" t="n"/>
+      <c r="I491" s="14" t="n"/>
     </row>
     <row r="492" ht="18" customHeight="1">
-      <c r="I492" s="16" t="n"/>
+      <c r="I492" s="14" t="n"/>
     </row>
     <row r="493" ht="18" customHeight="1">
-      <c r="I493" s="16" t="n"/>
+      <c r="I493" s="14" t="n"/>
     </row>
     <row r="494" ht="18" customHeight="1">
-      <c r="I494" s="16" t="n"/>
+      <c r="I494" s="14" t="n"/>
     </row>
     <row r="495" ht="18" customHeight="1">
-      <c r="I495" s="16" t="n"/>
+      <c r="I495" s="14" t="n"/>
     </row>
     <row r="496" ht="18" customHeight="1">
-      <c r="I496" s="16" t="n"/>
+      <c r="I496" s="14" t="n"/>
     </row>
     <row r="497" ht="18" customHeight="1">
-      <c r="I497" s="16" t="n"/>
+      <c r="I497" s="14" t="n"/>
     </row>
     <row r="498" ht="18" customHeight="1">
-      <c r="I498" s="16" t="n"/>
+      <c r="I498" s="14" t="n"/>
     </row>
     <row r="499" ht="18" customHeight="1">
-      <c r="I499" s="16" t="n"/>
+      <c r="I499" s="14" t="n"/>
     </row>
     <row r="500" ht="18" customHeight="1">
-      <c r="I500" s="16" t="n"/>
+      <c r="I500" s="14" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -5609,8 +5551,8 @@
     <mergeCell ref="E1:H1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="K4:K500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="CATEGORIA inválida" error="Valores: reclamo, compromiso, otros — o dejar vacío (pago normal)." type="list">
-      <formula1>"reclamo,compromiso,otros"</formula1>
+    <dataValidation sqref="K4:K500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="CATEGORIA inválida" error="Valores: reclamo, compromiso, exoneracion, otros — o dejar vacío (pago normal)." type="list">
+      <formula1>"reclamo,compromiso,exoneracion,otros"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
